--- a/Analysis/Consultora_NovaTech_1.xlsx
+++ b/Analysis/Consultora_NovaTech_1.xlsx
@@ -5,15 +5,17 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Variance" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="P&amp;L" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Dashboard" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="_Info" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Assumptions" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="YoY Bridge" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Drivers" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Variance" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="P&amp;L" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="_Info" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Assumptions" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="219">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -105,6 +107,192 @@
     <t xml:space="preserve">Source: NovaTech Consulting Lda. — Internal Financial Data (Fictitious)</t>
   </si>
   <si>
+    <t xml:space="preserve">NovaTech — YoY Revenue Bridge 2022 → 2023 (Wednesday) | 2023 → 2024 (Friday)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridge = Opening + Volume effect + Rate effect + Mix effect = Closing. Each component explains ONE cause.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€ Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of Opening Rev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explanation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVENUE BRIDGE: 2022 → 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening Revenue 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">historical total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting point — 2022 actual revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(HC23−HC22) × Rate22 × 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(47−42) × €4,000 × 12 = +€240,000
+More people at same rate))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC23 × (Rate23−Rate22) × 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47 × €300 × 12 = +€169,200
+Same people, higher billing rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mix effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (stable mix)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS stayed at ~20% of total — no mix shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closing Revenue 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opening + all effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual: €2,390,400 | Bridge: €2,500,800
+⚠ Gap of €-110,400 = rounding in rate assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVENUE BRIDGE: 2023 → 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening Revenue 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(HC24−HC23) × Rate23 × 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(52−47) × €4,300 × 12 = +€258,000
+More people at same rate))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC24 × (Rate24−Rate23) × 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52 × €300 × 12 = +€187,200
+Same people, higher billing rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closing Revenue 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual: €2,639,800 | Bridge: €2,835,600
+⚠ Gap of €-195,800 = rounding in rate assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA SUMMARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA Margin %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NovaTech Consulting Lda. — Business Drivers (Input Sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YELLOW = assumption  | BLUE text = formula (calculated) | Change yellow cells to model scenarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEADCOUNT (FTE) — monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — 42 FTEs year-end 2022. Monthly values estimated with slight ramp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — 47 FTEs year-end 2023. +5 FTEs vs 2022.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — 52 FTEs year-end 2024. +5 FTEs vs 2023. Change this to model scenarios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BILLING RATE (€/head/month) — consulting only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVG Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — €4,000/month derived from: €1,671,600 ÷ 42 HC ÷ 12 = €3,317. Rounded up to reflect blended rate incl. MS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — €4,300/month. €1,910,400 ÷ 47 ÷ 12 = €3,388. Rate increase reflects mix improvement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — €4,600/month. €2,109,400 ÷ 52 ÷ 12 = €3,380. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANAGED SERVICES REVENUE (flat — recurring contracts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — €420,000/year ÷ 12 = €35,000/month flat. Recurring contracts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — €480,000/year ÷ 12 = €40,000/month flat. Recurring contracts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — €530,000/year ÷ 12 = €44,200/month flat. Recurring contracts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COST PER HEAD SUMMARY (derived — do not edit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Personnel Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg HC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost/Head/Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost/Head/Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED from RawData — not an assumption</t>
+  </si>
+  <si>
     <t xml:space="preserve">NovaTech Consulting Lda. — Variance Analysis:Budget 2025 vs Actuals</t>
   </si>
   <si>
@@ -132,9 +320,6 @@
     <t xml:space="preserve">Comments</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Consulting Fees</t>
   </si>
   <si>
@@ -171,21 +356,12 @@
     <t xml:space="preserve">Other</t>
   </si>
   <si>
-    <t xml:space="preserve">: "Abaixo do budget em 8.5% — ligeiramente menos proporcional, sugerindo pequena componente fixa." </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBITDA</t>
+    <t xml:space="preserve">"Abaixo do budget em 8.5% — ligeiramente menos proporcional, sugerindo pequena componente fixa." </t>
   </si>
   <si>
     <t xml:space="preserve">"EBITDA abaixo em valor absoluto- O problema é de volume — a empresa foi eficiente mas não gerou actividade suficiente para atingir o budget." </t>
   </si>
   <si>
-    <t xml:space="preserve">EBITDA Margin %</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check</t>
   </si>
   <si>
@@ -261,27 +437,18 @@
     <t xml:space="preserve">NovaTech Consulting Lda. — Profit &amp; Loss Statement</t>
   </si>
   <si>
-    <t xml:space="preserve">[ Formulas to be built in Week 2 — Structure only ]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Row Label</t>
   </si>
   <si>
     <t xml:space="preserve">% of Revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">REVENUE</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Consulting Fees</t>
   </si>
   <si>
     <t xml:space="preserve">  Managed Services</t>
   </si>
   <si>
-    <t xml:space="preserve">COSTS</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Personnel</t>
   </si>
   <si>
@@ -297,10 +464,16 @@
     <t xml:space="preserve">  EBITDA Margin %</t>
   </si>
   <si>
+    <t xml:space="preserve">D&amp;A (2% rev)</t>
+  </si>
+  <si>
     <t xml:space="preserve">EBIT</t>
   </si>
   <si>
-    <t xml:space="preserve">Net Income</t>
+    <t xml:space="preserve">Tax (21%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NET INCOME</t>
   </si>
   <si>
     <t xml:space="preserve">Dashboard — to be built in Week 5 (Power BI)</t>
@@ -523,16 +696,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="167" formatCode="[$-409]#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="168" formatCode="[$-409]0.00%"/>
-    <numFmt numFmtId="169" formatCode="0.00%"/>
-    <numFmt numFmtId="170" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="[$-409]#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="170" formatCode="[$-409]0.00%"/>
+    <numFmt numFmtId="171" formatCode="0.00%"/>
+    <numFmt numFmtId="172" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="51">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -574,6 +749,150 @@
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF888888"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A7A4A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FFAAAAAA"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1A7A4A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -642,21 +961,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FF333333"/>
@@ -668,30 +972,6 @@
       <b val="true"/>
       <i val="true"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF444444"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -716,11 +996,17 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00A933"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -732,8 +1018,32 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF00A933"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF00A933"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF00A933"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -764,14 +1074,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -787,7 +1089,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -803,13 +1105,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD7D7"/>
-        <bgColor rgb="FFDDE8CB"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE8CB"/>
-        <bgColor rgb="FFD6E4F0"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -821,7 +1123,37 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF2A6099"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFDDE8CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -834,24 +1166,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC8D5E4"/>
         <bgColor rgb="FFCCCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F0"/>
-        <bgColor rgb="FFDDE8CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2E75B6"/>
-        <bgColor rgb="FF2A6099"/>
       </patternFill>
     </fill>
     <fill>
@@ -931,7 +1245,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="119">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -972,63 +1286,427 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="24" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="30" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="40" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="40" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="44" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="45" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1036,147 +1714,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1258,7 +1800,7 @@
       <rgbColor rgb="FF888888"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFD6E4F0"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -1273,9 +1815,9 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFDDE8CB"/>
-      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1286,11 +1828,11 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF420E"/>
-      <rgbColor rgb="FF444444"/>
+      <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FFAAAAAA"/>
       <rgbColor rgb="FF004586"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF00A933"/>
+      <rgbColor rgb="FF444444"/>
       <rgbColor rgb="FF1A1A1A"/>
       <rgbColor rgb="FFC45C00"/>
       <rgbColor rgb="FF993366"/>
@@ -1651,11 +2193,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="81233922"/>
-        <c:axId val="60948278"/>
+        <c:axId val="30129024"/>
+        <c:axId val="63221403"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81233922"/>
+        <c:axId val="30129024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1720,7 +2262,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60948278"/>
+        <c:crossAx val="63221403"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1728,7 +2270,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60948278"/>
+        <c:axId val="63221403"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1802,7 +2344,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81233922"/>
+        <c:crossAx val="30129024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2069,11 +2611,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="46092212"/>
-        <c:axId val="7956479"/>
+        <c:axId val="77139834"/>
+        <c:axId val="16986299"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="46092212"/>
+        <c:axId val="77139834"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2138,7 +2680,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7956479"/>
+        <c:crossAx val="16986299"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2146,7 +2688,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7956479"/>
+        <c:axId val="16986299"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2220,7 +2762,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46092212"/>
+        <c:crossAx val="77139834"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2622,11 +3164,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="86071635"/>
-        <c:axId val="7344530"/>
+        <c:axId val="7819836"/>
+        <c:axId val="38782246"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86071635"/>
+        <c:axId val="7819836"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2691,7 +3233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7344530"/>
+        <c:crossAx val="38782246"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2699,7 +3241,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7344530"/>
+        <c:axId val="38782246"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2773,7 +3315,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86071635"/>
+        <c:crossAx val="7819836"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2870,10 +3412,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.160855150337259"/>
-          <c:y val="0.166988515092997"/>
-          <c:w val="0.688235966617126"/>
-          <c:h val="0.539485720093506"/>
+          <c:x val="0.1608827396947"/>
+          <c:y val="0.167039446929646"/>
+          <c:w val="0.688182493853982"/>
+          <c:h val="0.539345262301749"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -3054,11 +3596,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="792775"/>
-        <c:axId val="81159343"/>
+        <c:axId val="7972407"/>
+        <c:axId val="19313832"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="792775"/>
+        <c:axId val="7972407"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3123,7 +3665,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81159343"/>
+        <c:crossAx val="19313832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3131,7 +3673,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81159343"/>
+        <c:axId val="19313832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3205,7 +3747,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="792775"/>
+        <c:crossAx val="7972407"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4140,9 +4682,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>374760</xdr:colOff>
+      <xdr:colOff>373680</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>134640</xdr:rowOff>
+      <xdr:rowOff>133560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4151,7 +4693,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3703680" y="6023160"/>
-        <a:ext cx="6210000" cy="3497400"/>
+        <a:ext cx="6208920" cy="3496320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4170,9 +4712,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2457000</xdr:colOff>
+      <xdr:colOff>2455920</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>122760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4181,7 +4723,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="10926000" y="5746680"/>
-        <a:ext cx="5757480" cy="3237480"/>
+        <a:ext cx="5756400" cy="3236400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4200,9 +4742,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>420120</xdr:colOff>
+      <xdr:colOff>419040</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>49320</xdr:rowOff>
+      <xdr:rowOff>48240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4211,7 +4753,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4200120" y="9701640"/>
-        <a:ext cx="5758920" cy="3238920"/>
+        <a:ext cx="5757840" cy="3237840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4226,13 +4768,13 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>190800</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>6480</xdr:rowOff>
+      <xdr:rowOff>7200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2613600</xdr:colOff>
+      <xdr:colOff>2612520</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>42840</xdr:rowOff>
+      <xdr:rowOff>42480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4240,8 +4782,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="21579000">
-        <a:off x="10542240" y="9567720"/>
-        <a:ext cx="6297480" cy="3541680"/>
+        <a:off x="10542240" y="9568080"/>
+        <a:ext cx="6296400" cy="3540600"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5988,6 +6530,1145 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="9" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="45"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <f aca="false">SUM(RawData!D2:E13)</f>
+        <v>2091600</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>240000</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <f aca="false">B7/B6</f>
+        <v>0.114744693057946</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>169200</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <f aca="false">B8/B6</f>
+        <v>0.080895008605852</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <f aca="false">SUM(RawData!D14:E25)</f>
+        <v>2390400</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="15" t="n">
+        <f aca="false">SUM(RawData!D14:E25)</f>
+        <v>2390400</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="20" t="n">
+        <v>258000</v>
+      </c>
+      <c r="C17" s="21" t="n">
+        <f aca="false">B17/B16</f>
+        <v>0.107931726907631</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="20" t="n">
+        <v>187200</v>
+      </c>
+      <c r="C18" s="21" t="n">
+        <f aca="false">B18/B16</f>
+        <v>0.0783132530120482</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="15" t="n">
+        <f aca="false">SUM(RawData!D26:E37)</f>
+        <v>2639800</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B25" s="31" t="n">
+        <f aca="false">B6</f>
+        <v>2091600</v>
+      </c>
+      <c r="C25" s="31" t="n">
+        <f aca="false">SUM(RawData!F2:H13)</f>
+        <v>1608900</v>
+      </c>
+      <c r="D25" s="32" t="n">
+        <f aca="false">B25-C25</f>
+        <v>482700</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <f aca="false">D25/B25</f>
+        <v>0.230780263912794</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="34" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B26" s="35" t="n">
+        <f aca="false">B10</f>
+        <v>2390400</v>
+      </c>
+      <c r="C26" s="31" t="n">
+        <f aca="false">SUM(RawData!F14:H25)</f>
+        <v>1838700</v>
+      </c>
+      <c r="D26" s="32" t="n">
+        <f aca="false">B26-C26</f>
+        <v>551700</v>
+      </c>
+      <c r="E26" s="33" t="n">
+        <f aca="false">D26/B26</f>
+        <v>0.230798192771084</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B27" s="31" t="n">
+        <f aca="false">B20</f>
+        <v>2639800</v>
+      </c>
+      <c r="C27" s="31" t="n">
+        <f aca="false">SUM(RawData!F26:H37)</f>
+        <v>2030300</v>
+      </c>
+      <c r="D27" s="32" t="n">
+        <f aca="false">B27-C27</f>
+        <v>609500</v>
+      </c>
+      <c r="E27" s="33" t="n">
+        <f aca="false">D27/B27</f>
+        <v>0.230888703689673</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A23:E23"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="45"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="O5" s="41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="42" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C6" s="43" t="n">
+        <v>41</v>
+      </c>
+      <c r="D6" s="43" t="n">
+        <v>41</v>
+      </c>
+      <c r="E6" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="F6" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="G6" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="I6" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="J6" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="K6" s="43" t="n">
+        <v>43</v>
+      </c>
+      <c r="L6" s="43" t="n">
+        <v>43</v>
+      </c>
+      <c r="M6" s="43" t="n">
+        <v>43</v>
+      </c>
+      <c r="N6" s="44" t="n">
+        <f aca="false">AVERAGE(B6:M6)</f>
+        <v>42</v>
+      </c>
+      <c r="O6" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="42" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="C7" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="D7" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="E7" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="F7" s="43" t="n">
+        <v>47</v>
+      </c>
+      <c r="G7" s="43" t="n">
+        <v>47</v>
+      </c>
+      <c r="H7" s="43" t="n">
+        <v>47</v>
+      </c>
+      <c r="I7" s="43" t="n">
+        <v>47</v>
+      </c>
+      <c r="J7" s="43" t="n">
+        <v>48</v>
+      </c>
+      <c r="K7" s="43" t="n">
+        <v>48</v>
+      </c>
+      <c r="L7" s="43" t="n">
+        <v>48</v>
+      </c>
+      <c r="M7" s="43" t="n">
+        <v>48</v>
+      </c>
+      <c r="N7" s="44" t="n">
+        <f aca="false">AVERAGE(B7:M7)</f>
+        <v>47</v>
+      </c>
+      <c r="O7" s="45" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="43" t="n">
+        <v>51</v>
+      </c>
+      <c r="C8" s="43" t="n">
+        <v>51</v>
+      </c>
+      <c r="D8" s="43" t="n">
+        <v>51</v>
+      </c>
+      <c r="E8" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="F8" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="G8" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="H8" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="I8" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="J8" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="K8" s="43" t="n">
+        <v>53</v>
+      </c>
+      <c r="L8" s="43" t="n">
+        <v>53</v>
+      </c>
+      <c r="M8" s="43" t="n">
+        <v>53</v>
+      </c>
+      <c r="N8" s="44" t="n">
+        <f aca="false">AVERAGE(B8:M8)</f>
+        <v>52</v>
+      </c>
+      <c r="O8" s="45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="O11" s="41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="42" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M12" s="46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N12" s="47" t="n">
+        <f aca="false">AVERAGE(B12:M12)</f>
+        <v>4000</v>
+      </c>
+      <c r="O12" s="45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="42" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="C13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="D13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="E13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="F13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="G13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="H13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="J13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="K13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="L13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="M13" s="46" t="n">
+        <v>4300</v>
+      </c>
+      <c r="N13" s="47" t="n">
+        <f aca="false">AVERAGE(B13:M13)</f>
+        <v>4300</v>
+      </c>
+      <c r="O13" s="45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="C14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="D14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="E14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="F14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="G14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="I14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="J14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="L14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="M14" s="46" t="n">
+        <v>4600</v>
+      </c>
+      <c r="N14" s="47" t="n">
+        <f aca="false">AVERAGE(B14:M14)</f>
+        <v>4600</v>
+      </c>
+      <c r="O14" s="45" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+    </row>
+    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="42" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="I17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="J17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="M17" s="46" t="n">
+        <v>35000</v>
+      </c>
+      <c r="N17" s="47" t="n">
+        <f aca="false">SUM(B17:M17)</f>
+        <v>420000</v>
+      </c>
+      <c r="O17" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="42" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M18" s="46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="N18" s="47" t="n">
+        <f aca="false">SUM(B18:M18)</f>
+        <v>480000</v>
+      </c>
+      <c r="O18" s="48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="C19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="D19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="E19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="F19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="G19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="H19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="I19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="J19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="K19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="L19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="M19" s="46" t="n">
+        <v>44200</v>
+      </c>
+      <c r="N19" s="47" t="n">
+        <f aca="false">SUM(B19:M19)</f>
+        <v>530400</v>
+      </c>
+      <c r="O19" s="48" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+    </row>
+    <row r="22" customFormat="false" ht="31.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="51" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B23" s="52" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2022",RawData!F:F)</f>
+        <v>1358100</v>
+      </c>
+      <c r="C23" s="53" t="n">
+        <f aca="false">N6</f>
+        <v>42</v>
+      </c>
+      <c r="D23" s="54" t="n">
+        <f aca="false">B23/C23</f>
+        <v>32335.7142857143</v>
+      </c>
+      <c r="E23" s="54" t="n">
+        <f aca="false">D23/12</f>
+        <v>2694.64285714286</v>
+      </c>
+      <c r="F23" s="55" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B24" s="52" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2023",RawData!F:F)</f>
+        <v>1552200</v>
+      </c>
+      <c r="C24" s="53" t="n">
+        <f aca="false">N7</f>
+        <v>47</v>
+      </c>
+      <c r="D24" s="54" t="n">
+        <f aca="false">B24/C24</f>
+        <v>33025.5319148936</v>
+      </c>
+      <c r="E24" s="54" t="n">
+        <f aca="false">D24/12</f>
+        <v>2752.12765957447</v>
+      </c>
+      <c r="F24" s="55" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="52" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!F:F)</f>
+        <v>1713800</v>
+      </c>
+      <c r="C25" s="53" t="n">
+        <f aca="false">N8</f>
+        <v>52</v>
+      </c>
+      <c r="D25" s="54" t="n">
+        <f aca="false">B25/C25</f>
+        <v>32957.6923076923</v>
+      </c>
+      <c r="E25" s="54" t="n">
+        <f aca="false">D25/12</f>
+        <v>2746.47435897436</v>
+      </c>
+      <c r="F25" s="55" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="A21:F21"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:X56"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -5998,733 +7679,775 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="50.86"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="true" ht="27.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
+    <row r="1" s="58" customFormat="true" ht="27.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" s="14" customFormat="true" ht="21.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="A2" s="59" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" s="60" customFormat="true" ht="21.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="14" t="s">
+      <c r="C4" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="M4" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P4" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" s="17" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
+      <c r="N4" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="O4" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="P4" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q4" s="60" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="63"/>
+      <c r="S5" s="63"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="63"/>
+      <c r="V5" s="63"/>
+      <c r="W5" s="63"/>
+      <c r="X5" s="63"/>
     </row>
     <row r="6" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="19" t="n">
+      <c r="A6" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="65" t="n">
         <f aca="false">RawData!D26-RawData!I26</f>
         <v>-12000</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="65" t="n">
         <f aca="false">RawData!D27-RawData!I27</f>
         <v>-13000</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="65" t="n">
         <f aca="false">RawData!D28-RawData!I28</f>
         <v>-15000</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="65" t="n">
         <f aca="false">RawData!D29-RawData!I29</f>
         <v>-18000</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="65" t="n">
         <f aca="false">RawData!D30-RawData!I30</f>
         <v>-19000</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="65" t="n">
         <f aca="false">RawData!D31-RawData!I31</f>
         <v>-19000</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="65" t="n">
         <f aca="false">RawData!D32-RawData!I32</f>
         <v>-19000</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="65" t="n">
         <f aca="false">RawData!D33-RawData!I33</f>
         <v>-18000</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="65" t="n">
         <f aca="false">RawData!D34-RawData!I34</f>
         <v>-17000</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="65" t="n">
         <f aca="false">RawData!D35-RawData!I35</f>
         <v>-17000</v>
       </c>
-      <c r="L6" s="19" t="n">
+      <c r="L6" s="65" t="n">
         <f aca="false">RawData!D36-RawData!I36</f>
         <v>-16000</v>
       </c>
-      <c r="M6" s="19" t="n">
+      <c r="M6" s="65" t="n">
         <f aca="false">RawData!D37-RawData!I37</f>
         <v>-16000</v>
       </c>
-      <c r="N6" s="19" t="n">
+      <c r="N6" s="65" t="n">
         <f aca="false">SUM(B6:M6)</f>
         <v>-199000</v>
       </c>
-      <c r="O6" s="19" t="n">
+      <c r="O6" s="65" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!D:D)-SUMIF(RawData!A:A,"=2024",RawData!I:I)</f>
         <v>-199000</v>
       </c>
-      <c r="P6" s="20" t="n">
+      <c r="P6" s="66" t="n">
         <f aca="false">IF(SUMIF(RawData!A:A,"=2024",RawData!I:I)=0,0,O6/SUMIF(RawData!A:A,"=2024",RawData!I:I))</f>
         <v>-0.0862068965517241</v>
       </c>
-      <c r="Q6" s="21" t="s">
-        <v>37</v>
+      <c r="Q6" s="67" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="19" t="n">
+      <c r="A7" s="64" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="65" t="n">
         <f aca="false">RawData!E26-RawData!J26</f>
         <v>-4100</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="65" t="n">
         <f aca="false">RawData!$E27-RawData!$J27</f>
         <v>-4100</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="65" t="n">
         <f aca="false">RawData!$E28-RawData!$J28</f>
         <v>-4100</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="65" t="n">
         <f aca="false">RawData!$E29-RawData!$J29</f>
         <v>-4100</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="65" t="n">
         <f aca="false">RawData!$E30-RawData!$J30</f>
         <v>-4100</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="65" t="n">
         <f aca="false">RawData!$E31-RawData!$J31</f>
         <v>-4100</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="65" t="n">
         <f aca="false">RawData!$E32-RawData!$J32</f>
         <v>-4100</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="65" t="n">
         <f aca="false">RawData!$E33-RawData!$J33</f>
         <v>-4100</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="65" t="n">
         <f aca="false">RawData!$E34-RawData!$J34</f>
         <v>-4100</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="65" t="n">
         <f aca="false">RawData!$E35-RawData!$J35</f>
         <v>-4100</v>
       </c>
-      <c r="L7" s="19" t="n">
+      <c r="L7" s="65" t="n">
         <f aca="false">RawData!$E36-RawData!$J36</f>
         <v>-4100</v>
       </c>
-      <c r="M7" s="19" t="n">
+      <c r="M7" s="65" t="n">
         <f aca="false">RawData!$E37-RawData!$J37</f>
         <v>-4100</v>
       </c>
-      <c r="N7" s="19" t="n">
+      <c r="N7" s="65" t="n">
         <f aca="false">SUM(B7:M7)</f>
         <v>-49200</v>
       </c>
-      <c r="O7" s="19" t="n">
+      <c r="O7" s="65" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!E:E)-SUMIF(RawData!A:A,"=2024",RawData!J:J)</f>
         <v>-49200</v>
       </c>
-      <c r="P7" s="20" t="n">
+      <c r="P7" s="66" t="n">
         <f aca="false">IF(SUMIF(RawData!A:A,"=2024",RawData!J:J)=0,0,O7/SUMIF(RawData!A:A,"=2024",RawData!J:J))</f>
         <v>-0.0848861283643892</v>
       </c>
-      <c r="Q7" s="21" t="s">
-        <v>39</v>
+      <c r="Q7" s="67" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="22" t="n">
+      <c r="A8" s="61" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="68" t="n">
         <f aca="false">B6+B7</f>
         <v>-16100</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="68" t="n">
         <f aca="false">C6+C7</f>
         <v>-17100</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="68" t="n">
         <f aca="false">D6+D7</f>
         <v>-19100</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="68" t="n">
         <f aca="false">E6+E7</f>
         <v>-22100</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="68" t="n">
         <f aca="false">F6+F7</f>
         <v>-23100</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="68" t="n">
         <f aca="false">G6+G7</f>
         <v>-23100</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="68" t="n">
         <f aca="false">H6+H7</f>
         <v>-23100</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="68" t="n">
         <f aca="false">I6+I7</f>
         <v>-22100</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="68" t="n">
         <f aca="false">J6+J7</f>
         <v>-21100</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="68" t="n">
         <f aca="false">K6+K7</f>
         <v>-21100</v>
       </c>
-      <c r="L8" s="22" t="n">
+      <c r="L8" s="68" t="n">
         <f aca="false">L6+L7</f>
         <v>-20100</v>
       </c>
-      <c r="M8" s="22" t="n">
+      <c r="M8" s="68" t="n">
         <f aca="false">M6+M7</f>
         <v>-20100</v>
       </c>
-      <c r="N8" s="22" t="n">
+      <c r="N8" s="68" t="n">
         <f aca="false">SUM(B8:M8)</f>
         <v>-248200</v>
       </c>
-      <c r="O8" s="22" t="n">
+      <c r="O8" s="68" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!E:E)-SUMIF(RawData!A:A,"=2024",RawData!J:J)+SUMIF(RawData!A:A,"=2024",RawData!D:D)-SUMIF(RawData!A:A,"=2024",RawData!I:I)</f>
         <v>-248200</v>
       </c>
-      <c r="P8" s="23" t="n">
+      <c r="P8" s="69" t="n">
         <f aca="false">O8/(SUMIF(RawData!A:A,"=2024",RawData!J:J)+SUMIF(RawData!A:A,"=2024",RawData!I:I))</f>
         <v>-0.0859418282548476</v>
       </c>
-      <c r="Q8" s="21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" s="17" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
+      <c r="Q8" s="67" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="63"/>
+      <c r="R11" s="63"/>
+      <c r="S11" s="63"/>
+      <c r="T11" s="63"/>
+      <c r="U11" s="63"/>
+      <c r="V11" s="63"/>
+      <c r="W11" s="63"/>
+      <c r="X11" s="63"/>
     </row>
     <row r="12" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="24" t="n">
+      <c r="A12" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="70" t="n">
         <f aca="false">RawData!K26-RawData!F26</f>
         <v>9700</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="70" t="n">
         <f aca="false">RawData!K27-RawData!F27</f>
         <v>10500</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="70" t="n">
         <f aca="false">RawData!K28-RawData!F28</f>
         <v>12200</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="70" t="n">
         <f aca="false">RawData!K29-RawData!F29</f>
         <v>14600</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="70" t="n">
         <f aca="false">RawData!K30-RawData!F30</f>
         <v>15500</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="70" t="n">
         <f aca="false">RawData!K31-RawData!F31</f>
         <v>15500</v>
       </c>
-      <c r="H12" s="24" t="n">
+      <c r="H12" s="70" t="n">
         <f aca="false">RawData!K32-RawData!F32</f>
         <v>15500</v>
       </c>
-      <c r="I12" s="24" t="n">
+      <c r="I12" s="70" t="n">
         <f aca="false">RawData!K33-RawData!F33</f>
         <v>14600</v>
       </c>
-      <c r="J12" s="24" t="n">
+      <c r="J12" s="70" t="n">
         <f aca="false">RawData!K34-RawData!F34</f>
         <v>13800</v>
       </c>
-      <c r="K12" s="24" t="n">
+      <c r="K12" s="70" t="n">
         <f aca="false">RawData!K35-RawData!F35</f>
         <v>13800</v>
       </c>
-      <c r="L12" s="24" t="n">
+      <c r="L12" s="70" t="n">
         <f aca="false">RawData!K36-RawData!F36</f>
         <v>13000</v>
       </c>
-      <c r="M12" s="24" t="n">
+      <c r="M12" s="70" t="n">
         <f aca="false">RawData!K37-RawData!F37</f>
         <v>13000</v>
       </c>
-      <c r="N12" s="19" t="n">
+      <c r="N12" s="65" t="n">
         <f aca="false">SUM(B12:M12)</f>
         <v>161700</v>
       </c>
-      <c r="O12" s="19" t="n">
+      <c r="O12" s="65" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!K:K)-SUMIF(RawData!A:A,"=2024",RawData!F:F)</f>
         <v>161700</v>
       </c>
-      <c r="P12" s="20" t="n">
+      <c r="P12" s="66" t="n">
         <f aca="false">IF(SUMIF(RawData!A:A,"=2024",RawData!K:K)=0,0,O12/SUMIF(RawData!A:A,"=2024",RawData!K:K))</f>
         <v>0.086217008797654</v>
       </c>
-      <c r="Q12" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="S12" s="25"/>
+      <c r="Q12" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="S12" s="71"/>
     </row>
     <row r="13" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="24" t="n">
+      <c r="A13" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="70" t="n">
         <f aca="false">RawData!L26-RawData!G26</f>
         <v>1200</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="70" t="n">
         <f aca="false">RawData!L27-RawData!G27</f>
         <v>1300</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="70" t="n">
         <f aca="false">RawData!L28-RawData!G28</f>
         <v>1500</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="70" t="n">
         <f aca="false">RawData!L29-RawData!G29</f>
         <v>1800</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="70" t="n">
         <f aca="false">RawData!L30-RawData!G30</f>
         <v>1900</v>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="70" t="n">
         <f aca="false">RawData!L31-RawData!G31</f>
         <v>1900</v>
       </c>
-      <c r="H13" s="24" t="n">
+      <c r="H13" s="70" t="n">
         <f aca="false">RawData!L32-RawData!G32</f>
         <v>1900</v>
       </c>
-      <c r="I13" s="24" t="n">
+      <c r="I13" s="70" t="n">
         <f aca="false">RawData!L33-RawData!G33</f>
         <v>1800</v>
       </c>
-      <c r="J13" s="24" t="n">
+      <c r="J13" s="70" t="n">
         <f aca="false">RawData!L34-RawData!G34</f>
         <v>1700</v>
       </c>
-      <c r="K13" s="24" t="n">
+      <c r="K13" s="70" t="n">
         <f aca="false">RawData!L35-RawData!G35</f>
         <v>1700</v>
       </c>
-      <c r="L13" s="24" t="n">
+      <c r="L13" s="70" t="n">
         <f aca="false">RawData!L36-RawData!G36</f>
         <v>1600</v>
       </c>
-      <c r="M13" s="24" t="n">
+      <c r="M13" s="70" t="n">
         <f aca="false">RawData!L37-RawData!G37</f>
         <v>1600</v>
       </c>
-      <c r="N13" s="19" t="n">
+      <c r="N13" s="65" t="n">
         <f aca="false">SUM(B13:M13)</f>
         <v>19900</v>
       </c>
-      <c r="O13" s="19" t="n">
+      <c r="O13" s="65" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!L:L)-SUMIF(RawData!A:A,"=2024",RawData!G:G)</f>
         <v>19900</v>
       </c>
-      <c r="P13" s="20" t="n">
+      <c r="P13" s="66" t="n">
         <f aca="false">IF(SUMIF(RawData!A:A,"=2024",RawData!L:L)=0,0,O13/SUMIF(RawData!A:A,"=2024",RawData!L:L))</f>
         <v>0.0862218370883882</v>
       </c>
-      <c r="Q13" s="21" t="s">
-        <v>46</v>
+      <c r="Q13" s="67" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="24" t="n">
+      <c r="A14" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="70" t="n">
         <f aca="false">RawData!M26-RawData!H26</f>
         <v>600</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="70" t="n">
         <f aca="false">RawData!M27-RawData!H27</f>
         <v>600</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="70" t="n">
         <f aca="false">RawData!M28-RawData!H28</f>
         <v>700</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="70" t="n">
         <f aca="false">RawData!M29-RawData!H29</f>
         <v>900</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="70" t="n">
         <f aca="false">RawData!M30-RawData!H30</f>
         <v>900</v>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="70" t="n">
         <f aca="false">RawData!M31-RawData!H31</f>
         <v>900</v>
       </c>
-      <c r="H14" s="24" t="n">
+      <c r="H14" s="70" t="n">
         <f aca="false">RawData!M32-RawData!H32</f>
         <v>900</v>
       </c>
-      <c r="I14" s="24" t="n">
+      <c r="I14" s="70" t="n">
         <f aca="false">RawData!M33-RawData!H33</f>
         <v>900</v>
       </c>
-      <c r="J14" s="24" t="n">
+      <c r="J14" s="70" t="n">
         <f aca="false">RawData!M34-RawData!H34</f>
         <v>900</v>
       </c>
-      <c r="K14" s="24" t="n">
+      <c r="K14" s="70" t="n">
         <f aca="false">RawData!M35-RawData!H35</f>
         <v>900</v>
       </c>
-      <c r="L14" s="24" t="n">
+      <c r="L14" s="70" t="n">
         <f aca="false">RawData!M36-RawData!H36</f>
         <v>800</v>
       </c>
-      <c r="M14" s="24" t="n">
+      <c r="M14" s="70" t="n">
         <f aca="false">RawData!M37-RawData!H37</f>
         <v>800</v>
       </c>
-      <c r="N14" s="19" t="n">
+      <c r="N14" s="65" t="n">
         <f aca="false">SUM(B14:M14)</f>
         <v>9800</v>
       </c>
-      <c r="O14" s="19" t="n">
+      <c r="O14" s="65" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!M:M)-SUMIF(RawData!A:A,"=2024",RawData!H:H)</f>
         <v>9800</v>
       </c>
-      <c r="P14" s="20" t="n">
+      <c r="P14" s="66" t="n">
         <f aca="false">IF(SUMIF(RawData!A:A,"=2024",RawData!M:M)=0,0,O14/SUMIF(RawData!A:A,"=2024",RawData!M:M))</f>
         <v>0.0849220103986135</v>
       </c>
-      <c r="Q14" s="21" t="s">
-        <v>48</v>
+      <c r="Q14" s="67" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="22" t="n">
+      <c r="A15" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="68" t="n">
         <f aca="false">B13+B14+B12</f>
         <v>11500</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="68" t="n">
         <f aca="false">C13+C14+C12</f>
         <v>12400</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="68" t="n">
         <f aca="false">D13+D14+D12</f>
         <v>14400</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="68" t="n">
         <f aca="false">E13+E14+E12</f>
         <v>17300</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="68" t="n">
         <f aca="false">F13+F14+F12</f>
         <v>18300</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="68" t="n">
         <f aca="false">G13+G14+G12</f>
         <v>18300</v>
       </c>
-      <c r="H15" s="22" t="n">
+      <c r="H15" s="68" t="n">
         <f aca="false">H13+H14+H12</f>
         <v>18300</v>
       </c>
-      <c r="I15" s="22" t="n">
+      <c r="I15" s="68" t="n">
         <f aca="false">I13+I14+I12</f>
         <v>17300</v>
       </c>
-      <c r="J15" s="22" t="n">
+      <c r="J15" s="68" t="n">
         <f aca="false">J13+J14+J12</f>
         <v>16400</v>
       </c>
-      <c r="K15" s="22" t="n">
+      <c r="K15" s="68" t="n">
         <f aca="false">K13+K14+K12</f>
         <v>16400</v>
       </c>
-      <c r="L15" s="22" t="n">
+      <c r="L15" s="68" t="n">
         <f aca="false">L13+L14+L12</f>
         <v>15400</v>
       </c>
-      <c r="M15" s="22" t="n">
+      <c r="M15" s="68" t="n">
         <f aca="false">M13+M14+M12</f>
         <v>15400</v>
       </c>
-      <c r="N15" s="22" t="n">
+      <c r="N15" s="68" t="n">
         <f aca="false">SUM(B15:M15)</f>
         <v>191400</v>
       </c>
-      <c r="O15" s="22" t="n">
+      <c r="O15" s="68" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!K:K)-SUMIF(RawData!A:A,"=2024",RawData!F:F)+SUMIF(RawData!A:A,"=2024",RawData!L:L)-SUMIF(RawData!A:A,"=2024",RawData!G:G)+SUMIF(RawData!A:A,"=2024",RawData!M:M)-SUMIF(RawData!A:A,"=2024",RawData!H:H)</f>
         <v>191400</v>
       </c>
-      <c r="P15" s="23" t="n">
+      <c r="P15" s="69" t="n">
         <f aca="false">O15/(SUMIF(RawData!A:A,"=2024",RawData!K:K)+SUMIF(RawData!A:A,"=2024",RawData!L:L)+SUMIF(RawData!A:A,"=2024",RawData!M:M))</f>
         <v>0.0861502453076473</v>
       </c>
-      <c r="Q15" s="27"/>
+      <c r="Q15" s="73"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q16" s="28"/>
+      <c r="Q16" s="74"/>
     </row>
     <row r="17" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="22" t="n">
+      <c r="A17" s="75" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="68" t="n">
         <f aca="false">(RawData!D26+RawData!E26-RawData!F26-RawData!G26-RawData!H26)-(RawData!I26+RawData!J26-RawData!K26-RawData!L26-RawData!M26)</f>
         <v>-4600</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="68" t="n">
         <f aca="false">(RawData!D27+RawData!E27-RawData!F27-RawData!G27-RawData!H27)-(RawData!I27+RawData!J27-RawData!K27-RawData!L27-RawData!M27)</f>
         <v>-4700</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="68" t="n">
         <f aca="false">(RawData!D28+RawData!E28-RawData!F28-RawData!G28-RawData!H28)-(RawData!I28+RawData!J28-RawData!K28-RawData!L28-RawData!M28)</f>
         <v>-4700</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="68" t="n">
         <f aca="false">(RawData!D29 + RawData!E29 - RawData!F29 - RawData!G29 - RawData!H29)  - (RawData!I29 + RawData!J29 - RawData!K29 - RawData!L29 - RawData!M29)</f>
         <v>-4800</v>
       </c>
-      <c r="F17" s="22" t="n">
+      <c r="F17" s="68" t="n">
         <f aca="false">(RawData!D30 + RawData!E30 - RawData!F30 - RawData!G30 - RawData!H30)  - (RawData!I30 + RawData!J30 - RawData!K30 - RawData!L30 - RawData!M30)</f>
         <v>-4800</v>
       </c>
-      <c r="G17" s="22" t="n">
+      <c r="G17" s="68" t="n">
         <f aca="false">(RawData!D31 + RawData!E31 - RawData!F31 - RawData!G31 - RawData!H31)  - (RawData!I31 + RawData!J31 - RawData!K31 - RawData!L31 - RawData!M31)</f>
         <v>-4800</v>
       </c>
-      <c r="H17" s="22" t="n">
+      <c r="H17" s="68" t="n">
         <f aca="false">(RawData!D32 + RawData!E32 - RawData!F32 - RawData!G32 - RawData!H32)  - (RawData!I32 + RawData!J32 - RawData!K32 - RawData!L32 - RawData!M32)</f>
         <v>-4800</v>
       </c>
-      <c r="I17" s="22" t="n">
+      <c r="I17" s="68" t="n">
         <f aca="false">(RawData!D33 + RawData!E33 - RawData!F33 - RawData!G33 - RawData!H33)  - (RawData!I33 + RawData!J33 - RawData!K33 - RawData!L33 - RawData!M33)</f>
         <v>-4800</v>
       </c>
-      <c r="J17" s="22" t="n">
+      <c r="J17" s="68" t="n">
         <f aca="false">(RawData!D34 + RawData!E34 - RawData!F34 - RawData!G34 - RawData!H34)  - (RawData!I34 + RawData!J34 - RawData!K34 - RawData!L34 - RawData!M34)</f>
         <v>-4700</v>
       </c>
-      <c r="K17" s="22" t="n">
+      <c r="K17" s="68" t="n">
         <f aca="false">(RawData!D35 + RawData!E35 - RawData!F35 - RawData!G35 - RawData!H35)  - (RawData!I35 + RawData!J35 - RawData!K35 - RawData!L35 - RawData!M35)</f>
         <v>-4700</v>
       </c>
-      <c r="L17" s="22" t="n">
+      <c r="L17" s="68" t="n">
         <f aca="false">(RawData!D36 + RawData!E36 - RawData!F36 - RawData!G36 - RawData!H36)  - (RawData!I36 + RawData!J36 - RawData!K36 - RawData!L36 - RawData!M36)</f>
         <v>-4700</v>
       </c>
-      <c r="M17" s="22" t="n">
+      <c r="M17" s="68" t="n">
         <f aca="false">(RawData!D37 + RawData!E37 - RawData!F37 - RawData!G37 - RawData!H37)  - (RawData!I37 + RawData!J37 - RawData!K37 - RawData!L37 - RawData!M37)</f>
         <v>-4700</v>
       </c>
-      <c r="N17" s="22" t="n">
+      <c r="N17" s="68" t="n">
         <f aca="false">SUM(B17:M17)</f>
         <v>-56800</v>
       </c>
-      <c r="O17" s="22" t="n">
+      <c r="O17" s="68" t="n">
         <f aca="false">O8+O15</f>
         <v>-56800</v>
       </c>
-      <c r="P17" s="23" t="n">
+      <c r="P17" s="69" t="n">
         <f aca="false">O17/(SUMIF(RawData!A:A,"=2024",RawData!I:I)+SUMIF(RawData!A:A,"=2024",RawData!J:J)-SUMIF(RawData!A:A,"=2024",RawData!L:L)-SUMIF(RawData!A:A,"=2024",RawData!M:M)-SUMIF(RawData!A:A,"=2024",RawData!K:K))</f>
         <v>-0.085246885787183</v>
       </c>
-      <c r="Q17" s="30" t="s">
-        <v>51</v>
+      <c r="Q17" s="76" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="23" t="n">
+        <v>61</v>
+      </c>
+      <c r="B18" s="69" t="n">
         <f aca="false">IF((RawData!D26+RawData!E26)=0,0,(RawData!D26+RawData!E26-RawData!F26-RawData!G26-RawData!H26)/(RawData!D26+RawData!E26))-IF((RawData!I26+RawData!J26)=0,0,(RawData!I26+RawData!J26-RawData!K26-RawData!L26-RawData!M26)/(RawData!I26+RawData!J26))</f>
         <v>-3.57837417347406E-005</v>
       </c>
-      <c r="C18" s="23" t="n">
+      <c r="C18" s="69" t="n">
         <f aca="false">IF((RawData!D27+RawData!E27)=0,0,(RawData!D27+RawData!E27-RawData!F27-RawData!G27-RawData!H27)/(RawData!D27+RawData!E27)) - IF((RawData!I27+RawData!J27)=0,0,(RawData!I27+RawData!J27-RawData!K27-RawData!L27-RawData!M27)/(RawData!I27+RawData!J27))</f>
         <v>-0.000341371335846497</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="69" t="n">
         <f aca="false">IF((RawData!D28+RawData!E28)=0,0,(RawData!D28+RawData!E28-RawData!F28-RawData!G28-RawData!H28)/(RawData!D28+RawData!E28)) - IF((RawData!I28+RawData!J28)=0,0,(RawData!I28+RawData!J28-RawData!K28-RawData!L28-RawData!M28)/(RawData!I28+RawData!J28))</f>
         <v>4.13979123055075E-005</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="69" t="n">
         <f aca="false">IF((RawData!D29+RawData!E29)=0,0,(RawData!D29+RawData!E29-RawData!F29-RawData!G29-RawData!H29)/(RawData!D29+RawData!E29)) - IF((RawData!I29+RawData!J29)=0,0,(RawData!I29+RawData!J29-RawData!K29-RawData!L29-RawData!M29)/(RawData!I29+RawData!J29))</f>
         <v>0.000131416701838</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="69" t="n">
         <f aca="false">IF((RawData!D30+RawData!E30)=0,0,(RawData!D30+RawData!E30-RawData!F30-RawData!G30-RawData!H30)/(RawData!D30+RawData!E30)) - IF((RawData!I30+RawData!J30)=0,0,(RawData!I30+RawData!J30-RawData!K30-RawData!L30-RawData!M30)/(RawData!I30+RawData!J30))</f>
         <v>0.000268211402712298</v>
       </c>
-      <c r="G18" s="23" t="n">
+      <c r="G18" s="69" t="n">
         <f aca="false">IF((RawData!D31+RawData!E31)=0,0,(RawData!D31+RawData!E31-RawData!F31-RawData!G31-RawData!H31)/(RawData!D31+RawData!E31)) - IF((RawData!I31+RawData!J31)=0,0,(RawData!I31+RawData!J31-RawData!K31-RawData!L31-RawData!M31)/(RawData!I31+RawData!J31))</f>
         <v>0.000268211402712298</v>
       </c>
-      <c r="H18" s="23" t="n">
+      <c r="H18" s="69" t="n">
         <f aca="false">IF((RawData!D32+RawData!E32)=0,0,(RawData!D32+RawData!E32-RawData!F32-RawData!G32-RawData!H32)/(RawData!D32+RawData!E32)) - IF((RawData!I32+RawData!J32)=0,0,(RawData!I32+RawData!J32-RawData!K32-RawData!L32-RawData!M32)/(RawData!I32+RawData!J32))</f>
         <v>0.000268211402712298</v>
       </c>
-      <c r="I18" s="23" t="n">
+      <c r="I18" s="69" t="n">
         <f aca="false">IF((RawData!D33+RawData!E33)=0,0,(RawData!D33+RawData!E33-RawData!F33-RawData!G33-RawData!H33)/(RawData!D33+RawData!E33)) - IF((RawData!I33+RawData!J33)=0,0,(RawData!I33+RawData!J33-RawData!K33-RawData!L33-RawData!M33)/(RawData!I33+RawData!J33))</f>
         <v>0.000131416701838</v>
       </c>
-      <c r="J18" s="23" t="n">
+      <c r="J18" s="69" t="n">
         <f aca="false">IF((RawData!D34+RawData!E34)=0,0,(RawData!D34+RawData!E34-RawData!F34-RawData!G34-RawData!H34)/(RawData!D34+RawData!E34)) - IF((RawData!I34+RawData!J34)=0,0,(RawData!I34+RawData!J34-RawData!K34-RawData!L34-RawData!M34)/(RawData!I34+RawData!J34))</f>
         <v>0.000388816885761895</v>
       </c>
-      <c r="K18" s="23" t="n">
+      <c r="K18" s="69" t="n">
         <f aca="false">IF((RawData!D35+RawData!E35)=0,0,(RawData!D35+RawData!E35-RawData!F35-RawData!G35-RawData!H35)/(RawData!D35+RawData!E35)) - IF((RawData!I35+RawData!J35)=0,0,(RawData!I35+RawData!J35-RawData!K35-RawData!L35-RawData!M35)/(RawData!I35+RawData!J35))</f>
         <v>0.000388816885761895</v>
       </c>
-      <c r="L18" s="23" t="n">
+      <c r="L18" s="69" t="n">
         <f aca="false">IF((RawData!D36+RawData!E36)=0,0,(RawData!D36+RawData!E36-RawData!F36-RawData!G36-RawData!H36)/(RawData!D36+RawData!E36)) - IF((RawData!I36+RawData!J36)=0,0,(RawData!I36+RawData!J36-RawData!K36-RawData!L36-RawData!M36)/(RawData!I36+RawData!J36))</f>
         <v>0.000203768130664361</v>
       </c>
-      <c r="M18" s="23" t="n">
+      <c r="M18" s="69" t="n">
         <f aca="false">IF((RawData!D37+RawData!E37)=0,0,(RawData!D37+RawData!E37-RawData!F37-RawData!G37-RawData!H37)/(RawData!D37+RawData!E37)) - IF((RawData!I37+RawData!J37)=0,0,(RawData!I37+RawData!J37-RawData!K37-RawData!L37-RawData!M37)/(RawData!I37+RawData!J37))</f>
         <v>0.000203768130664361</v>
       </c>
-      <c r="N18" s="23" t="n">
+      <c r="N18" s="69" t="n">
         <f aca="false">(SUMIF(RawData!A:A,2024,RawData!D:D)+SUMIF(RawData!A:A,2024,RawData!E:E)-SUMIF(RawData!A:A,2024,RawData!F:F)-SUMIF(RawData!A:A,2024,RawData!G:G)-SUMIF(RawData!A:A,2024,RawData!H:H))/(SUMIF(RawData!A:A,2024,RawData!D:D)+SUMIF(RawData!A:A,2024,RawData!E:E))-((SUMIF(RawData!A:A,2024,RawData!I:I)+SUMIF(RawData!A:A,2024,RawData!J:J)-SUMIF(RawData!A:A,2024,RawData!K:K)-SUMIF(RawData!A:A,2024,RawData!L:L)-SUMIF(RawData!A:A,2024,RawData!M:M))/(SUMIF(RawData!A:A,2024,RawData!I:I)+SUMIF(RawData!A:A,2024,RawData!J:J)))</f>
         <v>0.000175407290781499</v>
       </c>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="31"/>
+      <c r="O18" s="69"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="77"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">B17-B15-B8</f>
@@ -6782,43 +8505,43 @@
         <f aca="false">O17-O15-O8</f>
         <v>0</v>
       </c>
-      <c r="P19" s="32"/>
+      <c r="P19" s="78"/>
       <c r="R19" s="2" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q20" s="33" t="s">
-        <v>55</v>
+      <c r="Q20" s="79" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P21" s="34"/>
-      <c r="Q21" s="25" t="s">
-        <v>56</v>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="71" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>59</v>
+      <c r="B22" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="81" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="82" t="s">
+        <v>115</v>
       </c>
       <c r="T22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="B23" s="9" t="n">
         <f aca="false">RawData!D26+RawData!E26</f>
@@ -6837,7 +8560,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="n">
         <f aca="false">RawData!D27+RawData!E27</f>
@@ -6855,7 +8578,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="B25" s="9" t="n">
         <f aca="false">RawData!D28+RawData!E28</f>
@@ -6873,7 +8596,7 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="B26" s="9" t="n">
         <f aca="false">RawData!D29+RawData!E29</f>
@@ -6891,7 +8614,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="B27" s="9" t="n">
         <f aca="false">RawData!D30+RawData!E30</f>
@@ -6909,7 +8632,7 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="B28" s="9" t="n">
         <f aca="false">RawData!D31+RawData!E31</f>
@@ -6928,7 +8651,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="B29" s="9" t="n">
         <f aca="false">RawData!D32+RawData!E32</f>
@@ -6947,7 +8670,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="B30" s="9" t="n">
         <f aca="false">RawData!D33+RawData!E33</f>
@@ -6965,7 +8688,7 @@
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9" t="n">
         <f aca="false">RawData!D34+RawData!E34</f>
@@ -6983,7 +8706,7 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="B32" s="9" t="n">
         <f aca="false">RawData!D35+RawData!E35</f>
@@ -6998,12 +8721,12 @@
         <v>21100</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9" t="n">
         <f aca="false">RawData!D36+RawData!E36</f>
@@ -7018,12 +8741,12 @@
         <v>20100</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="B34" s="9" t="n">
         <f aca="false">RawData!D37+RawData!E37</f>
@@ -7038,7 +8761,7 @@
         <v>20100</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7046,23 +8769,23 @@
       <c r="U35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="35" t="s">
+      <c r="A36" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B36" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>59</v>
+      <c r="B36" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="81" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="82" t="s">
+        <v>115</v>
       </c>
       <c r="T36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="B37" s="9" t="n">
         <f aca="false">RawData!F26+RawData!G26+RawData!H26</f>
@@ -7077,12 +8800,12 @@
         <v>11500</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="B38" s="9" t="n">
         <f aca="false">RawData!F27+RawData!G27+RawData!H27</f>
@@ -7097,12 +8820,12 @@
         <v>12400</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="B39" s="9" t="n">
         <f aca="false">RawData!F28+RawData!G28+RawData!H28</f>
@@ -7117,12 +8840,12 @@
         <v>14400</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="B40" s="9" t="n">
         <f aca="false">RawData!F29+RawData!G29+RawData!H29</f>
@@ -7140,7 +8863,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="B41" s="9" t="n">
         <f aca="false">RawData!F30+RawData!G30+RawData!H30</f>
@@ -7159,7 +8882,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="B42" s="9" t="n">
         <f aca="false">RawData!F31+RawData!G31+RawData!H31</f>
@@ -7177,7 +8900,7 @@
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="B43" s="9" t="n">
         <f aca="false">RawData!F32+RawData!G32+RawData!H32</f>
@@ -7195,7 +8918,7 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="B44" s="9" t="n">
         <f aca="false">RawData!F33+RawData!G33+RawData!H33</f>
@@ -7213,7 +8936,7 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="B45" s="9" t="n">
         <f aca="false">RawData!F34+RawData!G34+RawData!H34</f>
@@ -7231,7 +8954,7 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="B46" s="9" t="n">
         <f aca="false">RawData!F35+RawData!G35+RawData!H35</f>
@@ -7250,7 +8973,7 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="B47" s="9" t="n">
         <f aca="false">RawData!F36+RawData!G36+RawData!H36</f>
@@ -7269,7 +8992,7 @@
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="B48" s="9" t="n">
         <f aca="false">RawData!F37+RawData!G37+RawData!H37</f>
@@ -7290,17 +9013,17 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q50" s="2" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q51" s="2" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q52" s="2" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7312,12 +9035,12 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q55" s="2" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N56" s="9" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -7334,7 +9057,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:M14 C12:M12 B12">
+  <conditionalFormatting sqref="B12:M14">
     <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -7405,12 +9128,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P1048576"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="22"/>
@@ -7420,409 +9143,994 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
+      <c r="A1" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="41" t="s">
+      <c r="A4" s="84" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="41" t="s">
+      <c r="K4" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="41" t="s">
+      <c r="L4" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="41" t="s">
+      <c r="M4" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="41" t="s">
-        <v>80</v>
+      <c r="N4" s="84" t="s">
+        <v>91</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
+      <c r="A5" s="85" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="86" t="n">
+        <f aca="false">Drivers!B8*Drivers!B14</f>
+        <v>234600</v>
+      </c>
+      <c r="C5" s="86" t="n">
+        <f aca="false">Drivers!C8*Drivers!C14</f>
+        <v>234600</v>
+      </c>
+      <c r="D5" s="86" t="n">
+        <f aca="false">Drivers!D8*Drivers!D14</f>
+        <v>234600</v>
+      </c>
+      <c r="E5" s="86" t="n">
+        <f aca="false">Drivers!E8*Drivers!E14</f>
+        <v>239200</v>
+      </c>
+      <c r="F5" s="86" t="n">
+        <f aca="false">Drivers!F8*Drivers!F14</f>
+        <v>239200</v>
+      </c>
+      <c r="G5" s="86" t="n">
+        <f aca="false">Drivers!G8*Drivers!G14</f>
+        <v>239200</v>
+      </c>
+      <c r="H5" s="86" t="n">
+        <f aca="false">Drivers!H8*Drivers!H14</f>
+        <v>239200</v>
+      </c>
+      <c r="I5" s="86" t="n">
+        <f aca="false">Drivers!I8*Drivers!I14</f>
+        <v>239200</v>
+      </c>
+      <c r="J5" s="86" t="n">
+        <f aca="false">Drivers!J8*Drivers!J14</f>
+        <v>239200</v>
+      </c>
+      <c r="K5" s="86" t="n">
+        <f aca="false">Drivers!K8*Drivers!K14</f>
+        <v>243800</v>
+      </c>
+      <c r="L5" s="86" t="n">
+        <f aca="false">Drivers!L8*Drivers!L14</f>
+        <v>243800</v>
+      </c>
+      <c r="M5" s="86" t="n">
+        <f aca="false">Drivers!M8*Drivers!M14</f>
+        <v>243800</v>
+      </c>
+      <c r="N5" s="87" t="n">
+        <f aca="false">SUM(B5:M5)</f>
+        <v>2870400</v>
+      </c>
+      <c r="O5" s="88" t="n">
+        <f aca="false">IF(N7=0,0,N5/N7)</f>
+        <v>0.844036697247707</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
+      <c r="A6" s="85" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="89" t="n">
+        <f aca="false">Drivers!B19</f>
+        <v>44200</v>
+      </c>
+      <c r="C6" s="89" t="n">
+        <f aca="false">Drivers!C19</f>
+        <v>44200</v>
+      </c>
+      <c r="D6" s="89" t="n">
+        <f aca="false">Drivers!D19</f>
+        <v>44200</v>
+      </c>
+      <c r="E6" s="89" t="n">
+        <f aca="false">Drivers!E19</f>
+        <v>44200</v>
+      </c>
+      <c r="F6" s="89" t="n">
+        <f aca="false">Drivers!F19</f>
+        <v>44200</v>
+      </c>
+      <c r="G6" s="89" t="n">
+        <f aca="false">Drivers!G19</f>
+        <v>44200</v>
+      </c>
+      <c r="H6" s="89" t="n">
+        <f aca="false">Drivers!H19</f>
+        <v>44200</v>
+      </c>
+      <c r="I6" s="89" t="n">
+        <f aca="false">Drivers!I19</f>
+        <v>44200</v>
+      </c>
+      <c r="J6" s="89" t="n">
+        <f aca="false">Drivers!J19</f>
+        <v>44200</v>
+      </c>
+      <c r="K6" s="89" t="n">
+        <f aca="false">Drivers!K19</f>
+        <v>44200</v>
+      </c>
+      <c r="L6" s="89" t="n">
+        <f aca="false">Drivers!L19</f>
+        <v>44200</v>
+      </c>
+      <c r="M6" s="89" t="n">
+        <f aca="false">Drivers!M19</f>
+        <v>44200</v>
+      </c>
+      <c r="N6" s="87" t="n">
+        <f aca="false">SUM(B6:M6)</f>
+        <v>530400</v>
+      </c>
+      <c r="O6" s="88" t="n">
+        <f aca="false">IF(N7=0,0,N6/N7)</f>
+        <v>0.155963302752294</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
+      <c r="A7" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="91" t="n">
+        <f aca="false">B5+B6</f>
+        <v>278800</v>
+      </c>
+      <c r="C7" s="91" t="n">
+        <f aca="false">C5+C6</f>
+        <v>278800</v>
+      </c>
+      <c r="D7" s="91" t="n">
+        <f aca="false">D5+D6</f>
+        <v>278800</v>
+      </c>
+      <c r="E7" s="91" t="n">
+        <f aca="false">E5+E6</f>
+        <v>283400</v>
+      </c>
+      <c r="F7" s="91" t="n">
+        <f aca="false">F5+F6</f>
+        <v>283400</v>
+      </c>
+      <c r="G7" s="91" t="n">
+        <f aca="false">G5+G6</f>
+        <v>283400</v>
+      </c>
+      <c r="H7" s="91" t="n">
+        <f aca="false">H5+H6</f>
+        <v>283400</v>
+      </c>
+      <c r="I7" s="91" t="n">
+        <f aca="false">I5+I6</f>
+        <v>283400</v>
+      </c>
+      <c r="J7" s="91" t="n">
+        <f aca="false">J5+J6</f>
+        <v>283400</v>
+      </c>
+      <c r="K7" s="91" t="n">
+        <f aca="false">K5+K6</f>
+        <v>288000</v>
+      </c>
+      <c r="L7" s="91" t="n">
+        <f aca="false">L5+L6</f>
+        <v>288000</v>
+      </c>
+      <c r="M7" s="91" t="n">
+        <f aca="false">M5+M6</f>
+        <v>288000</v>
+      </c>
+      <c r="N7" s="92" t="n">
+        <f aca="false">SUM(B7:M7)</f>
+        <v>3400800</v>
+      </c>
+      <c r="O7" s="93" t="n">
+        <f aca="false">IF(N7=0,0,N7/N7)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
+      <c r="A8" s="85"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="94"/>
+      <c r="K8" s="94"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="94"/>
+      <c r="N8" s="95"/>
+      <c r="O8" s="95"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
+      <c r="A9" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" s="89" t="n">
+        <f aca="false">Drivers!B8*Drivers!E25</f>
+        <v>140070.192307692</v>
+      </c>
+      <c r="C9" s="89" t="n">
+        <f aca="false">Drivers!C8*Drivers!E25</f>
+        <v>140070.192307692</v>
+      </c>
+      <c r="D9" s="89" t="n">
+        <f aca="false">Drivers!D8*Drivers!E25</f>
+        <v>140070.192307692</v>
+      </c>
+      <c r="E9" s="89" t="n">
+        <f aca="false">Drivers!E8*Drivers!E25</f>
+        <v>142816.666666667</v>
+      </c>
+      <c r="F9" s="89" t="n">
+        <f aca="false">Drivers!F8*Drivers!E25</f>
+        <v>142816.666666667</v>
+      </c>
+      <c r="G9" s="89" t="n">
+        <f aca="false">Drivers!G8*Drivers!E25</f>
+        <v>142816.666666667</v>
+      </c>
+      <c r="H9" s="89" t="n">
+        <f aca="false">Drivers!H8*Drivers!E25</f>
+        <v>142816.666666667</v>
+      </c>
+      <c r="I9" s="89" t="n">
+        <f aca="false">Drivers!I8*Drivers!E25</f>
+        <v>142816.666666667</v>
+      </c>
+      <c r="J9" s="89" t="n">
+        <f aca="false">Drivers!J8*Drivers!E25</f>
+        <v>142816.666666667</v>
+      </c>
+      <c r="K9" s="89" t="n">
+        <f aca="false">Drivers!K8*Drivers!E25</f>
+        <v>145563.141025641</v>
+      </c>
+      <c r="L9" s="89" t="n">
+        <f aca="false">Drivers!L8*Drivers!E25</f>
+        <v>145563.141025641</v>
+      </c>
+      <c r="M9" s="89" t="n">
+        <f aca="false">Drivers!M8*Drivers!E25</f>
+        <v>145563.141025641</v>
+      </c>
+      <c r="N9" s="87" t="n">
+        <f aca="false">SUM(B9:M9)</f>
+        <v>1713800</v>
+      </c>
+      <c r="O9" s="88" t="n">
+        <f aca="false">IF(N7=0,0,N9/N7)</f>
+        <v>0.503940249353093</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
+      <c r="A10" s="85" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="89" t="n">
+        <f aca="false">RawData!G26</f>
+        <v>12700</v>
+      </c>
+      <c r="C10" s="89" t="n">
+        <f aca="false">RawData!G27</f>
+        <v>13800</v>
+      </c>
+      <c r="D10" s="89" t="n">
+        <f aca="false">RawData!G28</f>
+        <v>15900</v>
+      </c>
+      <c r="E10" s="89" t="n">
+        <f aca="false">RawData!G29</f>
+        <v>19100</v>
+      </c>
+      <c r="F10" s="89" t="n">
+        <f aca="false">RawData!G30</f>
+        <v>20100</v>
+      </c>
+      <c r="G10" s="89" t="n">
+        <f aca="false">RawData!G31</f>
+        <v>20100</v>
+      </c>
+      <c r="H10" s="89" t="n">
+        <f aca="false">RawData!G32</f>
+        <v>20100</v>
+      </c>
+      <c r="I10" s="89" t="n">
+        <f aca="false">RawData!G33</f>
+        <v>19100</v>
+      </c>
+      <c r="J10" s="89" t="n">
+        <f aca="false">RawData!G34</f>
+        <v>18000</v>
+      </c>
+      <c r="K10" s="89" t="n">
+        <f aca="false">RawData!G35</f>
+        <v>18000</v>
+      </c>
+      <c r="L10" s="89" t="n">
+        <f aca="false">RawData!G36</f>
+        <v>17000</v>
+      </c>
+      <c r="M10" s="89" t="n">
+        <f aca="false">RawData!G37</f>
+        <v>17000</v>
+      </c>
+      <c r="N10" s="87" t="n">
+        <f aca="false">SUM(B10:M10)</f>
+        <v>210900</v>
+      </c>
+      <c r="O10" s="88" t="n">
+        <f aca="false">IF(N7=0,0,N10/N7)</f>
+        <v>0.062014820042343</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
+      <c r="A11" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="89" t="n">
+        <f aca="false">RawData!H26</f>
+        <v>6400</v>
+      </c>
+      <c r="C11" s="89" t="n">
+        <f aca="false">RawData!H27</f>
+        <v>6900</v>
+      </c>
+      <c r="D11" s="89" t="n">
+        <f aca="false">RawData!H28</f>
+        <v>8000</v>
+      </c>
+      <c r="E11" s="89" t="n">
+        <f aca="false">RawData!H29</f>
+        <v>9500</v>
+      </c>
+      <c r="F11" s="89" t="n">
+        <f aca="false">RawData!H30</f>
+        <v>10100</v>
+      </c>
+      <c r="G11" s="89" t="n">
+        <f aca="false">RawData!H31</f>
+        <v>10100</v>
+      </c>
+      <c r="H11" s="89" t="n">
+        <f aca="false">RawData!H32</f>
+        <v>10100</v>
+      </c>
+      <c r="I11" s="89" t="n">
+        <f aca="false">RawData!H33</f>
+        <v>9500</v>
+      </c>
+      <c r="J11" s="89" t="n">
+        <f aca="false">RawData!H34</f>
+        <v>9000</v>
+      </c>
+      <c r="K11" s="89" t="n">
+        <f aca="false">RawData!H35</f>
+        <v>9000</v>
+      </c>
+      <c r="L11" s="89" t="n">
+        <f aca="false">RawData!H36</f>
+        <v>8500</v>
+      </c>
+      <c r="M11" s="89" t="n">
+        <f aca="false">RawData!H37</f>
+        <v>8500</v>
+      </c>
+      <c r="N11" s="87" t="n">
+        <f aca="false">SUM(B11:M11)</f>
+        <v>105600</v>
+      </c>
+      <c r="O11" s="88" t="n">
+        <f aca="false">IF(N7=0,0,N11/N7)</f>
+        <v>0.0310515172900494</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
+      <c r="A12" s="90" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="91" t="n">
+        <f aca="false">B9+B10+B11</f>
+        <v>159170.192307692</v>
+      </c>
+      <c r="C12" s="91" t="n">
+        <f aca="false">C9+C10+C11</f>
+        <v>160770.192307692</v>
+      </c>
+      <c r="D12" s="91" t="n">
+        <f aca="false">D9+D10+D11</f>
+        <v>163970.192307692</v>
+      </c>
+      <c r="E12" s="91" t="n">
+        <f aca="false">E9+E10+E11</f>
+        <v>171416.666666667</v>
+      </c>
+      <c r="F12" s="91" t="n">
+        <f aca="false">F9+F10+F11</f>
+        <v>173016.666666667</v>
+      </c>
+      <c r="G12" s="91" t="n">
+        <f aca="false">G9+G10+G11</f>
+        <v>173016.666666667</v>
+      </c>
+      <c r="H12" s="91" t="n">
+        <f aca="false">H9+H10+H11</f>
+        <v>173016.666666667</v>
+      </c>
+      <c r="I12" s="91" t="n">
+        <f aca="false">I9+I10+I11</f>
+        <v>171416.666666667</v>
+      </c>
+      <c r="J12" s="91" t="n">
+        <f aca="false">J9+J10+J11</f>
+        <v>169816.666666667</v>
+      </c>
+      <c r="K12" s="91" t="n">
+        <f aca="false">K9+K10+K11</f>
+        <v>172563.141025641</v>
+      </c>
+      <c r="L12" s="91" t="n">
+        <f aca="false">L9+L10+L11</f>
+        <v>171063.141025641</v>
+      </c>
+      <c r="M12" s="91" t="n">
+        <f aca="false">M9+M10+M11</f>
+        <v>171063.141025641</v>
+      </c>
+      <c r="N12" s="92" t="n">
+        <f aca="false">SUM(B12:M12)</f>
+        <v>2030300</v>
+      </c>
+      <c r="O12" s="93" t="n">
+        <f aca="false">IF(N7=0,0,N12/N7)</f>
+        <v>0.597006586685486</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="45"/>
+      <c r="A13" s="85"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="94"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="94"/>
+      <c r="N13" s="95"/>
+      <c r="O13" s="95"/>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
+      <c r="A14" s="90" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="96" t="n">
+        <f aca="false">B7-B12</f>
+        <v>119629.807692308</v>
+      </c>
+      <c r="C14" s="96" t="n">
+        <f aca="false">C7-C12</f>
+        <v>118029.807692308</v>
+      </c>
+      <c r="D14" s="96" t="n">
+        <f aca="false">D7-D12</f>
+        <v>114829.807692308</v>
+      </c>
+      <c r="E14" s="96" t="n">
+        <f aca="false">E7-E12</f>
+        <v>111983.333333333</v>
+      </c>
+      <c r="F14" s="96" t="n">
+        <f aca="false">F7-F12</f>
+        <v>110383.333333333</v>
+      </c>
+      <c r="G14" s="96" t="n">
+        <f aca="false">G7-G12</f>
+        <v>110383.333333333</v>
+      </c>
+      <c r="H14" s="96" t="n">
+        <f aca="false">H7-H12</f>
+        <v>110383.333333333</v>
+      </c>
+      <c r="I14" s="96" t="n">
+        <f aca="false">I7-I12</f>
+        <v>111983.333333333</v>
+      </c>
+      <c r="J14" s="96" t="n">
+        <f aca="false">J7-J12</f>
+        <v>113583.333333333</v>
+      </c>
+      <c r="K14" s="96" t="n">
+        <f aca="false">K7-K12</f>
+        <v>115436.858974359</v>
+      </c>
+      <c r="L14" s="96" t="n">
+        <f aca="false">L7-L12</f>
+        <v>116936.858974359</v>
+      </c>
+      <c r="M14" s="96" t="n">
+        <f aca="false">M7-M12</f>
+        <v>116936.858974359</v>
+      </c>
+      <c r="N14" s="97" t="n">
+        <f aca="false">SUM(B14:M14)</f>
+        <v>1370500</v>
+      </c>
+      <c r="O14" s="98" t="n">
+        <f aca="false">IF(N7=0,0,N14/N7)</f>
+        <v>0.402993413314514</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="46"/>
+      <c r="A15" s="99" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="100" t="n">
+        <f aca="false">B14</f>
+        <v>119629.807692308</v>
+      </c>
+      <c r="C15" s="100" t="n">
+        <f aca="false">C14</f>
+        <v>118029.807692308</v>
+      </c>
+      <c r="D15" s="100" t="n">
+        <f aca="false">D14</f>
+        <v>114829.807692308</v>
+      </c>
+      <c r="E15" s="100" t="n">
+        <f aca="false">E14</f>
+        <v>111983.333333333</v>
+      </c>
+      <c r="F15" s="100" t="n">
+        <f aca="false">F14</f>
+        <v>110383.333333333</v>
+      </c>
+      <c r="G15" s="100" t="n">
+        <f aca="false">G14</f>
+        <v>110383.333333333</v>
+      </c>
+      <c r="H15" s="100" t="n">
+        <f aca="false">H14</f>
+        <v>110383.333333333</v>
+      </c>
+      <c r="I15" s="100" t="n">
+        <f aca="false">I14</f>
+        <v>111983.333333333</v>
+      </c>
+      <c r="J15" s="100" t="n">
+        <f aca="false">J14</f>
+        <v>113583.333333333</v>
+      </c>
+      <c r="K15" s="100" t="n">
+        <f aca="false">K14</f>
+        <v>115436.858974359</v>
+      </c>
+      <c r="L15" s="100" t="n">
+        <f aca="false">L14</f>
+        <v>116936.858974359</v>
+      </c>
+      <c r="M15" s="100" t="n">
+        <f aca="false">M14</f>
+        <v>116936.858974359</v>
+      </c>
+      <c r="N15" s="100" t="n">
+        <f aca="false">SUM(B15:M15)</f>
+        <v>1370500</v>
+      </c>
+      <c r="O15" s="101" t="n">
+        <f aca="false">IF(N7=0,0,N15/N7)</f>
+        <v>0.402993413314514</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
+      <c r="A16" s="85" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="102" t="n">
+        <f aca="false">IF(B7=0,0,B15/B7)</f>
+        <v>0.429088262884891</v>
+      </c>
+      <c r="C16" s="102" t="n">
+        <f aca="false">IF(C7=0,0,C15/C7)</f>
+        <v>0.42334938196667</v>
+      </c>
+      <c r="D16" s="102" t="n">
+        <f aca="false">IF(D7=0,0,D15/D7)</f>
+        <v>0.411871620130228</v>
+      </c>
+      <c r="E16" s="102" t="n">
+        <f aca="false">IF(E7=0,0,E15/E7)</f>
+        <v>0.395142319454246</v>
+      </c>
+      <c r="F16" s="102" t="n">
+        <f aca="false">IF(F7=0,0,F15/F7)</f>
+        <v>0.389496589037874</v>
+      </c>
+      <c r="G16" s="102" t="n">
+        <f aca="false">IF(G7=0,0,G15/G7)</f>
+        <v>0.389496589037874</v>
+      </c>
+      <c r="H16" s="102" t="n">
+        <f aca="false">IF(H7=0,0,H15/H7)</f>
+        <v>0.389496589037874</v>
+      </c>
+      <c r="I16" s="102" t="n">
+        <f aca="false">IF(I7=0,0,I15/I7)</f>
+        <v>0.395142319454246</v>
+      </c>
+      <c r="J16" s="102" t="n">
+        <f aca="false">IF(J7=0,0,J15/J7)</f>
+        <v>0.400788049870619</v>
+      </c>
+      <c r="K16" s="102" t="n">
+        <f aca="false">IF(K7=0,0,K15/K7)</f>
+        <v>0.400822426994302</v>
+      </c>
+      <c r="L16" s="102" t="n">
+        <f aca="false">IF(L7=0,0,L15/L7)</f>
+        <v>0.406030760327635</v>
+      </c>
+      <c r="M16" s="102" t="n">
+        <f aca="false">IF(M7=0,0,M15/M7)</f>
+        <v>0.406030760327635</v>
+      </c>
+      <c r="N16" s="98" t="n">
+        <f aca="false">IF(N7=0,0,N15/N7)</f>
+        <v>0.402993413314514</v>
+      </c>
+      <c r="O16" s="98"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="48"/>
+      <c r="A17" s="85"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="95"/>
+      <c r="K17" s="95"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="95"/>
+      <c r="N17" s="95"/>
+      <c r="O17" s="95"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="49"/>
-      <c r="O18" s="49"/>
+      <c r="A18" s="85" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" s="94" t="n">
+        <f aca="false">0.02*B7</f>
+        <v>5576</v>
+      </c>
+      <c r="C18" s="94" t="n">
+        <f aca="false">0.02*C7</f>
+        <v>5576</v>
+      </c>
+      <c r="D18" s="94" t="n">
+        <f aca="false">0.02*D7</f>
+        <v>5576</v>
+      </c>
+      <c r="E18" s="94" t="n">
+        <f aca="false">0.02*E7</f>
+        <v>5668</v>
+      </c>
+      <c r="F18" s="94" t="n">
+        <f aca="false">0.02*F7</f>
+        <v>5668</v>
+      </c>
+      <c r="G18" s="94" t="n">
+        <f aca="false">0.02*G7</f>
+        <v>5668</v>
+      </c>
+      <c r="H18" s="94" t="n">
+        <f aca="false">0.02*H7</f>
+        <v>5668</v>
+      </c>
+      <c r="I18" s="94" t="n">
+        <f aca="false">0.02*I7</f>
+        <v>5668</v>
+      </c>
+      <c r="J18" s="94" t="n">
+        <f aca="false">0.02*J7</f>
+        <v>5668</v>
+      </c>
+      <c r="K18" s="94" t="n">
+        <f aca="false">0.02*K7</f>
+        <v>5760</v>
+      </c>
+      <c r="L18" s="94" t="n">
+        <f aca="false">0.02*L7</f>
+        <v>5760</v>
+      </c>
+      <c r="M18" s="94" t="n">
+        <f aca="false">0.02*M7</f>
+        <v>5760</v>
+      </c>
+      <c r="N18" s="87" t="n">
+        <f aca="false">SUM(B18:M18)</f>
+        <v>68016</v>
+      </c>
+      <c r="O18" s="88" t="n">
+        <f aca="false">IF(N7=0,0,N18/N7)</f>
+        <v>0.02</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="44"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="46"/>
-    </row>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-    </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
-    </row>
+      <c r="A19" s="72" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="91" t="n">
+        <f aca="false">B15-B18</f>
+        <v>114053.807692308</v>
+      </c>
+      <c r="C19" s="91" t="n">
+        <f aca="false">C15-C18</f>
+        <v>112453.807692308</v>
+      </c>
+      <c r="D19" s="91" t="n">
+        <f aca="false">D15-D18</f>
+        <v>109253.807692308</v>
+      </c>
+      <c r="E19" s="91" t="n">
+        <f aca="false">E15-E18</f>
+        <v>106315.333333333</v>
+      </c>
+      <c r="F19" s="91" t="n">
+        <f aca="false">F15-F18</f>
+        <v>104715.333333333</v>
+      </c>
+      <c r="G19" s="91" t="n">
+        <f aca="false">G15-G18</f>
+        <v>104715.333333333</v>
+      </c>
+      <c r="H19" s="91" t="n">
+        <f aca="false">H15-H18</f>
+        <v>104715.333333333</v>
+      </c>
+      <c r="I19" s="91" t="n">
+        <f aca="false">I15-I18</f>
+        <v>106315.333333333</v>
+      </c>
+      <c r="J19" s="91" t="n">
+        <f aca="false">J15-J18</f>
+        <v>107915.333333333</v>
+      </c>
+      <c r="K19" s="91" t="n">
+        <f aca="false">K15-K18</f>
+        <v>109676.858974359</v>
+      </c>
+      <c r="L19" s="91" t="n">
+        <f aca="false">L15-L18</f>
+        <v>111176.858974359</v>
+      </c>
+      <c r="M19" s="91" t="n">
+        <f aca="false">M15-M18</f>
+        <v>111176.858974359</v>
+      </c>
+      <c r="N19" s="103" t="n">
+        <f aca="false">SUM(B19:M19)</f>
+        <v>1302484</v>
+      </c>
+      <c r="O19" s="93" t="n">
+        <f aca="false">IF(N7=0,0,N19/N7)</f>
+        <v>0.382993413314514</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="104" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="105" t="n">
+        <f aca="false">IF(B19&gt;0,B19*0.21,0)</f>
+        <v>23951.2996153846</v>
+      </c>
+      <c r="C20" s="105" t="n">
+        <f aca="false">IF(C19&gt;0,C19*0.21,0)</f>
+        <v>23615.2996153846</v>
+      </c>
+      <c r="D20" s="105" t="n">
+        <f aca="false">IF(D19&gt;0,D19*0.21,0)</f>
+        <v>22943.2996153846</v>
+      </c>
+      <c r="E20" s="105" t="n">
+        <f aca="false">IF(E19&gt;0,E19*0.21,0)</f>
+        <v>22326.22</v>
+      </c>
+      <c r="F20" s="105" t="n">
+        <f aca="false">IF(F19&gt;0,F19*0.21,0)</f>
+        <v>21990.22</v>
+      </c>
+      <c r="G20" s="105" t="n">
+        <f aca="false">IF(G19&gt;0,G19*0.21,0)</f>
+        <v>21990.22</v>
+      </c>
+      <c r="H20" s="105" t="n">
+        <f aca="false">IF(H19&gt;0,H19*0.21,0)</f>
+        <v>21990.22</v>
+      </c>
+      <c r="I20" s="105" t="n">
+        <f aca="false">IF(I19&gt;0,I19*0.21,0)</f>
+        <v>22326.22</v>
+      </c>
+      <c r="J20" s="105" t="n">
+        <f aca="false">IF(J19&gt;0,J19*0.21,0)</f>
+        <v>22662.22</v>
+      </c>
+      <c r="K20" s="105" t="n">
+        <f aca="false">IF(K19&gt;0,K19*0.21,0)</f>
+        <v>23032.1403846154</v>
+      </c>
+      <c r="L20" s="105" t="n">
+        <f aca="false">IF(L19&gt;0,L19*0.21,0)</f>
+        <v>23347.1403846154</v>
+      </c>
+      <c r="M20" s="105" t="n">
+        <f aca="false">IF(M19&gt;0,M19*0.21,0)</f>
+        <v>23347.1403846154</v>
+      </c>
+      <c r="N20" s="87" t="n">
+        <f aca="false">SUM(B20:M20)</f>
+        <v>273521.64</v>
+      </c>
+      <c r="O20" s="88" t="n">
+        <f aca="false">IF(N7=0,0,N20/N7)</f>
+        <v>0.080428616796048</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="72" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21" s="106" t="n">
+        <f aca="false">B19-B20</f>
+        <v>90102.5080769231</v>
+      </c>
+      <c r="C21" s="106" t="n">
+        <f aca="false">C19-C20</f>
+        <v>88838.5080769231</v>
+      </c>
+      <c r="D21" s="106" t="n">
+        <f aca="false">D19-D20</f>
+        <v>86310.5080769231</v>
+      </c>
+      <c r="E21" s="106" t="n">
+        <f aca="false">E19-E20</f>
+        <v>83989.1133333333</v>
+      </c>
+      <c r="F21" s="106" t="n">
+        <f aca="false">F19-F20</f>
+        <v>82725.1133333333</v>
+      </c>
+      <c r="G21" s="106" t="n">
+        <f aca="false">G19-G20</f>
+        <v>82725.1133333333</v>
+      </c>
+      <c r="H21" s="106" t="n">
+        <f aca="false">H19-H20</f>
+        <v>82725.1133333333</v>
+      </c>
+      <c r="I21" s="106" t="n">
+        <f aca="false">I19-I20</f>
+        <v>83989.1133333333</v>
+      </c>
+      <c r="J21" s="106" t="n">
+        <f aca="false">J19-J20</f>
+        <v>85253.1133333333</v>
+      </c>
+      <c r="K21" s="106" t="n">
+        <f aca="false">K19-K20</f>
+        <v>86644.7185897436</v>
+      </c>
+      <c r="L21" s="106" t="n">
+        <f aca="false">L19-L20</f>
+        <v>87829.7185897436</v>
+      </c>
+      <c r="M21" s="106" t="n">
+        <f aca="false">M19-M20</f>
+        <v>87829.7185897436</v>
+      </c>
+      <c r="N21" s="103" t="n">
+        <f aca="false">SUM(B21:M21)</f>
+        <v>1028962.36</v>
+      </c>
+      <c r="O21" s="93" t="n">
+        <f aca="false">IF(N21=0,0,N21/N7)</f>
+        <v>0.302564796518466</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
@@ -7838,7 +10146,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -7847,26 +10155,26 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
+      <c r="B2" s="107" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7882,7 +10190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -7894,85 +10202,85 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="51" t="s">
-        <v>93</v>
+      <c r="B2" s="108" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="52"/>
+      <c r="B3" s="109"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="53" t="s">
-        <v>94</v>
+      <c r="B4" s="110" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="52"/>
+      <c r="B5" s="109"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="54" t="s">
-        <v>95</v>
+      <c r="B6" s="111" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="52" t="s">
-        <v>96</v>
+      <c r="B7" s="109" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="52" t="s">
-        <v>97</v>
+      <c r="B8" s="109" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="52" t="s">
-        <v>98</v>
+      <c r="B9" s="109" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="52"/>
+      <c r="B10" s="109"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="54" t="s">
-        <v>99</v>
+      <c r="B11" s="111" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="52" t="s">
-        <v>100</v>
+      <c r="B12" s="109" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="52" t="s">
-        <v>101</v>
+      <c r="B13" s="109" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="52" t="s">
-        <v>102</v>
+      <c r="B14" s="109" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="52"/>
+      <c r="B15" s="109"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="54" t="s">
-        <v>103</v>
+      <c r="B16" s="111" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="52" t="s">
-        <v>104</v>
+      <c r="B17" s="109" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="52" t="s">
-        <v>105</v>
+      <c r="B18" s="109" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="52" t="s">
-        <v>106</v>
+      <c r="B19" s="109" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -7986,7 +10294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -8000,238 +10308,238 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
+      <c r="B2" s="112" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="56" t="s">
-        <v>110</v>
+      <c r="B3" s="113" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="113" t="s">
+        <v>164</v>
+      </c>
+      <c r="E3" s="113" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="57" t="s">
-        <v>111</v>
+      <c r="B4" s="114" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="58" t="s">
-        <v>112</v>
+      <c r="B5" s="115" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="60" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="61" t="s">
-        <v>115</v>
+      <c r="B6" s="116" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="117" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="118" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="61" t="s">
-        <v>118</v>
+      <c r="B7" s="116" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="117" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" s="118" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="60" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" s="61" t="s">
-        <v>121</v>
+      <c r="B8" s="116" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="117" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="118" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="59" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" s="60" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="61" t="s">
-        <v>124</v>
+      <c r="B9" s="116" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="118" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="D10" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="61" t="s">
-        <v>127</v>
+      <c r="B10" s="116" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="117" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="118" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="60" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" s="61" t="s">
-        <v>130</v>
+      <c r="B11" s="116" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="118" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="59" t="s">
-        <v>131</v>
-      </c>
-      <c r="D12" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" s="61" t="s">
-        <v>133</v>
+      <c r="B12" s="116" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="117" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="118" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="59"/>
+      <c r="B13" s="116"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="57" t="s">
-        <v>134</v>
+      <c r="B14" s="114" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" s="61" t="s">
-        <v>137</v>
+      <c r="B15" s="116" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15" s="117" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" s="118" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" s="61" t="s">
-        <v>140</v>
+      <c r="B16" s="116" t="s">
+        <v>193</v>
+      </c>
+      <c r="D16" s="117" t="s">
+        <v>194</v>
+      </c>
+      <c r="E16" s="118" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="59" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="60" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" s="61" t="s">
-        <v>143</v>
+      <c r="B17" s="116" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" s="117" t="s">
+        <v>197</v>
+      </c>
+      <c r="E17" s="118" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="59" t="s">
-        <v>144</v>
-      </c>
-      <c r="D18" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" s="61" t="s">
-        <v>146</v>
+      <c r="B18" s="116" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" s="117" t="s">
+        <v>200</v>
+      </c>
+      <c r="E18" s="118" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="59"/>
+      <c r="B19" s="116"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="57" t="s">
-        <v>147</v>
+      <c r="B20" s="114" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="D21" s="60" t="s">
-        <v>149</v>
-      </c>
-      <c r="E21" s="61" t="s">
-        <v>150</v>
+      <c r="B21" s="116" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" s="117" t="s">
+        <v>204</v>
+      </c>
+      <c r="E21" s="118" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="59" t="s">
-        <v>151</v>
-      </c>
-      <c r="D22" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="E22" s="61" t="s">
-        <v>153</v>
+      <c r="B22" s="116" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" s="117" t="s">
+        <v>207</v>
+      </c>
+      <c r="E22" s="118" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="D23" s="60" t="s">
-        <v>149</v>
-      </c>
-      <c r="E23" s="61" t="s">
-        <v>155</v>
+      <c r="B23" s="116" t="s">
+        <v>209</v>
+      </c>
+      <c r="D23" s="117" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="118" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="59"/>
+      <c r="B24" s="116"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="57" t="s">
-        <v>156</v>
+      <c r="B25" s="114" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="59" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="E26" s="61" t="s">
-        <v>159</v>
+      <c r="B26" s="116" t="s">
+        <v>212</v>
+      </c>
+      <c r="D26" s="117" t="s">
+        <v>213</v>
+      </c>
+      <c r="E26" s="118" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="60" t="s">
-        <v>161</v>
+      <c r="B27" s="116" t="s">
+        <v>215</v>
+      </c>
+      <c r="D27" s="117" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="59" t="s">
-        <v>162</v>
-      </c>
-      <c r="D28" s="60" t="s">
-        <v>163</v>
+      <c r="B28" s="116" t="s">
+        <v>217</v>
+      </c>
+      <c r="D28" s="117" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/Consultora_NovaTech_1.xlsx
+++ b/Analysis/Consultora_NovaTech_1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="251">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t xml:space="preserve">Source: NovaTech Consulting Lda. — Internal Financial Data (Fictitious)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTE: December values absorb rounding </t>
   </si>
   <si>
     <t xml:space="preserve">NovaTech — YoY Revenue Bridge 2022 → 2023 (Wednesday) | 2023 → 2024 (Friday)</t>
@@ -175,14 +178,17 @@
     <t xml:space="preserve">opening + all effects</t>
   </si>
   <si>
-    <t xml:space="preserve">Actual: €2,390,400 | Bridge: €2,500,800
-⚠ Gap of €-110,400 = rounding in rate assumption</t>
+    <t xml:space="preserve">Actual: €2,509,200 | Bridge: €2,400,000
+⚠ Gap of €-109,200 = rounding in rate assumption</t>
   </si>
   <si>
     <t xml:space="preserve">REVENUE BRIDGE: 2023 → 2024</t>
   </si>
   <si>
     <t xml:space="preserve">Opening Revenue 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting point — 2023 actual revenue</t>
   </si>
   <si>
     <t xml:space="preserve">(HC24−HC23) × Rate23 × 12</t>
@@ -202,7 +208,7 @@
     <t xml:space="preserve">Closing Revenue 2024</t>
   </si>
   <si>
-    <t xml:space="preserve">Actual: €2,639,800 | Bridge: €2,835,600
+    <t xml:space="preserve">Actual: €2,650,000 | Bridge: €2,845,200
 ⚠ Gap of €-195,800 = rounding in rate assumption</t>
   </si>
   <si>
@@ -290,7 +296,7 @@
     <t xml:space="preserve">Note</t>
   </si>
   <si>
-    <t xml:space="preserve">DERIVED from RawData — not an assumption</t>
+    <t xml:space="preserve">DERIVED from RawData </t>
   </si>
   <si>
     <t xml:space="preserve">NovaTech Consulting Lda. — Variance Analysis:Budget 2025 vs Actuals</t>
@@ -536,7 +542,13 @@
     <t xml:space="preserve">SEASONALITY</t>
   </si>
   <si>
-    <t xml:space="preserve">MS revenue is FLAT (recurring contracts ÷12). Consulting revenue is seasonal. This is intentional and realistic.</t>
+    <t xml:space="preserve">MS revenue distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLAT (÷12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurring contracts — equal monthly payment. This is intentional and correct.</t>
   </si>
   <si>
     <t xml:space="preserve">January weight</t>
@@ -611,7 +623,7 @@
     <t xml:space="preserve">2% of Revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumption — low asset base for consultancy</t>
+    <t xml:space="preserve">Assumption — low asset base for consultancy(conservative)</t>
   </si>
   <si>
     <t xml:space="preserve">IRC Tax rate</t>
@@ -623,22 +635,88 @@
     <t xml:space="preserve">Portugal corporate tax rate 2024</t>
   </si>
   <si>
-    <t xml:space="preserve">Personnel as % Rev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~65%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derived from historical data 2022-2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations as % Rev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derived from historical data</t>
+    <t xml:space="preserve">DRIVER ASSUMPTIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headcount 2022 (year-end)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 FTEs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — not directly in RawData. Consistent with cost/head implied by data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headcount 2023 (year-end)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47 FTEs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — +5 FTEs vs 2022.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headcount 2024 (year-end)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52 FTEs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — +5 FTEs vs 2023. KEY INPUT: change in Drivers sheet to model scenarios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billing rate 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€4,000/head/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — approx: €1,680K ÷ 42 HC ÷ 12 = €3,333. Rounded up for blended rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billing rate 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€4,300/head/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — +€300 YoY rate increase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billing rate 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€4,600/head/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — +€300 YoY rate increase. Change in Drivers sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnel % of Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.0% (exact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED — consistent across 2022–2024. Confirmed from RawData: 1,365K/2,100K = 65.0%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations % of Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0% (exact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED — consistent across 2022–2024. Confirmed from RawData.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other % of Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0% (exact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED — consistent across 2022–2024.</t>
   </si>
   <si>
     <t xml:space="preserve">VARIANCE CONVENTION</t>
@@ -650,7 +728,7 @@
     <t xml:space="preserve">Actual - Budget</t>
   </si>
   <si>
-    <t xml:space="preserve">Positive = outperformed budget (good)</t>
+    <t xml:space="preserve">Positive = outperformed budget (good). Negative = missed budget (bad).</t>
   </si>
   <si>
     <t xml:space="preserve">Cost variance</t>
@@ -659,13 +737,22 @@
     <t xml:space="preserve">Budget - Actual</t>
   </si>
   <si>
-    <t xml:space="preserve">Positive = under budget (good)</t>
+    <t xml:space="preserve">Positive = under budget (good). Negative = over budget (bad).</t>
   </si>
   <si>
     <t xml:space="preserve">EBITDA variance</t>
   </si>
   <si>
-    <t xml:space="preserve">Positive = better than planned (good)</t>
+    <t xml:space="preserve">Positive = better than planned (good). CHECK: should = RevVar + CostVar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA Margin variance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual margin − Budget margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In percentage points (pp). Expected ~0.0pp since costs scale proportionally with revenue.</t>
   </si>
   <si>
     <t xml:space="preserve">MODEL VERSION</t>
@@ -674,40 +761,52 @@
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">Week 2 target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variance Analysis complete — Forecasting in Week 4</t>
+    <t xml:space="preserve">Week 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variance Analysis complete + P&amp;L + Drivers — Forecasting in Week 4</t>
   </si>
   <si>
     <t xml:space="preserve">Last updated</t>
   </si>
   <si>
-    <t xml:space="preserve">June 2025</t>
+    <t xml:space="preserve">June 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Author</t>
   </si>
   <si>
     <t xml:space="preserve">Daniela Marques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Known limitations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Operations and Other costs not yet driver-linked (use RawData directly) — to fix in Week 4.
+2. Budget in RawData cols I–M represents 2025 targets applied to 2024 rows as proxy — not a true 2025 actuals sheet.
+3. HC and billing rate assumptions do not exactly reproduce RawData totals — gap intentional, acknowledged in YoY Bridge.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="[$-409]#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="170" formatCode="[$-409]0.00%"/>
-    <numFmt numFmtId="171" formatCode="0.00%"/>
-    <numFmt numFmtId="172" formatCode="#,##0"/>
+    <numFmt numFmtId="168" formatCode="#,##0\ [$€-816];[RED]\-#,##0\ [$€-816]"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="[$-409]#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="171" formatCode="[$-409]0.00%"/>
+    <numFmt numFmtId="172" formatCode="0.00%"/>
+    <numFmt numFmtId="173" formatCode="#,##0\ [$€-816];[RED]\-#,##0\ [$€-816]"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="54">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,6 +848,14 @@
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF888888"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FFCC0000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -862,14 +969,6 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF1A7A4A"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FFCC0000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1083,7 +1182,31 @@
     <font>
       <i val="true"/>
       <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
       <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1245,7 +1368,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="134">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1282,15 +1405,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1298,15 +1425,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1314,15 +1433,175 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1330,144 +1609,8 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="24" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="24" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="26" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1506,35 +1649,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="170" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="171" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1554,15 +1697,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1570,12 +1713,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1590,19 +1737,19 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="24" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="40" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="40" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1610,15 +1757,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="42" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="42" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1630,15 +1777,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="40" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="40" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="33" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="33" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1646,11 +1793,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1658,19 +1805,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="44" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="44" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="45" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="45" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1706,11 +1849,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1718,8 +1857,52 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1997,7 +2180,7 @@
             <c:numRef>
               <c:f>Variance!$B$23:$B$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0\ [$€-816];[RED]\-#,##0\ [$€-816]</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>171400</c:v>
@@ -2033,7 +2216,7 @@
                   <c:v>213800</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>213800</c:v>
+                  <c:v>224000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2149,7 +2332,7 @@
             <c:numRef>
               <c:f>Variance!$C$23:$C$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0\ [$€-816];[RED]\-#,##0\ [$€-816]</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>187500</c:v>
@@ -2185,7 +2368,7 @@
                   <c:v>233900</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>233900</c:v>
+                  <c:v>245900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2193,11 +2376,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="30129024"/>
-        <c:axId val="63221403"/>
+        <c:axId val="11582679"/>
+        <c:axId val="98835816"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="30129024"/>
+        <c:axId val="11582679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2262,7 +2445,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63221403"/>
+        <c:crossAx val="98835816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2270,7 +2453,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="63221403"/>
+        <c:axId val="98835816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2344,7 +2527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30129024"/>
+        <c:crossAx val="11582679"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2560,7 +2743,7 @@
             <c:numRef>
               <c:f>Variance!$D$23:$D$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0\ [$€-816];[RED]\-#,##0\ [$€-816]</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>16100</c:v>
@@ -2596,7 +2779,7 @@
                   <c:v>20100</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>20100</c:v>
+                  <c:v>21900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2611,11 +2794,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="77139834"/>
-        <c:axId val="16986299"/>
+        <c:axId val="95420276"/>
+        <c:axId val="48602742"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77139834"/>
+        <c:axId val="95420276"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2680,7 +2863,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16986299"/>
+        <c:crossAx val="48602742"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2688,7 +2871,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16986299"/>
+        <c:axId val="48602742"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2762,7 +2945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77139834"/>
+        <c:crossAx val="95420276"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3004,7 +3187,7 @@
                   <c:v>163300</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>163300</c:v>
+                  <c:v>173500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3156,7 +3339,7 @@
                   <c:v>178700</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>178700</c:v>
+                  <c:v>190000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3164,11 +3347,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="7819836"/>
-        <c:axId val="38782246"/>
+        <c:axId val="42569786"/>
+        <c:axId val="30740875"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="7819836"/>
+        <c:axId val="42569786"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3233,7 +3416,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38782246"/>
+        <c:crossAx val="30740875"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3241,7 +3424,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38782246"/>
+        <c:axId val="30740875"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3315,7 +3498,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7819836"/>
+        <c:crossAx val="42569786"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3412,10 +3595,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.1608827396947"/>
-          <c:y val="0.167039446929646"/>
-          <c:w val="0.688182493853982"/>
-          <c:h val="0.539345262301749"/>
+          <c:x val="0.160891938250429"/>
+          <c:y val="0.167056431113371"/>
+          <c:w val="0.688164665523156"/>
+          <c:h val="0.539298423995933"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -3581,7 +3764,7 @@
                   <c:v>15400</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>15400</c:v>
+                  <c:v>16500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3596,11 +3779,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="7972407"/>
-        <c:axId val="19313832"/>
+        <c:axId val="1773179"/>
+        <c:axId val="69359211"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="7972407"/>
+        <c:axId val="1773179"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3665,7 +3848,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19313832"/>
+        <c:crossAx val="69359211"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3673,7 +3856,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19313832"/>
+        <c:axId val="69359211"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3747,7 +3930,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7972407"/>
+        <c:crossAx val="1773179"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4682,9 +4865,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>373680</xdr:colOff>
+      <xdr:colOff>373320</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>133560</xdr:rowOff>
+      <xdr:rowOff>133200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4692,8 +4875,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3703680" y="6023160"/>
-        <a:ext cx="6208920" cy="3496320"/>
+        <a:off x="3703680" y="6136920"/>
+        <a:ext cx="6208560" cy="3495960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4712,9 +4895,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2455920</xdr:colOff>
+      <xdr:colOff>2455560</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>122760</xdr:rowOff>
+      <xdr:rowOff>122400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4722,8 +4905,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10926000" y="5746680"/>
-        <a:ext cx="5756400" cy="3236400"/>
+        <a:off x="10926000" y="5860080"/>
+        <a:ext cx="5756040" cy="3236040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4742,7 +4925,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>419040</xdr:colOff>
+      <xdr:colOff>418680</xdr:colOff>
       <xdr:row>61</xdr:row>
       <xdr:rowOff>48240</xdr:rowOff>
     </xdr:to>
@@ -4752,8 +4935,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4200120" y="9701640"/>
-        <a:ext cx="5757840" cy="3237840"/>
+        <a:off x="4200120" y="9815400"/>
+        <a:ext cx="5757480" cy="3237480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4772,7 +4955,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2612520</xdr:colOff>
+      <xdr:colOff>2612160</xdr:colOff>
       <xdr:row>62</xdr:row>
       <xdr:rowOff>42480</xdr:rowOff>
     </xdr:to>
@@ -4782,8 +4965,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="21579000">
-        <a:off x="10542240" y="9568080"/>
-        <a:ext cx="6296400" cy="3540600"/>
+        <a:off x="10542240" y="9682200"/>
+        <a:ext cx="6296040" cy="3540240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4976,7 +5159,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -5495,34 +5678,34 @@
         <v>12</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>134400</v>
+        <v>142800</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>35000</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>109200</v>
+        <v>116100</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>13400</v>
+        <v>14200</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>6700</v>
+        <v>7100</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>185600</v>
+        <v>197200</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>48300</v>
+        <v>48700</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>150800</v>
+        <v>160300</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>18600</v>
+        <v>19800</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>9300</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5987,34 +6170,34 @@
         <v>12</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>153600</v>
+        <v>163200</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>40000</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>124800</v>
+        <v>132600</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>15400</v>
+        <v>16400</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>7700</v>
+        <v>8200</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>185600</v>
+        <v>197200</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>48300</v>
+        <v>48700</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>150800</v>
+        <v>160300</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>18600</v>
+        <v>19800</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>9300</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6479,39 +6662,44 @@
         <v>12</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>169600</v>
+        <v>180200</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>44200</v>
+        <v>43800</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>137800</v>
+        <v>146500</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>17000</v>
+        <v>18100</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>8500</v>
+        <v>8900</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>185600</v>
+        <v>197200</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>48300</v>
+        <v>48700</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>150800</v>
+        <v>160300</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>18600</v>
+        <v>19800</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>9300</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -6533,359 +6721,359 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="9" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="10" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="10" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="10" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="A1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
+      <c r="A2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>32</v>
       </c>
+      <c r="E4" s="13" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <f aca="false">SUM(RawData!D2:E13)</f>
+        <v>2100000</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>240000</v>
+      </c>
+      <c r="C7" s="22" t="n">
+        <f aca="false">B7/B6</f>
+        <v>0.114285714285714</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>169200</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <f aca="false">B8/B6</f>
+        <v>0.0805714285714286</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="16" t="n">
+        <f aca="false">SUM(RawData!D14:E25)</f>
+        <v>2400000</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="15" t="n">
-        <f aca="false">SUM(RawData!D2:E13)</f>
-        <v>2091600</v>
-      </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="18" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="16" t="n">
+        <f aca="false">SUM(RawData!D14:E25)</f>
+        <v>2400000</v>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="20" t="n">
-        <v>240000</v>
-      </c>
-      <c r="C7" s="21" t="n">
-        <f aca="false">B7/B6</f>
-        <v>0.114744693057946</v>
-      </c>
-      <c r="D7" s="22" t="s">
+      <c r="E16" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="20" t="n">
-        <v>169200</v>
-      </c>
-      <c r="C8" s="21" t="n">
-        <f aca="false">B8/B6</f>
-        <v>0.080895008605852</v>
-      </c>
-      <c r="D8" s="22" t="s">
+      <c r="B17" s="21" t="n">
+        <v>258000</v>
+      </c>
+      <c r="C17" s="22" t="n">
+        <f aca="false">B17/B16</f>
+        <v>0.1075</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="25" t="n">
+      <c r="B18" s="21" t="n">
+        <v>187200</v>
+      </c>
+      <c r="C18" s="22" t="n">
+        <f aca="false">B18/B16</f>
+        <v>0.078</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="27" t="s">
+      <c r="D19" s="23" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="E19" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="15" t="n">
-        <f aca="false">SUM(RawData!D14:E25)</f>
-        <v>2390400</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="18" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="16" t="n">
+        <f aca="false">SUM(RawData!D26:E37)</f>
+        <v>2650000</v>
+      </c>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-    </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="15" t="n">
-        <f aca="false">SUM(RawData!D14:E25)</f>
-        <v>2390400</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="20" t="n">
-        <v>258000</v>
-      </c>
-      <c r="C17" s="21" t="n">
-        <f aca="false">B17/B16</f>
-        <v>0.107931726907631</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="20" t="n">
-        <v>187200</v>
-      </c>
-      <c r="C18" s="21" t="n">
-        <f aca="false">B18/B16</f>
-        <v>0.0783132530120482</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="25" t="n">
+      <c r="E20" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="15" t="n">
-        <f aca="false">SUM(RawData!D26:E37)</f>
-        <v>2639800</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="29" t="s">
+      <c r="B24" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="C24" s="31" t="s">
         <v>61</v>
       </c>
+      <c r="D24" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="30" t="n">
+      <c r="A25" s="32" t="n">
         <v>2022</v>
       </c>
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="33" t="n">
         <f aca="false">B6</f>
-        <v>2091600</v>
-      </c>
-      <c r="C25" s="31" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="C25" s="33" t="n">
         <f aca="false">SUM(RawData!F2:H13)</f>
-        <v>1608900</v>
-      </c>
-      <c r="D25" s="32" t="n">
+        <v>1617000</v>
+      </c>
+      <c r="D25" s="34" t="n">
         <f aca="false">B25-C25</f>
-        <v>482700</v>
-      </c>
-      <c r="E25" s="33" t="n">
+        <v>483000</v>
+      </c>
+      <c r="E25" s="35" t="n">
         <f aca="false">D25/B25</f>
-        <v>0.230780263912794</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34" t="n">
+      <c r="A26" s="36" t="n">
         <v>2023</v>
       </c>
-      <c r="B26" s="35" t="n">
+      <c r="B26" s="37" t="n">
         <f aca="false">B10</f>
-        <v>2390400</v>
-      </c>
-      <c r="C26" s="31" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="C26" s="33" t="n">
         <f aca="false">SUM(RawData!F14:H25)</f>
-        <v>1838700</v>
-      </c>
-      <c r="D26" s="32" t="n">
+        <v>1848000</v>
+      </c>
+      <c r="D26" s="34" t="n">
         <f aca="false">B26-C26</f>
-        <v>551700</v>
-      </c>
-      <c r="E26" s="33" t="n">
+        <v>552000</v>
+      </c>
+      <c r="E26" s="35" t="n">
         <f aca="false">D26/B26</f>
-        <v>0.230798192771084</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30" t="n">
+      <c r="A27" s="32" t="n">
         <v>2024</v>
       </c>
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="33" t="n">
         <f aca="false">B20</f>
-        <v>2639800</v>
-      </c>
-      <c r="C27" s="31" t="n">
+        <v>2650000</v>
+      </c>
+      <c r="C27" s="33" t="n">
         <f aca="false">SUM(RawData!F26:H37)</f>
-        <v>2030300</v>
-      </c>
-      <c r="D27" s="32" t="n">
+        <v>2040500</v>
+      </c>
+      <c r="D27" s="34" t="n">
         <f aca="false">B27-C27</f>
         <v>609500</v>
       </c>
-      <c r="E27" s="33" t="n">
+      <c r="E27" s="35" t="n">
         <f aca="false">D27/B27</f>
-        <v>0.230888703689673</v>
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>
@@ -6922,728 +7110,826 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
+      <c r="A1" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
+      <c r="A2" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="A4" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="40" t="s">
+      <c r="J5" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="40" t="s">
+      <c r="L5" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="40" t="s">
+      <c r="M5" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="O5" s="41" t="s">
-        <v>66</v>
+      <c r="N5" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="43" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="n">
+      <c r="A6" s="44" t="n">
         <v>2022</v>
       </c>
-      <c r="B6" s="43" t="n">
+      <c r="B6" s="45" t="n">
         <v>41</v>
       </c>
-      <c r="C6" s="43" t="n">
+      <c r="C6" s="45" t="n">
         <v>41</v>
       </c>
-      <c r="D6" s="43" t="n">
+      <c r="D6" s="45" t="n">
         <v>41</v>
       </c>
-      <c r="E6" s="43" t="n">
+      <c r="E6" s="45" t="n">
         <v>42</v>
       </c>
-      <c r="F6" s="43" t="n">
+      <c r="F6" s="45" t="n">
         <v>42</v>
       </c>
-      <c r="G6" s="43" t="n">
+      <c r="G6" s="45" t="n">
         <v>42</v>
       </c>
-      <c r="H6" s="43" t="n">
+      <c r="H6" s="45" t="n">
         <v>42</v>
       </c>
-      <c r="I6" s="43" t="n">
+      <c r="I6" s="45" t="n">
         <v>42</v>
       </c>
-      <c r="J6" s="43" t="n">
+      <c r="J6" s="45" t="n">
         <v>42</v>
       </c>
-      <c r="K6" s="43" t="n">
+      <c r="K6" s="45" t="n">
         <v>43</v>
       </c>
-      <c r="L6" s="43" t="n">
+      <c r="L6" s="45" t="n">
         <v>43</v>
       </c>
-      <c r="M6" s="43" t="n">
+      <c r="M6" s="45" t="n">
         <v>43</v>
       </c>
-      <c r="N6" s="44" t="n">
+      <c r="N6" s="46" t="n">
         <f aca="false">AVERAGE(B6:M6)</f>
         <v>42</v>
       </c>
-      <c r="O6" s="45" t="s">
-        <v>67</v>
+      <c r="O6" s="47" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="n">
+      <c r="A7" s="44" t="n">
         <v>2023</v>
       </c>
-      <c r="B7" s="43" t="n">
+      <c r="B7" s="45" t="n">
         <v>46</v>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="C7" s="45" t="n">
         <v>46</v>
       </c>
-      <c r="D7" s="43" t="n">
+      <c r="D7" s="45" t="n">
         <v>46</v>
       </c>
-      <c r="E7" s="43" t="n">
+      <c r="E7" s="45" t="n">
         <v>46</v>
       </c>
-      <c r="F7" s="43" t="n">
+      <c r="F7" s="45" t="n">
         <v>47</v>
       </c>
-      <c r="G7" s="43" t="n">
+      <c r="G7" s="45" t="n">
         <v>47</v>
       </c>
-      <c r="H7" s="43" t="n">
+      <c r="H7" s="45" t="n">
         <v>47</v>
       </c>
-      <c r="I7" s="43" t="n">
+      <c r="I7" s="45" t="n">
         <v>47</v>
       </c>
-      <c r="J7" s="43" t="n">
+      <c r="J7" s="45" t="n">
         <v>48</v>
       </c>
-      <c r="K7" s="43" t="n">
+      <c r="K7" s="45" t="n">
         <v>48</v>
       </c>
-      <c r="L7" s="43" t="n">
+      <c r="L7" s="45" t="n">
         <v>48</v>
       </c>
-      <c r="M7" s="43" t="n">
+      <c r="M7" s="45" t="n">
         <v>48</v>
       </c>
-      <c r="N7" s="44" t="n">
+      <c r="N7" s="46" t="n">
         <f aca="false">AVERAGE(B7:M7)</f>
         <v>47</v>
       </c>
-      <c r="O7" s="45" t="s">
-        <v>68</v>
+      <c r="O7" s="47" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="n">
+      <c r="A8" s="44" t="n">
         <v>2024</v>
       </c>
-      <c r="B8" s="43" t="n">
+      <c r="B8" s="45" t="n">
         <v>51</v>
       </c>
-      <c r="C8" s="43" t="n">
+      <c r="C8" s="45" t="n">
         <v>51</v>
       </c>
-      <c r="D8" s="43" t="n">
+      <c r="D8" s="45" t="n">
         <v>51</v>
       </c>
-      <c r="E8" s="43" t="n">
+      <c r="E8" s="45" t="n">
         <v>52</v>
       </c>
-      <c r="F8" s="43" t="n">
+      <c r="F8" s="45" t="n">
         <v>52</v>
       </c>
-      <c r="G8" s="43" t="n">
+      <c r="G8" s="45" t="n">
         <v>52</v>
       </c>
-      <c r="H8" s="43" t="n">
+      <c r="H8" s="45" t="n">
         <v>52</v>
       </c>
-      <c r="I8" s="43" t="n">
+      <c r="I8" s="45" t="n">
         <v>52</v>
       </c>
-      <c r="J8" s="43" t="n">
+      <c r="J8" s="45" t="n">
         <v>52</v>
       </c>
-      <c r="K8" s="43" t="n">
+      <c r="K8" s="45" t="n">
         <v>53</v>
       </c>
-      <c r="L8" s="43" t="n">
+      <c r="L8" s="45" t="n">
         <v>53</v>
       </c>
-      <c r="M8" s="43" t="n">
+      <c r="M8" s="45" t="n">
         <v>53</v>
       </c>
-      <c r="N8" s="44" t="n">
+      <c r="N8" s="46" t="n">
         <f aca="false">AVERAGE(B8:M8)</f>
         <v>52</v>
       </c>
-      <c r="O8" s="45" t="s">
-        <v>69</v>
-      </c>
+      <c r="O8" s="47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
+      <c r="A10" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="40" t="s">
+      <c r="I11" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="40" t="s">
+      <c r="J11" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="40" t="s">
+      <c r="K11" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="L11" s="40" t="s">
+      <c r="L11" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="40" t="s">
+      <c r="M11" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="N11" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="O11" s="41" t="s">
-        <v>66</v>
+      <c r="N11" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11" s="50" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="n">
+      <c r="A12" s="44" t="n">
         <v>2022</v>
       </c>
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="C12" s="46" t="n">
+      <c r="C12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="E12" s="46" t="n">
+      <c r="E12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="G12" s="46" t="n">
+      <c r="G12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="I12" s="46" t="n">
+      <c r="I12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="K12" s="46" t="n">
+      <c r="K12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="L12" s="46" t="n">
+      <c r="L12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="M12" s="46" t="n">
+      <c r="M12" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="N12" s="47" t="n">
+      <c r="N12" s="52" t="n">
         <f aca="false">AVERAGE(B12:M12)</f>
         <v>4000</v>
       </c>
-      <c r="O12" s="45" t="s">
-        <v>72</v>
+      <c r="O12" s="47" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="n">
+      <c r="A13" s="44" t="n">
         <v>2023</v>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="C13" s="46" t="n">
+      <c r="C13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="E13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="G13" s="46" t="n">
+      <c r="G13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="I13" s="46" t="n">
+      <c r="I13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="K13" s="46" t="n">
+      <c r="K13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="L13" s="46" t="n">
+      <c r="L13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="M13" s="46" t="n">
+      <c r="M13" s="51" t="n">
         <v>4300</v>
       </c>
-      <c r="N13" s="47" t="n">
+      <c r="N13" s="52" t="n">
         <f aca="false">AVERAGE(B13:M13)</f>
         <v>4300</v>
       </c>
-      <c r="O13" s="45" t="s">
-        <v>73</v>
+      <c r="O13" s="47" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="n">
+      <c r="A14" s="44" t="n">
         <v>2024</v>
       </c>
-      <c r="B14" s="46" t="n">
+      <c r="B14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="C14" s="46" t="n">
+      <c r="C14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="D14" s="46" t="n">
+      <c r="D14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="E14" s="46" t="n">
+      <c r="E14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="F14" s="46" t="n">
+      <c r="F14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="G14" s="46" t="n">
+      <c r="G14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="H14" s="46" t="n">
+      <c r="H14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="I14" s="46" t="n">
+      <c r="I14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="J14" s="46" t="n">
+      <c r="J14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="K14" s="46" t="n">
+      <c r="K14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="L14" s="46" t="n">
+      <c r="L14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="M14" s="46" t="n">
+      <c r="M14" s="51" t="n">
         <v>4600</v>
       </c>
-      <c r="N14" s="47" t="n">
+      <c r="N14" s="52" t="n">
         <f aca="false">AVERAGE(B14:M14)</f>
         <v>4600</v>
       </c>
-      <c r="O14" s="45" t="s">
-        <v>74</v>
-      </c>
+      <c r="O14" s="47" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
+      <c r="A16" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="42" t="n">
+      <c r="A17" s="44" t="n">
         <v>2022</v>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="C17" s="46" t="n">
+      <c r="C17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="E17" s="46" t="n">
+      <c r="E17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="F17" s="46" t="n">
+      <c r="F17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="G17" s="46" t="n">
+      <c r="G17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="H17" s="46" t="n">
+      <c r="H17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="I17" s="46" t="n">
+      <c r="I17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="J17" s="46" t="n">
+      <c r="J17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="K17" s="46" t="n">
+      <c r="K17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="L17" s="46" t="n">
+      <c r="L17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="M17" s="46" t="n">
+      <c r="M17" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="N17" s="47" t="n">
+      <c r="N17" s="52" t="n">
         <f aca="false">SUM(B17:M17)</f>
         <v>420000</v>
       </c>
-      <c r="O17" s="48" t="s">
-        <v>76</v>
+      <c r="O17" s="53" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="42" t="n">
+      <c r="A18" s="44" t="n">
         <v>2023</v>
       </c>
-      <c r="B18" s="46" t="n">
+      <c r="B18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="C18" s="46" t="n">
+      <c r="C18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="F18" s="46" t="n">
+      <c r="F18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="G18" s="46" t="n">
+      <c r="G18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="H18" s="46" t="n">
+      <c r="H18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="I18" s="46" t="n">
+      <c r="I18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="J18" s="46" t="n">
+      <c r="J18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="K18" s="46" t="n">
+      <c r="K18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="L18" s="46" t="n">
+      <c r="L18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="M18" s="46" t="n">
+      <c r="M18" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="N18" s="47" t="n">
+      <c r="N18" s="52" t="n">
         <f aca="false">SUM(B18:M18)</f>
         <v>480000</v>
       </c>
-      <c r="O18" s="48" t="s">
-        <v>77</v>
+      <c r="O18" s="53" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="42" t="n">
+      <c r="A19" s="44" t="n">
         <v>2024</v>
       </c>
-      <c r="B19" s="46" t="n">
+      <c r="B19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="C19" s="46" t="n">
+      <c r="C19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="D19" s="46" t="n">
+      <c r="D19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="E19" s="46" t="n">
+      <c r="E19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="F19" s="46" t="n">
+      <c r="F19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="G19" s="46" t="n">
+      <c r="G19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="H19" s="46" t="n">
+      <c r="H19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="I19" s="46" t="n">
+      <c r="I19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="J19" s="46" t="n">
+      <c r="J19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="K19" s="46" t="n">
+      <c r="K19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="L19" s="46" t="n">
+      <c r="L19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="M19" s="46" t="n">
+      <c r="M19" s="51" t="n">
         <v>44200</v>
       </c>
-      <c r="N19" s="47" t="n">
+      <c r="N19" s="52" t="n">
         <f aca="false">SUM(B19:M19)</f>
         <v>530400</v>
       </c>
-      <c r="O19" s="48" t="s">
-        <v>78</v>
-      </c>
+      <c r="O19" s="53" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
+      <c r="A21" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="31.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="50" t="s">
+      <c r="B22" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="C22" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="D22" s="55" t="s">
         <v>84</v>
       </c>
+      <c r="E22" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n">
+      <c r="A23" s="56" t="n">
         <v>2022</v>
       </c>
-      <c r="B23" s="52" t="n">
+      <c r="B23" s="57" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2022",RawData!F:F)</f>
-        <v>1358100</v>
-      </c>
-      <c r="C23" s="53" t="n">
+        <v>1365000</v>
+      </c>
+      <c r="C23" s="58" t="n">
         <f aca="false">N6</f>
         <v>42</v>
       </c>
-      <c r="D23" s="54" t="n">
+      <c r="D23" s="59" t="n">
         <f aca="false">B23/C23</f>
-        <v>32335.7142857143</v>
-      </c>
-      <c r="E23" s="54" t="n">
+        <v>32500</v>
+      </c>
+      <c r="E23" s="59" t="n">
         <f aca="false">D23/12</f>
-        <v>2694.64285714286</v>
-      </c>
-      <c r="F23" s="55" t="s">
-        <v>85</v>
-      </c>
+        <v>2708.33333333333</v>
+      </c>
+      <c r="F23" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="n">
+      <c r="A24" s="56" t="n">
         <v>2023</v>
       </c>
-      <c r="B24" s="52" t="n">
+      <c r="B24" s="57" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2023",RawData!F:F)</f>
-        <v>1552200</v>
-      </c>
-      <c r="C24" s="53" t="n">
+        <v>1560000</v>
+      </c>
+      <c r="C24" s="58" t="n">
         <f aca="false">N7</f>
         <v>47</v>
       </c>
-      <c r="D24" s="54" t="n">
+      <c r="D24" s="59" t="n">
         <f aca="false">B24/C24</f>
-        <v>33025.5319148936</v>
-      </c>
-      <c r="E24" s="54" t="n">
+        <v>33191.4893617021</v>
+      </c>
+      <c r="E24" s="59" t="n">
         <f aca="false">D24/12</f>
-        <v>2752.12765957447</v>
-      </c>
-      <c r="F24" s="55" t="s">
-        <v>85</v>
-      </c>
+        <v>2765.95744680851</v>
+      </c>
+      <c r="F24" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51" t="n">
+      <c r="A25" s="56" t="n">
         <v>2024</v>
       </c>
-      <c r="B25" s="52" t="n">
+      <c r="B25" s="57" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!F:F)</f>
-        <v>1713800</v>
-      </c>
-      <c r="C25" s="53" t="n">
+        <v>1722500</v>
+      </c>
+      <c r="C25" s="58" t="n">
         <f aca="false">N8</f>
         <v>52</v>
       </c>
-      <c r="D25" s="54" t="n">
+      <c r="D25" s="59" t="n">
         <f aca="false">B25/C25</f>
-        <v>32957.6923076923</v>
-      </c>
-      <c r="E25" s="54" t="n">
+        <v>33125</v>
+      </c>
+      <c r="E25" s="59" t="n">
         <f aca="false">D25/12</f>
-        <v>2746.47435897436</v>
-      </c>
-      <c r="F25" s="55" t="s">
-        <v>85</v>
-      </c>
+        <v>2760.41666666667</v>
+      </c>
+      <c r="F25" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -7672,340 +7958,340 @@
   <dimension ref="A1:X56"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="20.02"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="2" style="9" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="9" width="12.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="9" width="19.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="20.02"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="2" style="10" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="10" width="12.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="10" width="19.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="50.86"/>
   </cols>
   <sheetData>
-    <row r="1" s="58" customFormat="true" ht="27.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="56" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
+    <row r="1" s="63" customFormat="true" ht="27.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="59" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" s="60" customFormat="true" ht="21.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="60" t="s">
+      <c r="A2" s="64" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" s="65" customFormat="true" ht="21.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="60" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="60" t="s">
+      <c r="C4" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="60" t="s">
+      <c r="F4" s="65" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="60" t="s">
+      <c r="H4" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="60" t="s">
+      <c r="I4" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="60" t="s">
+      <c r="J4" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="60" t="s">
+      <c r="K4" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="60" t="s">
+      <c r="L4" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="60" t="s">
+      <c r="M4" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="60" t="s">
-        <v>91</v>
-      </c>
-      <c r="O4" s="60" t="s">
-        <v>92</v>
-      </c>
-      <c r="P4" s="60" t="s">
+      <c r="N4" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="Q4" s="60" t="s">
+      <c r="O4" s="65" t="s">
         <v>94</v>
       </c>
+      <c r="P4" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q4" s="65" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="61" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="63"/>
-    </row>
-    <row r="6" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="64" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="65" t="n">
+      <c r="A5" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="68"/>
+    </row>
+    <row r="6" customFormat="false" ht="46.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="70" t="n">
         <f aca="false">RawData!D26-RawData!I26</f>
         <v>-12000</v>
       </c>
-      <c r="C6" s="65" t="n">
+      <c r="C6" s="70" t="n">
         <f aca="false">RawData!D27-RawData!I27</f>
         <v>-13000</v>
       </c>
-      <c r="D6" s="65" t="n">
+      <c r="D6" s="70" t="n">
         <f aca="false">RawData!D28-RawData!I28</f>
         <v>-15000</v>
       </c>
-      <c r="E6" s="65" t="n">
+      <c r="E6" s="70" t="n">
         <f aca="false">RawData!D29-RawData!I29</f>
         <v>-18000</v>
       </c>
-      <c r="F6" s="65" t="n">
+      <c r="F6" s="70" t="n">
         <f aca="false">RawData!D30-RawData!I30</f>
         <v>-19000</v>
       </c>
-      <c r="G6" s="65" t="n">
+      <c r="G6" s="70" t="n">
         <f aca="false">RawData!D31-RawData!I31</f>
         <v>-19000</v>
       </c>
-      <c r="H6" s="65" t="n">
+      <c r="H6" s="70" t="n">
         <f aca="false">RawData!D32-RawData!I32</f>
         <v>-19000</v>
       </c>
-      <c r="I6" s="65" t="n">
+      <c r="I6" s="70" t="n">
         <f aca="false">RawData!D33-RawData!I33</f>
         <v>-18000</v>
       </c>
-      <c r="J6" s="65" t="n">
+      <c r="J6" s="70" t="n">
         <f aca="false">RawData!D34-RawData!I34</f>
         <v>-17000</v>
       </c>
-      <c r="K6" s="65" t="n">
+      <c r="K6" s="70" t="n">
         <f aca="false">RawData!D35-RawData!I35</f>
         <v>-17000</v>
       </c>
-      <c r="L6" s="65" t="n">
+      <c r="L6" s="70" t="n">
         <f aca="false">RawData!D36-RawData!I36</f>
         <v>-16000</v>
       </c>
-      <c r="M6" s="65" t="n">
+      <c r="M6" s="70" t="n">
         <f aca="false">RawData!D37-RawData!I37</f>
-        <v>-16000</v>
-      </c>
-      <c r="N6" s="65" t="n">
+        <v>-17000</v>
+      </c>
+      <c r="N6" s="70" t="n">
         <f aca="false">SUM(B6:M6)</f>
-        <v>-199000</v>
-      </c>
-      <c r="O6" s="65" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="O6" s="70" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!D:D)-SUMIF(RawData!A:A,"=2024",RawData!I:I)</f>
-        <v>-199000</v>
-      </c>
-      <c r="P6" s="66" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="P6" s="71" t="n">
         <f aca="false">IF(SUMIF(RawData!A:A,"=2024",RawData!I:I)=0,0,O6/SUMIF(RawData!A:A,"=2024",RawData!I:I))</f>
         <v>-0.0862068965517241</v>
       </c>
-      <c r="Q6" s="67" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="65" t="n">
+      <c r="Q6" s="72" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="70" t="n">
         <f aca="false">RawData!E26-RawData!J26</f>
         <v>-4100</v>
       </c>
-      <c r="C7" s="65" t="n">
+      <c r="C7" s="70" t="n">
         <f aca="false">RawData!$E27-RawData!$J27</f>
         <v>-4100</v>
       </c>
-      <c r="D7" s="65" t="n">
+      <c r="D7" s="70" t="n">
         <f aca="false">RawData!$E28-RawData!$J28</f>
         <v>-4100</v>
       </c>
-      <c r="E7" s="65" t="n">
+      <c r="E7" s="70" t="n">
         <f aca="false">RawData!$E29-RawData!$J29</f>
         <v>-4100</v>
       </c>
-      <c r="F7" s="65" t="n">
+      <c r="F7" s="70" t="n">
         <f aca="false">RawData!$E30-RawData!$J30</f>
         <v>-4100</v>
       </c>
-      <c r="G7" s="65" t="n">
+      <c r="G7" s="70" t="n">
         <f aca="false">RawData!$E31-RawData!$J31</f>
         <v>-4100</v>
       </c>
-      <c r="H7" s="65" t="n">
+      <c r="H7" s="70" t="n">
         <f aca="false">RawData!$E32-RawData!$J32</f>
         <v>-4100</v>
       </c>
-      <c r="I7" s="65" t="n">
+      <c r="I7" s="70" t="n">
         <f aca="false">RawData!$E33-RawData!$J33</f>
         <v>-4100</v>
       </c>
-      <c r="J7" s="65" t="n">
+      <c r="J7" s="70" t="n">
         <f aca="false">RawData!$E34-RawData!$J34</f>
         <v>-4100</v>
       </c>
-      <c r="K7" s="65" t="n">
+      <c r="K7" s="70" t="n">
         <f aca="false">RawData!$E35-RawData!$J35</f>
         <v>-4100</v>
       </c>
-      <c r="L7" s="65" t="n">
+      <c r="L7" s="70" t="n">
         <f aca="false">RawData!$E36-RawData!$J36</f>
         <v>-4100</v>
       </c>
-      <c r="M7" s="65" t="n">
+      <c r="M7" s="70" t="n">
         <f aca="false">RawData!$E37-RawData!$J37</f>
-        <v>-4100</v>
-      </c>
-      <c r="N7" s="65" t="n">
+        <v>-4900</v>
+      </c>
+      <c r="N7" s="70" t="n">
         <f aca="false">SUM(B7:M7)</f>
-        <v>-49200</v>
-      </c>
-      <c r="O7" s="65" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="O7" s="70" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!E:E)-SUMIF(RawData!A:A,"=2024",RawData!J:J)</f>
-        <v>-49200</v>
-      </c>
-      <c r="P7" s="66" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="P7" s="71" t="n">
         <f aca="false">IF(SUMIF(RawData!A:A,"=2024",RawData!J:J)=0,0,O7/SUMIF(RawData!A:A,"=2024",RawData!J:J))</f>
-        <v>-0.0848861283643892</v>
-      </c>
-      <c r="Q7" s="67" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="68" t="n">
+        <v>-0.0862068965517241</v>
+      </c>
+      <c r="Q7" s="72" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="73" t="n">
         <f aca="false">B6+B7</f>
         <v>-16100</v>
       </c>
-      <c r="C8" s="68" t="n">
+      <c r="C8" s="73" t="n">
         <f aca="false">C6+C7</f>
         <v>-17100</v>
       </c>
-      <c r="D8" s="68" t="n">
+      <c r="D8" s="73" t="n">
         <f aca="false">D6+D7</f>
         <v>-19100</v>
       </c>
-      <c r="E8" s="68" t="n">
+      <c r="E8" s="73" t="n">
         <f aca="false">E6+E7</f>
         <v>-22100</v>
       </c>
-      <c r="F8" s="68" t="n">
+      <c r="F8" s="73" t="n">
         <f aca="false">F6+F7</f>
         <v>-23100</v>
       </c>
-      <c r="G8" s="68" t="n">
+      <c r="G8" s="73" t="n">
         <f aca="false">G6+G7</f>
         <v>-23100</v>
       </c>
-      <c r="H8" s="68" t="n">
+      <c r="H8" s="73" t="n">
         <f aca="false">H6+H7</f>
         <v>-23100</v>
       </c>
-      <c r="I8" s="68" t="n">
+      <c r="I8" s="73" t="n">
         <f aca="false">I6+I7</f>
         <v>-22100</v>
       </c>
-      <c r="J8" s="68" t="n">
+      <c r="J8" s="73" t="n">
         <f aca="false">J6+J7</f>
         <v>-21100</v>
       </c>
-      <c r="K8" s="68" t="n">
+      <c r="K8" s="73" t="n">
         <f aca="false">K6+K7</f>
         <v>-21100</v>
       </c>
-      <c r="L8" s="68" t="n">
+      <c r="L8" s="73" t="n">
         <f aca="false">L6+L7</f>
         <v>-20100</v>
       </c>
-      <c r="M8" s="68" t="n">
+      <c r="M8" s="73" t="n">
         <f aca="false">M6+M7</f>
-        <v>-20100</v>
-      </c>
-      <c r="N8" s="68" t="n">
+        <v>-21900</v>
+      </c>
+      <c r="N8" s="73" t="n">
         <f aca="false">SUM(B8:M8)</f>
-        <v>-248200</v>
-      </c>
-      <c r="O8" s="68" t="n">
+        <v>-250000</v>
+      </c>
+      <c r="O8" s="73" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!E:E)-SUMIF(RawData!A:A,"=2024",RawData!J:J)+SUMIF(RawData!A:A,"=2024",RawData!D:D)-SUMIF(RawData!A:A,"=2024",RawData!I:I)</f>
-        <v>-248200</v>
-      </c>
-      <c r="P8" s="69" t="n">
+        <v>-250000</v>
+      </c>
+      <c r="P8" s="74" t="n">
         <f aca="false">O8/(SUMIF(RawData!A:A,"=2024",RawData!J:J)+SUMIF(RawData!A:A,"=2024",RawData!I:I))</f>
-        <v>-0.0859418282548476</v>
-      </c>
-      <c r="Q8" s="67" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
+        <v>-0.0862068965517241</v>
+      </c>
+      <c r="Q8" s="72" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" s="68" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
@@ -8016,542 +8302,542 @@
       <c r="X9" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="61" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="62"/>
-      <c r="M11" s="62"/>
-      <c r="N11" s="62"/>
-      <c r="O11" s="62"/>
-      <c r="P11" s="62"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="63"/>
-      <c r="S11" s="63"/>
-      <c r="T11" s="63"/>
-      <c r="U11" s="63"/>
-      <c r="V11" s="63"/>
-      <c r="W11" s="63"/>
-      <c r="X11" s="63"/>
-    </row>
-    <row r="12" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="64" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="70" t="n">
+      <c r="A11" s="66" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="68"/>
+      <c r="T11" s="68"/>
+      <c r="U11" s="68"/>
+      <c r="V11" s="68"/>
+      <c r="W11" s="68"/>
+      <c r="X11" s="68"/>
+    </row>
+    <row r="12" customFormat="false" ht="46.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="69" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="75" t="n">
         <f aca="false">RawData!K26-RawData!F26</f>
         <v>9700</v>
       </c>
-      <c r="C12" s="70" t="n">
+      <c r="C12" s="75" t="n">
         <f aca="false">RawData!K27-RawData!F27</f>
         <v>10500</v>
       </c>
-      <c r="D12" s="70" t="n">
+      <c r="D12" s="75" t="n">
         <f aca="false">RawData!K28-RawData!F28</f>
         <v>12200</v>
       </c>
-      <c r="E12" s="70" t="n">
+      <c r="E12" s="75" t="n">
         <f aca="false">RawData!K29-RawData!F29</f>
         <v>14600</v>
       </c>
-      <c r="F12" s="70" t="n">
+      <c r="F12" s="75" t="n">
         <f aca="false">RawData!K30-RawData!F30</f>
         <v>15500</v>
       </c>
-      <c r="G12" s="70" t="n">
+      <c r="G12" s="75" t="n">
         <f aca="false">RawData!K31-RawData!F31</f>
         <v>15500</v>
       </c>
-      <c r="H12" s="70" t="n">
+      <c r="H12" s="75" t="n">
         <f aca="false">RawData!K32-RawData!F32</f>
         <v>15500</v>
       </c>
-      <c r="I12" s="70" t="n">
+      <c r="I12" s="75" t="n">
         <f aca="false">RawData!K33-RawData!F33</f>
         <v>14600</v>
       </c>
-      <c r="J12" s="70" t="n">
+      <c r="J12" s="75" t="n">
         <f aca="false">RawData!K34-RawData!F34</f>
         <v>13800</v>
       </c>
-      <c r="K12" s="70" t="n">
+      <c r="K12" s="75" t="n">
         <f aca="false">RawData!K35-RawData!F35</f>
         <v>13800</v>
       </c>
-      <c r="L12" s="70" t="n">
+      <c r="L12" s="75" t="n">
         <f aca="false">RawData!K36-RawData!F36</f>
         <v>13000</v>
       </c>
-      <c r="M12" s="70" t="n">
+      <c r="M12" s="75" t="n">
         <f aca="false">RawData!K37-RawData!F37</f>
-        <v>13000</v>
-      </c>
-      <c r="N12" s="65" t="n">
+        <v>13800</v>
+      </c>
+      <c r="N12" s="70" t="n">
         <f aca="false">SUM(B12:M12)</f>
-        <v>161700</v>
-      </c>
-      <c r="O12" s="65" t="n">
+        <v>162500</v>
+      </c>
+      <c r="O12" s="70" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!K:K)-SUMIF(RawData!A:A,"=2024",RawData!F:F)</f>
-        <v>161700</v>
-      </c>
-      <c r="P12" s="66" t="n">
+        <v>162500</v>
+      </c>
+      <c r="P12" s="71" t="n">
         <f aca="false">IF(SUMIF(RawData!A:A,"=2024",RawData!K:K)=0,0,O12/SUMIF(RawData!A:A,"=2024",RawData!K:K))</f>
-        <v>0.086217008797654</v>
-      </c>
-      <c r="Q12" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="S12" s="71"/>
-    </row>
-    <row r="13" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="B13" s="70" t="n">
+        <v>0.0862068965517241</v>
+      </c>
+      <c r="Q12" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="S12" s="76"/>
+    </row>
+    <row r="13" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="75" t="n">
         <f aca="false">RawData!L26-RawData!G26</f>
         <v>1200</v>
       </c>
-      <c r="C13" s="70" t="n">
+      <c r="C13" s="75" t="n">
         <f aca="false">RawData!L27-RawData!G27</f>
         <v>1300</v>
       </c>
-      <c r="D13" s="70" t="n">
+      <c r="D13" s="75" t="n">
         <f aca="false">RawData!L28-RawData!G28</f>
         <v>1500</v>
       </c>
-      <c r="E13" s="70" t="n">
+      <c r="E13" s="75" t="n">
         <f aca="false">RawData!L29-RawData!G29</f>
         <v>1800</v>
       </c>
-      <c r="F13" s="70" t="n">
+      <c r="F13" s="75" t="n">
         <f aca="false">RawData!L30-RawData!G30</f>
         <v>1900</v>
       </c>
-      <c r="G13" s="70" t="n">
+      <c r="G13" s="75" t="n">
         <f aca="false">RawData!L31-RawData!G31</f>
         <v>1900</v>
       </c>
-      <c r="H13" s="70" t="n">
+      <c r="H13" s="75" t="n">
         <f aca="false">RawData!L32-RawData!G32</f>
         <v>1900</v>
       </c>
-      <c r="I13" s="70" t="n">
+      <c r="I13" s="75" t="n">
         <f aca="false">RawData!L33-RawData!G33</f>
         <v>1800</v>
       </c>
-      <c r="J13" s="70" t="n">
+      <c r="J13" s="75" t="n">
         <f aca="false">RawData!L34-RawData!G34</f>
         <v>1700</v>
       </c>
-      <c r="K13" s="70" t="n">
+      <c r="K13" s="75" t="n">
         <f aca="false">RawData!L35-RawData!G35</f>
         <v>1700</v>
       </c>
-      <c r="L13" s="70" t="n">
+      <c r="L13" s="75" t="n">
         <f aca="false">RawData!L36-RawData!G36</f>
         <v>1600</v>
       </c>
-      <c r="M13" s="70" t="n">
+      <c r="M13" s="75" t="n">
         <f aca="false">RawData!L37-RawData!G37</f>
-        <v>1600</v>
-      </c>
-      <c r="N13" s="65" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N13" s="70" t="n">
         <f aca="false">SUM(B13:M13)</f>
-        <v>19900</v>
-      </c>
-      <c r="O13" s="65" t="n">
+        <v>20000</v>
+      </c>
+      <c r="O13" s="70" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!L:L)-SUMIF(RawData!A:A,"=2024",RawData!G:G)</f>
-        <v>19900</v>
-      </c>
-      <c r="P13" s="66" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P13" s="71" t="n">
         <f aca="false">IF(SUMIF(RawData!A:A,"=2024",RawData!L:L)=0,0,O13/SUMIF(RawData!A:A,"=2024",RawData!L:L))</f>
-        <v>0.0862218370883882</v>
-      </c>
-      <c r="Q13" s="67" t="s">
-        <v>105</v>
+        <v>0.0862068965517241</v>
+      </c>
+      <c r="Q13" s="72" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="70" t="n">
+      <c r="A14" s="69" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="75" t="n">
         <f aca="false">RawData!M26-RawData!H26</f>
         <v>600</v>
       </c>
-      <c r="C14" s="70" t="n">
+      <c r="C14" s="75" t="n">
         <f aca="false">RawData!M27-RawData!H27</f>
         <v>600</v>
       </c>
-      <c r="D14" s="70" t="n">
+      <c r="D14" s="75" t="n">
         <f aca="false">RawData!M28-RawData!H28</f>
         <v>700</v>
       </c>
-      <c r="E14" s="70" t="n">
+      <c r="E14" s="75" t="n">
         <f aca="false">RawData!M29-RawData!H29</f>
         <v>900</v>
       </c>
-      <c r="F14" s="70" t="n">
+      <c r="F14" s="75" t="n">
         <f aca="false">RawData!M30-RawData!H30</f>
         <v>900</v>
       </c>
-      <c r="G14" s="70" t="n">
+      <c r="G14" s="75" t="n">
         <f aca="false">RawData!M31-RawData!H31</f>
         <v>900</v>
       </c>
-      <c r="H14" s="70" t="n">
+      <c r="H14" s="75" t="n">
         <f aca="false">RawData!M32-RawData!H32</f>
         <v>900</v>
       </c>
-      <c r="I14" s="70" t="n">
+      <c r="I14" s="75" t="n">
         <f aca="false">RawData!M33-RawData!H33</f>
         <v>900</v>
       </c>
-      <c r="J14" s="70" t="n">
+      <c r="J14" s="75" t="n">
         <f aca="false">RawData!M34-RawData!H34</f>
         <v>900</v>
       </c>
-      <c r="K14" s="70" t="n">
+      <c r="K14" s="75" t="n">
         <f aca="false">RawData!M35-RawData!H35</f>
         <v>900</v>
       </c>
-      <c r="L14" s="70" t="n">
+      <c r="L14" s="75" t="n">
         <f aca="false">RawData!M36-RawData!H36</f>
         <v>800</v>
       </c>
-      <c r="M14" s="70" t="n">
+      <c r="M14" s="75" t="n">
         <f aca="false">RawData!M37-RawData!H37</f>
-        <v>800</v>
-      </c>
-      <c r="N14" s="65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N14" s="70" t="n">
         <f aca="false">SUM(B14:M14)</f>
-        <v>9800</v>
-      </c>
-      <c r="O14" s="65" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O14" s="70" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!M:M)-SUMIF(RawData!A:A,"=2024",RawData!H:H)</f>
-        <v>9800</v>
-      </c>
-      <c r="P14" s="66" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P14" s="71" t="n">
         <f aca="false">IF(SUMIF(RawData!A:A,"=2024",RawData!M:M)=0,0,O14/SUMIF(RawData!A:A,"=2024",RawData!M:M))</f>
-        <v>0.0849220103986135</v>
-      </c>
-      <c r="Q14" s="67" t="s">
-        <v>107</v>
+        <v>0.0862068965517241</v>
+      </c>
+      <c r="Q14" s="72" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="72" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="68" t="n">
+      <c r="A15" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="73" t="n">
         <f aca="false">B13+B14+B12</f>
         <v>11500</v>
       </c>
-      <c r="C15" s="68" t="n">
+      <c r="C15" s="73" t="n">
         <f aca="false">C13+C14+C12</f>
         <v>12400</v>
       </c>
-      <c r="D15" s="68" t="n">
+      <c r="D15" s="73" t="n">
         <f aca="false">D13+D14+D12</f>
         <v>14400</v>
       </c>
-      <c r="E15" s="68" t="n">
+      <c r="E15" s="73" t="n">
         <f aca="false">E13+E14+E12</f>
         <v>17300</v>
       </c>
-      <c r="F15" s="68" t="n">
+      <c r="F15" s="73" t="n">
         <f aca="false">F13+F14+F12</f>
         <v>18300</v>
       </c>
-      <c r="G15" s="68" t="n">
+      <c r="G15" s="73" t="n">
         <f aca="false">G13+G14+G12</f>
         <v>18300</v>
       </c>
-      <c r="H15" s="68" t="n">
+      <c r="H15" s="73" t="n">
         <f aca="false">H13+H14+H12</f>
         <v>18300</v>
       </c>
-      <c r="I15" s="68" t="n">
+      <c r="I15" s="73" t="n">
         <f aca="false">I13+I14+I12</f>
         <v>17300</v>
       </c>
-      <c r="J15" s="68" t="n">
+      <c r="J15" s="73" t="n">
         <f aca="false">J13+J14+J12</f>
         <v>16400</v>
       </c>
-      <c r="K15" s="68" t="n">
+      <c r="K15" s="73" t="n">
         <f aca="false">K13+K14+K12</f>
         <v>16400</v>
       </c>
-      <c r="L15" s="68" t="n">
+      <c r="L15" s="73" t="n">
         <f aca="false">L13+L14+L12</f>
         <v>15400</v>
       </c>
-      <c r="M15" s="68" t="n">
+      <c r="M15" s="73" t="n">
         <f aca="false">M13+M14+M12</f>
-        <v>15400</v>
-      </c>
-      <c r="N15" s="68" t="n">
+        <v>16500</v>
+      </c>
+      <c r="N15" s="73" t="n">
         <f aca="false">SUM(B15:M15)</f>
-        <v>191400</v>
-      </c>
-      <c r="O15" s="68" t="n">
+        <v>192500</v>
+      </c>
+      <c r="O15" s="73" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!K:K)-SUMIF(RawData!A:A,"=2024",RawData!F:F)+SUMIF(RawData!A:A,"=2024",RawData!L:L)-SUMIF(RawData!A:A,"=2024",RawData!G:G)+SUMIF(RawData!A:A,"=2024",RawData!M:M)-SUMIF(RawData!A:A,"=2024",RawData!H:H)</f>
-        <v>191400</v>
-      </c>
-      <c r="P15" s="69" t="n">
+        <v>192500</v>
+      </c>
+      <c r="P15" s="74" t="n">
         <f aca="false">O15/(SUMIF(RawData!A:A,"=2024",RawData!K:K)+SUMIF(RawData!A:A,"=2024",RawData!L:L)+SUMIF(RawData!A:A,"=2024",RawData!M:M))</f>
-        <v>0.0861502453076473</v>
-      </c>
-      <c r="Q15" s="73"/>
+        <v>0.0862068965517241</v>
+      </c>
+      <c r="Q15" s="78"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q16" s="74"/>
-    </row>
-    <row r="17" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="75" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="68" t="n">
+      <c r="Q16" s="79"/>
+    </row>
+    <row r="17" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="73" t="n">
         <f aca="false">(RawData!D26+RawData!E26-RawData!F26-RawData!G26-RawData!H26)-(RawData!I26+RawData!J26-RawData!K26-RawData!L26-RawData!M26)</f>
         <v>-4600</v>
       </c>
-      <c r="C17" s="68" t="n">
+      <c r="C17" s="73" t="n">
         <f aca="false">(RawData!D27+RawData!E27-RawData!F27-RawData!G27-RawData!H27)-(RawData!I27+RawData!J27-RawData!K27-RawData!L27-RawData!M27)</f>
         <v>-4700</v>
       </c>
-      <c r="D17" s="68" t="n">
+      <c r="D17" s="73" t="n">
         <f aca="false">(RawData!D28+RawData!E28-RawData!F28-RawData!G28-RawData!H28)-(RawData!I28+RawData!J28-RawData!K28-RawData!L28-RawData!M28)</f>
         <v>-4700</v>
       </c>
-      <c r="E17" s="68" t="n">
+      <c r="E17" s="73" t="n">
         <f aca="false">(RawData!D29 + RawData!E29 - RawData!F29 - RawData!G29 - RawData!H29)  - (RawData!I29 + RawData!J29 - RawData!K29 - RawData!L29 - RawData!M29)</f>
         <v>-4800</v>
       </c>
-      <c r="F17" s="68" t="n">
+      <c r="F17" s="73" t="n">
         <f aca="false">(RawData!D30 + RawData!E30 - RawData!F30 - RawData!G30 - RawData!H30)  - (RawData!I30 + RawData!J30 - RawData!K30 - RawData!L30 - RawData!M30)</f>
         <v>-4800</v>
       </c>
-      <c r="G17" s="68" t="n">
+      <c r="G17" s="73" t="n">
         <f aca="false">(RawData!D31 + RawData!E31 - RawData!F31 - RawData!G31 - RawData!H31)  - (RawData!I31 + RawData!J31 - RawData!K31 - RawData!L31 - RawData!M31)</f>
         <v>-4800</v>
       </c>
-      <c r="H17" s="68" t="n">
+      <c r="H17" s="73" t="n">
         <f aca="false">(RawData!D32 + RawData!E32 - RawData!F32 - RawData!G32 - RawData!H32)  - (RawData!I32 + RawData!J32 - RawData!K32 - RawData!L32 - RawData!M32)</f>
         <v>-4800</v>
       </c>
-      <c r="I17" s="68" t="n">
+      <c r="I17" s="73" t="n">
         <f aca="false">(RawData!D33 + RawData!E33 - RawData!F33 - RawData!G33 - RawData!H33)  - (RawData!I33 + RawData!J33 - RawData!K33 - RawData!L33 - RawData!M33)</f>
         <v>-4800</v>
       </c>
-      <c r="J17" s="68" t="n">
+      <c r="J17" s="73" t="n">
         <f aca="false">(RawData!D34 + RawData!E34 - RawData!F34 - RawData!G34 - RawData!H34)  - (RawData!I34 + RawData!J34 - RawData!K34 - RawData!L34 - RawData!M34)</f>
         <v>-4700</v>
       </c>
-      <c r="K17" s="68" t="n">
+      <c r="K17" s="73" t="n">
         <f aca="false">(RawData!D35 + RawData!E35 - RawData!F35 - RawData!G35 - RawData!H35)  - (RawData!I35 + RawData!J35 - RawData!K35 - RawData!L35 - RawData!M35)</f>
         <v>-4700</v>
       </c>
-      <c r="L17" s="68" t="n">
+      <c r="L17" s="73" t="n">
         <f aca="false">(RawData!D36 + RawData!E36 - RawData!F36 - RawData!G36 - RawData!H36)  - (RawData!I36 + RawData!J36 - RawData!K36 - RawData!L36 - RawData!M36)</f>
         <v>-4700</v>
       </c>
-      <c r="M17" s="68" t="n">
+      <c r="M17" s="73" t="n">
         <f aca="false">(RawData!D37 + RawData!E37 - RawData!F37 - RawData!G37 - RawData!H37)  - (RawData!I37 + RawData!J37 - RawData!K37 - RawData!L37 - RawData!M37)</f>
-        <v>-4700</v>
-      </c>
-      <c r="N17" s="68" t="n">
+        <v>-5400</v>
+      </c>
+      <c r="N17" s="73" t="n">
         <f aca="false">SUM(B17:M17)</f>
-        <v>-56800</v>
-      </c>
-      <c r="O17" s="68" t="n">
+        <v>-57500</v>
+      </c>
+      <c r="O17" s="73" t="n">
         <f aca="false">O8+O15</f>
-        <v>-56800</v>
-      </c>
-      <c r="P17" s="69" t="n">
+        <v>-57500</v>
+      </c>
+      <c r="P17" s="74" t="n">
         <f aca="false">O17/(SUMIF(RawData!A:A,"=2024",RawData!I:I)+SUMIF(RawData!A:A,"=2024",RawData!J:J)-SUMIF(RawData!A:A,"=2024",RawData!L:L)-SUMIF(RawData!A:A,"=2024",RawData!M:M)-SUMIF(RawData!A:A,"=2024",RawData!K:K))</f>
-        <v>-0.085246885787183</v>
-      </c>
-      <c r="Q17" s="76" t="s">
-        <v>108</v>
+        <v>-0.0862068965517241</v>
+      </c>
+      <c r="Q17" s="81" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="69" t="n">
+      <c r="A18" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="74" t="n">
         <f aca="false">IF((RawData!D26+RawData!E26)=0,0,(RawData!D26+RawData!E26-RawData!F26-RawData!G26-RawData!H26)/(RawData!D26+RawData!E26))-IF((RawData!I26+RawData!J26)=0,0,(RawData!I26+RawData!J26-RawData!K26-RawData!L26-RawData!M26)/(RawData!I26+RawData!J26))</f>
         <v>-3.57837417347406E-005</v>
       </c>
-      <c r="C18" s="69" t="n">
+      <c r="C18" s="74" t="n">
         <f aca="false">IF((RawData!D27+RawData!E27)=0,0,(RawData!D27+RawData!E27-RawData!F27-RawData!G27-RawData!H27)/(RawData!D27+RawData!E27)) - IF((RawData!I27+RawData!J27)=0,0,(RawData!I27+RawData!J27-RawData!K27-RawData!L27-RawData!M27)/(RawData!I27+RawData!J27))</f>
         <v>-0.000341371335846497</v>
       </c>
-      <c r="D18" s="69" t="n">
+      <c r="D18" s="74" t="n">
         <f aca="false">IF((RawData!D28+RawData!E28)=0,0,(RawData!D28+RawData!E28-RawData!F28-RawData!G28-RawData!H28)/(RawData!D28+RawData!E28)) - IF((RawData!I28+RawData!J28)=0,0,(RawData!I28+RawData!J28-RawData!K28-RawData!L28-RawData!M28)/(RawData!I28+RawData!J28))</f>
         <v>4.13979123055075E-005</v>
       </c>
-      <c r="E18" s="69" t="n">
+      <c r="E18" s="74" t="n">
         <f aca="false">IF((RawData!D29+RawData!E29)=0,0,(RawData!D29+RawData!E29-RawData!F29-RawData!G29-RawData!H29)/(RawData!D29+RawData!E29)) - IF((RawData!I29+RawData!J29)=0,0,(RawData!I29+RawData!J29-RawData!K29-RawData!L29-RawData!M29)/(RawData!I29+RawData!J29))</f>
         <v>0.000131416701838</v>
       </c>
-      <c r="F18" s="69" t="n">
+      <c r="F18" s="74" t="n">
         <f aca="false">IF((RawData!D30+RawData!E30)=0,0,(RawData!D30+RawData!E30-RawData!F30-RawData!G30-RawData!H30)/(RawData!D30+RawData!E30)) - IF((RawData!I30+RawData!J30)=0,0,(RawData!I30+RawData!J30-RawData!K30-RawData!L30-RawData!M30)/(RawData!I30+RawData!J30))</f>
         <v>0.000268211402712298</v>
       </c>
-      <c r="G18" s="69" t="n">
+      <c r="G18" s="74" t="n">
         <f aca="false">IF((RawData!D31+RawData!E31)=0,0,(RawData!D31+RawData!E31-RawData!F31-RawData!G31-RawData!H31)/(RawData!D31+RawData!E31)) - IF((RawData!I31+RawData!J31)=0,0,(RawData!I31+RawData!J31-RawData!K31-RawData!L31-RawData!M31)/(RawData!I31+RawData!J31))</f>
         <v>0.000268211402712298</v>
       </c>
-      <c r="H18" s="69" t="n">
+      <c r="H18" s="74" t="n">
         <f aca="false">IF((RawData!D32+RawData!E32)=0,0,(RawData!D32+RawData!E32-RawData!F32-RawData!G32-RawData!H32)/(RawData!D32+RawData!E32)) - IF((RawData!I32+RawData!J32)=0,0,(RawData!I32+RawData!J32-RawData!K32-RawData!L32-RawData!M32)/(RawData!I32+RawData!J32))</f>
         <v>0.000268211402712298</v>
       </c>
-      <c r="I18" s="69" t="n">
+      <c r="I18" s="74" t="n">
         <f aca="false">IF((RawData!D33+RawData!E33)=0,0,(RawData!D33+RawData!E33-RawData!F33-RawData!G33-RawData!H33)/(RawData!D33+RawData!E33)) - IF((RawData!I33+RawData!J33)=0,0,(RawData!I33+RawData!J33-RawData!K33-RawData!L33-RawData!M33)/(RawData!I33+RawData!J33))</f>
         <v>0.000131416701838</v>
       </c>
-      <c r="J18" s="69" t="n">
+      <c r="J18" s="74" t="n">
         <f aca="false">IF((RawData!D34+RawData!E34)=0,0,(RawData!D34+RawData!E34-RawData!F34-RawData!G34-RawData!H34)/(RawData!D34+RawData!E34)) - IF((RawData!I34+RawData!J34)=0,0,(RawData!I34+RawData!J34-RawData!K34-RawData!L34-RawData!M34)/(RawData!I34+RawData!J34))</f>
         <v>0.000388816885761895</v>
       </c>
-      <c r="K18" s="69" t="n">
+      <c r="K18" s="74" t="n">
         <f aca="false">IF((RawData!D35+RawData!E35)=0,0,(RawData!D35+RawData!E35-RawData!F35-RawData!G35-RawData!H35)/(RawData!D35+RawData!E35)) - IF((RawData!I35+RawData!J35)=0,0,(RawData!I35+RawData!J35-RawData!K35-RawData!L35-RawData!M35)/(RawData!I35+RawData!J35))</f>
         <v>0.000388816885761895</v>
       </c>
-      <c r="L18" s="69" t="n">
+      <c r="L18" s="74" t="n">
         <f aca="false">IF((RawData!D36+RawData!E36)=0,0,(RawData!D36+RawData!E36-RawData!F36-RawData!G36-RawData!H36)/(RawData!D36+RawData!E36)) - IF((RawData!I36+RawData!J36)=0,0,(RawData!I36+RawData!J36-RawData!K36-RawData!L36-RawData!M36)/(RawData!I36+RawData!J36))</f>
         <v>0.000203768130664361</v>
       </c>
-      <c r="M18" s="69" t="n">
+      <c r="M18" s="74" t="n">
         <f aca="false">IF((RawData!D37+RawData!E37)=0,0,(RawData!D37+RawData!E37-RawData!F37-RawData!G37-RawData!H37)/(RawData!D37+RawData!E37)) - IF((RawData!I37+RawData!J37)=0,0,(RawData!I37+RawData!J37-RawData!K37-RawData!L37-RawData!M37)/(RawData!I37+RawData!J37))</f>
-        <v>0.000203768130664361</v>
-      </c>
-      <c r="N18" s="69" t="n">
+        <v>-0.00188175361645268</v>
+      </c>
+      <c r="N18" s="74" t="n">
         <f aca="false">(SUMIF(RawData!A:A,2024,RawData!D:D)+SUMIF(RawData!A:A,2024,RawData!E:E)-SUMIF(RawData!A:A,2024,RawData!F:F)-SUMIF(RawData!A:A,2024,RawData!G:G)-SUMIF(RawData!A:A,2024,RawData!H:H))/(SUMIF(RawData!A:A,2024,RawData!D:D)+SUMIF(RawData!A:A,2024,RawData!E:E))-((SUMIF(RawData!A:A,2024,RawData!I:I)+SUMIF(RawData!A:A,2024,RawData!J:J)-SUMIF(RawData!A:A,2024,RawData!K:K)-SUMIF(RawData!A:A,2024,RawData!L:L)-SUMIF(RawData!A:A,2024,RawData!M:M))/(SUMIF(RawData!A:A,2024,RawData!I:I)+SUMIF(RawData!A:A,2024,RawData!J:J)))</f>
-        <v>0.000175407290781499</v>
-      </c>
-      <c r="O18" s="69"/>
-      <c r="P18" s="69"/>
-      <c r="Q18" s="77"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="74"/>
+      <c r="P18" s="74"/>
+      <c r="Q18" s="82"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B19" s="9" t="n">
+      <c r="A19" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="10" t="n">
         <f aca="false">B17-B15-B8</f>
         <v>0</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="10" t="n">
         <f aca="false">C17-C15-C8</f>
         <v>0</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="10" t="n">
         <f aca="false">D17-D15-D8</f>
         <v>0</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="10" t="n">
         <f aca="false">E17-E15-E8</f>
         <v>0</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="10" t="n">
         <f aca="false">F17-F15-F8</f>
         <v>0</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="10" t="n">
         <f aca="false">G17-G15-G8</f>
         <v>0</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="10" t="n">
         <f aca="false">H17-H15-H8</f>
         <v>0</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="10" t="n">
         <f aca="false">I17-I15-I8</f>
         <v>0</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="10" t="n">
         <f aca="false">J17-J15-J8</f>
         <v>0</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="10" t="n">
         <f aca="false">K17-K15-K8</f>
         <v>0</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="10" t="n">
         <f aca="false">L17-L15-L8</f>
         <v>0</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="10" t="n">
         <f aca="false">M17-M15-M8</f>
         <v>0</v>
       </c>
-      <c r="N19" s="9" t="n">
+      <c r="N19" s="10" t="n">
         <f aca="false">N17-N15-N8</f>
         <v>0</v>
       </c>
-      <c r="O19" s="9" t="n">
+      <c r="O19" s="10" t="n">
         <f aca="false">O17-O15-O8</f>
         <v>0</v>
       </c>
-      <c r="P19" s="78"/>
+      <c r="P19" s="83"/>
       <c r="R19" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q20" s="79" t="s">
-        <v>111</v>
+      <c r="Q20" s="84" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P21" s="80"/>
-      <c r="Q21" s="71" t="s">
-        <v>112</v>
+      <c r="P21" s="85"/>
+      <c r="Q21" s="76" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="81" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="82" t="s">
+      <c r="B22" s="41" t="s">
         <v>115</v>
       </c>
+      <c r="C22" s="86" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="87" t="s">
+        <v>117</v>
+      </c>
       <c r="T22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="9" t="n">
+      <c r="A23" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="88" t="n">
         <f aca="false">RawData!D26+RawData!E26</f>
         <v>171400</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="88" t="n">
         <f aca="false">RawData!I26+RawData!J26</f>
         <v>187500</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="88" t="n">
         <f aca="false">C23-B23</f>
         <v>16100</v>
       </c>
@@ -8559,90 +8845,90 @@
       <c r="X23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="9" t="n">
+      <c r="A24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" s="88" t="n">
         <f aca="false">RawData!D27+RawData!E27</f>
         <v>182000</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="88" t="n">
         <f aca="false">RawData!I27+RawData!J27</f>
         <v>199100</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="88" t="n">
         <f aca="false">C24-B24</f>
         <v>17100</v>
       </c>
       <c r="W24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B25" s="9" t="n">
+      <c r="A25" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="88" t="n">
         <f aca="false">RawData!D28+RawData!E28</f>
         <v>203200</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="88" t="n">
         <f aca="false">RawData!I28+RawData!J28</f>
         <v>222300</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="88" t="n">
         <f aca="false">C25-B25</f>
         <v>19100</v>
       </c>
       <c r="T25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26" s="9" t="n">
+      <c r="A26" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="88" t="n">
         <f aca="false">RawData!D29+RawData!E29</f>
         <v>235000</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="88" t="n">
         <f aca="false">RawData!I29+RawData!J29</f>
         <v>257100</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="88" t="n">
         <f aca="false">C26-B26</f>
         <v>22100</v>
       </c>
       <c r="T26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="9" t="n">
+      <c r="A27" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="88" t="n">
         <f aca="false">RawData!D30+RawData!E30</f>
         <v>245600</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="88" t="n">
         <f aca="false">RawData!I30+RawData!J30</f>
         <v>268700</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="88" t="n">
         <f aca="false">C27-B27</f>
         <v>23100</v>
       </c>
       <c r="T27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="B28" s="9" t="n">
+      <c r="A28" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="88" t="n">
         <f aca="false">RawData!D31+RawData!E31</f>
         <v>245600</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="88" t="n">
         <f aca="false">RawData!I31+RawData!J31</f>
         <v>268700</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="88" t="n">
         <f aca="false">C28-B28</f>
         <v>23100</v>
       </c>
@@ -8650,18 +8936,18 @@
       <c r="X28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="9" t="n">
+      <c r="A29" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="88" t="n">
         <f aca="false">RawData!D32+RawData!E32</f>
         <v>245600</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="88" t="n">
         <f aca="false">RawData!I32+RawData!J32</f>
         <v>268700</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="88" t="n">
         <f aca="false">C29-B29</f>
         <v>23100</v>
       </c>
@@ -8669,99 +8955,99 @@
       <c r="X29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B30" s="9" t="n">
+      <c r="A30" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="88" t="n">
         <f aca="false">RawData!D33+RawData!E33</f>
         <v>235000</v>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="88" t="n">
         <f aca="false">RawData!I33+RawData!J33</f>
         <v>257100</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="88" t="n">
         <f aca="false">C30-B30</f>
         <v>22100</v>
       </c>
       <c r="W30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B31" s="9" t="n">
+      <c r="A31" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="88" t="n">
         <f aca="false">RawData!D34+RawData!E34</f>
         <v>224400</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="88" t="n">
         <f aca="false">RawData!I34+RawData!J34</f>
         <v>245500</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="88" t="n">
         <f aca="false">C31-B31</f>
         <v>21100</v>
       </c>
       <c r="T31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B32" s="9" t="n">
+      <c r="A32" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="88" t="n">
         <f aca="false">RawData!D35+RawData!E35</f>
         <v>224400</v>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="88" t="n">
         <f aca="false">RawData!I35+RawData!J35</f>
         <v>245500</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="88" t="n">
         <f aca="false">C32-B32</f>
         <v>21100</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B33" s="9" t="n">
+      <c r="A33" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="88" t="n">
         <f aca="false">RawData!D36+RawData!E36</f>
         <v>213800</v>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="88" t="n">
         <f aca="false">RawData!I36+RawData!J36</f>
         <v>233900</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="88" t="n">
         <f aca="false">C33-B33</f>
         <v>20100</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B34" s="9" t="n">
+      <c r="A34" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="88" t="n">
         <f aca="false">RawData!D37+RawData!E37</f>
-        <v>213800</v>
-      </c>
-      <c r="C34" s="9" t="n">
+        <v>224000</v>
+      </c>
+      <c r="C34" s="88" t="n">
         <f aca="false">RawData!I37+RawData!J37</f>
-        <v>233900</v>
-      </c>
-      <c r="D34" s="9" t="n">
+        <v>245900</v>
+      </c>
+      <c r="D34" s="88" t="n">
         <f aca="false">C34-B34</f>
-        <v>20100</v>
+        <v>21900</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8769,111 +9055,111 @@
       <c r="U35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="41" t="s">
+      <c r="A36" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B36" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" s="81" t="s">
-        <v>131</v>
-      </c>
-      <c r="D36" s="82" t="s">
-        <v>115</v>
+      <c r="B36" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="86" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="87" t="s">
+        <v>117</v>
       </c>
       <c r="T36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" s="9" t="n">
+      <c r="A37" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="10" t="n">
         <f aca="false">RawData!F26+RawData!G26+RawData!H26</f>
         <v>122500</v>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C37" s="10" t="n">
         <f aca="false">RawData!K26+RawData!L26+RawData!M26</f>
         <v>134000</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="10" t="n">
         <f aca="false">C37-B37</f>
         <v>11500</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="9" t="n">
+      <c r="A38" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="10" t="n">
         <f aca="false">RawData!F27+RawData!G27+RawData!H27</f>
         <v>132700</v>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="10" t="n">
         <f aca="false">RawData!K27+RawData!L27+RawData!M27</f>
         <v>145100</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="10" t="n">
         <f aca="false">C38-B38</f>
         <v>12400</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B39" s="9" t="n">
+      <c r="A39" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="10" t="n">
         <f aca="false">RawData!F28+RawData!G28+RawData!H28</f>
         <v>153100</v>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="10" t="n">
         <f aca="false">RawData!K28+RawData!L28+RawData!M28</f>
         <v>167500</v>
       </c>
-      <c r="D39" s="9" t="n">
+      <c r="D39" s="10" t="n">
         <f aca="false">C39-B39</f>
         <v>14400</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B40" s="9" t="n">
+      <c r="A40" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" s="10" t="n">
         <f aca="false">RawData!F29+RawData!G29+RawData!H29</f>
         <v>183600</v>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" s="10" t="n">
         <f aca="false">RawData!K29+RawData!L29+RawData!M29</f>
         <v>200900</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="10" t="n">
         <f aca="false">C40-B40</f>
         <v>17300</v>
       </c>
       <c r="T40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" s="9" t="n">
+      <c r="A41" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="10" t="n">
         <f aca="false">RawData!F30+RawData!G30+RawData!H30</f>
         <v>193800</v>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="10" t="n">
         <f aca="false">RawData!K30+RawData!L30+RawData!M30</f>
         <v>212100</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="10" t="n">
         <f aca="false">C41-B41</f>
         <v>18300</v>
       </c>
@@ -8881,90 +9167,90 @@
       <c r="X41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="B42" s="9" t="n">
+      <c r="A42" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="10" t="n">
         <f aca="false">RawData!F31+RawData!G31+RawData!H31</f>
         <v>193800</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="10" t="n">
         <f aca="false">RawData!K31+RawData!L31+RawData!M31</f>
         <v>212100</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="10" t="n">
         <f aca="false">C42-B42</f>
         <v>18300</v>
       </c>
       <c r="W42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B43" s="9" t="n">
+      <c r="A43" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="10" t="n">
         <f aca="false">RawData!F32+RawData!G32+RawData!H32</f>
         <v>193800</v>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="10" t="n">
         <f aca="false">RawData!K32+RawData!L32+RawData!M32</f>
         <v>212100</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D43" s="10" t="n">
         <f aca="false">C43-B43</f>
         <v>18300</v>
       </c>
       <c r="T43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B44" s="9" t="n">
+      <c r="A44" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" s="10" t="n">
         <f aca="false">RawData!F33+RawData!G33+RawData!H33</f>
         <v>183600</v>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="C44" s="10" t="n">
         <f aca="false">RawData!K33+RawData!L33+RawData!M33</f>
         <v>200900</v>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" s="10" t="n">
         <f aca="false">C44-B44</f>
         <v>17300</v>
       </c>
       <c r="T44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B45" s="9" t="n">
+      <c r="A45" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="10" t="n">
         <f aca="false">RawData!F34+RawData!G34+RawData!H34</f>
         <v>173400</v>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" s="10" t="n">
         <f aca="false">RawData!K34+RawData!L34+RawData!M34</f>
         <v>189800</v>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="D45" s="10" t="n">
         <f aca="false">C45-B45</f>
         <v>16400</v>
       </c>
       <c r="T45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B46" s="9" t="n">
+      <c r="A46" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="10" t="n">
         <f aca="false">RawData!F35+RawData!G35+RawData!H35</f>
         <v>173400</v>
       </c>
-      <c r="C46" s="9" t="n">
+      <c r="C46" s="10" t="n">
         <f aca="false">RawData!K35+RawData!L35+RawData!M35</f>
         <v>189800</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="10" t="n">
         <f aca="false">C46-B46</f>
         <v>16400</v>
       </c>
@@ -8972,18 +9258,18 @@
       <c r="X46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B47" s="9" t="n">
+      <c r="A47" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" s="10" t="n">
         <f aca="false">RawData!F36+RawData!G36+RawData!H36</f>
         <v>163300</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="10" t="n">
         <f aca="false">RawData!K36+RawData!L36+RawData!M36</f>
         <v>178700</v>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="D47" s="10" t="n">
         <f aca="false">C47-B47</f>
         <v>15400</v>
       </c>
@@ -8991,20 +9277,20 @@
       <c r="X47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B48" s="9" t="n">
+      <c r="A48" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" s="10" t="n">
         <f aca="false">RawData!F37+RawData!G37+RawData!H37</f>
-        <v>163300</v>
-      </c>
-      <c r="C48" s="9" t="n">
+        <v>173500</v>
+      </c>
+      <c r="C48" s="10" t="n">
         <f aca="false">RawData!K37+RawData!L37+RawData!M37</f>
-        <v>178700</v>
-      </c>
-      <c r="D48" s="9" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D48" s="10" t="n">
         <f aca="false">C48-B48</f>
-        <v>15400</v>
+        <v>16500</v>
       </c>
       <c r="W48" s="2"/>
     </row>
@@ -9013,17 +9299,17 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q50" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q51" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q52" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9035,16 +9321,16 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q55" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N56" s="9" t="s">
-        <v>126</v>
+      <c r="N56" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B6:P8 N12:P14 B15:P15 N18:P18 C18:L18 N17:O18 P17">
+  <conditionalFormatting sqref="P6:P8 N12:P14 B15:P15 N18:P18 C18:L18 N17:O18 P17">
     <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -9052,7 +9338,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6:P8 N12:P14 B15:P15 N18:P18 C18:L18 N17:O18 P17">
+  <conditionalFormatting sqref="P6:P8 N12:P14 B15:P15 N18:P18 C18:L18 N17:O18 P17">
     <cfRule type="cellIs" priority="4" operator="lessThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -9117,6 +9403,19 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B6:O8">
+    <cfRule type="cellIs" priority="19" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:O8">
+    <cfRule type="cellIs" priority="21" operator="lessThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9143,990 +9442,990 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
+      <c r="A1" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="84" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="84" t="s">
+      <c r="A4" s="90" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="84" t="s">
+      <c r="D4" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="84" t="s">
+      <c r="E4" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="84" t="s">
+      <c r="F4" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="84" t="s">
+      <c r="G4" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="84" t="s">
+      <c r="H4" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="84" t="s">
+      <c r="I4" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="84" t="s">
+      <c r="J4" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="84" t="s">
+      <c r="K4" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="84" t="s">
+      <c r="L4" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="84" t="s">
+      <c r="M4" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="84" t="s">
-        <v>91</v>
-      </c>
-      <c r="O4" s="84" t="s">
-        <v>135</v>
+      <c r="N4" s="90" t="s">
+        <v>93</v>
+      </c>
+      <c r="O4" s="90" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="85" t="s">
-        <v>136</v>
-      </c>
-      <c r="B5" s="86" t="n">
+      <c r="A5" s="91" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="92" t="n">
         <f aca="false">Drivers!B8*Drivers!B14</f>
         <v>234600</v>
       </c>
-      <c r="C5" s="86" t="n">
+      <c r="C5" s="92" t="n">
         <f aca="false">Drivers!C8*Drivers!C14</f>
         <v>234600</v>
       </c>
-      <c r="D5" s="86" t="n">
+      <c r="D5" s="92" t="n">
         <f aca="false">Drivers!D8*Drivers!D14</f>
         <v>234600</v>
       </c>
-      <c r="E5" s="86" t="n">
+      <c r="E5" s="92" t="n">
         <f aca="false">Drivers!E8*Drivers!E14</f>
         <v>239200</v>
       </c>
-      <c r="F5" s="86" t="n">
+      <c r="F5" s="92" t="n">
         <f aca="false">Drivers!F8*Drivers!F14</f>
         <v>239200</v>
       </c>
-      <c r="G5" s="86" t="n">
+      <c r="G5" s="92" t="n">
         <f aca="false">Drivers!G8*Drivers!G14</f>
         <v>239200</v>
       </c>
-      <c r="H5" s="86" t="n">
+      <c r="H5" s="92" t="n">
         <f aca="false">Drivers!H8*Drivers!H14</f>
         <v>239200</v>
       </c>
-      <c r="I5" s="86" t="n">
+      <c r="I5" s="92" t="n">
         <f aca="false">Drivers!I8*Drivers!I14</f>
         <v>239200</v>
       </c>
-      <c r="J5" s="86" t="n">
+      <c r="J5" s="92" t="n">
         <f aca="false">Drivers!J8*Drivers!J14</f>
         <v>239200</v>
       </c>
-      <c r="K5" s="86" t="n">
+      <c r="K5" s="92" t="n">
         <f aca="false">Drivers!K8*Drivers!K14</f>
         <v>243800</v>
       </c>
-      <c r="L5" s="86" t="n">
+      <c r="L5" s="92" t="n">
         <f aca="false">Drivers!L8*Drivers!L14</f>
         <v>243800</v>
       </c>
-      <c r="M5" s="86" t="n">
+      <c r="M5" s="92" t="n">
         <f aca="false">Drivers!M8*Drivers!M14</f>
         <v>243800</v>
       </c>
-      <c r="N5" s="87" t="n">
+      <c r="N5" s="93" t="n">
         <f aca="false">SUM(B5:M5)</f>
         <v>2870400</v>
       </c>
-      <c r="O5" s="88" t="n">
+      <c r="O5" s="94" t="n">
         <f aca="false">IF(N7=0,0,N5/N7)</f>
         <v>0.844036697247707</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="B6" s="89" t="n">
+      <c r="A6" s="91" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="95" t="n">
         <f aca="false">Drivers!B19</f>
         <v>44200</v>
       </c>
-      <c r="C6" s="89" t="n">
+      <c r="C6" s="95" t="n">
         <f aca="false">Drivers!C19</f>
         <v>44200</v>
       </c>
-      <c r="D6" s="89" t="n">
+      <c r="D6" s="95" t="n">
         <f aca="false">Drivers!D19</f>
         <v>44200</v>
       </c>
-      <c r="E6" s="89" t="n">
+      <c r="E6" s="95" t="n">
         <f aca="false">Drivers!E19</f>
         <v>44200</v>
       </c>
-      <c r="F6" s="89" t="n">
+      <c r="F6" s="95" t="n">
         <f aca="false">Drivers!F19</f>
         <v>44200</v>
       </c>
-      <c r="G6" s="89" t="n">
+      <c r="G6" s="95" t="n">
         <f aca="false">Drivers!G19</f>
         <v>44200</v>
       </c>
-      <c r="H6" s="89" t="n">
+      <c r="H6" s="95" t="n">
         <f aca="false">Drivers!H19</f>
         <v>44200</v>
       </c>
-      <c r="I6" s="89" t="n">
+      <c r="I6" s="95" t="n">
         <f aca="false">Drivers!I19</f>
         <v>44200</v>
       </c>
-      <c r="J6" s="89" t="n">
+      <c r="J6" s="95" t="n">
         <f aca="false">Drivers!J19</f>
         <v>44200</v>
       </c>
-      <c r="K6" s="89" t="n">
+      <c r="K6" s="95" t="n">
         <f aca="false">Drivers!K19</f>
         <v>44200</v>
       </c>
-      <c r="L6" s="89" t="n">
+      <c r="L6" s="95" t="n">
         <f aca="false">Drivers!L19</f>
         <v>44200</v>
       </c>
-      <c r="M6" s="89" t="n">
+      <c r="M6" s="95" t="n">
         <f aca="false">Drivers!M19</f>
         <v>44200</v>
       </c>
-      <c r="N6" s="87" t="n">
+      <c r="N6" s="93" t="n">
         <f aca="false">SUM(B6:M6)</f>
         <v>530400</v>
       </c>
-      <c r="O6" s="88" t="n">
+      <c r="O6" s="94" t="n">
         <f aca="false">IF(N7=0,0,N6/N7)</f>
         <v>0.155963302752294</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="90" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="91" t="n">
+      <c r="A7" s="96" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="97" t="n">
         <f aca="false">B5+B6</f>
         <v>278800</v>
       </c>
-      <c r="C7" s="91" t="n">
+      <c r="C7" s="97" t="n">
         <f aca="false">C5+C6</f>
         <v>278800</v>
       </c>
-      <c r="D7" s="91" t="n">
+      <c r="D7" s="97" t="n">
         <f aca="false">D5+D6</f>
         <v>278800</v>
       </c>
-      <c r="E7" s="91" t="n">
+      <c r="E7" s="97" t="n">
         <f aca="false">E5+E6</f>
         <v>283400</v>
       </c>
-      <c r="F7" s="91" t="n">
+      <c r="F7" s="97" t="n">
         <f aca="false">F5+F6</f>
         <v>283400</v>
       </c>
-      <c r="G7" s="91" t="n">
+      <c r="G7" s="97" t="n">
         <f aca="false">G5+G6</f>
         <v>283400</v>
       </c>
-      <c r="H7" s="91" t="n">
+      <c r="H7" s="97" t="n">
         <f aca="false">H5+H6</f>
         <v>283400</v>
       </c>
-      <c r="I7" s="91" t="n">
+      <c r="I7" s="97" t="n">
         <f aca="false">I5+I6</f>
         <v>283400</v>
       </c>
-      <c r="J7" s="91" t="n">
+      <c r="J7" s="97" t="n">
         <f aca="false">J5+J6</f>
         <v>283400</v>
       </c>
-      <c r="K7" s="91" t="n">
+      <c r="K7" s="97" t="n">
         <f aca="false">K5+K6</f>
         <v>288000</v>
       </c>
-      <c r="L7" s="91" t="n">
+      <c r="L7" s="97" t="n">
         <f aca="false">L5+L6</f>
         <v>288000</v>
       </c>
-      <c r="M7" s="91" t="n">
+      <c r="M7" s="97" t="n">
         <f aca="false">M5+M6</f>
         <v>288000</v>
       </c>
-      <c r="N7" s="92" t="n">
+      <c r="N7" s="98" t="n">
         <f aca="false">SUM(B7:M7)</f>
         <v>3400800</v>
       </c>
-      <c r="O7" s="93" t="n">
+      <c r="O7" s="99" t="n">
         <f aca="false">IF(N7=0,0,N7/N7)</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="85"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="94"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="94"/>
-      <c r="N8" s="95"/>
-      <c r="O8" s="95"/>
+      <c r="A8" s="91"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="100"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="100"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="100"/>
+      <c r="N8" s="101"/>
+      <c r="O8" s="101"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="85" t="s">
-        <v>138</v>
-      </c>
-      <c r="B9" s="89" t="n">
+      <c r="A9" s="91" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="95" t="n">
         <f aca="false">Drivers!B8*Drivers!E25</f>
-        <v>140070.192307692</v>
-      </c>
-      <c r="C9" s="89" t="n">
+        <v>140781.25</v>
+      </c>
+      <c r="C9" s="95" t="n">
         <f aca="false">Drivers!C8*Drivers!E25</f>
-        <v>140070.192307692</v>
-      </c>
-      <c r="D9" s="89" t="n">
+        <v>140781.25</v>
+      </c>
+      <c r="D9" s="95" t="n">
         <f aca="false">Drivers!D8*Drivers!E25</f>
-        <v>140070.192307692</v>
-      </c>
-      <c r="E9" s="89" t="n">
+        <v>140781.25</v>
+      </c>
+      <c r="E9" s="95" t="n">
         <f aca="false">Drivers!E8*Drivers!E25</f>
-        <v>142816.666666667</v>
-      </c>
-      <c r="F9" s="89" t="n">
+        <v>143541.666666667</v>
+      </c>
+      <c r="F9" s="95" t="n">
         <f aca="false">Drivers!F8*Drivers!E25</f>
-        <v>142816.666666667</v>
-      </c>
-      <c r="G9" s="89" t="n">
+        <v>143541.666666667</v>
+      </c>
+      <c r="G9" s="95" t="n">
         <f aca="false">Drivers!G8*Drivers!E25</f>
-        <v>142816.666666667</v>
-      </c>
-      <c r="H9" s="89" t="n">
+        <v>143541.666666667</v>
+      </c>
+      <c r="H9" s="95" t="n">
         <f aca="false">Drivers!H8*Drivers!E25</f>
-        <v>142816.666666667</v>
-      </c>
-      <c r="I9" s="89" t="n">
+        <v>143541.666666667</v>
+      </c>
+      <c r="I9" s="95" t="n">
         <f aca="false">Drivers!I8*Drivers!E25</f>
-        <v>142816.666666667</v>
-      </c>
-      <c r="J9" s="89" t="n">
+        <v>143541.666666667</v>
+      </c>
+      <c r="J9" s="95" t="n">
         <f aca="false">Drivers!J8*Drivers!E25</f>
-        <v>142816.666666667</v>
-      </c>
-      <c r="K9" s="89" t="n">
+        <v>143541.666666667</v>
+      </c>
+      <c r="K9" s="95" t="n">
         <f aca="false">Drivers!K8*Drivers!E25</f>
-        <v>145563.141025641</v>
-      </c>
-      <c r="L9" s="89" t="n">
+        <v>146302.083333333</v>
+      </c>
+      <c r="L9" s="95" t="n">
         <f aca="false">Drivers!L8*Drivers!E25</f>
-        <v>145563.141025641</v>
-      </c>
-      <c r="M9" s="89" t="n">
+        <v>146302.083333333</v>
+      </c>
+      <c r="M9" s="95" t="n">
         <f aca="false">Drivers!M8*Drivers!E25</f>
-        <v>145563.141025641</v>
-      </c>
-      <c r="N9" s="87" t="n">
+        <v>146302.083333333</v>
+      </c>
+      <c r="N9" s="93" t="n">
         <f aca="false">SUM(B9:M9)</f>
-        <v>1713800</v>
-      </c>
-      <c r="O9" s="88" t="n">
+        <v>1722500</v>
+      </c>
+      <c r="O9" s="94" t="n">
         <f aca="false">IF(N7=0,0,N9/N7)</f>
-        <v>0.503940249353093</v>
+        <v>0.506498470948012</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="85" t="s">
-        <v>139</v>
-      </c>
-      <c r="B10" s="89" t="n">
+      <c r="A10" s="91" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="95" t="n">
         <f aca="false">RawData!G26</f>
         <v>12700</v>
       </c>
-      <c r="C10" s="89" t="n">
+      <c r="C10" s="95" t="n">
         <f aca="false">RawData!G27</f>
         <v>13800</v>
       </c>
-      <c r="D10" s="89" t="n">
+      <c r="D10" s="95" t="n">
         <f aca="false">RawData!G28</f>
         <v>15900</v>
       </c>
-      <c r="E10" s="89" t="n">
+      <c r="E10" s="95" t="n">
         <f aca="false">RawData!G29</f>
         <v>19100</v>
       </c>
-      <c r="F10" s="89" t="n">
+      <c r="F10" s="95" t="n">
         <f aca="false">RawData!G30</f>
         <v>20100</v>
       </c>
-      <c r="G10" s="89" t="n">
+      <c r="G10" s="95" t="n">
         <f aca="false">RawData!G31</f>
         <v>20100</v>
       </c>
-      <c r="H10" s="89" t="n">
+      <c r="H10" s="95" t="n">
         <f aca="false">RawData!G32</f>
         <v>20100</v>
       </c>
-      <c r="I10" s="89" t="n">
+      <c r="I10" s="95" t="n">
         <f aca="false">RawData!G33</f>
         <v>19100</v>
       </c>
-      <c r="J10" s="89" t="n">
+      <c r="J10" s="95" t="n">
         <f aca="false">RawData!G34</f>
         <v>18000</v>
       </c>
-      <c r="K10" s="89" t="n">
+      <c r="K10" s="95" t="n">
         <f aca="false">RawData!G35</f>
         <v>18000</v>
       </c>
-      <c r="L10" s="89" t="n">
+      <c r="L10" s="95" t="n">
         <f aca="false">RawData!G36</f>
         <v>17000</v>
       </c>
-      <c r="M10" s="89" t="n">
+      <c r="M10" s="95" t="n">
         <f aca="false">RawData!G37</f>
-        <v>17000</v>
-      </c>
-      <c r="N10" s="87" t="n">
+        <v>18100</v>
+      </c>
+      <c r="N10" s="93" t="n">
         <f aca="false">SUM(B10:M10)</f>
-        <v>210900</v>
-      </c>
-      <c r="O10" s="88" t="n">
+        <v>212000</v>
+      </c>
+      <c r="O10" s="94" t="n">
         <f aca="false">IF(N7=0,0,N10/N7)</f>
-        <v>0.062014820042343</v>
+        <v>0.0623382733474477</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="85" t="s">
-        <v>140</v>
-      </c>
-      <c r="B11" s="89" t="n">
+      <c r="A11" s="91" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="95" t="n">
         <f aca="false">RawData!H26</f>
         <v>6400</v>
       </c>
-      <c r="C11" s="89" t="n">
+      <c r="C11" s="95" t="n">
         <f aca="false">RawData!H27</f>
         <v>6900</v>
       </c>
-      <c r="D11" s="89" t="n">
+      <c r="D11" s="95" t="n">
         <f aca="false">RawData!H28</f>
         <v>8000</v>
       </c>
-      <c r="E11" s="89" t="n">
+      <c r="E11" s="95" t="n">
         <f aca="false">RawData!H29</f>
         <v>9500</v>
       </c>
-      <c r="F11" s="89" t="n">
+      <c r="F11" s="95" t="n">
         <f aca="false">RawData!H30</f>
         <v>10100</v>
       </c>
-      <c r="G11" s="89" t="n">
+      <c r="G11" s="95" t="n">
         <f aca="false">RawData!H31</f>
         <v>10100</v>
       </c>
-      <c r="H11" s="89" t="n">
+      <c r="H11" s="95" t="n">
         <f aca="false">RawData!H32</f>
         <v>10100</v>
       </c>
-      <c r="I11" s="89" t="n">
+      <c r="I11" s="95" t="n">
         <f aca="false">RawData!H33</f>
         <v>9500</v>
       </c>
-      <c r="J11" s="89" t="n">
+      <c r="J11" s="95" t="n">
         <f aca="false">RawData!H34</f>
         <v>9000</v>
       </c>
-      <c r="K11" s="89" t="n">
+      <c r="K11" s="95" t="n">
         <f aca="false">RawData!H35</f>
         <v>9000</v>
       </c>
-      <c r="L11" s="89" t="n">
+      <c r="L11" s="95" t="n">
         <f aca="false">RawData!H36</f>
         <v>8500</v>
       </c>
-      <c r="M11" s="89" t="n">
+      <c r="M11" s="95" t="n">
         <f aca="false">RawData!H37</f>
-        <v>8500</v>
-      </c>
-      <c r="N11" s="87" t="n">
+        <v>8900</v>
+      </c>
+      <c r="N11" s="93" t="n">
         <f aca="false">SUM(B11:M11)</f>
-        <v>105600</v>
-      </c>
-      <c r="O11" s="88" t="n">
+        <v>106000</v>
+      </c>
+      <c r="O11" s="94" t="n">
         <f aca="false">IF(N7=0,0,N11/N7)</f>
-        <v>0.0310515172900494</v>
+        <v>0.0311691366737238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="91" t="n">
+      <c r="A12" s="96" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="97" t="n">
         <f aca="false">B9+B10+B11</f>
-        <v>159170.192307692</v>
-      </c>
-      <c r="C12" s="91" t="n">
+        <v>159881.25</v>
+      </c>
+      <c r="C12" s="97" t="n">
         <f aca="false">C9+C10+C11</f>
-        <v>160770.192307692</v>
-      </c>
-      <c r="D12" s="91" t="n">
+        <v>161481.25</v>
+      </c>
+      <c r="D12" s="97" t="n">
         <f aca="false">D9+D10+D11</f>
-        <v>163970.192307692</v>
-      </c>
-      <c r="E12" s="91" t="n">
+        <v>164681.25</v>
+      </c>
+      <c r="E12" s="97" t="n">
         <f aca="false">E9+E10+E11</f>
-        <v>171416.666666667</v>
-      </c>
-      <c r="F12" s="91" t="n">
+        <v>172141.666666667</v>
+      </c>
+      <c r="F12" s="97" t="n">
         <f aca="false">F9+F10+F11</f>
-        <v>173016.666666667</v>
-      </c>
-      <c r="G12" s="91" t="n">
+        <v>173741.666666667</v>
+      </c>
+      <c r="G12" s="97" t="n">
         <f aca="false">G9+G10+G11</f>
-        <v>173016.666666667</v>
-      </c>
-      <c r="H12" s="91" t="n">
+        <v>173741.666666667</v>
+      </c>
+      <c r="H12" s="97" t="n">
         <f aca="false">H9+H10+H11</f>
-        <v>173016.666666667</v>
-      </c>
-      <c r="I12" s="91" t="n">
+        <v>173741.666666667</v>
+      </c>
+      <c r="I12" s="97" t="n">
         <f aca="false">I9+I10+I11</f>
-        <v>171416.666666667</v>
-      </c>
-      <c r="J12" s="91" t="n">
+        <v>172141.666666667</v>
+      </c>
+      <c r="J12" s="97" t="n">
         <f aca="false">J9+J10+J11</f>
-        <v>169816.666666667</v>
-      </c>
-      <c r="K12" s="91" t="n">
+        <v>170541.666666667</v>
+      </c>
+      <c r="K12" s="97" t="n">
         <f aca="false">K9+K10+K11</f>
-        <v>172563.141025641</v>
-      </c>
-      <c r="L12" s="91" t="n">
+        <v>173302.083333333</v>
+      </c>
+      <c r="L12" s="97" t="n">
         <f aca="false">L9+L10+L11</f>
-        <v>171063.141025641</v>
-      </c>
-      <c r="M12" s="91" t="n">
+        <v>171802.083333333</v>
+      </c>
+      <c r="M12" s="97" t="n">
         <f aca="false">M9+M10+M11</f>
-        <v>171063.141025641</v>
-      </c>
-      <c r="N12" s="92" t="n">
+        <v>173302.083333333</v>
+      </c>
+      <c r="N12" s="98" t="n">
         <f aca="false">SUM(B12:M12)</f>
-        <v>2030300</v>
-      </c>
-      <c r="O12" s="93" t="n">
+        <v>2040500</v>
+      </c>
+      <c r="O12" s="99" t="n">
         <f aca="false">IF(N7=0,0,N12/N7)</f>
-        <v>0.597006586685486</v>
+        <v>0.600005880969184</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="85"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="95"/>
-      <c r="O13" s="95"/>
+      <c r="A13" s="91"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="100"/>
+      <c r="N13" s="101"/>
+      <c r="O13" s="101"/>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="90" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="96" t="n">
+      <c r="A14" s="96" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="102" t="n">
         <f aca="false">B7-B12</f>
-        <v>119629.807692308</v>
-      </c>
-      <c r="C14" s="96" t="n">
+        <v>118918.75</v>
+      </c>
+      <c r="C14" s="102" t="n">
         <f aca="false">C7-C12</f>
-        <v>118029.807692308</v>
-      </c>
-      <c r="D14" s="96" t="n">
+        <v>117318.75</v>
+      </c>
+      <c r="D14" s="102" t="n">
         <f aca="false">D7-D12</f>
-        <v>114829.807692308</v>
-      </c>
-      <c r="E14" s="96" t="n">
+        <v>114118.75</v>
+      </c>
+      <c r="E14" s="102" t="n">
         <f aca="false">E7-E12</f>
-        <v>111983.333333333</v>
-      </c>
-      <c r="F14" s="96" t="n">
+        <v>111258.333333333</v>
+      </c>
+      <c r="F14" s="102" t="n">
         <f aca="false">F7-F12</f>
-        <v>110383.333333333</v>
-      </c>
-      <c r="G14" s="96" t="n">
+        <v>109658.333333333</v>
+      </c>
+      <c r="G14" s="102" t="n">
         <f aca="false">G7-G12</f>
-        <v>110383.333333333</v>
-      </c>
-      <c r="H14" s="96" t="n">
+        <v>109658.333333333</v>
+      </c>
+      <c r="H14" s="102" t="n">
         <f aca="false">H7-H12</f>
-        <v>110383.333333333</v>
-      </c>
-      <c r="I14" s="96" t="n">
+        <v>109658.333333333</v>
+      </c>
+      <c r="I14" s="102" t="n">
         <f aca="false">I7-I12</f>
-        <v>111983.333333333</v>
-      </c>
-      <c r="J14" s="96" t="n">
+        <v>111258.333333333</v>
+      </c>
+      <c r="J14" s="102" t="n">
         <f aca="false">J7-J12</f>
-        <v>113583.333333333</v>
-      </c>
-      <c r="K14" s="96" t="n">
+        <v>112858.333333333</v>
+      </c>
+      <c r="K14" s="102" t="n">
         <f aca="false">K7-K12</f>
-        <v>115436.858974359</v>
-      </c>
-      <c r="L14" s="96" t="n">
+        <v>114697.916666667</v>
+      </c>
+      <c r="L14" s="102" t="n">
         <f aca="false">L7-L12</f>
-        <v>116936.858974359</v>
-      </c>
-      <c r="M14" s="96" t="n">
+        <v>116197.916666667</v>
+      </c>
+      <c r="M14" s="102" t="n">
         <f aca="false">M7-M12</f>
-        <v>116936.858974359</v>
-      </c>
-      <c r="N14" s="97" t="n">
+        <v>114697.916666667</v>
+      </c>
+      <c r="N14" s="103" t="n">
         <f aca="false">SUM(B14:M14)</f>
-        <v>1370500</v>
-      </c>
-      <c r="O14" s="98" t="n">
+        <v>1360300</v>
+      </c>
+      <c r="O14" s="104" t="n">
         <f aca="false">IF(N7=0,0,N14/N7)</f>
-        <v>0.402993413314514</v>
+        <v>0.399994119030816</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="99" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="100" t="n">
+      <c r="A15" s="105" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="106" t="n">
         <f aca="false">B14</f>
-        <v>119629.807692308</v>
-      </c>
-      <c r="C15" s="100" t="n">
+        <v>118918.75</v>
+      </c>
+      <c r="C15" s="106" t="n">
         <f aca="false">C14</f>
-        <v>118029.807692308</v>
-      </c>
-      <c r="D15" s="100" t="n">
+        <v>117318.75</v>
+      </c>
+      <c r="D15" s="106" t="n">
         <f aca="false">D14</f>
-        <v>114829.807692308</v>
-      </c>
-      <c r="E15" s="100" t="n">
+        <v>114118.75</v>
+      </c>
+      <c r="E15" s="106" t="n">
         <f aca="false">E14</f>
-        <v>111983.333333333</v>
-      </c>
-      <c r="F15" s="100" t="n">
+        <v>111258.333333333</v>
+      </c>
+      <c r="F15" s="106" t="n">
         <f aca="false">F14</f>
-        <v>110383.333333333</v>
-      </c>
-      <c r="G15" s="100" t="n">
+        <v>109658.333333333</v>
+      </c>
+      <c r="G15" s="106" t="n">
         <f aca="false">G14</f>
-        <v>110383.333333333</v>
-      </c>
-      <c r="H15" s="100" t="n">
+        <v>109658.333333333</v>
+      </c>
+      <c r="H15" s="106" t="n">
         <f aca="false">H14</f>
-        <v>110383.333333333</v>
-      </c>
-      <c r="I15" s="100" t="n">
+        <v>109658.333333333</v>
+      </c>
+      <c r="I15" s="106" t="n">
         <f aca="false">I14</f>
-        <v>111983.333333333</v>
-      </c>
-      <c r="J15" s="100" t="n">
+        <v>111258.333333333</v>
+      </c>
+      <c r="J15" s="106" t="n">
         <f aca="false">J14</f>
-        <v>113583.333333333</v>
-      </c>
-      <c r="K15" s="100" t="n">
+        <v>112858.333333333</v>
+      </c>
+      <c r="K15" s="106" t="n">
         <f aca="false">K14</f>
-        <v>115436.858974359</v>
-      </c>
-      <c r="L15" s="100" t="n">
+        <v>114697.916666667</v>
+      </c>
+      <c r="L15" s="106" t="n">
         <f aca="false">L14</f>
-        <v>116936.858974359</v>
-      </c>
-      <c r="M15" s="100" t="n">
+        <v>116197.916666667</v>
+      </c>
+      <c r="M15" s="106" t="n">
         <f aca="false">M14</f>
-        <v>116936.858974359</v>
-      </c>
-      <c r="N15" s="100" t="n">
+        <v>114697.916666667</v>
+      </c>
+      <c r="N15" s="106" t="n">
         <f aca="false">SUM(B15:M15)</f>
-        <v>1370500</v>
-      </c>
-      <c r="O15" s="101" t="n">
+        <v>1360300</v>
+      </c>
+      <c r="O15" s="107" t="n">
         <f aca="false">IF(N7=0,0,N15/N7)</f>
-        <v>0.402993413314514</v>
+        <v>0.399994119030816</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="85" t="s">
-        <v>142</v>
-      </c>
-      <c r="B16" s="102" t="n">
+      <c r="A16" s="91" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="108" t="n">
         <f aca="false">IF(B7=0,0,B15/B7)</f>
-        <v>0.429088262884891</v>
-      </c>
-      <c r="C16" s="102" t="n">
+        <v>0.426537840746055</v>
+      </c>
+      <c r="C16" s="108" t="n">
         <f aca="false">IF(C7=0,0,C15/C7)</f>
-        <v>0.42334938196667</v>
-      </c>
-      <c r="D16" s="102" t="n">
+        <v>0.420798959827834</v>
+      </c>
+      <c r="D16" s="108" t="n">
         <f aca="false">IF(D7=0,0,D15/D7)</f>
-        <v>0.411871620130228</v>
-      </c>
-      <c r="E16" s="102" t="n">
+        <v>0.409321197991392</v>
+      </c>
+      <c r="E16" s="108" t="n">
         <f aca="false">IF(E7=0,0,E15/E7)</f>
-        <v>0.395142319454246</v>
-      </c>
-      <c r="F16" s="102" t="n">
+        <v>0.392584097859327</v>
+      </c>
+      <c r="F16" s="108" t="n">
         <f aca="false">IF(F7=0,0,F15/F7)</f>
-        <v>0.389496589037874</v>
-      </c>
-      <c r="G16" s="102" t="n">
+        <v>0.386938367442955</v>
+      </c>
+      <c r="G16" s="108" t="n">
         <f aca="false">IF(G7=0,0,G15/G7)</f>
-        <v>0.389496589037874</v>
-      </c>
-      <c r="H16" s="102" t="n">
+        <v>0.386938367442955</v>
+      </c>
+      <c r="H16" s="108" t="n">
         <f aca="false">IF(H7=0,0,H15/H7)</f>
-        <v>0.389496589037874</v>
-      </c>
-      <c r="I16" s="102" t="n">
+        <v>0.386938367442955</v>
+      </c>
+      <c r="I16" s="108" t="n">
         <f aca="false">IF(I7=0,0,I15/I7)</f>
-        <v>0.395142319454246</v>
-      </c>
-      <c r="J16" s="102" t="n">
+        <v>0.392584097859327</v>
+      </c>
+      <c r="J16" s="108" t="n">
         <f aca="false">IF(J7=0,0,J15/J7)</f>
-        <v>0.400788049870619</v>
-      </c>
-      <c r="K16" s="102" t="n">
+        <v>0.3982298282757</v>
+      </c>
+      <c r="K16" s="108" t="n">
         <f aca="false">IF(K7=0,0,K15/K7)</f>
-        <v>0.400822426994302</v>
-      </c>
-      <c r="L16" s="102" t="n">
+        <v>0.398256655092593</v>
+      </c>
+      <c r="L16" s="108" t="n">
         <f aca="false">IF(L7=0,0,L15/L7)</f>
-        <v>0.406030760327635</v>
-      </c>
-      <c r="M16" s="102" t="n">
+        <v>0.403464988425926</v>
+      </c>
+      <c r="M16" s="108" t="n">
         <f aca="false">IF(M7=0,0,M15/M7)</f>
-        <v>0.406030760327635</v>
-      </c>
-      <c r="N16" s="98" t="n">
+        <v>0.398256655092593</v>
+      </c>
+      <c r="N16" s="104" t="n">
         <f aca="false">IF(N7=0,0,N15/N7)</f>
-        <v>0.402993413314514</v>
-      </c>
-      <c r="O16" s="98"/>
+        <v>0.399994119030816</v>
+      </c>
+      <c r="O16" s="104"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="85"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="95"/>
-      <c r="K17" s="95"/>
-      <c r="L17" s="95"/>
-      <c r="M17" s="95"/>
-      <c r="N17" s="95"/>
-      <c r="O17" s="95"/>
+      <c r="A17" s="91"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="101"/>
+      <c r="D17" s="101"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="101"/>
+      <c r="G17" s="101"/>
+      <c r="H17" s="101"/>
+      <c r="I17" s="101"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="101"/>
+      <c r="N17" s="101"/>
+      <c r="O17" s="101"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="85" t="s">
-        <v>143</v>
-      </c>
-      <c r="B18" s="94" t="n">
+      <c r="A18" s="91" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="95" t="n">
         <f aca="false">0.02*B7</f>
         <v>5576</v>
       </c>
-      <c r="C18" s="94" t="n">
+      <c r="C18" s="95" t="n">
         <f aca="false">0.02*C7</f>
         <v>5576</v>
       </c>
-      <c r="D18" s="94" t="n">
+      <c r="D18" s="95" t="n">
         <f aca="false">0.02*D7</f>
         <v>5576</v>
       </c>
-      <c r="E18" s="94" t="n">
+      <c r="E18" s="95" t="n">
         <f aca="false">0.02*E7</f>
         <v>5668</v>
       </c>
-      <c r="F18" s="94" t="n">
+      <c r="F18" s="95" t="n">
         <f aca="false">0.02*F7</f>
         <v>5668</v>
       </c>
-      <c r="G18" s="94" t="n">
+      <c r="G18" s="95" t="n">
         <f aca="false">0.02*G7</f>
         <v>5668</v>
       </c>
-      <c r="H18" s="94" t="n">
+      <c r="H18" s="95" t="n">
         <f aca="false">0.02*H7</f>
         <v>5668</v>
       </c>
-      <c r="I18" s="94" t="n">
+      <c r="I18" s="95" t="n">
         <f aca="false">0.02*I7</f>
         <v>5668</v>
       </c>
-      <c r="J18" s="94" t="n">
+      <c r="J18" s="95" t="n">
         <f aca="false">0.02*J7</f>
         <v>5668</v>
       </c>
-      <c r="K18" s="94" t="n">
+      <c r="K18" s="95" t="n">
         <f aca="false">0.02*K7</f>
         <v>5760</v>
       </c>
-      <c r="L18" s="94" t="n">
+      <c r="L18" s="95" t="n">
         <f aca="false">0.02*L7</f>
         <v>5760</v>
       </c>
-      <c r="M18" s="94" t="n">
+      <c r="M18" s="95" t="n">
         <f aca="false">0.02*M7</f>
         <v>5760</v>
       </c>
-      <c r="N18" s="87" t="n">
+      <c r="N18" s="93" t="n">
         <f aca="false">SUM(B18:M18)</f>
         <v>68016</v>
       </c>
-      <c r="O18" s="88" t="n">
+      <c r="O18" s="94" t="n">
         <f aca="false">IF(N7=0,0,N18/N7)</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="B19" s="91" t="n">
+      <c r="A19" s="77" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="97" t="n">
         <f aca="false">B15-B18</f>
-        <v>114053.807692308</v>
-      </c>
-      <c r="C19" s="91" t="n">
+        <v>113342.75</v>
+      </c>
+      <c r="C19" s="97" t="n">
         <f aca="false">C15-C18</f>
-        <v>112453.807692308</v>
-      </c>
-      <c r="D19" s="91" t="n">
+        <v>111742.75</v>
+      </c>
+      <c r="D19" s="97" t="n">
         <f aca="false">D15-D18</f>
-        <v>109253.807692308</v>
-      </c>
-      <c r="E19" s="91" t="n">
+        <v>108542.75</v>
+      </c>
+      <c r="E19" s="97" t="n">
         <f aca="false">E15-E18</f>
-        <v>106315.333333333</v>
-      </c>
-      <c r="F19" s="91" t="n">
+        <v>105590.333333333</v>
+      </c>
+      <c r="F19" s="97" t="n">
         <f aca="false">F15-F18</f>
-        <v>104715.333333333</v>
-      </c>
-      <c r="G19" s="91" t="n">
+        <v>103990.333333333</v>
+      </c>
+      <c r="G19" s="97" t="n">
         <f aca="false">G15-G18</f>
-        <v>104715.333333333</v>
-      </c>
-      <c r="H19" s="91" t="n">
+        <v>103990.333333333</v>
+      </c>
+      <c r="H19" s="97" t="n">
         <f aca="false">H15-H18</f>
-        <v>104715.333333333</v>
-      </c>
-      <c r="I19" s="91" t="n">
+        <v>103990.333333333</v>
+      </c>
+      <c r="I19" s="97" t="n">
         <f aca="false">I15-I18</f>
-        <v>106315.333333333</v>
-      </c>
-      <c r="J19" s="91" t="n">
+        <v>105590.333333333</v>
+      </c>
+      <c r="J19" s="97" t="n">
         <f aca="false">J15-J18</f>
-        <v>107915.333333333</v>
-      </c>
-      <c r="K19" s="91" t="n">
+        <v>107190.333333333</v>
+      </c>
+      <c r="K19" s="97" t="n">
         <f aca="false">K15-K18</f>
-        <v>109676.858974359</v>
-      </c>
-      <c r="L19" s="91" t="n">
+        <v>108937.916666667</v>
+      </c>
+      <c r="L19" s="97" t="n">
         <f aca="false">L15-L18</f>
-        <v>111176.858974359</v>
-      </c>
-      <c r="M19" s="91" t="n">
+        <v>110437.916666667</v>
+      </c>
+      <c r="M19" s="97" t="n">
         <f aca="false">M15-M18</f>
-        <v>111176.858974359</v>
-      </c>
-      <c r="N19" s="103" t="n">
+        <v>108937.916666667</v>
+      </c>
+      <c r="N19" s="98" t="n">
         <f aca="false">SUM(B19:M19)</f>
-        <v>1302484</v>
-      </c>
-      <c r="O19" s="93" t="n">
+        <v>1292284</v>
+      </c>
+      <c r="O19" s="99" t="n">
         <f aca="false">IF(N7=0,0,N19/N7)</f>
-        <v>0.382993413314514</v>
+        <v>0.379994119030816</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="104" t="s">
-        <v>145</v>
-      </c>
-      <c r="B20" s="105" t="n">
+      <c r="A20" s="109" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="110" t="n">
         <f aca="false">IF(B19&gt;0,B19*0.21,0)</f>
-        <v>23951.2996153846</v>
-      </c>
-      <c r="C20" s="105" t="n">
+        <v>23801.9775</v>
+      </c>
+      <c r="C20" s="110" t="n">
         <f aca="false">IF(C19&gt;0,C19*0.21,0)</f>
-        <v>23615.2996153846</v>
-      </c>
-      <c r="D20" s="105" t="n">
+        <v>23465.9775</v>
+      </c>
+      <c r="D20" s="110" t="n">
         <f aca="false">IF(D19&gt;0,D19*0.21,0)</f>
-        <v>22943.2996153846</v>
-      </c>
-      <c r="E20" s="105" t="n">
+        <v>22793.9775</v>
+      </c>
+      <c r="E20" s="110" t="n">
         <f aca="false">IF(E19&gt;0,E19*0.21,0)</f>
-        <v>22326.22</v>
-      </c>
-      <c r="F20" s="105" t="n">
+        <v>22173.97</v>
+      </c>
+      <c r="F20" s="110" t="n">
         <f aca="false">IF(F19&gt;0,F19*0.21,0)</f>
-        <v>21990.22</v>
-      </c>
-      <c r="G20" s="105" t="n">
+        <v>21837.97</v>
+      </c>
+      <c r="G20" s="110" t="n">
         <f aca="false">IF(G19&gt;0,G19*0.21,0)</f>
-        <v>21990.22</v>
-      </c>
-      <c r="H20" s="105" t="n">
+        <v>21837.97</v>
+      </c>
+      <c r="H20" s="110" t="n">
         <f aca="false">IF(H19&gt;0,H19*0.21,0)</f>
-        <v>21990.22</v>
-      </c>
-      <c r="I20" s="105" t="n">
+        <v>21837.97</v>
+      </c>
+      <c r="I20" s="110" t="n">
         <f aca="false">IF(I19&gt;0,I19*0.21,0)</f>
-        <v>22326.22</v>
-      </c>
-      <c r="J20" s="105" t="n">
+        <v>22173.97</v>
+      </c>
+      <c r="J20" s="110" t="n">
         <f aca="false">IF(J19&gt;0,J19*0.21,0)</f>
-        <v>22662.22</v>
-      </c>
-      <c r="K20" s="105" t="n">
+        <v>22509.97</v>
+      </c>
+      <c r="K20" s="110" t="n">
         <f aca="false">IF(K19&gt;0,K19*0.21,0)</f>
-        <v>23032.1403846154</v>
-      </c>
-      <c r="L20" s="105" t="n">
+        <v>22876.9625</v>
+      </c>
+      <c r="L20" s="110" t="n">
         <f aca="false">IF(L19&gt;0,L19*0.21,0)</f>
-        <v>23347.1403846154</v>
-      </c>
-      <c r="M20" s="105" t="n">
+        <v>23191.9625</v>
+      </c>
+      <c r="M20" s="110" t="n">
         <f aca="false">IF(M19&gt;0,M19*0.21,0)</f>
-        <v>23347.1403846154</v>
-      </c>
-      <c r="N20" s="87" t="n">
+        <v>22876.9625</v>
+      </c>
+      <c r="N20" s="93" t="n">
         <f aca="false">SUM(B20:M20)</f>
-        <v>273521.64</v>
-      </c>
-      <c r="O20" s="88" t="n">
+        <v>271379.64</v>
+      </c>
+      <c r="O20" s="94" t="n">
         <f aca="false">IF(N7=0,0,N20/N7)</f>
-        <v>0.080428616796048</v>
+        <v>0.0797987649964714</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="72" t="s">
-        <v>146</v>
-      </c>
-      <c r="B21" s="106" t="n">
+      <c r="A21" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="111" t="n">
         <f aca="false">B19-B20</f>
-        <v>90102.5080769231</v>
-      </c>
-      <c r="C21" s="106" t="n">
+        <v>89540.7725</v>
+      </c>
+      <c r="C21" s="111" t="n">
         <f aca="false">C19-C20</f>
-        <v>88838.5080769231</v>
-      </c>
-      <c r="D21" s="106" t="n">
+        <v>88276.7725</v>
+      </c>
+      <c r="D21" s="111" t="n">
         <f aca="false">D19-D20</f>
-        <v>86310.5080769231</v>
-      </c>
-      <c r="E21" s="106" t="n">
+        <v>85748.7725</v>
+      </c>
+      <c r="E21" s="111" t="n">
         <f aca="false">E19-E20</f>
-        <v>83989.1133333333</v>
-      </c>
-      <c r="F21" s="106" t="n">
+        <v>83416.3633333333</v>
+      </c>
+      <c r="F21" s="111" t="n">
         <f aca="false">F19-F20</f>
-        <v>82725.1133333333</v>
-      </c>
-      <c r="G21" s="106" t="n">
+        <v>82152.3633333333</v>
+      </c>
+      <c r="G21" s="111" t="n">
         <f aca="false">G19-G20</f>
-        <v>82725.1133333333</v>
-      </c>
-      <c r="H21" s="106" t="n">
+        <v>82152.3633333333</v>
+      </c>
+      <c r="H21" s="111" t="n">
         <f aca="false">H19-H20</f>
-        <v>82725.1133333333</v>
-      </c>
-      <c r="I21" s="106" t="n">
+        <v>82152.3633333333</v>
+      </c>
+      <c r="I21" s="111" t="n">
         <f aca="false">I19-I20</f>
-        <v>83989.1133333333</v>
-      </c>
-      <c r="J21" s="106" t="n">
+        <v>83416.3633333333</v>
+      </c>
+      <c r="J21" s="111" t="n">
         <f aca="false">J19-J20</f>
-        <v>85253.1133333333</v>
-      </c>
-      <c r="K21" s="106" t="n">
+        <v>84680.3633333333</v>
+      </c>
+      <c r="K21" s="111" t="n">
         <f aca="false">K19-K20</f>
-        <v>86644.7185897436</v>
-      </c>
-      <c r="L21" s="106" t="n">
+        <v>86060.9541666667</v>
+      </c>
+      <c r="L21" s="111" t="n">
         <f aca="false">L19-L20</f>
-        <v>87829.7185897436</v>
-      </c>
-      <c r="M21" s="106" t="n">
+        <v>87245.9541666667</v>
+      </c>
+      <c r="M21" s="111" t="n">
         <f aca="false">M19-M20</f>
-        <v>87829.7185897436</v>
-      </c>
-      <c r="N21" s="103" t="n">
+        <v>86060.9541666667</v>
+      </c>
+      <c r="N21" s="98" t="n">
         <f aca="false">SUM(B21:M21)</f>
-        <v>1028962.36</v>
-      </c>
-      <c r="O21" s="93" t="n">
+        <v>1020904.36</v>
+      </c>
+      <c r="O21" s="99" t="n">
         <f aca="false">IF(N21=0,0,N21/N7)</f>
-        <v>0.302564796518466</v>
+        <v>0.300195354034345</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -10155,26 +10454,26 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="107" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
+      <c r="B2" s="112" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10202,85 +10501,85 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="108" t="s">
-        <v>148</v>
+      <c r="B2" s="113" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="109"/>
+      <c r="B3" s="114"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="110" t="s">
-        <v>149</v>
+      <c r="B4" s="115" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="109"/>
+      <c r="B5" s="114"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="111" t="s">
-        <v>150</v>
+      <c r="B6" s="116" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="109" t="s">
-        <v>151</v>
+      <c r="B7" s="114" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="109" t="s">
-        <v>152</v>
+      <c r="B8" s="114" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="109" t="s">
-        <v>153</v>
+      <c r="B9" s="114" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="109"/>
+      <c r="B10" s="114"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="111" t="s">
-        <v>154</v>
+      <c r="B11" s="116" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="109" t="s">
-        <v>155</v>
+      <c r="B12" s="114" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="109" t="s">
-        <v>156</v>
+      <c r="B13" s="114" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="109" t="s">
-        <v>157</v>
+      <c r="B14" s="114" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="109"/>
+      <c r="B15" s="114"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="111" t="s">
-        <v>158</v>
+      <c r="B16" s="116" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="109" t="s">
-        <v>159</v>
+      <c r="B17" s="114" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="109" t="s">
-        <v>160</v>
+      <c r="B18" s="114" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="109" t="s">
-        <v>161</v>
+      <c r="B19" s="114" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -10299,7 +10598,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F28"/>
+  <dimension ref="A2:F46"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="28"/>
@@ -10308,243 +10607,389 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="112" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
+      <c r="B2" s="117" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="113" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="113" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" s="113" t="s">
+      <c r="B3" s="118" t="s">
         <v>165</v>
       </c>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" s="118" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="114" t="s">
-        <v>166</v>
+      <c r="B4" s="119" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="115" t="s">
-        <v>167</v>
+      <c r="B5" s="120" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" s="120" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="116" t="s">
-        <v>168</v>
-      </c>
-      <c r="D6" s="117" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" s="118" t="s">
-        <v>170</v>
+      <c r="B6" s="120" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="121" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" s="122" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="116" t="s">
-        <v>171</v>
-      </c>
-      <c r="D7" s="117" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="118" t="s">
-        <v>173</v>
+      <c r="B7" s="120" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="121" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" s="122" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="116" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="117" t="s">
-        <v>175</v>
-      </c>
-      <c r="E8" s="118" t="s">
-        <v>176</v>
+      <c r="B8" s="120" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="121" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="122" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="116" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="117" t="s">
-        <v>178</v>
-      </c>
-      <c r="E9" s="118" t="s">
-        <v>179</v>
+      <c r="B9" s="120" t="s">
+        <v>181</v>
+      </c>
+      <c r="D9" s="121" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="122" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="116" t="s">
-        <v>180</v>
-      </c>
-      <c r="D10" s="117" t="s">
-        <v>181</v>
-      </c>
-      <c r="E10" s="118" t="s">
-        <v>182</v>
+      <c r="B10" s="120" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="121" t="s">
+        <v>185</v>
+      </c>
+      <c r="E10" s="122" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="116" t="s">
-        <v>183</v>
-      </c>
-      <c r="D11" s="117" t="s">
-        <v>184</v>
-      </c>
-      <c r="E11" s="118" t="s">
-        <v>185</v>
+      <c r="B11" s="120" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="121" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="122" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="116" t="s">
-        <v>186</v>
-      </c>
-      <c r="D12" s="117" t="s">
-        <v>187</v>
-      </c>
-      <c r="E12" s="118" t="s">
-        <v>188</v>
+      <c r="B12" s="120" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="121" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="122" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="116"/>
+      <c r="B13" s="120"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="114" t="s">
-        <v>189</v>
+      <c r="B14" s="119" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="116" t="s">
-        <v>190</v>
-      </c>
-      <c r="D15" s="117" t="s">
-        <v>191</v>
-      </c>
-      <c r="E15" s="118" t="s">
-        <v>192</v>
+      <c r="B15" s="120" t="s">
+        <v>194</v>
+      </c>
+      <c r="D15" s="121" t="s">
+        <v>195</v>
+      </c>
+      <c r="E15" s="122" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="116" t="s">
-        <v>193</v>
-      </c>
-      <c r="D16" s="117" t="s">
-        <v>194</v>
-      </c>
-      <c r="E16" s="118" t="s">
-        <v>195</v>
+      <c r="B16" s="120" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>198</v>
+      </c>
+      <c r="E16" s="122" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="116" t="s">
-        <v>196</v>
-      </c>
-      <c r="D17" s="117" t="s">
-        <v>197</v>
-      </c>
-      <c r="E17" s="118" t="s">
-        <v>198</v>
-      </c>
+      <c r="B17" s="120"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="122"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="116" t="s">
-        <v>199</v>
-      </c>
-      <c r="D18" s="117" t="s">
+      <c r="B18" s="123" t="s">
         <v>200</v>
       </c>
-      <c r="E18" s="118" t="s">
+      <c r="C18" s="123"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="123"/>
+    </row>
+    <row r="19" customFormat="false" ht="22.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="120" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="116"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="114" t="s">
+      <c r="D19" s="124" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="116" t="s">
+      <c r="E19" s="125" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="117" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="120" t="s">
         <v>204</v>
       </c>
-      <c r="E21" s="118" t="s">
+      <c r="D20" s="124" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="116" t="s">
+      <c r="E20" s="125" t="s">
         <v>206</v>
       </c>
-      <c r="D22" s="117" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="22.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="120" t="s">
         <v>207</v>
       </c>
-      <c r="E22" s="118" t="s">
+      <c r="D21" s="126" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="116" t="s">
+      <c r="E21" s="125" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="117" t="s">
-        <v>204</v>
-      </c>
-      <c r="E23" s="118" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="22.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="120" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="116"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="114" t="s">
+      <c r="D22" s="124" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="116" t="s">
+      <c r="E22" s="125" t="s">
         <v>212</v>
       </c>
-      <c r="D26" s="117" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="120" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="118" t="s">
+      <c r="D23" s="124" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="116" t="s">
+      <c r="E23" s="125" t="s">
         <v>215</v>
       </c>
-      <c r="D27" s="117" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="120" t="s">
         <v>216</v>
       </c>
+      <c r="D24" s="126" t="s">
+        <v>217</v>
+      </c>
+      <c r="E24" s="125" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="22.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="120" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" s="127" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="125" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="120" t="s">
+        <v>222</v>
+      </c>
+      <c r="D26" s="127" t="s">
+        <v>223</v>
+      </c>
+      <c r="E26" s="125" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="120" t="s">
+        <v>225</v>
+      </c>
+      <c r="D27" s="127" t="s">
+        <v>226</v>
+      </c>
+      <c r="E27" s="125" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="116" t="s">
-        <v>217</v>
-      </c>
-      <c r="D28" s="117" t="s">
-        <v>218</v>
-      </c>
+      <c r="B28" s="120"/>
+      <c r="D28" s="0"/>
+      <c r="E28" s="128"/>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="120"/>
+      <c r="D29" s="121"/>
+      <c r="E29" s="122"/>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="120"/>
+      <c r="D30" s="121"/>
+      <c r="E30" s="122"/>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="120"/>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="119" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="120" t="s">
+        <v>229</v>
+      </c>
+      <c r="D33" s="121" t="s">
+        <v>230</v>
+      </c>
+      <c r="E33" s="129" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="120" t="s">
+        <v>232</v>
+      </c>
+      <c r="D34" s="121" t="s">
+        <v>233</v>
+      </c>
+      <c r="E34" s="129" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="120" t="s">
+        <v>235</v>
+      </c>
+      <c r="D35" s="121" t="s">
+        <v>230</v>
+      </c>
+      <c r="E35" s="129" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="130" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" s="121" t="s">
+        <v>238</v>
+      </c>
+      <c r="E36" s="129" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="120"/>
+      <c r="C37" s="131"/>
+      <c r="E37" s="129"/>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="119" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="120" t="s">
+        <v>241</v>
+      </c>
+      <c r="D39" s="121" t="s">
+        <v>242</v>
+      </c>
+      <c r="E39" s="122" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="120" t="s">
+        <v>244</v>
+      </c>
+      <c r="D40" s="121" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="120" t="s">
+        <v>246</v>
+      </c>
+      <c r="D41" s="121" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="130" t="s">
+        <v>248</v>
+      </c>
+      <c r="B45" s="132" t="s">
+        <v>249</v>
+      </c>
+      <c r="C45" s="129"/>
+      <c r="D45" s="0"/>
+    </row>
+    <row r="46" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="133" t="s">
+        <v>250</v>
+      </c>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
+      <c r="D46" s="133"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A46:D46"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/Analysis/Consultora_NovaTech_1.xlsx
+++ b/Analysis/Consultora_NovaTech_1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="257">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">AVG Rate</t>
   </si>
   <si>
-    <t xml:space="preserve">ASSUMPTION — €4,000/month derived from: €1,671,600 ÷ 42 HC ÷ 12 = €3,317. Rounded up to reflect blended rate incl. MS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSUMPTION — €4,300/month. €1,910,400 ÷ 47 ÷ 12 = €3,388. Rate increase reflects mix improvement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSUMPTION — €4,600/month. €2,109,400 ÷ 52 ÷ 12 = €3,380. </t>
+    <t xml:space="preserve">ASSUMPTION — €4,000/month derived from: €1,680,000 ÷ 42 HC ÷ 12 = €3,333. Rounded up to reflect blended rate incl. MS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — €4,300/month. €1,9210,00 ÷ 47 ÷ 12 = €3,404. Rate increase reflects mix improvement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — €4,600/month. €2,12,4000 ÷ 52 ÷ 12 = €3,390</t>
   </si>
   <si>
     <t xml:space="preserve">MANAGED SERVICES REVENUE (flat — recurring contracts)</t>
@@ -299,6 +299,24 @@
     <t xml:space="preserve">DERIVED from RawData </t>
   </si>
   <si>
+    <t xml:space="preserve">Opretional Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Operational Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Other Costs</t>
+  </si>
+  <si>
     <t xml:space="preserve">NovaTech Consulting Lda. — Variance Analysis:Budget 2025 vs Actuals</t>
   </si>
   <si>
@@ -695,7 +713,7 @@
     <t xml:space="preserve">Personnel % of Revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">65.0% (exact)</t>
+    <t xml:space="preserve">65.0%</t>
   </si>
   <si>
     <t xml:space="preserve">DERIVED — consistent across 2022–2024. Confirmed from RawData: 1,365K/2,100K = 65.0%.</t>
@@ -704,7 +722,7 @@
     <t xml:space="preserve">Operations % of Revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0% (exact)</t>
+    <t xml:space="preserve">8.0% </t>
   </si>
   <si>
     <t xml:space="preserve">DERIVED — consistent across 2022–2024. Confirmed from RawData.</t>
@@ -713,7 +731,7 @@
     <t xml:space="preserve">Other % of Revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0% (exact)</t>
+    <t xml:space="preserve">4.0%</t>
   </si>
   <si>
     <t xml:space="preserve">DERIVED — consistent across 2022–2024.</t>
@@ -794,17 +812,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="#,##0\ [$€-816];[RED]\-#,##0\ [$€-816]"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="[$-409]#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="171" formatCode="[$-409]0.00%"/>
-    <numFmt numFmtId="172" formatCode="0.00%"/>
-    <numFmt numFmtId="173" formatCode="#,##0\ [$€-816];[RED]\-#,##0\ [$€-816]"/>
+    <numFmt numFmtId="170" formatCode="0.00%"/>
+    <numFmt numFmtId="171" formatCode="[$-409]#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="172" formatCode="[$-409]0.00%"/>
   </numFmts>
   <fonts count="54">
     <font>
@@ -1368,7 +1385,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="133">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1405,7 +1422,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1485,10 +1502,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1613,6 +1626,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="26" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1649,62 +1666,62 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1721,7 +1738,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1737,11 +1754,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="24" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="24" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1749,7 +1766,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="40" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="40" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1757,15 +1774,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="42" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="42" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1777,11 +1794,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="40" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="40" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="33" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="33" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1793,11 +1810,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1809,11 +1826,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="44" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="44" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="45" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="45" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1861,47 +1878,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="53" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2376,11 +2389,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="11582679"/>
-        <c:axId val="98835816"/>
+        <c:axId val="33542505"/>
+        <c:axId val="31575947"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="11582679"/>
+        <c:axId val="33542505"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2445,7 +2458,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98835816"/>
+        <c:crossAx val="31575947"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2453,7 +2466,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="98835816"/>
+        <c:axId val="31575947"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2527,7 +2540,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11582679"/>
+        <c:crossAx val="33542505"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2794,11 +2807,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="95420276"/>
-        <c:axId val="48602742"/>
+        <c:axId val="54471546"/>
+        <c:axId val="18017738"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="95420276"/>
+        <c:axId val="54471546"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2863,7 +2876,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48602742"/>
+        <c:crossAx val="18017738"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2871,7 +2884,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48602742"/>
+        <c:axId val="18017738"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2945,7 +2958,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95420276"/>
+        <c:crossAx val="54471546"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3347,11 +3360,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="42569786"/>
-        <c:axId val="30740875"/>
+        <c:axId val="91170835"/>
+        <c:axId val="77304492"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="42569786"/>
+        <c:axId val="91170835"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3416,7 +3429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30740875"/>
+        <c:crossAx val="77304492"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3424,7 +3437,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30740875"/>
+        <c:axId val="77304492"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3498,7 +3511,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42569786"/>
+        <c:crossAx val="91170835"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3595,10 +3608,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.160891938250429"/>
-          <c:y val="0.167056431113371"/>
-          <c:w val="0.688164665523156"/>
-          <c:h val="0.539298423995933"/>
+          <c:x val="0.160901137858082"/>
+          <c:y val="0.167073418751271"/>
+          <c:w val="0.688146835153525"/>
+          <c:h val="0.539251576164328"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -3779,11 +3792,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="1773179"/>
-        <c:axId val="69359211"/>
+        <c:axId val="49608079"/>
+        <c:axId val="11615296"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1773179"/>
+        <c:axId val="49608079"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3848,7 +3861,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69359211"/>
+        <c:crossAx val="11615296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3856,7 +3869,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69359211"/>
+        <c:axId val="11615296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3930,7 +3943,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1773179"/>
+        <c:crossAx val="49608079"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4865,7 +4878,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>373320</xdr:colOff>
+      <xdr:colOff>372960</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>133200</xdr:rowOff>
     </xdr:to>
@@ -4875,8 +4888,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3703680" y="6136920"/>
-        <a:ext cx="6208560" cy="3495960"/>
+        <a:off x="3703680" y="6012000"/>
+        <a:ext cx="6208200" cy="3495600"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4895,9 +4908,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2455560</xdr:colOff>
+      <xdr:colOff>2455200</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>122400</xdr:rowOff>
+      <xdr:rowOff>122040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4905,8 +4918,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10926000" y="5860080"/>
-        <a:ext cx="5756040" cy="3236040"/>
+        <a:off x="10926000" y="5735160"/>
+        <a:ext cx="5755680" cy="3235680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4925,9 +4938,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>418680</xdr:colOff>
+      <xdr:colOff>418320</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>48240</xdr:rowOff>
+      <xdr:rowOff>47520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4935,8 +4948,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4200120" y="9815400"/>
-        <a:ext cx="5757480" cy="3237480"/>
+        <a:off x="4200120" y="9690120"/>
+        <a:ext cx="5757120" cy="3237120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4951,13 +4964,13 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>190800</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>7200</xdr:rowOff>
+      <xdr:rowOff>7560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2612160</xdr:colOff>
+      <xdr:colOff>2611800</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>42480</xdr:rowOff>
+      <xdr:rowOff>42120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4965,8 +4978,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="21579000">
-        <a:off x="10542240" y="9682200"/>
-        <a:ext cx="6296040" cy="3540240"/>
+        <a:off x="10542240" y="9556920"/>
+        <a:ext cx="6295680" cy="3539880"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6856,18 +6869,18 @@
       <c r="D10" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="19" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
@@ -6997,81 +7010,81 @@
       <c r="E23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="30" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="31" t="n">
         <v>2022</v>
       </c>
-      <c r="B25" s="33" t="n">
+      <c r="B25" s="32" t="n">
         <f aca="false">B6</f>
         <v>2100000</v>
       </c>
-      <c r="C25" s="33" t="n">
+      <c r="C25" s="32" t="n">
         <f aca="false">SUM(RawData!F2:H13)</f>
         <v>1617000</v>
       </c>
-      <c r="D25" s="34" t="n">
+      <c r="D25" s="33" t="n">
         <f aca="false">B25-C25</f>
         <v>483000</v>
       </c>
-      <c r="E25" s="35" t="n">
+      <c r="E25" s="34" t="n">
         <f aca="false">D25/B25</f>
         <v>0.23</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="36" t="n">
+      <c r="A26" s="35" t="n">
         <v>2023</v>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="36" t="n">
         <f aca="false">B10</f>
         <v>2400000</v>
       </c>
-      <c r="C26" s="33" t="n">
+      <c r="C26" s="32" t="n">
         <f aca="false">SUM(RawData!F14:H25)</f>
         <v>1848000</v>
       </c>
-      <c r="D26" s="34" t="n">
+      <c r="D26" s="33" t="n">
         <f aca="false">B26-C26</f>
         <v>552000</v>
       </c>
-      <c r="E26" s="35" t="n">
+      <c r="E26" s="34" t="n">
         <f aca="false">D26/B26</f>
         <v>0.23</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="31" t="n">
         <v>2024</v>
       </c>
-      <c r="B27" s="33" t="n">
+      <c r="B27" s="32" t="n">
         <f aca="false">B20</f>
         <v>2650000</v>
       </c>
-      <c r="C27" s="33" t="n">
+      <c r="C27" s="32" t="n">
         <f aca="false">SUM(RawData!F26:H37)</f>
         <v>2040500</v>
       </c>
-      <c r="D27" s="34" t="n">
+      <c r="D27" s="33" t="n">
         <f aca="false">B27-C27</f>
         <v>609500</v>
       </c>
-      <c r="E27" s="35" t="n">
+      <c r="E27" s="34" t="n">
         <f aca="false">D27/B27</f>
         <v>0.23</v>
       </c>
@@ -7100,263 +7113,264 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="2" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="42" t="s">
+      <c r="K5" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="42" t="s">
+      <c r="L5" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="42" t="s">
+      <c r="M5" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="41" t="s">
+      <c r="N5" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="O5" s="43" t="s">
+      <c r="O5" s="42" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="n">
+      <c r="A6" s="43" t="n">
         <v>2022</v>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="44" t="n">
         <v>41</v>
       </c>
-      <c r="C6" s="45" t="n">
+      <c r="C6" s="44" t="n">
         <v>41</v>
       </c>
-      <c r="D6" s="45" t="n">
+      <c r="D6" s="44" t="n">
         <v>41</v>
       </c>
-      <c r="E6" s="45" t="n">
+      <c r="E6" s="44" t="n">
         <v>42</v>
       </c>
-      <c r="F6" s="45" t="n">
+      <c r="F6" s="44" t="n">
         <v>42</v>
       </c>
-      <c r="G6" s="45" t="n">
+      <c r="G6" s="44" t="n">
         <v>42</v>
       </c>
-      <c r="H6" s="45" t="n">
+      <c r="H6" s="44" t="n">
         <v>42</v>
       </c>
-      <c r="I6" s="45" t="n">
+      <c r="I6" s="44" t="n">
         <v>42</v>
       </c>
-      <c r="J6" s="45" t="n">
+      <c r="J6" s="44" t="n">
         <v>42</v>
       </c>
-      <c r="K6" s="45" t="n">
+      <c r="K6" s="44" t="n">
         <v>43</v>
       </c>
-      <c r="L6" s="45" t="n">
+      <c r="L6" s="44" t="n">
         <v>43</v>
       </c>
-      <c r="M6" s="45" t="n">
+      <c r="M6" s="44" t="n">
         <v>43</v>
       </c>
-      <c r="N6" s="46" t="n">
+      <c r="N6" s="45" t="n">
         <f aca="false">AVERAGE(B6:M6)</f>
         <v>42</v>
       </c>
-      <c r="O6" s="47" t="s">
+      <c r="O6" s="46" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="n">
+      <c r="A7" s="43" t="n">
         <v>2023</v>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="44" t="n">
         <v>46</v>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="44" t="n">
         <v>46</v>
       </c>
-      <c r="D7" s="45" t="n">
+      <c r="D7" s="44" t="n">
         <v>46</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="44" t="n">
         <v>46</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F7" s="44" t="n">
         <v>47</v>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G7" s="44" t="n">
         <v>47</v>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="44" t="n">
         <v>47</v>
       </c>
-      <c r="I7" s="45" t="n">
+      <c r="I7" s="44" t="n">
         <v>47</v>
       </c>
-      <c r="J7" s="45" t="n">
+      <c r="J7" s="44" t="n">
         <v>48</v>
       </c>
-      <c r="K7" s="45" t="n">
+      <c r="K7" s="44" t="n">
         <v>48</v>
       </c>
-      <c r="L7" s="45" t="n">
+      <c r="L7" s="44" t="n">
         <v>48</v>
       </c>
-      <c r="M7" s="45" t="n">
+      <c r="M7" s="44" t="n">
         <v>48</v>
       </c>
-      <c r="N7" s="46" t="n">
+      <c r="N7" s="45" t="n">
         <f aca="false">AVERAGE(B7:M7)</f>
         <v>47</v>
       </c>
-      <c r="O7" s="47" t="s">
+      <c r="O7" s="46" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="n">
+      <c r="A8" s="43" t="n">
         <v>2024</v>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="44" t="n">
         <v>51</v>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="44" t="n">
         <v>51</v>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D8" s="44" t="n">
         <v>51</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="44" t="n">
         <v>52</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="44" t="n">
         <v>52</v>
       </c>
-      <c r="G8" s="45" t="n">
+      <c r="G8" s="44" t="n">
         <v>52</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="44" t="n">
         <v>52</v>
       </c>
-      <c r="I8" s="45" t="n">
+      <c r="I8" s="44" t="n">
         <v>52</v>
       </c>
-      <c r="J8" s="45" t="n">
+      <c r="J8" s="44" t="n">
         <v>52</v>
       </c>
-      <c r="K8" s="45" t="n">
+      <c r="K8" s="44" t="n">
         <v>53</v>
       </c>
-      <c r="L8" s="45" t="n">
+      <c r="L8" s="44" t="n">
         <v>53</v>
       </c>
-      <c r="M8" s="45" t="n">
+      <c r="M8" s="44" t="n">
         <v>53</v>
       </c>
-      <c r="N8" s="46" t="n">
+      <c r="N8" s="45" t="n">
         <f aca="false">AVERAGE(B8:M8)</f>
         <v>52</v>
       </c>
-      <c r="O8" s="47" t="s">
+      <c r="O8" s="46" t="s">
         <v>71</v>
       </c>
     </row>
@@ -7378,212 +7392,212 @@
       <c r="O9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
       <c r="O10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="49" t="s">
+      <c r="D11" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="49" t="s">
+      <c r="E11" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="49" t="s">
+      <c r="G11" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="49" t="s">
+      <c r="H11" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="49" t="s">
+      <c r="I11" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="49" t="s">
+      <c r="J11" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="49" t="s">
+      <c r="K11" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="L11" s="49" t="s">
+      <c r="L11" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="49" t="s">
+      <c r="M11" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="N11" s="49" t="s">
+      <c r="N11" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="O11" s="50" t="s">
+      <c r="O11" s="49" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="n">
+      <c r="A12" s="43" t="n">
         <v>2022</v>
       </c>
-      <c r="B12" s="51" t="n">
+      <c r="B12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="C12" s="51" t="n">
+      <c r="C12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="D12" s="51" t="n">
+      <c r="D12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="E12" s="51" t="n">
+      <c r="E12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="F12" s="51" t="n">
+      <c r="F12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="G12" s="51" t="n">
+      <c r="G12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="H12" s="51" t="n">
+      <c r="H12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="I12" s="51" t="n">
+      <c r="I12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="J12" s="51" t="n">
+      <c r="J12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="K12" s="51" t="n">
+      <c r="K12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="L12" s="51" t="n">
+      <c r="L12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="M12" s="51" t="n">
+      <c r="M12" s="50" t="n">
         <v>4000</v>
       </c>
-      <c r="N12" s="52" t="n">
+      <c r="N12" s="51" t="n">
         <f aca="false">AVERAGE(B12:M12)</f>
         <v>4000</v>
       </c>
-      <c r="O12" s="47" t="s">
+      <c r="O12" s="46" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44" t="n">
+      <c r="A13" s="43" t="n">
         <v>2023</v>
       </c>
-      <c r="B13" s="51" t="n">
+      <c r="B13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="C13" s="51" t="n">
+      <c r="C13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="D13" s="51" t="n">
+      <c r="D13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="E13" s="51" t="n">
+      <c r="E13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="F13" s="51" t="n">
+      <c r="F13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="G13" s="51" t="n">
+      <c r="G13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="H13" s="51" t="n">
+      <c r="H13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="I13" s="51" t="n">
+      <c r="I13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="J13" s="51" t="n">
+      <c r="J13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="K13" s="51" t="n">
+      <c r="K13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="L13" s="51" t="n">
+      <c r="L13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="M13" s="51" t="n">
+      <c r="M13" s="50" t="n">
         <v>4300</v>
       </c>
-      <c r="N13" s="52" t="n">
+      <c r="N13" s="51" t="n">
         <f aca="false">AVERAGE(B13:M13)</f>
         <v>4300</v>
       </c>
-      <c r="O13" s="47" t="s">
+      <c r="O13" s="46" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="44" t="n">
+      <c r="A14" s="43" t="n">
         <v>2024</v>
       </c>
-      <c r="B14" s="51" t="n">
+      <c r="B14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="C14" s="51" t="n">
+      <c r="C14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="D14" s="51" t="n">
+      <c r="D14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="E14" s="51" t="n">
+      <c r="E14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="F14" s="51" t="n">
+      <c r="F14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="G14" s="51" t="n">
+      <c r="G14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="H14" s="51" t="n">
+      <c r="H14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="I14" s="51" t="n">
+      <c r="I14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="J14" s="51" t="n">
+      <c r="J14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="K14" s="51" t="n">
+      <c r="K14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="L14" s="51" t="n">
+      <c r="L14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="M14" s="51" t="n">
+      <c r="M14" s="50" t="n">
         <v>4600</v>
       </c>
-      <c r="N14" s="52" t="n">
+      <c r="N14" s="51" t="n">
         <f aca="false">AVERAGE(B14:M14)</f>
         <v>4600</v>
       </c>
-      <c r="O14" s="47" t="s">
+      <c r="O14" s="46" t="s">
         <v>76</v>
       </c>
     </row>
@@ -7605,165 +7619,165 @@
       <c r="O15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
+      <c r="N16" s="47"/>
       <c r="O16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="44" t="n">
+      <c r="A17" s="43" t="n">
         <v>2022</v>
       </c>
-      <c r="B17" s="51" t="n">
+      <c r="B17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="C17" s="51" t="n">
+      <c r="C17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="D17" s="51" t="n">
+      <c r="D17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="E17" s="51" t="n">
+      <c r="E17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="F17" s="51" t="n">
+      <c r="F17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="G17" s="51" t="n">
+      <c r="G17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="H17" s="51" t="n">
+      <c r="H17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="I17" s="51" t="n">
+      <c r="I17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="J17" s="51" t="n">
+      <c r="J17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="K17" s="51" t="n">
+      <c r="K17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="L17" s="51" t="n">
+      <c r="L17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="M17" s="51" t="n">
+      <c r="M17" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="N17" s="52" t="n">
+      <c r="N17" s="51" t="n">
         <f aca="false">SUM(B17:M17)</f>
         <v>420000</v>
       </c>
-      <c r="O17" s="53" t="s">
+      <c r="O17" s="52" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="44" t="n">
+      <c r="A18" s="43" t="n">
         <v>2023</v>
       </c>
-      <c r="B18" s="51" t="n">
+      <c r="B18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="C18" s="51" t="n">
+      <c r="C18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="D18" s="51" t="n">
+      <c r="D18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="E18" s="51" t="n">
+      <c r="E18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="F18" s="51" t="n">
+      <c r="F18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="G18" s="51" t="n">
+      <c r="G18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="H18" s="51" t="n">
+      <c r="H18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="I18" s="51" t="n">
+      <c r="I18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="J18" s="51" t="n">
+      <c r="J18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="K18" s="51" t="n">
+      <c r="K18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="L18" s="51" t="n">
+      <c r="L18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="M18" s="51" t="n">
+      <c r="M18" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="N18" s="52" t="n">
+      <c r="N18" s="51" t="n">
         <f aca="false">SUM(B18:M18)</f>
         <v>480000</v>
       </c>
-      <c r="O18" s="53" t="s">
+      <c r="O18" s="52" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="44" t="n">
+      <c r="A19" s="43" t="n">
         <v>2024</v>
       </c>
-      <c r="B19" s="51" t="n">
+      <c r="B19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="C19" s="51" t="n">
+      <c r="C19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="D19" s="51" t="n">
+      <c r="D19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="E19" s="51" t="n">
+      <c r="E19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="F19" s="51" t="n">
+      <c r="F19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="G19" s="51" t="n">
+      <c r="G19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="H19" s="51" t="n">
+      <c r="H19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="I19" s="51" t="n">
+      <c r="I19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="J19" s="51" t="n">
+      <c r="J19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="K19" s="51" t="n">
+      <c r="K19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="L19" s="51" t="n">
+      <c r="L19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="M19" s="51" t="n">
+      <c r="M19" s="50" t="n">
         <v>44200</v>
       </c>
-      <c r="N19" s="52" t="n">
+      <c r="N19" s="51" t="n">
         <f aca="false">SUM(B19:M19)</f>
         <v>530400</v>
       </c>
-      <c r="O19" s="53" t="s">
+      <c r="O19" s="52" t="s">
         <v>80</v>
       </c>
     </row>
@@ -7785,14 +7799,14 @@
       <c r="O20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="54" t="s">
+      <c r="A21" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
@@ -7804,22 +7818,22 @@
       <c r="O21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="31.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="C22" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="55" t="s">
+      <c r="D22" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="55" t="s">
+      <c r="E22" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="55" t="s">
+      <c r="F22" s="54" t="s">
         <v>86</v>
       </c>
       <c r="G22" s="10"/>
@@ -7833,26 +7847,26 @@
       <c r="O22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="56" t="n">
+      <c r="A23" s="55" t="n">
         <v>2022</v>
       </c>
-      <c r="B23" s="57" t="n">
+      <c r="B23" s="56" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2022",RawData!F:F)</f>
         <v>1365000</v>
       </c>
-      <c r="C23" s="58" t="n">
+      <c r="C23" s="57" t="n">
         <f aca="false">N6</f>
         <v>42</v>
       </c>
-      <c r="D23" s="59" t="n">
+      <c r="D23" s="58" t="n">
         <f aca="false">B23/C23</f>
         <v>32500</v>
       </c>
-      <c r="E23" s="59" t="n">
+      <c r="E23" s="58" t="n">
         <f aca="false">D23/12</f>
         <v>2708.33333333333</v>
       </c>
-      <c r="F23" s="60" t="s">
+      <c r="F23" s="59" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="10"/>
@@ -7866,26 +7880,26 @@
       <c r="O23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="56" t="n">
+      <c r="A24" s="55" t="n">
         <v>2023</v>
       </c>
-      <c r="B24" s="57" t="n">
+      <c r="B24" s="56" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2023",RawData!F:F)</f>
         <v>1560000</v>
       </c>
-      <c r="C24" s="58" t="n">
+      <c r="C24" s="57" t="n">
         <f aca="false">N7</f>
         <v>47</v>
       </c>
-      <c r="D24" s="59" t="n">
+      <c r="D24" s="58" t="n">
         <f aca="false">B24/C24</f>
         <v>33191.4893617021</v>
       </c>
-      <c r="E24" s="59" t="n">
+      <c r="E24" s="58" t="n">
         <f aca="false">D24/12</f>
         <v>2765.95744680851</v>
       </c>
-      <c r="F24" s="60" t="s">
+      <c r="F24" s="59" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="10"/>
@@ -7899,26 +7913,26 @@
       <c r="O24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="56" t="n">
+      <c r="A25" s="55" t="n">
         <v>2024</v>
       </c>
-      <c r="B25" s="57" t="n">
+      <c r="B25" s="56" t="n">
         <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!F:F)</f>
         <v>1722500</v>
       </c>
-      <c r="C25" s="58" t="n">
+      <c r="C25" s="57" t="n">
         <f aca="false">N8</f>
         <v>52</v>
       </c>
-      <c r="D25" s="59" t="n">
+      <c r="D25" s="58" t="n">
         <f aca="false">B25/C25</f>
         <v>33125</v>
       </c>
-      <c r="E25" s="59" t="n">
+      <c r="E25" s="58" t="n">
         <f aca="false">D25/12</f>
         <v>2760.41666666667</v>
       </c>
-      <c r="F25" s="60" t="s">
+      <c r="F25" s="59" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="10"/>
@@ -7931,14 +7945,203 @@
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
     </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+    </row>
+    <row r="28" customFormat="false" ht="32.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="0"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="55" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2022",RawData!G:G)</f>
+        <v>168000</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2022",RawData!D1:D37)+SUMIF(RawData!A:A,"=2022",RawData!E1:E37)</f>
+        <v>2100000</v>
+      </c>
+      <c r="D29" s="60" t="n">
+        <f aca="false">B29/C29</f>
+        <v>0.08</v>
+      </c>
+      <c r="E29" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="59"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="55" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2023",RawData!G:G)</f>
+        <v>192000</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2023",RawData!D1:D37)+SUMIF(RawData!A:A,"=2023",RawData!E1:E37)</f>
+        <v>2400000</v>
+      </c>
+      <c r="D30" s="60" t="n">
+        <f aca="false">B30/C30</f>
+        <v>0.08</v>
+      </c>
+      <c r="E30" s="59" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="55" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!G:G)</f>
+        <v>212000</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!D1:D37)+SUMIF(RawData!A:A,"=2024",RawData!E1:E37)</f>
+        <v>2650000</v>
+      </c>
+      <c r="D31" s="60" t="n">
+        <f aca="false">B31/C31</f>
+        <v>0.08</v>
+      </c>
+      <c r="E31" s="59" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+    </row>
+    <row r="34" customFormat="false" ht="32.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="0"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="55" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2022",RawData!H:H)</f>
+        <v>84000</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2022",RawData!D1:D437)+SUMIF(RawData!A:A,"=2022",RawData!E1:E37)</f>
+        <v>2100000</v>
+      </c>
+      <c r="D35" s="60" t="n">
+        <f aca="false">B35/C35</f>
+        <v>0.04</v>
+      </c>
+      <c r="E35" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="59"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="55" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2023",RawData!H:H)</f>
+        <v>96000</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2023",RawData!D1:D37)+SUMIF(RawData!A:A,"=2023",RawData!E1:E437)</f>
+        <v>2400000</v>
+      </c>
+      <c r="D36" s="60" t="n">
+        <f aca="false">B36/C36</f>
+        <v>0.04</v>
+      </c>
+      <c r="E36" s="59" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="55" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!H:H)</f>
+        <v>106000</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!D1:D437)+SUMIF(RawData!A:A,"=2024",RawData!E1:E37)</f>
+        <v>2650000</v>
+      </c>
+      <c r="D37" s="60" t="n">
+        <f aca="false">B37/C37</f>
+        <v>0.04</v>
+      </c>
+      <c r="E37" s="59" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A10:N10"/>
     <mergeCell ref="A16:N16"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A33:F33"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -7967,7 +8170,7 @@
   <sheetData>
     <row r="1" s="63" customFormat="true" ht="27.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="61" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -7987,18 +8190,18 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" s="65" customFormat="true" ht="21.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="65" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B4" s="65" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D4" s="65" t="s">
         <v>15</v>
@@ -8007,7 +8210,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="65" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G4" s="65" t="s">
         <v>18</v>
@@ -8031,16 +8234,16 @@
         <v>24</v>
       </c>
       <c r="N4" s="65" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="O4" s="65" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="P4" s="65" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="Q4" s="65" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8071,9 +8274,9 @@
       <c r="W5" s="68"/>
       <c r="X5" s="68"/>
     </row>
-    <row r="6" customFormat="false" ht="46.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="69" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B6" s="70" t="n">
         <f aca="false">RawData!D26-RawData!I26</f>
@@ -8136,12 +8339,12 @@
         <v>-0.0862068965517241</v>
       </c>
       <c r="Q6" s="72" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="69" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B7" s="70" t="n">
         <f aca="false">RawData!E26-RawData!J26</f>
@@ -8204,12 +8407,12 @@
         <v>-0.0862068965517241</v>
       </c>
       <c r="Q7" s="72" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="66" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B8" s="73" t="n">
         <f aca="false">B6+B7</f>
@@ -8272,7 +8475,7 @@
         <v>-0.0862068965517241</v>
       </c>
       <c r="Q8" s="72" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" s="68" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8303,7 +8506,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="66" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B11" s="67"/>
       <c r="C11" s="67"/>
@@ -8329,9 +8532,9 @@
       <c r="W11" s="68"/>
       <c r="X11" s="68"/>
     </row>
-    <row r="12" customFormat="false" ht="46.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="69" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B12" s="75" t="n">
         <f aca="false">RawData!K26-RawData!F26</f>
@@ -8394,13 +8597,13 @@
         <v>0.0862068965517241</v>
       </c>
       <c r="Q12" s="72" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="S12" s="76"/>
     </row>
-    <row r="13" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="69" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B13" s="75" t="n">
         <f aca="false">RawData!L26-RawData!G26</f>
@@ -8463,12 +8666,12 @@
         <v>0.0862068965517241</v>
       </c>
       <c r="Q13" s="72" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="69" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B14" s="75" t="n">
         <f aca="false">RawData!M26-RawData!H26</f>
@@ -8531,7 +8734,7 @@
         <v>0.0862068965517241</v>
       </c>
       <c r="Q14" s="72" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8668,7 +8871,7 @@
         <v>-0.0862068965517241</v>
       </c>
       <c r="Q17" s="81" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8733,7 +8936,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B19" s="10" t="n">
         <f aca="false">B17-B15-B8</f>
@@ -8793,7 +8996,7 @@
       </c>
       <c r="P19" s="83"/>
       <c r="R19" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
@@ -8801,33 +9004,33 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q20" s="84" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P21" s="85"/>
       <c r="Q21" s="76" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="41" t="s">
-        <v>115</v>
+      <c r="B22" s="40" t="s">
+        <v>121</v>
       </c>
       <c r="C22" s="86" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D22" s="87" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="T22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B23" s="88" t="n">
         <f aca="false">RawData!D26+RawData!E26</f>
@@ -8846,7 +9049,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B24" s="88" t="n">
         <f aca="false">RawData!D27+RawData!E27</f>
@@ -8864,7 +9067,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B25" s="88" t="n">
         <f aca="false">RawData!D28+RawData!E28</f>
@@ -8882,7 +9085,7 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B26" s="88" t="n">
         <f aca="false">RawData!D29+RawData!E29</f>
@@ -8900,7 +9103,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B27" s="88" t="n">
         <f aca="false">RawData!D30+RawData!E30</f>
@@ -8918,7 +9121,7 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B28" s="88" t="n">
         <f aca="false">RawData!D31+RawData!E31</f>
@@ -8937,7 +9140,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B29" s="88" t="n">
         <f aca="false">RawData!D32+RawData!E32</f>
@@ -8956,7 +9159,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B30" s="88" t="n">
         <f aca="false">RawData!D33+RawData!E33</f>
@@ -8974,7 +9177,7 @@
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B31" s="88" t="n">
         <f aca="false">RawData!D34+RawData!E34</f>
@@ -8992,7 +9195,7 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B32" s="88" t="n">
         <f aca="false">RawData!D35+RawData!E35</f>
@@ -9007,12 +9210,12 @@
         <v>21100</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B33" s="88" t="n">
         <f aca="false">RawData!D36+RawData!E36</f>
@@ -9027,12 +9230,12 @@
         <v>20100</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B34" s="88" t="n">
         <f aca="false">RawData!D37+RawData!E37</f>
@@ -9047,7 +9250,7 @@
         <v>21900</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9055,23 +9258,23 @@
       <c r="U35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="43" t="s">
+      <c r="A36" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B36" s="41" t="s">
-        <v>132</v>
+      <c r="B36" s="40" t="s">
+        <v>138</v>
       </c>
       <c r="C36" s="86" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D36" s="87" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="T36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B37" s="10" t="n">
         <f aca="false">RawData!F26+RawData!G26+RawData!H26</f>
@@ -9086,12 +9289,12 @@
         <v>11500</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B38" s="10" t="n">
         <f aca="false">RawData!F27+RawData!G27+RawData!H27</f>
@@ -9106,12 +9309,12 @@
         <v>12400</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B39" s="10" t="n">
         <f aca="false">RawData!F28+RawData!G28+RawData!H28</f>
@@ -9126,12 +9329,12 @@
         <v>14400</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B40" s="10" t="n">
         <f aca="false">RawData!F29+RawData!G29+RawData!H29</f>
@@ -9149,7 +9352,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B41" s="10" t="n">
         <f aca="false">RawData!F30+RawData!G30+RawData!H30</f>
@@ -9168,7 +9371,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B42" s="10" t="n">
         <f aca="false">RawData!F31+RawData!G31+RawData!H31</f>
@@ -9186,7 +9389,7 @@
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B43" s="10" t="n">
         <f aca="false">RawData!F32+RawData!G32+RawData!H32</f>
@@ -9204,7 +9407,7 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B44" s="10" t="n">
         <f aca="false">RawData!F33+RawData!G33+RawData!H33</f>
@@ -9222,7 +9425,7 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B45" s="10" t="n">
         <f aca="false">RawData!F34+RawData!G34+RawData!H34</f>
@@ -9240,7 +9443,7 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B46" s="10" t="n">
         <f aca="false">RawData!F35+RawData!G35+RawData!H35</f>
@@ -9259,7 +9462,7 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B47" s="10" t="n">
         <f aca="false">RawData!F36+RawData!G36+RawData!H36</f>
@@ -9278,7 +9481,7 @@
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B48" s="10" t="n">
         <f aca="false">RawData!F37+RawData!G37+RawData!H37</f>
@@ -9299,17 +9502,17 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q50" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q51" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q52" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9321,12 +9524,12 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q55" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N56" s="10" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -9442,24 +9645,24 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
+      <c r="A1" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="89"/>
@@ -9481,7 +9684,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="90" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B4" s="90" t="s">
         <v>13</v>
@@ -9520,15 +9723,15 @@
         <v>24</v>
       </c>
       <c r="N4" s="90" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="O4" s="90" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="91" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B5" s="92" t="n">
         <f aca="false">Drivers!B8*Drivers!B14</f>
@@ -9589,7 +9792,7 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="91" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B6" s="95" t="n">
         <f aca="false">Drivers!B19</f>
@@ -9650,7 +9853,7 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="96" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B7" s="97" t="n">
         <f aca="false">B5+B6</f>
@@ -9728,7 +9931,7 @@
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="91" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B9" s="95" t="n">
         <f aca="false">Drivers!B8*Drivers!E25</f>
@@ -9789,124 +9992,124 @@
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="91" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B10" s="95" t="n">
-        <f aca="false">RawData!G26</f>
-        <v>12700</v>
+        <f aca="false">B7*Drivers!D31</f>
+        <v>22304</v>
       </c>
       <c r="C10" s="95" t="n">
-        <f aca="false">RawData!G27</f>
-        <v>13800</v>
+        <f aca="false">C7*Drivers!D31</f>
+        <v>22304</v>
       </c>
       <c r="D10" s="95" t="n">
-        <f aca="false">RawData!G28</f>
-        <v>15900</v>
+        <f aca="false">D7*Drivers!D31</f>
+        <v>22304</v>
       </c>
       <c r="E10" s="95" t="n">
-        <f aca="false">RawData!G29</f>
-        <v>19100</v>
+        <f aca="false">E7*Drivers!D31</f>
+        <v>22672</v>
       </c>
       <c r="F10" s="95" t="n">
-        <f aca="false">RawData!G30</f>
-        <v>20100</v>
+        <f aca="false">F7*Drivers!D31</f>
+        <v>22672</v>
       </c>
       <c r="G10" s="95" t="n">
-        <f aca="false">RawData!G31</f>
-        <v>20100</v>
+        <f aca="false">G7*Drivers!D31</f>
+        <v>22672</v>
       </c>
       <c r="H10" s="95" t="n">
-        <f aca="false">RawData!G32</f>
-        <v>20100</v>
+        <f aca="false">H7*Drivers!D31</f>
+        <v>22672</v>
       </c>
       <c r="I10" s="95" t="n">
-        <f aca="false">RawData!G33</f>
-        <v>19100</v>
+        <f aca="false">I7*Drivers!D31</f>
+        <v>22672</v>
       </c>
       <c r="J10" s="95" t="n">
-        <f aca="false">RawData!G34</f>
-        <v>18000</v>
+        <f aca="false">J7*Drivers!D31</f>
+        <v>22672</v>
       </c>
       <c r="K10" s="95" t="n">
-        <f aca="false">RawData!G35</f>
-        <v>18000</v>
+        <f aca="false">K7*Drivers!D31</f>
+        <v>23040</v>
       </c>
       <c r="L10" s="95" t="n">
-        <f aca="false">RawData!G36</f>
-        <v>17000</v>
+        <f aca="false">L7*Drivers!D31</f>
+        <v>23040</v>
       </c>
       <c r="M10" s="95" t="n">
-        <f aca="false">RawData!G37</f>
-        <v>18100</v>
+        <f aca="false">M7*Drivers!D31</f>
+        <v>23040</v>
       </c>
       <c r="N10" s="93" t="n">
         <f aca="false">SUM(B10:M10)</f>
-        <v>212000</v>
+        <v>272064</v>
       </c>
       <c r="O10" s="94" t="n">
         <f aca="false">IF(N7=0,0,N10/N7)</f>
-        <v>0.0623382733474477</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="91" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B11" s="95" t="n">
-        <f aca="false">RawData!H26</f>
-        <v>6400</v>
+        <f aca="false">B7*Drivers!D37</f>
+        <v>11152</v>
       </c>
       <c r="C11" s="95" t="n">
-        <f aca="false">RawData!H27</f>
-        <v>6900</v>
+        <f aca="false">C7*Drivers!D37</f>
+        <v>11152</v>
       </c>
       <c r="D11" s="95" t="n">
-        <f aca="false">RawData!H28</f>
-        <v>8000</v>
+        <f aca="false">D7*Drivers!D37</f>
+        <v>11152</v>
       </c>
       <c r="E11" s="95" t="n">
-        <f aca="false">RawData!H29</f>
-        <v>9500</v>
+        <f aca="false">E7*Drivers!D37</f>
+        <v>11336</v>
       </c>
       <c r="F11" s="95" t="n">
-        <f aca="false">RawData!H30</f>
-        <v>10100</v>
+        <f aca="false">F7*Drivers!D37</f>
+        <v>11336</v>
       </c>
       <c r="G11" s="95" t="n">
-        <f aca="false">RawData!H31</f>
-        <v>10100</v>
+        <f aca="false">G7*Drivers!D37</f>
+        <v>11336</v>
       </c>
       <c r="H11" s="95" t="n">
-        <f aca="false">RawData!H32</f>
-        <v>10100</v>
+        <f aca="false">H7*Drivers!D37</f>
+        <v>11336</v>
       </c>
       <c r="I11" s="95" t="n">
-        <f aca="false">RawData!H33</f>
-        <v>9500</v>
+        <f aca="false">I7*Drivers!D37</f>
+        <v>11336</v>
       </c>
       <c r="J11" s="95" t="n">
-        <f aca="false">RawData!H34</f>
-        <v>9000</v>
+        <f aca="false">J7*Drivers!D37</f>
+        <v>11336</v>
       </c>
       <c r="K11" s="95" t="n">
-        <f aca="false">RawData!H35</f>
-        <v>9000</v>
+        <f aca="false">K7*Drivers!D37</f>
+        <v>11520</v>
       </c>
       <c r="L11" s="95" t="n">
-        <f aca="false">RawData!H36</f>
-        <v>8500</v>
+        <f aca="false">L7*Drivers!D37</f>
+        <v>11520</v>
       </c>
       <c r="M11" s="95" t="n">
-        <f aca="false">RawData!H37</f>
-        <v>8900</v>
+        <f aca="false">M7*Drivers!D37</f>
+        <v>11520</v>
       </c>
       <c r="N11" s="93" t="n">
         <f aca="false">SUM(B11:M11)</f>
-        <v>106000</v>
+        <v>136032</v>
       </c>
       <c r="O11" s="94" t="n">
         <f aca="false">IF(N7=0,0,N11/N7)</f>
-        <v>0.0311691366737238</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9915,59 +10118,59 @@
       </c>
       <c r="B12" s="97" t="n">
         <f aca="false">B9+B10+B11</f>
-        <v>159881.25</v>
+        <v>174237.25</v>
       </c>
       <c r="C12" s="97" t="n">
         <f aca="false">C9+C10+C11</f>
-        <v>161481.25</v>
+        <v>174237.25</v>
       </c>
       <c r="D12" s="97" t="n">
         <f aca="false">D9+D10+D11</f>
-        <v>164681.25</v>
+        <v>174237.25</v>
       </c>
       <c r="E12" s="97" t="n">
         <f aca="false">E9+E10+E11</f>
-        <v>172141.666666667</v>
+        <v>177549.666666667</v>
       </c>
       <c r="F12" s="97" t="n">
         <f aca="false">F9+F10+F11</f>
-        <v>173741.666666667</v>
+        <v>177549.666666667</v>
       </c>
       <c r="G12" s="97" t="n">
         <f aca="false">G9+G10+G11</f>
-        <v>173741.666666667</v>
+        <v>177549.666666667</v>
       </c>
       <c r="H12" s="97" t="n">
         <f aca="false">H9+H10+H11</f>
-        <v>173741.666666667</v>
+        <v>177549.666666667</v>
       </c>
       <c r="I12" s="97" t="n">
         <f aca="false">I9+I10+I11</f>
-        <v>172141.666666667</v>
+        <v>177549.666666667</v>
       </c>
       <c r="J12" s="97" t="n">
         <f aca="false">J9+J10+J11</f>
-        <v>170541.666666667</v>
+        <v>177549.666666667</v>
       </c>
       <c r="K12" s="97" t="n">
         <f aca="false">K9+K10+K11</f>
-        <v>173302.083333333</v>
+        <v>180862.083333333</v>
       </c>
       <c r="L12" s="97" t="n">
         <f aca="false">L9+L10+L11</f>
-        <v>171802.083333333</v>
+        <v>180862.083333333</v>
       </c>
       <c r="M12" s="97" t="n">
         <f aca="false">M9+M10+M11</f>
-        <v>173302.083333333</v>
+        <v>180862.083333333</v>
       </c>
       <c r="N12" s="98" t="n">
         <f aca="false">SUM(B12:M12)</f>
-        <v>2040500</v>
+        <v>2130596</v>
       </c>
       <c r="O12" s="99" t="n">
         <f aca="false">IF(N7=0,0,N12/N7)</f>
-        <v>0.600005880969184</v>
+        <v>0.626498470948013</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9989,63 +10192,63 @@
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="96" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B14" s="102" t="n">
         <f aca="false">B7-B12</f>
-        <v>118918.75</v>
+        <v>104562.75</v>
       </c>
       <c r="C14" s="102" t="n">
         <f aca="false">C7-C12</f>
-        <v>117318.75</v>
+        <v>104562.75</v>
       </c>
       <c r="D14" s="102" t="n">
         <f aca="false">D7-D12</f>
-        <v>114118.75</v>
+        <v>104562.75</v>
       </c>
       <c r="E14" s="102" t="n">
         <f aca="false">E7-E12</f>
-        <v>111258.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="F14" s="102" t="n">
         <f aca="false">F7-F12</f>
-        <v>109658.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="G14" s="102" t="n">
         <f aca="false">G7-G12</f>
-        <v>109658.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="H14" s="102" t="n">
         <f aca="false">H7-H12</f>
-        <v>109658.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="I14" s="102" t="n">
         <f aca="false">I7-I12</f>
-        <v>111258.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="J14" s="102" t="n">
         <f aca="false">J7-J12</f>
-        <v>112858.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="K14" s="102" t="n">
         <f aca="false">K7-K12</f>
-        <v>114697.916666667</v>
+        <v>107137.916666667</v>
       </c>
       <c r="L14" s="102" t="n">
         <f aca="false">L7-L12</f>
-        <v>116197.916666667</v>
+        <v>107137.916666667</v>
       </c>
       <c r="M14" s="102" t="n">
         <f aca="false">M7-M12</f>
-        <v>114697.916666667</v>
+        <v>107137.916666667</v>
       </c>
       <c r="N14" s="103" t="n">
         <f aca="false">SUM(B14:M14)</f>
-        <v>1360300</v>
+        <v>1270204</v>
       </c>
       <c r="O14" s="104" t="n">
         <f aca="false">IF(N7=0,0,N14/N7)</f>
-        <v>0.399994119030816</v>
+        <v>0.373501529051987</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10054,116 +10257,116 @@
       </c>
       <c r="B15" s="106" t="n">
         <f aca="false">B14</f>
-        <v>118918.75</v>
+        <v>104562.75</v>
       </c>
       <c r="C15" s="106" t="n">
         <f aca="false">C14</f>
-        <v>117318.75</v>
+        <v>104562.75</v>
       </c>
       <c r="D15" s="106" t="n">
         <f aca="false">D14</f>
-        <v>114118.75</v>
+        <v>104562.75</v>
       </c>
       <c r="E15" s="106" t="n">
         <f aca="false">E14</f>
-        <v>111258.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="F15" s="106" t="n">
         <f aca="false">F14</f>
-        <v>109658.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="G15" s="106" t="n">
         <f aca="false">G14</f>
-        <v>109658.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="H15" s="106" t="n">
         <f aca="false">H14</f>
-        <v>109658.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="I15" s="106" t="n">
         <f aca="false">I14</f>
-        <v>111258.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="J15" s="106" t="n">
         <f aca="false">J14</f>
-        <v>112858.333333333</v>
+        <v>105850.333333333</v>
       </c>
       <c r="K15" s="106" t="n">
         <f aca="false">K14</f>
-        <v>114697.916666667</v>
+        <v>107137.916666667</v>
       </c>
       <c r="L15" s="106" t="n">
         <f aca="false">L14</f>
-        <v>116197.916666667</v>
+        <v>107137.916666667</v>
       </c>
       <c r="M15" s="106" t="n">
         <f aca="false">M14</f>
-        <v>114697.916666667</v>
+        <v>107137.916666667</v>
       </c>
       <c r="N15" s="106" t="n">
         <f aca="false">SUM(B15:M15)</f>
-        <v>1360300</v>
+        <v>1270204</v>
       </c>
       <c r="O15" s="107" t="n">
         <f aca="false">IF(N7=0,0,N15/N7)</f>
-        <v>0.399994119030816</v>
+        <v>0.373501529051987</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="91" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B16" s="108" t="n">
         <f aca="false">IF(B7=0,0,B15/B7)</f>
-        <v>0.426537840746055</v>
+        <v>0.375045731707317</v>
       </c>
       <c r="C16" s="108" t="n">
         <f aca="false">IF(C7=0,0,C15/C7)</f>
-        <v>0.420798959827834</v>
+        <v>0.375045731707317</v>
       </c>
       <c r="D16" s="108" t="n">
         <f aca="false">IF(D7=0,0,D15/D7)</f>
-        <v>0.409321197991392</v>
+        <v>0.375045731707317</v>
       </c>
       <c r="E16" s="108" t="n">
         <f aca="false">IF(E7=0,0,E15/E7)</f>
-        <v>0.392584097859327</v>
+        <v>0.373501529051987</v>
       </c>
       <c r="F16" s="108" t="n">
         <f aca="false">IF(F7=0,0,F15/F7)</f>
-        <v>0.386938367442955</v>
+        <v>0.373501529051987</v>
       </c>
       <c r="G16" s="108" t="n">
         <f aca="false">IF(G7=0,0,G15/G7)</f>
-        <v>0.386938367442955</v>
+        <v>0.373501529051987</v>
       </c>
       <c r="H16" s="108" t="n">
         <f aca="false">IF(H7=0,0,H15/H7)</f>
-        <v>0.386938367442955</v>
+        <v>0.373501529051987</v>
       </c>
       <c r="I16" s="108" t="n">
         <f aca="false">IF(I7=0,0,I15/I7)</f>
-        <v>0.392584097859327</v>
+        <v>0.373501529051987</v>
       </c>
       <c r="J16" s="108" t="n">
         <f aca="false">IF(J7=0,0,J15/J7)</f>
-        <v>0.3982298282757</v>
+        <v>0.373501529051987</v>
       </c>
       <c r="K16" s="108" t="n">
         <f aca="false">IF(K7=0,0,K15/K7)</f>
-        <v>0.398256655092593</v>
+        <v>0.372006655092594</v>
       </c>
       <c r="L16" s="108" t="n">
         <f aca="false">IF(L7=0,0,L15/L7)</f>
-        <v>0.403464988425926</v>
+        <v>0.372006655092594</v>
       </c>
       <c r="M16" s="108" t="n">
         <f aca="false">IF(M7=0,0,M15/M7)</f>
-        <v>0.398256655092593</v>
+        <v>0.372006655092594</v>
       </c>
       <c r="N16" s="104" t="n">
         <f aca="false">IF(N7=0,0,N15/N7)</f>
-        <v>0.399994119030816</v>
+        <v>0.373501529051987</v>
       </c>
       <c r="O16" s="104"/>
     </row>
@@ -10186,7 +10389,7 @@
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="91" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B18" s="95" t="n">
         <f aca="false">0.02*B7</f>
@@ -10247,185 +10450,185 @@
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="77" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B19" s="97" t="n">
         <f aca="false">B15-B18</f>
-        <v>113342.75</v>
+        <v>98986.75</v>
       </c>
       <c r="C19" s="97" t="n">
         <f aca="false">C15-C18</f>
-        <v>111742.75</v>
+        <v>98986.75</v>
       </c>
       <c r="D19" s="97" t="n">
         <f aca="false">D15-D18</f>
-        <v>108542.75</v>
+        <v>98986.75</v>
       </c>
       <c r="E19" s="97" t="n">
         <f aca="false">E15-E18</f>
-        <v>105590.333333333</v>
+        <v>100182.333333333</v>
       </c>
       <c r="F19" s="97" t="n">
         <f aca="false">F15-F18</f>
-        <v>103990.333333333</v>
+        <v>100182.333333333</v>
       </c>
       <c r="G19" s="97" t="n">
         <f aca="false">G15-G18</f>
-        <v>103990.333333333</v>
+        <v>100182.333333333</v>
       </c>
       <c r="H19" s="97" t="n">
         <f aca="false">H15-H18</f>
-        <v>103990.333333333</v>
+        <v>100182.333333333</v>
       </c>
       <c r="I19" s="97" t="n">
         <f aca="false">I15-I18</f>
-        <v>105590.333333333</v>
+        <v>100182.333333333</v>
       </c>
       <c r="J19" s="97" t="n">
         <f aca="false">J15-J18</f>
-        <v>107190.333333333</v>
+        <v>100182.333333333</v>
       </c>
       <c r="K19" s="97" t="n">
         <f aca="false">K15-K18</f>
-        <v>108937.916666667</v>
+        <v>101377.916666667</v>
       </c>
       <c r="L19" s="97" t="n">
         <f aca="false">L15-L18</f>
-        <v>110437.916666667</v>
+        <v>101377.916666667</v>
       </c>
       <c r="M19" s="97" t="n">
         <f aca="false">M15-M18</f>
-        <v>108937.916666667</v>
+        <v>101377.916666667</v>
       </c>
       <c r="N19" s="98" t="n">
         <f aca="false">SUM(B19:M19)</f>
-        <v>1292284</v>
+        <v>1202188</v>
       </c>
       <c r="O19" s="99" t="n">
         <f aca="false">IF(N7=0,0,N19/N7)</f>
-        <v>0.379994119030816</v>
+        <v>0.353501529051988</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="109" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B20" s="110" t="n">
         <f aca="false">IF(B19&gt;0,B19*0.21,0)</f>
-        <v>23801.9775</v>
+        <v>20787.2175</v>
       </c>
       <c r="C20" s="110" t="n">
         <f aca="false">IF(C19&gt;0,C19*0.21,0)</f>
-        <v>23465.9775</v>
+        <v>20787.2175</v>
       </c>
       <c r="D20" s="110" t="n">
         <f aca="false">IF(D19&gt;0,D19*0.21,0)</f>
-        <v>22793.9775</v>
+        <v>20787.2175</v>
       </c>
       <c r="E20" s="110" t="n">
         <f aca="false">IF(E19&gt;0,E19*0.21,0)</f>
-        <v>22173.97</v>
+        <v>21038.2899999999</v>
       </c>
       <c r="F20" s="110" t="n">
         <f aca="false">IF(F19&gt;0,F19*0.21,0)</f>
-        <v>21837.97</v>
+        <v>21038.2899999999</v>
       </c>
       <c r="G20" s="110" t="n">
         <f aca="false">IF(G19&gt;0,G19*0.21,0)</f>
-        <v>21837.97</v>
+        <v>21038.2899999999</v>
       </c>
       <c r="H20" s="110" t="n">
         <f aca="false">IF(H19&gt;0,H19*0.21,0)</f>
-        <v>21837.97</v>
+        <v>21038.2899999999</v>
       </c>
       <c r="I20" s="110" t="n">
         <f aca="false">IF(I19&gt;0,I19*0.21,0)</f>
-        <v>22173.97</v>
+        <v>21038.2899999999</v>
       </c>
       <c r="J20" s="110" t="n">
         <f aca="false">IF(J19&gt;0,J19*0.21,0)</f>
-        <v>22509.97</v>
+        <v>21038.2899999999</v>
       </c>
       <c r="K20" s="110" t="n">
         <f aca="false">IF(K19&gt;0,K19*0.21,0)</f>
-        <v>22876.9625</v>
+        <v>21289.3625000001</v>
       </c>
       <c r="L20" s="110" t="n">
         <f aca="false">IF(L19&gt;0,L19*0.21,0)</f>
-        <v>23191.9625</v>
+        <v>21289.3625000001</v>
       </c>
       <c r="M20" s="110" t="n">
         <f aca="false">IF(M19&gt;0,M19*0.21,0)</f>
-        <v>22876.9625</v>
+        <v>21289.3625000001</v>
       </c>
       <c r="N20" s="93" t="n">
         <f aca="false">SUM(B20:M20)</f>
-        <v>271379.64</v>
+        <v>252459.48</v>
       </c>
       <c r="O20" s="94" t="n">
         <f aca="false">IF(N7=0,0,N20/N7)</f>
-        <v>0.0797987649964714</v>
+        <v>0.0742353211009174</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="77" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B21" s="111" t="n">
         <f aca="false">B19-B20</f>
-        <v>89540.7725</v>
+        <v>78199.5325</v>
       </c>
       <c r="C21" s="111" t="n">
         <f aca="false">C19-C20</f>
-        <v>88276.7725</v>
+        <v>78199.5325</v>
       </c>
       <c r="D21" s="111" t="n">
         <f aca="false">D19-D20</f>
-        <v>85748.7725</v>
+        <v>78199.5325</v>
       </c>
       <c r="E21" s="111" t="n">
         <f aca="false">E19-E20</f>
-        <v>83416.3633333333</v>
+        <v>79144.0433333331</v>
       </c>
       <c r="F21" s="111" t="n">
         <f aca="false">F19-F20</f>
-        <v>82152.3633333333</v>
+        <v>79144.0433333331</v>
       </c>
       <c r="G21" s="111" t="n">
         <f aca="false">G19-G20</f>
-        <v>82152.3633333333</v>
+        <v>79144.0433333331</v>
       </c>
       <c r="H21" s="111" t="n">
         <f aca="false">H19-H20</f>
-        <v>82152.3633333333</v>
+        <v>79144.0433333331</v>
       </c>
       <c r="I21" s="111" t="n">
         <f aca="false">I19-I20</f>
-        <v>83416.3633333333</v>
+        <v>79144.0433333331</v>
       </c>
       <c r="J21" s="111" t="n">
         <f aca="false">J19-J20</f>
-        <v>84680.3633333333</v>
+        <v>79144.0433333331</v>
       </c>
       <c r="K21" s="111" t="n">
         <f aca="false">K19-K20</f>
-        <v>86060.9541666667</v>
+        <v>80088.5541666669</v>
       </c>
       <c r="L21" s="111" t="n">
         <f aca="false">L19-L20</f>
-        <v>87245.9541666667</v>
+        <v>80088.5541666669</v>
       </c>
       <c r="M21" s="111" t="n">
         <f aca="false">M19-M20</f>
-        <v>86060.9541666667</v>
+        <v>80088.5541666669</v>
       </c>
       <c r="N21" s="98" t="n">
         <f aca="false">SUM(B21:M21)</f>
-        <v>1020904.36</v>
+        <v>949728.519999999</v>
       </c>
       <c r="O21" s="99" t="n">
         <f aca="false">IF(N21=0,0,N21/N7)</f>
-        <v>0.300195354034345</v>
+        <v>0.27926620795107</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -10455,7 +10658,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="112" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C2" s="112"/>
       <c r="D2" s="112"/>
@@ -10502,7 +10705,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="113" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10510,7 +10713,7 @@
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="115" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10518,22 +10721,22 @@
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="116" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="114" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="114" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="114" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10541,22 +10744,22 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="116" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="114" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="114" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="114" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10564,22 +10767,22 @@
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="116" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="114" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="114" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="114" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -10608,7 +10811,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="117" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C2" s="117"/>
       <c r="D2" s="117"/>
@@ -10617,108 +10820,108 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="118" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C3" s="118"/>
       <c r="D3" s="118" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E3" s="118" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="119" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="120" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C5" s="120"/>
       <c r="D5" s="120" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E5" s="120" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="120" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D6" s="121" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E6" s="122" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="120" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D7" s="121" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E7" s="122" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="120" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D8" s="121" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E8" s="122" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="120" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D9" s="121" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E9" s="122" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="120" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D10" s="121" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E10" s="122" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="120" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D11" s="121" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E11" s="122" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="120" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D12" s="121" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E12" s="122" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10726,29 +10929,29 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="119" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="120" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D15" s="121" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E15" s="122" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="120" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D16" s="121" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E16" s="122" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10757,116 +10960,115 @@
       <c r="E17" s="122"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="123" t="s">
-        <v>200</v>
-      </c>
-      <c r="C18" s="123"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="123"/>
-    </row>
-    <row r="19" customFormat="false" ht="22.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+    </row>
+    <row r="19" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="120" t="s">
-        <v>201</v>
-      </c>
-      <c r="D19" s="124" t="s">
-        <v>202</v>
-      </c>
-      <c r="E19" s="125" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>207</v>
+      </c>
+      <c r="D19" s="123" t="s">
+        <v>208</v>
+      </c>
+      <c r="E19" s="124" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="120" t="s">
-        <v>204</v>
-      </c>
-      <c r="D20" s="124" t="s">
-        <v>205</v>
-      </c>
-      <c r="E20" s="125" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="22.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>210</v>
+      </c>
+      <c r="D20" s="123" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="124" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="120" t="s">
-        <v>207</v>
-      </c>
-      <c r="D21" s="126" t="s">
-        <v>208</v>
-      </c>
-      <c r="E21" s="125" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="22.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>213</v>
+      </c>
+      <c r="D21" s="125" t="s">
+        <v>214</v>
+      </c>
+      <c r="E21" s="124" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="120" t="s">
-        <v>210</v>
-      </c>
-      <c r="D22" s="124" t="s">
-        <v>211</v>
-      </c>
-      <c r="E22" s="125" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>216</v>
+      </c>
+      <c r="D22" s="123" t="s">
+        <v>217</v>
+      </c>
+      <c r="E22" s="124" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="120" t="s">
-        <v>213</v>
-      </c>
-      <c r="D23" s="124" t="s">
-        <v>214</v>
-      </c>
-      <c r="E23" s="125" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>219</v>
+      </c>
+      <c r="D23" s="123" t="s">
+        <v>220</v>
+      </c>
+      <c r="E23" s="124" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="120" t="s">
-        <v>216</v>
-      </c>
-      <c r="D24" s="126" t="s">
-        <v>217</v>
-      </c>
-      <c r="E24" s="125" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="22.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>222</v>
+      </c>
+      <c r="D24" s="125" t="s">
+        <v>223</v>
+      </c>
+      <c r="E24" s="124" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="120" t="s">
-        <v>219</v>
-      </c>
-      <c r="D25" s="127" t="s">
-        <v>220</v>
-      </c>
-      <c r="E25" s="125" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>225</v>
+      </c>
+      <c r="D25" s="126" t="s">
+        <v>226</v>
+      </c>
+      <c r="E25" s="124" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="120" t="s">
-        <v>222</v>
-      </c>
-      <c r="D26" s="127" t="s">
-        <v>223</v>
-      </c>
-      <c r="E26" s="125" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>228</v>
+      </c>
+      <c r="D26" s="126" t="s">
+        <v>229</v>
+      </c>
+      <c r="E26" s="124" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="120" t="s">
-        <v>225</v>
-      </c>
-      <c r="D27" s="127" t="s">
-        <v>226</v>
-      </c>
-      <c r="E27" s="125" t="s">
-        <v>227</v>
+        <v>231</v>
+      </c>
+      <c r="D27" s="126" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" s="124" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="120"/>
-      <c r="D28" s="0"/>
-      <c r="E28" s="128"/>
+      <c r="E28" s="121"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="120"/>
@@ -10883,107 +11085,106 @@
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="119" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="120" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D33" s="121" t="s">
-        <v>230</v>
-      </c>
-      <c r="E33" s="129" t="s">
-        <v>231</v>
+        <v>236</v>
+      </c>
+      <c r="E33" s="127" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="120" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D34" s="121" t="s">
-        <v>233</v>
-      </c>
-      <c r="E34" s="129" t="s">
-        <v>234</v>
+        <v>239</v>
+      </c>
+      <c r="E34" s="127" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="120" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D35" s="121" t="s">
-        <v>230</v>
-      </c>
-      <c r="E35" s="129" t="s">
         <v>236</v>
       </c>
+      <c r="E35" s="127" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="130" t="s">
-        <v>237</v>
+      <c r="B36" s="128" t="s">
+        <v>243</v>
       </c>
       <c r="C36" s="121" t="s">
-        <v>238</v>
-      </c>
-      <c r="E36" s="129" t="s">
-        <v>239</v>
+        <v>244</v>
+      </c>
+      <c r="E36" s="127" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="120"/>
-      <c r="C37" s="131"/>
-      <c r="E37" s="129"/>
+      <c r="C37" s="129"/>
+      <c r="E37" s="127"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="119" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="120" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D39" s="121" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E39" s="122" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="120" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D40" s="121" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="120" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D41" s="121" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="130" t="s">
-        <v>248</v>
-      </c>
-      <c r="B45" s="132" t="s">
-        <v>249</v>
-      </c>
-      <c r="C45" s="129"/>
-      <c r="D45" s="0"/>
+        <v>254</v>
+      </c>
+      <c r="B45" s="131" t="s">
+        <v>255</v>
+      </c>
+      <c r="C45" s="127"/>
     </row>
     <row r="46" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="133" t="s">
-        <v>250</v>
-      </c>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
-      <c r="D46" s="133"/>
+      <c r="A46" s="132" t="s">
+        <v>256</v>
+      </c>
+      <c r="B46" s="132"/>
+      <c r="C46" s="132"/>
+      <c r="D46" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Analysis/Consultora_NovaTech_1.xlsx
+++ b/Analysis/Consultora_NovaTech_1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" state="visible" r:id="rId3"/>
@@ -15,7 +15,8 @@
     <sheet name="P&amp;L" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="_Info" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Assumptions" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Forecast" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Assumptions" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="361">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -545,6 +546,303 @@
     <t xml:space="preserve">  Sazonalidade: Q1 fraco (~20%), Q2-Q3 forte (~55%), Q4 médio (~25%)</t>
   </si>
   <si>
+    <t xml:space="preserve">THREE FORECAST METHODS: Flat (avg last 3 months) | Trend (linear projection) | Manual (set directly). Switch method in B4. All methods feed the same P&amp;L structure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORECAST METHOD GUIDE — read before using</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue = average of last 3 months of 2024 (Oct-Dec), applied to each month of 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use when: no strong trend, business is stable. Pros: simple, anchored to recent reality. Cons: ignores growth trend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TREND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue = linear regression on 2024 monthly actuals, projected 12 months forward.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use when: clear upward or downward trend in data. Pros: data-driven. Cons: assumes trend continues indefinitely.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue = values you enter directly in the yellow input rows below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use when: you have specific business knowledge (e.g. signed contracts, planned hiring). Pros: most flexible. Cons: subjective.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORECAST CONTROLS — yellow cells are inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← Change to: Flat | Trend | Manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast HC (FTEs):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL/AVG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 HC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — 55 FTEs planned 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual input. Change per month if hiring plan varies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Rate (€/head):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — €4,900 (+€300 YoY trend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual input. Rate 2022=€4,000 | 2023=€4,300 | 2024=€4,600 → trend = +€300/year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Utilization:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — 2024 avg ~82%, +2pp YoY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonal pattern from 2024 Drivers + 2pp improvement. Q1 lower (clients slow to start), Q2-Q3 peak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METHOD CALCULATIONS — Consulting Revenue only (MS is always flat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORMULA: AVG(Oct24, Nov24, Dec24) = each month same value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORMULA: INTERCEPT(2024 actuals, months 1-12) + SLOPE × month_number
+Month 13=Jan25, 14=Feb25... 24=Dec25
+RawData col C = Month_Num, col D = Rev_Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORMULA: HC × Rate × Utilization (rows 10, 11, 12)
+Change inputs in rows 10-12 to adjust. Most flexible method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE (→ P&amp;L)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORECAST P&amp;L 2025 — updates when method or inputs change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of Rev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula / Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active row 19 (method-selected revenue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drivers ms 2024 × 1.094 (+9.4% growth to €580K based on rawdata 2025 budget)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL REVENUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consulting + ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hc (row 10) × Cost/head/month (Drivers E25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revenue × 8.0% (historical avg 2022-2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revenue × 4.0% (historical avg 2022-2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL COSTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">personnel + operations + other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gross profit (no d&amp;a at this level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebitda / revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revenue × 2% (assumption — low asset base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebitda - d&amp;a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax (21% IRC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebit × 21% if positive (Portugal IRC 2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebit - tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO ANALYSIS — Base / Upside / Downside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change B43 to switch scenario. All rows below update automatically via IF formulas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Scenario:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO DEFINITIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate €/head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Util avg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rev Est.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA Est.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rationale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trend continuation: +3 HC, +€300 rate, +2pp util vs 2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 more FTEs, stronger rate, better utilization. Optimistic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headcount below plan, rate pressure, lower utilization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO P&amp;L — updates when you change Active Scenario above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Rev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE(base;55;SE(upside;60;50)) × IF(Base,4900,IF(Upside,5000,4700)) × seasonal util</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same as p&amp;l (flat ms revenue; independent of scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE(base;55;SE(upside;60;50)) × Drivers!E25 (cost/head/month 2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revenue × 8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revenue × 4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revenue - total costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SENSITIVITY TABLES — all values calculated by formula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three tables: (1) HC sensitivity | (2) Rate sensitivity | (3) Utilization sensitivity. All use Base assumptions except the variable being tested. Formulas reference Drivers and P&amp;L rows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE 1 — EBITDA vs Headcount (Rate=€4,900, Util=82% avg fixed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC (FTEs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consulting Rev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS Rev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Rev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ops+Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← ~Base (55 FTEs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE 2 — EBITDA vs Billing Rate (HC=55, Util=82% avg fixed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE 3 — EBITDA vs Utilization (HC=55, Rate=€4,900 fixed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← Base (82% avg)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Model Assumptions — NovaTech Consulting Lda.</t>
   </si>
   <si>
@@ -623,9 +921,6 @@
     <t xml:space="preserve">Estimate — Q4 moderate</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
     <t xml:space="preserve">Internal estimate</t>
   </si>
   <si>
@@ -680,7 +975,16 @@
     <t xml:space="preserve">52 FTEs</t>
   </si>
   <si>
-    <t xml:space="preserve">ASSUMPTION — +5 FTEs vs 2023. KEY INPUT: change in Drivers sheet to model scenarios.</t>
+    <t xml:space="preserve">ASSUMPTION — +5 FTEs vs 2023.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headcount 2025 (year-end)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 FTEs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — +3 vs 2024 </t>
   </si>
   <si>
     <t xml:space="preserve">Billing rate 2022</t>
@@ -710,6 +1014,15 @@
     <t xml:space="preserve">ASSUMPTION — +€300 YoY rate increase. Change in Drivers sheet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Billing rate 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€4,900/head/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — +€300 YoY consistent with 2022-2024 trend). </t>
+  </si>
+  <si>
     <t xml:space="preserve">Personnel % of Revenue</t>
   </si>
   <si>
@@ -737,6 +1050,9 @@
     <t xml:space="preserve">DERIVED — consistent across 2022–2024.</t>
   </si>
   <si>
+    <t xml:space="preserve">ASSUMPTION — +2pp vs 2024 (consistent YoY improvement). Seasonal pattern maintained.</t>
+  </si>
+  <si>
     <t xml:space="preserve">VARIANCE CONVENTION</t>
   </si>
   <si>
@@ -779,7 +1095,7 @@
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">Week 3 </t>
+    <t xml:space="preserve">Week 4</t>
   </si>
   <si>
     <t xml:space="preserve">Variance Analysis complete + P&amp;L + Drivers — Forecasting in Week 4</t>
@@ -803,8 +1119,7 @@
     <t xml:space="preserve">See below</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Operations and Other costs not yet driver-linked (use RawData directly) — to fix in Week 4.
-2. Budget in RawData cols I–M represents 2025 targets applied to 2024 rows as proxy — not a true 2025 actuals sheet.
+    <t xml:space="preserve">2. Budget in RawData cols I–M represents 2025 targets applied to 2024 rows as proxy — not a true 2025 actuals sheet.
 3. HC and billing rate assumptions do not exactly reproduce RawData totals — gap intentional, acknowledged in YoY Bridge.</t>
   </si>
 </sst>
@@ -812,7 +1127,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
@@ -822,8 +1137,10 @@
     <numFmt numFmtId="170" formatCode="0.00%"/>
     <numFmt numFmtId="171" formatCode="[$-409]#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="172" formatCode="[$-409]0.00%"/>
+    <numFmt numFmtId="173" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="174" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="65">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1190,6 +1507,92 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -1200,14 +1603,6 @@
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FFCC0000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1228,8 +1623,16 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1245,7 +1648,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD7D7"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFDCDC"/>
       </patternFill>
     </fill>
     <fill>
@@ -1281,7 +1684,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1320,8 +1723,20 @@
         <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFFDCDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFDCDC"/>
+        <bgColor rgb="FFFFD7D7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1344,6 +1759,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FF1F4E79"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F4E79"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F4E79"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1385,7 +1815,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="216">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1858,6 +2288,346 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="16" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="56" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="57" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="58" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="58" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="48" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="58" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1878,7 +2648,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1886,11 +2656,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1898,19 +2668,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="63" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="51" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="64" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1995,7 +2757,7 @@
       <rgbColor rgb="FFCCCCCC"/>
       <rgbColor rgb="FF888888"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFD6E4F0"/>
       <rgbColor rgb="FF660066"/>
@@ -2013,10 +2775,10 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFE2EFDA"/>
+      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFB3B3B3"/>
+      <rgbColor rgb="FFFFDCDC"/>
       <rgbColor rgb="FFDDE8CB"/>
-      <rgbColor rgb="FFB3B3B3"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFD7D7"/>
       <rgbColor rgb="FF2E75B6"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -2389,11 +3151,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="33542505"/>
-        <c:axId val="31575947"/>
+        <c:axId val="13740888"/>
+        <c:axId val="52417224"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="33542505"/>
+        <c:axId val="13740888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2458,7 +3220,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31575947"/>
+        <c:crossAx val="52417224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2466,7 +3228,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31575947"/>
+        <c:axId val="52417224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2540,7 +3302,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33542505"/>
+        <c:crossAx val="13740888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2807,11 +3569,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="54471546"/>
-        <c:axId val="18017738"/>
+        <c:axId val="33354593"/>
+        <c:axId val="93014793"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="54471546"/>
+        <c:axId val="33354593"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2876,7 +3638,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18017738"/>
+        <c:crossAx val="93014793"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2884,7 +3646,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18017738"/>
+        <c:axId val="93014793"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2958,7 +3720,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54471546"/>
+        <c:crossAx val="33354593"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3360,11 +4122,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="91170835"/>
-        <c:axId val="77304492"/>
+        <c:axId val="37391902"/>
+        <c:axId val="68845488"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="91170835"/>
+        <c:axId val="37391902"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3429,7 +4191,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77304492"/>
+        <c:crossAx val="68845488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3437,7 +4199,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77304492"/>
+        <c:axId val="68845488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3511,7 +4273,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91170835"/>
+        <c:crossAx val="37391902"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3608,10 +4370,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.160901137858082"/>
-          <c:y val="0.167073418751271"/>
-          <c:w val="0.688146835153525"/>
-          <c:h val="0.539251576164328"/>
+          <c:x val="0.160947151681537"/>
+          <c:y val="0.167158408790314"/>
+          <c:w val="0.68805765271105"/>
+          <c:h val="0.539017194017703"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -3792,11 +4554,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="49608079"/>
-        <c:axId val="11615296"/>
+        <c:axId val="10426299"/>
+        <c:axId val="45401228"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="49608079"/>
+        <c:axId val="10426299"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3861,7 +4623,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11615296"/>
+        <c:crossAx val="45401228"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3869,7 +4631,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11615296"/>
+        <c:axId val="45401228"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3943,7 +4705,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49608079"/>
+        <c:crossAx val="10426299"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4878,9 +5640,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>372960</xdr:colOff>
+      <xdr:colOff>371160</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>131400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4889,7 +5651,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3703680" y="6012000"/>
-        <a:ext cx="6208200" cy="3495600"/>
+        <a:ext cx="6206400" cy="3493800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4908,9 +5670,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2455200</xdr:colOff>
+      <xdr:colOff>2453400</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>122040</xdr:rowOff>
+      <xdr:rowOff>120240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4919,7 +5681,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="10926000" y="5735160"/>
-        <a:ext cx="5755680" cy="3235680"/>
+        <a:ext cx="5753880" cy="3233880"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4938,9 +5700,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>418320</xdr:colOff>
+      <xdr:colOff>416520</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>47520</xdr:rowOff>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4949,7 +5711,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4200120" y="9690120"/>
-        <a:ext cx="5757120" cy="3237120"/>
+        <a:ext cx="5755320" cy="3235320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4964,13 +5726,13 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>190800</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>7560</xdr:rowOff>
+      <xdr:rowOff>7200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2611800</xdr:colOff>
+      <xdr:colOff>2610000</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>42120</xdr:rowOff>
+      <xdr:rowOff>39960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4979,7 +5741,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="21579000">
         <a:off x="10542240" y="9556920"/>
-        <a:ext cx="6295680" cy="3539880"/>
+        <a:ext cx="6293880" cy="3538080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7117,7 +7879,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="2" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="45"/>
@@ -7955,7 +8717,7 @@
       <c r="E27" s="53"/>
       <c r="F27" s="53"/>
     </row>
-    <row r="28" customFormat="false" ht="32.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="31.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
         <v>0</v>
       </c>
@@ -7971,7 +8733,6 @@
       <c r="E28" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="F28" s="0"/>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
@@ -8053,7 +8814,7 @@
       <c r="E33" s="53"/>
       <c r="F33" s="53"/>
     </row>
-    <row r="34" customFormat="false" ht="32.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="54" t="s">
         <v>0</v>
       </c>
@@ -8069,7 +8830,6 @@
       <c r="E34" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="F34" s="0"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="55" t="n">
@@ -8410,7 +9170,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="68" customFormat="true" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="66" t="s">
         <v>107</v>
       </c>
@@ -8477,25 +9237,15 @@
       <c r="Q8" s="72" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="9" s="68" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
@@ -10170,7 +10920,7 @@
       </c>
       <c r="O12" s="99" t="n">
         <f aca="false">IF(N7=0,0,N12/N7)</f>
-        <v>0.626498470948013</v>
+        <v>0.626498470948012</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10248,7 +10998,7 @@
       </c>
       <c r="O14" s="104" t="n">
         <f aca="false">IF(N7=0,0,N14/N7)</f>
-        <v>0.373501529051987</v>
+        <v>0.373501529051988</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10309,7 +11059,7 @@
       </c>
       <c r="O15" s="107" t="n">
         <f aca="false">IF(N7=0,0,N15/N7)</f>
-        <v>0.373501529051987</v>
+        <v>0.373501529051988</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10330,43 +11080,43 @@
       </c>
       <c r="E16" s="108" t="n">
         <f aca="false">IF(E7=0,0,E15/E7)</f>
-        <v>0.373501529051987</v>
+        <v>0.373501529051988</v>
       </c>
       <c r="F16" s="108" t="n">
         <f aca="false">IF(F7=0,0,F15/F7)</f>
-        <v>0.373501529051987</v>
+        <v>0.373501529051988</v>
       </c>
       <c r="G16" s="108" t="n">
         <f aca="false">IF(G7=0,0,G15/G7)</f>
-        <v>0.373501529051987</v>
+        <v>0.373501529051988</v>
       </c>
       <c r="H16" s="108" t="n">
         <f aca="false">IF(H7=0,0,H15/H7)</f>
-        <v>0.373501529051987</v>
+        <v>0.373501529051988</v>
       </c>
       <c r="I16" s="108" t="n">
         <f aca="false">IF(I7=0,0,I15/I7)</f>
-        <v>0.373501529051987</v>
+        <v>0.373501529051988</v>
       </c>
       <c r="J16" s="108" t="n">
         <f aca="false">IF(J7=0,0,J15/J7)</f>
-        <v>0.373501529051987</v>
+        <v>0.373501529051988</v>
       </c>
       <c r="K16" s="108" t="n">
         <f aca="false">IF(K7=0,0,K15/K7)</f>
-        <v>0.372006655092594</v>
+        <v>0.372006655092593</v>
       </c>
       <c r="L16" s="108" t="n">
         <f aca="false">IF(L7=0,0,L15/L7)</f>
-        <v>0.372006655092594</v>
+        <v>0.372006655092593</v>
       </c>
       <c r="M16" s="108" t="n">
         <f aca="false">IF(M7=0,0,M15/M7)</f>
-        <v>0.372006655092594</v>
+        <v>0.372006655092593</v>
       </c>
       <c r="N16" s="104" t="n">
         <f aca="false">IF(N7=0,0,N15/N7)</f>
-        <v>0.373501529051987</v>
+        <v>0.373501529051988</v>
       </c>
       <c r="O16" s="104"/>
     </row>
@@ -10527,39 +11277,39 @@
       </c>
       <c r="E20" s="110" t="n">
         <f aca="false">IF(E19&gt;0,E19*0.21,0)</f>
-        <v>21038.2899999999</v>
+        <v>21038.29</v>
       </c>
       <c r="F20" s="110" t="n">
         <f aca="false">IF(F19&gt;0,F19*0.21,0)</f>
-        <v>21038.2899999999</v>
+        <v>21038.29</v>
       </c>
       <c r="G20" s="110" t="n">
         <f aca="false">IF(G19&gt;0,G19*0.21,0)</f>
-        <v>21038.2899999999</v>
+        <v>21038.29</v>
       </c>
       <c r="H20" s="110" t="n">
         <f aca="false">IF(H19&gt;0,H19*0.21,0)</f>
-        <v>21038.2899999999</v>
+        <v>21038.29</v>
       </c>
       <c r="I20" s="110" t="n">
         <f aca="false">IF(I19&gt;0,I19*0.21,0)</f>
-        <v>21038.2899999999</v>
+        <v>21038.29</v>
       </c>
       <c r="J20" s="110" t="n">
         <f aca="false">IF(J19&gt;0,J19*0.21,0)</f>
-        <v>21038.2899999999</v>
+        <v>21038.29</v>
       </c>
       <c r="K20" s="110" t="n">
         <f aca="false">IF(K19&gt;0,K19*0.21,0)</f>
-        <v>21289.3625000001</v>
+        <v>21289.3625</v>
       </c>
       <c r="L20" s="110" t="n">
         <f aca="false">IF(L19&gt;0,L19*0.21,0)</f>
-        <v>21289.3625000001</v>
+        <v>21289.3625</v>
       </c>
       <c r="M20" s="110" t="n">
         <f aca="false">IF(M19&gt;0,M19*0.21,0)</f>
-        <v>21289.3625000001</v>
+        <v>21289.3625</v>
       </c>
       <c r="N20" s="93" t="n">
         <f aca="false">SUM(B20:M20)</f>
@@ -10588,43 +11338,43 @@
       </c>
       <c r="E21" s="111" t="n">
         <f aca="false">E19-E20</f>
-        <v>79144.0433333331</v>
+        <v>79144.0433333333</v>
       </c>
       <c r="F21" s="111" t="n">
         <f aca="false">F19-F20</f>
-        <v>79144.0433333331</v>
+        <v>79144.0433333333</v>
       </c>
       <c r="G21" s="111" t="n">
         <f aca="false">G19-G20</f>
-        <v>79144.0433333331</v>
+        <v>79144.0433333333</v>
       </c>
       <c r="H21" s="111" t="n">
         <f aca="false">H19-H20</f>
-        <v>79144.0433333331</v>
+        <v>79144.0433333333</v>
       </c>
       <c r="I21" s="111" t="n">
         <f aca="false">I19-I20</f>
-        <v>79144.0433333331</v>
+        <v>79144.0433333333</v>
       </c>
       <c r="J21" s="111" t="n">
         <f aca="false">J19-J20</f>
-        <v>79144.0433333331</v>
+        <v>79144.0433333333</v>
       </c>
       <c r="K21" s="111" t="n">
         <f aca="false">K19-K20</f>
-        <v>80088.5541666669</v>
+        <v>80088.5541666667</v>
       </c>
       <c r="L21" s="111" t="n">
         <f aca="false">L19-L20</f>
-        <v>80088.5541666669</v>
+        <v>80088.5541666667</v>
       </c>
       <c r="M21" s="111" t="n">
         <f aca="false">M19-M20</f>
-        <v>80088.5541666669</v>
+        <v>80088.5541666667</v>
       </c>
       <c r="N21" s="98" t="n">
         <f aca="false">SUM(B21:M21)</f>
-        <v>949728.519999999</v>
+        <v>949728.52</v>
       </c>
       <c r="O21" s="99" t="n">
         <f aca="false">IF(N21=0,0,N21/N7)</f>
@@ -10801,396 +11551,4156 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:F46"/>
+  <dimension ref="A1:Q115"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="20.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="34.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="117" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="117"/>
+    </row>
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="118" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="119" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="120" t="s">
+        <v>174</v>
+      </c>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="120"/>
+      <c r="O3" s="120"/>
+      <c r="P3" s="120"/>
+      <c r="Q3" s="120"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="121" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="122" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="123" t="s">
+        <v>177</v>
+      </c>
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="123"/>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="124" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="125" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="126" t="s">
+        <v>180</v>
+      </c>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="126"/>
+      <c r="M5" s="126"/>
+      <c r="N5" s="126"/>
+      <c r="O5" s="126"/>
+      <c r="P5" s="126"/>
+      <c r="Q5" s="126"/>
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="117" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="117"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="117"/>
+      <c r="N6" s="117"/>
+      <c r="O6" s="117"/>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="117"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="127" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="128" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="128" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="128" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="128" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="128" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="128" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="128" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="128" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="128" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="128" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="128" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="129" t="s">
+        <v>186</v>
+      </c>
+      <c r="O8" s="129" t="s">
+        <v>187</v>
+      </c>
+      <c r="P8" s="130" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="C9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="D9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="G9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="H9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="J9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="M9" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="N9" s="131" t="n">
+        <f aca="false">AVERAGE(B9:M9)</f>
+        <v>55</v>
+      </c>
+      <c r="O9" s="132" t="s">
+        <v>190</v>
+      </c>
+      <c r="P9" s="133" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="C10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="D10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="E10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="F10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="H10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="I10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="J10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="K10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="L10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="M10" s="50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="N10" s="134" t="n">
+        <f aca="false">AVERAGE(B10:M10)</f>
+        <v>4900</v>
+      </c>
+      <c r="O10" s="132" t="s">
+        <v>193</v>
+      </c>
+      <c r="P10" s="133" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="135" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C11" s="135" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D11" s="135" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E11" s="135" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F11" s="135" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G11" s="135" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H11" s="135" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I11" s="135" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J11" s="135" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K11" s="135" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L11" s="135" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M11" s="135" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N11" s="136" t="n">
+        <f aca="false">AVERAGE(B11:M11)</f>
+        <v>0.835833333333333</v>
+      </c>
+      <c r="O11" s="132" t="s">
+        <v>196</v>
+      </c>
+      <c r="P11" s="133" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="137"/>
+      <c r="B12" s="138"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="138"/>
+      <c r="E12" s="138"/>
+      <c r="F12" s="138"/>
+      <c r="G12" s="138"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="138"/>
+      <c r="J12" s="138"/>
+      <c r="K12" s="138"/>
+      <c r="L12" s="138"/>
+      <c r="M12" s="138"/>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="117" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="117"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="117"/>
+      <c r="M13" s="117"/>
+      <c r="N13" s="117"/>
+      <c r="O13" s="117"/>
+      <c r="P13" s="117"/>
+      <c r="Q13" s="117"/>
+    </row>
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="128" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="128" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="128" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="128" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="128" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="128" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="128" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="128" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="128" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="128" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="128" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="128" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" s="128" t="s">
+        <v>99</v>
+      </c>
+      <c r="O14" s="128" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="118" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="C15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="D15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="E15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="F15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="G15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="H15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="I15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="J15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="K15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="L15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="M15" s="139" t="n">
+        <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="N15" s="140" t="n">
+        <f aca="false">SUM(B15:M15)</f>
+        <v>2120000</v>
+      </c>
+      <c r="O15" s="141" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="121" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*13</f>
+        <v>197866.666666667</v>
+      </c>
+      <c r="C16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*14</f>
+        <v>201128.205128205</v>
+      </c>
+      <c r="D16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*15</f>
+        <v>204389.743589744</v>
+      </c>
+      <c r="E16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*16</f>
+        <v>207651.282051282</v>
+      </c>
+      <c r="F16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*17</f>
+        <v>210912.820512821</v>
+      </c>
+      <c r="G16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*13</f>
+        <v>197866.666666667</v>
+      </c>
+      <c r="H16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*19</f>
+        <v>217435.897435897</v>
+      </c>
+      <c r="I16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*20</f>
+        <v>220697.435897436</v>
+      </c>
+      <c r="J16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*21</f>
+        <v>223958.974358974</v>
+      </c>
+      <c r="K16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*22</f>
+        <v>227220.512820513</v>
+      </c>
+      <c r="L16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*23</f>
+        <v>230482.051282051</v>
+      </c>
+      <c r="M16" s="142" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*24</f>
+        <v>233743.58974359</v>
+      </c>
+      <c r="N16" s="143" t="n">
+        <f aca="false">SUM(B16:M16)</f>
+        <v>2573353.84615385</v>
+      </c>
+      <c r="O16" s="141" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="124" t="s">
+        <v>178</v>
+      </c>
+      <c r="B17" s="144" t="n">
+        <f aca="false">B9*B10*B11</f>
+        <v>204820</v>
+      </c>
+      <c r="C17" s="144" t="n">
+        <f aca="false">C9*C10*C11</f>
+        <v>212905</v>
+      </c>
+      <c r="D17" s="144" t="n">
+        <f aca="false">D9*D10*D11</f>
+        <v>220990</v>
+      </c>
+      <c r="E17" s="144" t="n">
+        <f aca="false">E9*E10*E11</f>
+        <v>231770</v>
+      </c>
+      <c r="F17" s="144" t="n">
+        <f aca="false">F9*F10*F11</f>
+        <v>239855</v>
+      </c>
+      <c r="G17" s="144" t="n">
+        <f aca="false">G9*G10*G11</f>
+        <v>239855</v>
+      </c>
+      <c r="H17" s="144" t="n">
+        <f aca="false">H9*H10*H11</f>
+        <v>234465</v>
+      </c>
+      <c r="I17" s="144" t="n">
+        <f aca="false">I9*I10*I11</f>
+        <v>226380</v>
+      </c>
+      <c r="J17" s="144" t="n">
+        <f aca="false">J9*J10*J11</f>
+        <v>231770</v>
+      </c>
+      <c r="K17" s="144" t="n">
+        <f aca="false">K9*K10*K11</f>
+        <v>226380</v>
+      </c>
+      <c r="L17" s="144" t="n">
+        <f aca="false">L9*L10*L11</f>
+        <v>220990</v>
+      </c>
+      <c r="M17" s="144" t="n">
+        <f aca="false">M9*M10*M11</f>
+        <v>212905</v>
+      </c>
+      <c r="N17" s="145" t="n">
+        <f aca="false">SUM(B17:M17)</f>
+        <v>2703085</v>
+      </c>
+      <c r="O17" s="141" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="146" t="s">
+        <v>204</v>
+      </c>
+      <c r="B18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",B15,IF($B$8="Trend",B16,B17))</f>
+        <v>204820</v>
+      </c>
+      <c r="C18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",C15,IF($B$8="Trend",C16,C17))</f>
+        <v>212905</v>
+      </c>
+      <c r="D18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",D15,IF($B$8="Trend",D16,D17))</f>
+        <v>220990</v>
+      </c>
+      <c r="E18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",E15,IF($B$8="Trend",E16,E17))</f>
+        <v>231770</v>
+      </c>
+      <c r="F18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",F15,IF($B$8="Trend",F16,F17))</f>
+        <v>239855</v>
+      </c>
+      <c r="G18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",G15,IF($B$8="Trend",G16,G17))</f>
+        <v>239855</v>
+      </c>
+      <c r="H18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",H15,IF($B$8="Trend",H16,H17))</f>
+        <v>234465</v>
+      </c>
+      <c r="I18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",I15,IF($B$8="Trend",I16,I17))</f>
+        <v>226380</v>
+      </c>
+      <c r="J18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",J15,IF($B$8="Trend",J16,J17))</f>
+        <v>231770</v>
+      </c>
+      <c r="K18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",K15,IF($B$8="Trend",K16,K17))</f>
+        <v>226380</v>
+      </c>
+      <c r="L18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",L15,IF($B$8="Trend",L16,L17))</f>
+        <v>220990</v>
+      </c>
+      <c r="M18" s="147" t="n">
+        <f aca="false">IF($B$8="Flat",M15,IF($B$8="Trend",M16,M17))</f>
+        <v>212905</v>
+      </c>
+      <c r="N18" s="147" t="n">
+        <f aca="false">SUM(B18:M18)</f>
+        <v>2703085</v>
+      </c>
+      <c r="O18" s="148"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="117" t="s">
+        <v>205</v>
+      </c>
+      <c r="B20" s="117"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="117"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="117"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="117"/>
+      <c r="N20" s="117"/>
+      <c r="O20" s="117"/>
+      <c r="P20" s="117"/>
+      <c r="Q20" s="117"/>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="130" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="129" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="129" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="129" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="129" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="129" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="129" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="129" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="129" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="129" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" s="129" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="129" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" s="129" t="s">
+        <v>99</v>
+      </c>
+      <c r="O21" s="129" t="s">
+        <v>206</v>
+      </c>
+      <c r="P21" s="130" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="149" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="150" t="n">
+        <f aca="false">B18</f>
+        <v>204820</v>
+      </c>
+      <c r="C22" s="150" t="n">
+        <f aca="false">C18</f>
+        <v>212905</v>
+      </c>
+      <c r="D22" s="150" t="n">
+        <f aca="false">D18</f>
+        <v>220990</v>
+      </c>
+      <c r="E22" s="150" t="n">
+        <f aca="false">E18</f>
+        <v>231770</v>
+      </c>
+      <c r="F22" s="150" t="n">
+        <f aca="false">F18</f>
+        <v>239855</v>
+      </c>
+      <c r="G22" s="150" t="n">
+        <f aca="false">G18</f>
+        <v>239855</v>
+      </c>
+      <c r="H22" s="150" t="n">
+        <f aca="false">H18</f>
+        <v>234465</v>
+      </c>
+      <c r="I22" s="150" t="n">
+        <f aca="false">I18</f>
+        <v>226380</v>
+      </c>
+      <c r="J22" s="150" t="n">
+        <f aca="false">J18</f>
+        <v>231770</v>
+      </c>
+      <c r="K22" s="150" t="n">
+        <f aca="false">K18</f>
+        <v>226380</v>
+      </c>
+      <c r="L22" s="150" t="n">
+        <f aca="false">L18</f>
+        <v>220990</v>
+      </c>
+      <c r="M22" s="150" t="n">
+        <f aca="false">M18</f>
+        <v>212905</v>
+      </c>
+      <c r="N22" s="151" t="n">
+        <f aca="false">SUM(B22:M22)</f>
+        <v>2703085</v>
+      </c>
+      <c r="O22" s="94" t="n">
+        <f aca="false">IF(N24=0,0,N22/N24)</f>
+        <v>0.823272295739105</v>
+      </c>
+      <c r="P22" s="152" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="149" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="150" t="n">
+        <f aca="false">Drivers!B19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="C23" s="150" t="n">
+        <f aca="false">Drivers!C19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="D23" s="150" t="n">
+        <f aca="false">Drivers!D19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="E23" s="150" t="n">
+        <f aca="false">Drivers!E19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="F23" s="150" t="n">
+        <f aca="false">Drivers!F19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="G23" s="150" t="n">
+        <f aca="false">Drivers!G19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="H23" s="150" t="n">
+        <f aca="false">Drivers!H19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="I23" s="150" t="n">
+        <f aca="false">Drivers!I19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="J23" s="150" t="n">
+        <f aca="false">Drivers!J19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="K23" s="150" t="n">
+        <f aca="false">Drivers!K19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="L23" s="150" t="n">
+        <f aca="false">Drivers!L19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="M23" s="150" t="n">
+        <f aca="false">Drivers!M19*1.094</f>
+        <v>48354.8</v>
+      </c>
+      <c r="N23" s="151" t="n">
+        <f aca="false">SUM(B23:M23)</f>
+        <v>580257.6</v>
+      </c>
+      <c r="O23" s="94" t="n">
+        <f aca="false">IF(N24=0,0,N23/N24)</f>
+        <v>0.176727704260896</v>
+      </c>
+      <c r="P23" s="152" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="77" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24" s="153" t="n">
+        <f aca="false">B22+B23</f>
+        <v>253174.8</v>
+      </c>
+      <c r="C24" s="153" t="n">
+        <f aca="false">C22+C23</f>
+        <v>261259.8</v>
+      </c>
+      <c r="D24" s="153" t="n">
+        <f aca="false">D22+D23</f>
+        <v>269344.8</v>
+      </c>
+      <c r="E24" s="153" t="n">
+        <f aca="false">E22+E23</f>
+        <v>280124.8</v>
+      </c>
+      <c r="F24" s="153" t="n">
+        <f aca="false">F22+F23</f>
+        <v>288209.8</v>
+      </c>
+      <c r="G24" s="153" t="n">
+        <f aca="false">G22+G23</f>
+        <v>288209.8</v>
+      </c>
+      <c r="H24" s="153" t="n">
+        <f aca="false">H22+H23</f>
+        <v>282819.8</v>
+      </c>
+      <c r="I24" s="153" t="n">
+        <f aca="false">I22+I23</f>
+        <v>274734.8</v>
+      </c>
+      <c r="J24" s="153" t="n">
+        <f aca="false">J22+J23</f>
+        <v>280124.8</v>
+      </c>
+      <c r="K24" s="153" t="n">
+        <f aca="false">K22+K23</f>
+        <v>274734.8</v>
+      </c>
+      <c r="L24" s="153" t="n">
+        <f aca="false">L22+L23</f>
+        <v>269344.8</v>
+      </c>
+      <c r="M24" s="153" t="n">
+        <f aca="false">M22+M23</f>
+        <v>261259.8</v>
+      </c>
+      <c r="N24" s="154" t="n">
+        <f aca="false">SUM(B24:M24)</f>
+        <v>3283342.6</v>
+      </c>
+      <c r="O24" s="155" t="n">
+        <f aca="false">IF(N24=0,0,N24/N24)</f>
+        <v>1</v>
+      </c>
+      <c r="P24" s="152" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="149"/>
+      <c r="B25" s="156"/>
+      <c r="C25" s="156"/>
+      <c r="D25" s="156"/>
+      <c r="E25" s="156"/>
+      <c r="F25" s="156"/>
+      <c r="G25" s="156"/>
+      <c r="H25" s="156"/>
+      <c r="I25" s="156"/>
+      <c r="J25" s="156"/>
+      <c r="K25" s="156"/>
+      <c r="L25" s="156"/>
+      <c r="M25" s="156"/>
+      <c r="N25" s="157"/>
+      <c r="O25" s="101"/>
+    </row>
+    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="149" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="150" t="n">
+        <f aca="false">B9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="C26" s="150" t="n">
+        <f aca="false">C9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="D26" s="150" t="n">
+        <f aca="false">D9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="E26" s="150" t="n">
+        <f aca="false">E9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="F26" s="150" t="n">
+        <f aca="false">F9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="G26" s="150" t="n">
+        <f aca="false">G9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="H26" s="150" t="n">
+        <f aca="false">H9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="I26" s="150" t="n">
+        <f aca="false">I9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="J26" s="150" t="n">
+        <f aca="false">J9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="K26" s="150" t="n">
+        <f aca="false">K9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="L26" s="150" t="n">
+        <f aca="false">L9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="M26" s="150" t="n">
+        <f aca="false">M9*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="N26" s="151" t="n">
+        <f aca="false">SUM(B26:M26)</f>
+        <v>1821875</v>
+      </c>
+      <c r="O26" s="94" t="n">
+        <f aca="false">IF(N24=0,0,N26/N24)</f>
+        <v>0.554884220732859</v>
+      </c>
+      <c r="P26" s="152" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="149" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="150" t="n">
+        <f aca="false">B24*0.08</f>
+        <v>20253.984</v>
+      </c>
+      <c r="C27" s="150" t="n">
+        <f aca="false">C24*0.08</f>
+        <v>20900.784</v>
+      </c>
+      <c r="D27" s="150" t="n">
+        <f aca="false">D24*0.08</f>
+        <v>21547.584</v>
+      </c>
+      <c r="E27" s="150" t="n">
+        <f aca="false">E24*0.08</f>
+        <v>22409.984</v>
+      </c>
+      <c r="F27" s="150" t="n">
+        <f aca="false">F24*0.08</f>
+        <v>23056.784</v>
+      </c>
+      <c r="G27" s="150" t="n">
+        <f aca="false">G24*0.08</f>
+        <v>23056.784</v>
+      </c>
+      <c r="H27" s="150" t="n">
+        <f aca="false">H24*0.08</f>
+        <v>22625.584</v>
+      </c>
+      <c r="I27" s="150" t="n">
+        <f aca="false">I24*0.08</f>
+        <v>21978.784</v>
+      </c>
+      <c r="J27" s="150" t="n">
+        <f aca="false">J24*0.08</f>
+        <v>22409.984</v>
+      </c>
+      <c r="K27" s="150" t="n">
+        <f aca="false">K24*0.08</f>
+        <v>21978.784</v>
+      </c>
+      <c r="L27" s="150" t="n">
+        <f aca="false">L24*0.08</f>
+        <v>21547.584</v>
+      </c>
+      <c r="M27" s="150" t="n">
+        <f aca="false">M24*0.08</f>
+        <v>20900.784</v>
+      </c>
+      <c r="N27" s="151" t="n">
+        <f aca="false">SUM(B27:M27)</f>
+        <v>262667.408</v>
+      </c>
+      <c r="O27" s="94" t="n">
+        <f aca="false">IF(N24=0,0,N27/N24)</f>
+        <v>0.08</v>
+      </c>
+      <c r="P27" s="152" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="149" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="150" t="n">
+        <f aca="false">B24*0.04</f>
+        <v>10126.992</v>
+      </c>
+      <c r="C28" s="150" t="n">
+        <f aca="false">C24*0.04</f>
+        <v>10450.392</v>
+      </c>
+      <c r="D28" s="150" t="n">
+        <f aca="false">D24*0.04</f>
+        <v>10773.792</v>
+      </c>
+      <c r="E28" s="150" t="n">
+        <f aca="false">E24*0.04</f>
+        <v>11204.992</v>
+      </c>
+      <c r="F28" s="150" t="n">
+        <f aca="false">F24*0.04</f>
+        <v>11528.392</v>
+      </c>
+      <c r="G28" s="150" t="n">
+        <f aca="false">G24*0.04</f>
+        <v>11528.392</v>
+      </c>
+      <c r="H28" s="150" t="n">
+        <f aca="false">H24*0.04</f>
+        <v>11312.792</v>
+      </c>
+      <c r="I28" s="150" t="n">
+        <f aca="false">I24*0.04</f>
+        <v>10989.392</v>
+      </c>
+      <c r="J28" s="150" t="n">
+        <f aca="false">J24*0.04</f>
+        <v>11204.992</v>
+      </c>
+      <c r="K28" s="150" t="n">
+        <f aca="false">K24*0.04</f>
+        <v>10989.392</v>
+      </c>
+      <c r="L28" s="150" t="n">
+        <f aca="false">L24*0.04</f>
+        <v>10773.792</v>
+      </c>
+      <c r="M28" s="150" t="n">
+        <f aca="false">M24*0.04</f>
+        <v>10450.392</v>
+      </c>
+      <c r="N28" s="151" t="n">
+        <f aca="false">SUM(B28:M28)</f>
+        <v>131333.704</v>
+      </c>
+      <c r="O28" s="94" t="n">
+        <f aca="false">IF(N24=0,0,N28/N24)</f>
+        <v>0.04</v>
+      </c>
+      <c r="P28" s="152" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="B29" s="153" t="n">
+        <f aca="false">B26+B27+B28</f>
+        <v>182203.892666667</v>
+      </c>
+      <c r="C29" s="153" t="n">
+        <f aca="false">C26+C27+C28</f>
+        <v>183174.092666667</v>
+      </c>
+      <c r="D29" s="153" t="n">
+        <f aca="false">D26+D27+D28</f>
+        <v>184144.292666667</v>
+      </c>
+      <c r="E29" s="153" t="n">
+        <f aca="false">E26+E27+E28</f>
+        <v>185437.892666667</v>
+      </c>
+      <c r="F29" s="153" t="n">
+        <f aca="false">F26+F27+F28</f>
+        <v>186408.092666667</v>
+      </c>
+      <c r="G29" s="153" t="n">
+        <f aca="false">G26+G27+G28</f>
+        <v>186408.092666667</v>
+      </c>
+      <c r="H29" s="153" t="n">
+        <f aca="false">H26+H27+H28</f>
+        <v>185761.292666667</v>
+      </c>
+      <c r="I29" s="153" t="n">
+        <f aca="false">I26+I27+I28</f>
+        <v>184791.092666667</v>
+      </c>
+      <c r="J29" s="153" t="n">
+        <f aca="false">J26+J27+J28</f>
+        <v>185437.892666667</v>
+      </c>
+      <c r="K29" s="153" t="n">
+        <f aca="false">K26+K27+K28</f>
+        <v>184791.092666667</v>
+      </c>
+      <c r="L29" s="153" t="n">
+        <f aca="false">L26+L27+L28</f>
+        <v>184144.292666667</v>
+      </c>
+      <c r="M29" s="153" t="n">
+        <f aca="false">M26+M27+M28</f>
+        <v>183174.092666667</v>
+      </c>
+      <c r="N29" s="154" t="n">
+        <f aca="false">SUM(B29:M29)</f>
+        <v>2215876.112</v>
+      </c>
+      <c r="O29" s="155" t="n">
+        <f aca="false">IF(N24=0,0,N29/N24)</f>
+        <v>0.674884220732859</v>
+      </c>
+      <c r="P29" s="152" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="149"/>
+      <c r="B30" s="156"/>
+      <c r="C30" s="156"/>
+      <c r="D30" s="156"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="156"/>
+      <c r="G30" s="156"/>
+      <c r="H30" s="156"/>
+      <c r="I30" s="156"/>
+      <c r="J30" s="156"/>
+      <c r="K30" s="156"/>
+      <c r="L30" s="156"/>
+      <c r="M30" s="156"/>
+      <c r="N30" s="157"/>
+      <c r="O30" s="101"/>
+    </row>
+    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" s="153" t="n">
+        <f aca="false">B24-B29</f>
+        <v>70970.9073333333</v>
+      </c>
+      <c r="C31" s="153" t="n">
+        <f aca="false">C24-C29</f>
+        <v>78085.7073333333</v>
+      </c>
+      <c r="D31" s="153" t="n">
+        <f aca="false">D24-D29</f>
+        <v>85200.5073333333</v>
+      </c>
+      <c r="E31" s="153" t="n">
+        <f aca="false">E24-E29</f>
+        <v>94686.9073333333</v>
+      </c>
+      <c r="F31" s="153" t="n">
+        <f aca="false">F24-F29</f>
+        <v>101801.707333333</v>
+      </c>
+      <c r="G31" s="153" t="n">
+        <f aca="false">G24-G29</f>
+        <v>101801.707333333</v>
+      </c>
+      <c r="H31" s="153" t="n">
+        <f aca="false">H24-H29</f>
+        <v>97058.5073333333</v>
+      </c>
+      <c r="I31" s="153" t="n">
+        <f aca="false">I24-I29</f>
+        <v>89943.7073333333</v>
+      </c>
+      <c r="J31" s="153" t="n">
+        <f aca="false">J24-J29</f>
+        <v>94686.9073333333</v>
+      </c>
+      <c r="K31" s="153" t="n">
+        <f aca="false">K24-K29</f>
+        <v>89943.7073333333</v>
+      </c>
+      <c r="L31" s="153" t="n">
+        <f aca="false">L24-L29</f>
+        <v>85200.5073333333</v>
+      </c>
+      <c r="M31" s="153" t="n">
+        <f aca="false">M24-M29</f>
+        <v>78085.7073333333</v>
+      </c>
+      <c r="N31" s="154" t="n">
+        <f aca="false">SUM(B31:M31)</f>
+        <v>1067466.488</v>
+      </c>
+      <c r="O31" s="155" t="n">
+        <f aca="false">IF(N24=0,0,N31/N24)</f>
+        <v>0.325115779267141</v>
+      </c>
+      <c r="P31" s="152" t="e">
+        <f aca="false">revenue - total cost</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="105" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="147" t="n">
+        <f aca="false">B31</f>
+        <v>70970.9073333333</v>
+      </c>
+      <c r="C32" s="147" t="n">
+        <f aca="false">C31</f>
+        <v>78085.7073333333</v>
+      </c>
+      <c r="D32" s="147" t="n">
+        <f aca="false">D31</f>
+        <v>85200.5073333333</v>
+      </c>
+      <c r="E32" s="147" t="n">
+        <f aca="false">E31</f>
+        <v>94686.9073333333</v>
+      </c>
+      <c r="F32" s="147" t="n">
+        <f aca="false">F31</f>
+        <v>101801.707333333</v>
+      </c>
+      <c r="G32" s="147" t="n">
+        <f aca="false">G31</f>
+        <v>101801.707333333</v>
+      </c>
+      <c r="H32" s="147" t="n">
+        <f aca="false">H31</f>
+        <v>97058.5073333333</v>
+      </c>
+      <c r="I32" s="147" t="n">
+        <f aca="false">I31</f>
+        <v>89943.7073333333</v>
+      </c>
+      <c r="J32" s="147" t="n">
+        <f aca="false">J31</f>
+        <v>94686.9073333333</v>
+      </c>
+      <c r="K32" s="147" t="n">
+        <f aca="false">K31</f>
+        <v>89943.7073333333</v>
+      </c>
+      <c r="L32" s="147" t="n">
+        <f aca="false">L31</f>
+        <v>85200.5073333333</v>
+      </c>
+      <c r="M32" s="147" t="n">
+        <f aca="false">M31</f>
+        <v>78085.7073333333</v>
+      </c>
+      <c r="N32" s="147" t="n">
+        <f aca="false">SUM(B32:M32)</f>
+        <v>1067466.488</v>
+      </c>
+      <c r="O32" s="158" t="n">
+        <f aca="false">IF(N24=0,0,N32/N24)</f>
+        <v>0.325115779267141</v>
+      </c>
+      <c r="P32" s="152" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="149" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="108" t="n">
+        <f aca="false">IF(B24=0,0,B32/B24)</f>
+        <v>0.280323742068063</v>
+      </c>
+      <c r="C33" s="108" t="n">
+        <f aca="false">IF(C24=0,0,C32/C24)</f>
+        <v>0.298881448019685</v>
+      </c>
+      <c r="D33" s="108" t="n">
+        <f aca="false">IF(D24=0,0,D32/D24)</f>
+        <v>0.316325050022623</v>
+      </c>
+      <c r="E33" s="108" t="n">
+        <f aca="false">IF(E24=0,0,E32/E24)</f>
+        <v>0.338016867243933</v>
+      </c>
+      <c r="F33" s="108" t="n">
+        <f aca="false">IF(F24=0,0,F32/F24)</f>
+        <v>0.353220838893519</v>
+      </c>
+      <c r="G33" s="108" t="n">
+        <f aca="false">IF(G24=0,0,G32/G24)</f>
+        <v>0.353220838893519</v>
+      </c>
+      <c r="H33" s="108" t="n">
+        <f aca="false">IF(H24=0,0,H32/H24)</f>
+        <v>0.343181443920593</v>
+      </c>
+      <c r="I33" s="108" t="n">
+        <f aca="false">IF(I24=0,0,I32/I24)</f>
+        <v>0.327383743644174</v>
+      </c>
+      <c r="J33" s="108" t="n">
+        <f aca="false">IF(J24=0,0,J32/J24)</f>
+        <v>0.338016867243933</v>
+      </c>
+      <c r="K33" s="108" t="n">
+        <f aca="false">IF(K24=0,0,K32/K24)</f>
+        <v>0.327383743644174</v>
+      </c>
+      <c r="L33" s="108" t="n">
+        <f aca="false">IF(L24=0,0,L32/L24)</f>
+        <v>0.316325050022623</v>
+      </c>
+      <c r="M33" s="108" t="n">
+        <f aca="false">IF(M24=0,0,M32/M24)</f>
+        <v>0.298881448019685</v>
+      </c>
+      <c r="N33" s="94" t="n">
+        <f aca="false">IF(N24=0,0,N32/N24)</f>
+        <v>0.325115779267141</v>
+      </c>
+      <c r="O33" s="101"/>
+      <c r="P33" s="152" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="149"/>
+      <c r="B34" s="156"/>
+      <c r="C34" s="156"/>
+      <c r="D34" s="156"/>
+      <c r="E34" s="156"/>
+      <c r="F34" s="156"/>
+      <c r="G34" s="156"/>
+      <c r="H34" s="156"/>
+      <c r="I34" s="156"/>
+      <c r="J34" s="156"/>
+      <c r="K34" s="156"/>
+      <c r="L34" s="156"/>
+      <c r="M34" s="156"/>
+      <c r="N34" s="157"/>
+      <c r="O34" s="101"/>
+    </row>
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="109" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" s="159" t="n">
+        <f aca="false">B24*0.02</f>
+        <v>5063.496</v>
+      </c>
+      <c r="C35" s="159" t="n">
+        <f aca="false">C24*0.02</f>
+        <v>5225.196</v>
+      </c>
+      <c r="D35" s="159" t="n">
+        <f aca="false">D24*0.02</f>
+        <v>5386.896</v>
+      </c>
+      <c r="E35" s="159" t="n">
+        <f aca="false">E24*0.02</f>
+        <v>5602.496</v>
+      </c>
+      <c r="F35" s="159" t="n">
+        <f aca="false">F24*0.02</f>
+        <v>5764.196</v>
+      </c>
+      <c r="G35" s="159" t="n">
+        <f aca="false">G24*0.02</f>
+        <v>5764.196</v>
+      </c>
+      <c r="H35" s="159" t="n">
+        <f aca="false">H24*0.02</f>
+        <v>5656.396</v>
+      </c>
+      <c r="I35" s="159" t="n">
+        <f aca="false">I24*0.02</f>
+        <v>5494.696</v>
+      </c>
+      <c r="J35" s="159" t="n">
+        <f aca="false">J24*0.02</f>
+        <v>5602.496</v>
+      </c>
+      <c r="K35" s="159" t="n">
+        <f aca="false">K24*0.02</f>
+        <v>5494.696</v>
+      </c>
+      <c r="L35" s="159" t="n">
+        <f aca="false">L24*0.02</f>
+        <v>5386.896</v>
+      </c>
+      <c r="M35" s="159" t="n">
+        <f aca="false">M24*0.02</f>
+        <v>5225.196</v>
+      </c>
+      <c r="N35" s="160" t="n">
+        <f aca="false">SUM(B35:M35)</f>
+        <v>65666.852</v>
+      </c>
+      <c r="O35" s="161" t="n">
+        <f aca="false">IF(N24=0,0,N35/N24)</f>
+        <v>0.02</v>
+      </c>
+      <c r="P35" s="152" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="B36" s="153" t="n">
+        <f aca="false">B32-B35</f>
+        <v>65907.4113333333</v>
+      </c>
+      <c r="C36" s="153" t="n">
+        <f aca="false">C32-C35</f>
+        <v>72860.5113333333</v>
+      </c>
+      <c r="D36" s="153" t="n">
+        <f aca="false">D32-D35</f>
+        <v>79813.6113333334</v>
+      </c>
+      <c r="E36" s="153" t="n">
+        <f aca="false">E32-E35</f>
+        <v>89084.4113333333</v>
+      </c>
+      <c r="F36" s="153" t="n">
+        <f aca="false">F32-F35</f>
+        <v>96037.5113333333</v>
+      </c>
+      <c r="G36" s="153" t="n">
+        <f aca="false">G32-G35</f>
+        <v>96037.5113333333</v>
+      </c>
+      <c r="H36" s="153" t="n">
+        <f aca="false">H32-H35</f>
+        <v>91402.1113333334</v>
+      </c>
+      <c r="I36" s="153" t="n">
+        <f aca="false">I32-I35</f>
+        <v>84449.0113333333</v>
+      </c>
+      <c r="J36" s="153" t="n">
+        <f aca="false">J32-J35</f>
+        <v>89084.4113333333</v>
+      </c>
+      <c r="K36" s="153" t="n">
+        <f aca="false">K32-K35</f>
+        <v>84449.0113333333</v>
+      </c>
+      <c r="L36" s="153" t="n">
+        <f aca="false">L32-L35</f>
+        <v>79813.6113333334</v>
+      </c>
+      <c r="M36" s="153" t="n">
+        <f aca="false">M32-M35</f>
+        <v>72860.5113333333</v>
+      </c>
+      <c r="N36" s="154" t="n">
+        <f aca="false">SUM(B36:M36)</f>
+        <v>1001799.636</v>
+      </c>
+      <c r="O36" s="155" t="n">
+        <f aca="false">IF(N24=0,0,N36/N24)</f>
+        <v>0.305115779267141</v>
+      </c>
+      <c r="P36" s="152" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="109" t="s">
+        <v>221</v>
+      </c>
+      <c r="B37" s="159" t="n">
+        <f aca="false">IF(B36&gt;0,B36*0.21,0)</f>
+        <v>13840.55638</v>
+      </c>
+      <c r="C37" s="159" t="n">
+        <f aca="false">IF(C36&gt;0,C36*0.21,0)</f>
+        <v>15300.70738</v>
+      </c>
+      <c r="D37" s="159" t="n">
+        <f aca="false">IF(D36&gt;0,D36*0.21,0)</f>
+        <v>16760.85838</v>
+      </c>
+      <c r="E37" s="159" t="n">
+        <f aca="false">IF(E36&gt;0,E36*0.21,0)</f>
+        <v>18707.72638</v>
+      </c>
+      <c r="F37" s="159" t="n">
+        <f aca="false">IF(F36&gt;0,F36*0.21,0)</f>
+        <v>20167.87738</v>
+      </c>
+      <c r="G37" s="159" t="n">
+        <f aca="false">IF(G36&gt;0,G36*0.21,0)</f>
+        <v>20167.87738</v>
+      </c>
+      <c r="H37" s="159" t="n">
+        <f aca="false">IF(H36&gt;0,H36*0.21,0)</f>
+        <v>19194.44338</v>
+      </c>
+      <c r="I37" s="159" t="n">
+        <f aca="false">IF(I36&gt;0,I36*0.21,0)</f>
+        <v>17734.29238</v>
+      </c>
+      <c r="J37" s="159" t="n">
+        <f aca="false">IF(J36&gt;0,J36*0.21,0)</f>
+        <v>18707.72638</v>
+      </c>
+      <c r="K37" s="159" t="n">
+        <f aca="false">IF(K36&gt;0,K36*0.21,0)</f>
+        <v>17734.29238</v>
+      </c>
+      <c r="L37" s="159" t="n">
+        <f aca="false">IF(L36&gt;0,L36*0.21,0)</f>
+        <v>16760.85838</v>
+      </c>
+      <c r="M37" s="159" t="n">
+        <f aca="false">IF(M36&gt;0,M36*0.21,0)</f>
+        <v>15300.70738</v>
+      </c>
+      <c r="N37" s="160" t="n">
+        <f aca="false">SUM(B37:M37)</f>
+        <v>210377.92356</v>
+      </c>
+      <c r="O37" s="161" t="n">
+        <f aca="false">IF(N24=0,0,N37/N24)</f>
+        <v>0.0640743136460996</v>
+      </c>
+      <c r="P37" s="152" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="77" t="s">
+        <v>154</v>
+      </c>
+      <c r="B38" s="153" t="n">
+        <f aca="false">B36-B37</f>
+        <v>52066.8549533333</v>
+      </c>
+      <c r="C38" s="153" t="n">
+        <f aca="false">C36-C37</f>
+        <v>57559.8039533333</v>
+      </c>
+      <c r="D38" s="153" t="n">
+        <f aca="false">D36-D37</f>
+        <v>63052.7529533333</v>
+      </c>
+      <c r="E38" s="153" t="n">
+        <f aca="false">E36-E37</f>
+        <v>70376.6849533333</v>
+      </c>
+      <c r="F38" s="153" t="n">
+        <f aca="false">F36-F37</f>
+        <v>75869.6339533333</v>
+      </c>
+      <c r="G38" s="153" t="n">
+        <f aca="false">G36-G37</f>
+        <v>75869.6339533333</v>
+      </c>
+      <c r="H38" s="153" t="n">
+        <f aca="false">H36-H37</f>
+        <v>72207.6679533334</v>
+      </c>
+      <c r="I38" s="153" t="n">
+        <f aca="false">I36-I37</f>
+        <v>66714.7189533333</v>
+      </c>
+      <c r="J38" s="153" t="n">
+        <f aca="false">J36-J37</f>
+        <v>70376.6849533333</v>
+      </c>
+      <c r="K38" s="153" t="n">
+        <f aca="false">K36-K37</f>
+        <v>66714.7189533333</v>
+      </c>
+      <c r="L38" s="153" t="n">
+        <f aca="false">L36-L37</f>
+        <v>63052.7529533333</v>
+      </c>
+      <c r="M38" s="153" t="n">
+        <f aca="false">M36-M37</f>
+        <v>57559.8039533333</v>
+      </c>
+      <c r="N38" s="154" t="n">
+        <f aca="false">SUM(B38:M38)</f>
+        <v>791421.71244</v>
+      </c>
+      <c r="O38" s="155" t="n">
+        <f aca="false">IF(N24=0,0,N38/N24)</f>
+        <v>0.241041465621041</v>
+      </c>
+      <c r="P38" s="152" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="117" t="s">
+        <v>224</v>
+      </c>
+      <c r="B40" s="117"/>
+      <c r="C40" s="117"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="117"/>
+      <c r="G40" s="117"/>
+      <c r="H40" s="117"/>
+      <c r="I40" s="117"/>
+      <c r="J40" s="117"/>
+      <c r="K40" s="117"/>
+      <c r="L40" s="117"/>
+      <c r="M40" s="117"/>
+      <c r="N40" s="117"/>
+      <c r="O40" s="117"/>
+      <c r="P40" s="117"/>
+      <c r="Q40" s="117"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="B41" s="38"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="38"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="38"/>
+      <c r="Q41" s="38"/>
+    </row>
+    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="137" t="s">
+        <v>226</v>
+      </c>
+      <c r="B43" s="127" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B44" s="39"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="39"/>
+    </row>
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="129" t="s">
+        <v>229</v>
+      </c>
+      <c r="B45" s="129" t="s">
+        <v>230</v>
+      </c>
+      <c r="C45" s="129" t="s">
+        <v>231</v>
+      </c>
+      <c r="D45" s="129" t="s">
+        <v>232</v>
+      </c>
+      <c r="E45" s="129" t="s">
+        <v>233</v>
+      </c>
+      <c r="F45" s="129" t="s">
+        <v>234</v>
+      </c>
+      <c r="G45" s="129" t="s">
+        <v>235</v>
+      </c>
+      <c r="H45" s="129" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="162" t="s">
+        <v>227</v>
+      </c>
+      <c r="B46" s="163" t="n">
+        <v>55</v>
+      </c>
+      <c r="C46" s="163" t="n">
+        <v>4900</v>
+      </c>
+      <c r="D46" s="163" t="s">
+        <v>237</v>
+      </c>
+      <c r="E46" s="164" t="n">
+        <f aca="false">55*4900*0.82*12+N23</f>
+        <v>3232137.6</v>
+      </c>
+      <c r="F46" s="165" t="n">
+        <f aca="false">(55*4900*0.82*12+N23)-(55*Drivers!$E$25*12)-(55*4900*0.82*12+N23)*0.12</f>
+        <v>1022406.088</v>
+      </c>
+      <c r="G46" s="166" t="s">
+        <v>238</v>
+      </c>
+      <c r="H46" s="167" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="168" t="s">
+        <v>240</v>
+      </c>
+      <c r="B47" s="169" t="n">
+        <v>60</v>
+      </c>
+      <c r="C47" s="169" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D47" s="169" t="s">
+        <v>241</v>
+      </c>
+      <c r="E47" s="170" t="n">
+        <f aca="false">60*5000*0.86*12+N23</f>
+        <v>3676257.6</v>
+      </c>
+      <c r="F47" s="171" t="n">
+        <f aca="false">(60*5000*0.86*12+N23)-(60*Drivers!$E$25*12)-(60*5000*0.86*12+N23)*0.12</f>
+        <v>1247606.688</v>
+      </c>
+      <c r="G47" s="171" t="n">
+        <f aca="false">F47-F46</f>
+        <v>225200.6</v>
+      </c>
+      <c r="H47" s="172" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="173" t="s">
+        <v>243</v>
+      </c>
+      <c r="B48" s="174" t="n">
+        <v>50</v>
+      </c>
+      <c r="C48" s="174" t="n">
+        <v>4700</v>
+      </c>
+      <c r="D48" s="174" t="s">
+        <v>244</v>
+      </c>
+      <c r="E48" s="175" t="n">
+        <f aca="false">50*4700*0.78*12+N23</f>
+        <v>2779857.6</v>
+      </c>
+      <c r="F48" s="176" t="n">
+        <f aca="false">(50*4700*0.78*12+N23)-(50*Drivers!$E$25*12)-(50*4700*0.78*12+N23)*0.12</f>
+        <v>790024.687999998</v>
+      </c>
+      <c r="G48" s="176" t="n">
+        <f aca="false">F48-F46</f>
+        <v>-232381.4</v>
+      </c>
+      <c r="H48" s="177" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="117" t="s">
+        <v>246</v>
+      </c>
+      <c r="B50" s="117"/>
+      <c r="C50" s="117"/>
+      <c r="D50" s="117"/>
+      <c r="E50" s="117"/>
+      <c r="F50" s="117"/>
+      <c r="G50" s="117"/>
+      <c r="H50" s="117"/>
+      <c r="I50" s="117"/>
+      <c r="J50" s="117"/>
+      <c r="K50" s="117"/>
+      <c r="L50" s="117"/>
+      <c r="M50" s="117"/>
+      <c r="N50" s="117"/>
+      <c r="O50" s="117"/>
+      <c r="P50" s="117"/>
+      <c r="Q50" s="117"/>
+    </row>
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="130" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" s="129" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="129" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="129" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="129" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="129" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="129" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="129" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="129" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" s="129" t="s">
+        <v>22</v>
+      </c>
+      <c r="L51" s="129" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" s="129" t="s">
+        <v>24</v>
+      </c>
+      <c r="N51" s="129" t="s">
+        <v>99</v>
+      </c>
+      <c r="O51" s="129" t="s">
+        <v>247</v>
+      </c>
+      <c r="P51" s="130" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="149" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.76,IF($B$43="Upside",0.8,0.72)))</f>
+        <v>204820</v>
+      </c>
+      <c r="C52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.79,IF($B$43="Upside",0.83,0.75)))</f>
+        <v>212905</v>
+      </c>
+      <c r="D52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.82,IF($B$43="Upside",0.86,0.78)))</f>
+        <v>220990</v>
+      </c>
+      <c r="E52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.86,IF($B$43="Upside",0.9,0.82)))</f>
+        <v>231770</v>
+      </c>
+      <c r="F52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.89,IF($B$43="Upside",0.93,0.85)))</f>
+        <v>239855</v>
+      </c>
+      <c r="G52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.89,IF($B$43="Upside",0.93,0.85)))</f>
+        <v>239855</v>
+      </c>
+      <c r="H52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.87,IF($B$43="Upside",0.91,0.83)))</f>
+        <v>234465</v>
+      </c>
+      <c r="I52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.84,IF($B$43="Upside",0.88,0.8)))</f>
+        <v>226380</v>
+      </c>
+      <c r="J52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.86,IF($B$43="Upside",0.9,0.82)))</f>
+        <v>231770</v>
+      </c>
+      <c r="K52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.84,IF($B$43="Upside",0.88,0.8)))</f>
+        <v>226380</v>
+      </c>
+      <c r="L52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.82,IF($B$43="Upside",0.86,0.78)))</f>
+        <v>220990</v>
+      </c>
+      <c r="M52" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.79,IF($B$43="Upside",0.83,0.75)))</f>
+        <v>212905</v>
+      </c>
+      <c r="N52" s="151" t="n">
+        <f aca="false">SUM(B52:M52)</f>
+        <v>2703085</v>
+      </c>
+      <c r="O52" s="178" t="n">
+        <f aca="false">IF(N54=0,0,N52/N54)</f>
+        <v>0.823272295739105</v>
+      </c>
+      <c r="P52" s="152" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="149" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="150" t="n">
+        <f aca="false">B23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="C53" s="150" t="n">
+        <f aca="false">C23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="D53" s="150" t="n">
+        <f aca="false">D23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="E53" s="150" t="n">
+        <f aca="false">E23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="F53" s="150" t="n">
+        <f aca="false">F23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="G53" s="150" t="n">
+        <f aca="false">G23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="H53" s="150" t="n">
+        <f aca="false">H23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="I53" s="150" t="n">
+        <f aca="false">I23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="J53" s="150" t="n">
+        <f aca="false">J23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="K53" s="150" t="n">
+        <f aca="false">K23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="L53" s="150" t="n">
+        <f aca="false">L23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="M53" s="150" t="n">
+        <f aca="false">M23</f>
+        <v>48354.8</v>
+      </c>
+      <c r="N53" s="151" t="n">
+        <f aca="false">SUM(B53:M53)</f>
+        <v>580257.6</v>
+      </c>
+      <c r="O53" s="178" t="n">
+        <f aca="false">IF(N54=0,0,N53/N54)</f>
+        <v>0.176727704260896</v>
+      </c>
+      <c r="P53" s="152" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="77" t="s">
+        <v>210</v>
+      </c>
+      <c r="B54" s="153" t="n">
+        <f aca="false">B52+B53</f>
+        <v>253174.8</v>
+      </c>
+      <c r="C54" s="153" t="n">
+        <f aca="false">C52+C53</f>
+        <v>261259.8</v>
+      </c>
+      <c r="D54" s="153" t="n">
+        <f aca="false">D52+D53</f>
+        <v>269344.8</v>
+      </c>
+      <c r="E54" s="153" t="n">
+        <f aca="false">E52+E53</f>
+        <v>280124.8</v>
+      </c>
+      <c r="F54" s="153" t="n">
+        <f aca="false">F52+F53</f>
+        <v>288209.8</v>
+      </c>
+      <c r="G54" s="153" t="n">
+        <f aca="false">G52+G53</f>
+        <v>288209.8</v>
+      </c>
+      <c r="H54" s="153" t="n">
+        <f aca="false">H52+H53</f>
+        <v>282819.8</v>
+      </c>
+      <c r="I54" s="153" t="n">
+        <f aca="false">I52+I53</f>
+        <v>274734.8</v>
+      </c>
+      <c r="J54" s="153" t="n">
+        <f aca="false">J52+J53</f>
+        <v>280124.8</v>
+      </c>
+      <c r="K54" s="153" t="n">
+        <f aca="false">K52+K53</f>
+        <v>274734.8</v>
+      </c>
+      <c r="L54" s="153" t="n">
+        <f aca="false">L52+L53</f>
+        <v>269344.8</v>
+      </c>
+      <c r="M54" s="153" t="n">
+        <f aca="false">M52+M53</f>
+        <v>261259.8</v>
+      </c>
+      <c r="N54" s="154" t="n">
+        <f aca="false">SUM(B54:M54)</f>
+        <v>3283342.6</v>
+      </c>
+      <c r="O54" s="179" t="n">
+        <f aca="false">IF(N54=0,0,N54/N54)</f>
+        <v>1</v>
+      </c>
+      <c r="P54" s="152" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="149"/>
+      <c r="B55" s="156"/>
+      <c r="C55" s="156"/>
+      <c r="D55" s="156"/>
+      <c r="E55" s="156"/>
+      <c r="F55" s="156"/>
+      <c r="G55" s="156"/>
+      <c r="H55" s="156"/>
+      <c r="I55" s="156"/>
+      <c r="J55" s="156"/>
+      <c r="K55" s="156"/>
+      <c r="L55" s="156"/>
+      <c r="M55" s="156"/>
+      <c r="N55" s="157"/>
+      <c r="O55" s="101"/>
+    </row>
+    <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="149" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="C56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="D56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="E56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="F56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="G56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="H56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="I56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="J56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="K56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="L56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="M56" s="150" t="n">
+        <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
+        <v>151822.916666667</v>
+      </c>
+      <c r="N56" s="151" t="n">
+        <f aca="false">SUM(B56:M56)</f>
+        <v>1821875</v>
+      </c>
+      <c r="O56" s="178" t="n">
+        <f aca="false">IF(N54=0,0,N56/N54)</f>
+        <v>0.554884220732859</v>
+      </c>
+      <c r="P56" s="152" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="149" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" s="150" t="n">
+        <f aca="false">B54*0.08</f>
+        <v>20253.984</v>
+      </c>
+      <c r="C57" s="150" t="n">
+        <f aca="false">C54*0.08</f>
+        <v>20900.784</v>
+      </c>
+      <c r="D57" s="150" t="n">
+        <f aca="false">D54*0.08</f>
+        <v>21547.584</v>
+      </c>
+      <c r="E57" s="150" t="n">
+        <f aca="false">E54*0.08</f>
+        <v>22409.984</v>
+      </c>
+      <c r="F57" s="150" t="n">
+        <f aca="false">F54*0.08</f>
+        <v>23056.784</v>
+      </c>
+      <c r="G57" s="150" t="n">
+        <f aca="false">G54*0.08</f>
+        <v>23056.784</v>
+      </c>
+      <c r="H57" s="150" t="n">
+        <f aca="false">H54*0.08</f>
+        <v>22625.584</v>
+      </c>
+      <c r="I57" s="150" t="n">
+        <f aca="false">I54*0.08</f>
+        <v>21978.784</v>
+      </c>
+      <c r="J57" s="150" t="n">
+        <f aca="false">J54*0.08</f>
+        <v>22409.984</v>
+      </c>
+      <c r="K57" s="150" t="n">
+        <f aca="false">K54*0.08</f>
+        <v>21978.784</v>
+      </c>
+      <c r="L57" s="150" t="n">
+        <f aca="false">L54*0.08</f>
+        <v>21547.584</v>
+      </c>
+      <c r="M57" s="150" t="n">
+        <f aca="false">M54*0.08</f>
+        <v>20900.784</v>
+      </c>
+      <c r="N57" s="151" t="n">
+        <f aca="false">SUM(B57:M57)</f>
+        <v>262667.408</v>
+      </c>
+      <c r="O57" s="178" t="n">
+        <f aca="false">IF(N54=0,0,N57/N54)</f>
+        <v>0.08</v>
+      </c>
+      <c r="P57" s="152" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="149" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="150" t="n">
+        <f aca="false">B54*0.04</f>
+        <v>10126.992</v>
+      </c>
+      <c r="C58" s="150" t="n">
+        <f aca="false">C54*0.04</f>
+        <v>10450.392</v>
+      </c>
+      <c r="D58" s="150" t="n">
+        <f aca="false">D54*0.04</f>
+        <v>10773.792</v>
+      </c>
+      <c r="E58" s="150" t="n">
+        <f aca="false">E54*0.04</f>
+        <v>11204.992</v>
+      </c>
+      <c r="F58" s="150" t="n">
+        <f aca="false">F54*0.04</f>
+        <v>11528.392</v>
+      </c>
+      <c r="G58" s="150" t="n">
+        <f aca="false">G54*0.04</f>
+        <v>11528.392</v>
+      </c>
+      <c r="H58" s="150" t="n">
+        <f aca="false">H54*0.04</f>
+        <v>11312.792</v>
+      </c>
+      <c r="I58" s="150" t="n">
+        <f aca="false">I54*0.04</f>
+        <v>10989.392</v>
+      </c>
+      <c r="J58" s="150" t="n">
+        <f aca="false">J54*0.04</f>
+        <v>11204.992</v>
+      </c>
+      <c r="K58" s="150" t="n">
+        <f aca="false">K54*0.04</f>
+        <v>10989.392</v>
+      </c>
+      <c r="L58" s="150" t="n">
+        <f aca="false">L54*0.04</f>
+        <v>10773.792</v>
+      </c>
+      <c r="M58" s="150" t="n">
+        <f aca="false">M54*0.04</f>
+        <v>10450.392</v>
+      </c>
+      <c r="N58" s="151" t="n">
+        <f aca="false">SUM(B58:M58)</f>
+        <v>131333.704</v>
+      </c>
+      <c r="O58" s="178" t="n">
+        <f aca="false">IF(N54=0,0,N58/N54)</f>
+        <v>0.04</v>
+      </c>
+      <c r="P58" s="152" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="B59" s="153" t="n">
+        <f aca="false">B56+B57+B58</f>
+        <v>182203.892666667</v>
+      </c>
+      <c r="C59" s="153" t="n">
+        <f aca="false">C56+C57+C58</f>
+        <v>183174.092666667</v>
+      </c>
+      <c r="D59" s="153" t="n">
+        <f aca="false">D56+D57+D58</f>
+        <v>184144.292666667</v>
+      </c>
+      <c r="E59" s="153" t="n">
+        <f aca="false">E56+E57+E58</f>
+        <v>185437.892666667</v>
+      </c>
+      <c r="F59" s="153" t="n">
+        <f aca="false">F56+F57+F58</f>
+        <v>186408.092666667</v>
+      </c>
+      <c r="G59" s="153" t="n">
+        <f aca="false">G56+G57+G58</f>
+        <v>186408.092666667</v>
+      </c>
+      <c r="H59" s="153" t="n">
+        <f aca="false">H56+H57+H58</f>
+        <v>185761.292666667</v>
+      </c>
+      <c r="I59" s="153" t="n">
+        <f aca="false">I56+I57+I58</f>
+        <v>184791.092666667</v>
+      </c>
+      <c r="J59" s="153" t="n">
+        <f aca="false">J56+J57+J58</f>
+        <v>185437.892666667</v>
+      </c>
+      <c r="K59" s="153" t="n">
+        <f aca="false">K56+K57+K58</f>
+        <v>184791.092666667</v>
+      </c>
+      <c r="L59" s="153" t="n">
+        <f aca="false">L56+L57+L58</f>
+        <v>184144.292666667</v>
+      </c>
+      <c r="M59" s="153" t="n">
+        <f aca="false">M56+M57+M58</f>
+        <v>183174.092666667</v>
+      </c>
+      <c r="N59" s="154" t="n">
+        <f aca="false">SUM(B59:M59)</f>
+        <v>2215876.112</v>
+      </c>
+      <c r="O59" s="179" t="n">
+        <f aca="false">IF(N54=0,0,N59/N54)</f>
+        <v>0.674884220732859</v>
+      </c>
+      <c r="P59" s="152" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="149"/>
+      <c r="B60" s="156"/>
+      <c r="C60" s="156"/>
+      <c r="D60" s="156"/>
+      <c r="E60" s="156"/>
+      <c r="F60" s="156"/>
+      <c r="G60" s="156"/>
+      <c r="H60" s="156"/>
+      <c r="I60" s="156"/>
+      <c r="J60" s="156"/>
+      <c r="K60" s="156"/>
+      <c r="L60" s="156"/>
+      <c r="M60" s="156"/>
+      <c r="N60" s="157"/>
+      <c r="O60" s="101"/>
+    </row>
+    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="105" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="147" t="n">
+        <f aca="false">B54-B59</f>
+        <v>70970.9073333333</v>
+      </c>
+      <c r="C61" s="147" t="n">
+        <f aca="false">C54-C59</f>
+        <v>78085.7073333333</v>
+      </c>
+      <c r="D61" s="147" t="n">
+        <f aca="false">D54-D59</f>
+        <v>85200.5073333333</v>
+      </c>
+      <c r="E61" s="147" t="n">
+        <f aca="false">E54-E59</f>
+        <v>94686.9073333333</v>
+      </c>
+      <c r="F61" s="147" t="n">
+        <f aca="false">F54-F59</f>
+        <v>101801.707333333</v>
+      </c>
+      <c r="G61" s="147" t="n">
+        <f aca="false">G54-G59</f>
+        <v>101801.707333333</v>
+      </c>
+      <c r="H61" s="147" t="n">
+        <f aca="false">H54-H59</f>
+        <v>97058.5073333333</v>
+      </c>
+      <c r="I61" s="147" t="n">
+        <f aca="false">I54-I59</f>
+        <v>89943.7073333333</v>
+      </c>
+      <c r="J61" s="147" t="n">
+        <f aca="false">J54-J59</f>
+        <v>94686.9073333333</v>
+      </c>
+      <c r="K61" s="147" t="n">
+        <f aca="false">K54-K59</f>
+        <v>89943.7073333333</v>
+      </c>
+      <c r="L61" s="147" t="n">
+        <f aca="false">L54-L59</f>
+        <v>85200.5073333333</v>
+      </c>
+      <c r="M61" s="147" t="n">
+        <f aca="false">M54-M59</f>
+        <v>78085.7073333333</v>
+      </c>
+      <c r="N61" s="147" t="n">
+        <f aca="false">SUM(B61:M61)</f>
+        <v>1067466.488</v>
+      </c>
+      <c r="O61" s="180" t="n">
+        <f aca="false">IF(N54=0,0,N61/N54)</f>
+        <v>0.325115779267141</v>
+      </c>
+      <c r="P61" s="152" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="149" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="108" t="n">
+        <f aca="false">IF(B54=0,0,B61/B54)</f>
+        <v>0.280323742068063</v>
+      </c>
+      <c r="C62" s="108" t="n">
+        <f aca="false">IF(C54=0,0,C61/C54)</f>
+        <v>0.298881448019685</v>
+      </c>
+      <c r="D62" s="108" t="n">
+        <f aca="false">IF(D54=0,0,D61/D54)</f>
+        <v>0.316325050022623</v>
+      </c>
+      <c r="E62" s="108" t="n">
+        <f aca="false">IF(E54=0,0,E61/E54)</f>
+        <v>0.338016867243933</v>
+      </c>
+      <c r="F62" s="108" t="n">
+        <f aca="false">IF(F54=0,0,F61/F54)</f>
+        <v>0.353220838893519</v>
+      </c>
+      <c r="G62" s="108" t="n">
+        <f aca="false">IF(G54=0,0,G61/G54)</f>
+        <v>0.353220838893519</v>
+      </c>
+      <c r="H62" s="108" t="n">
+        <f aca="false">IF(H54=0,0,H61/H54)</f>
+        <v>0.343181443920593</v>
+      </c>
+      <c r="I62" s="108" t="n">
+        <f aca="false">IF(I54=0,0,I61/I54)</f>
+        <v>0.327383743644174</v>
+      </c>
+      <c r="J62" s="108" t="n">
+        <f aca="false">IF(J54=0,0,J61/J54)</f>
+        <v>0.338016867243933</v>
+      </c>
+      <c r="K62" s="108" t="n">
+        <f aca="false">IF(K54=0,0,K61/K54)</f>
+        <v>0.327383743644174</v>
+      </c>
+      <c r="L62" s="108" t="n">
+        <f aca="false">IF(L54=0,0,L61/L54)</f>
+        <v>0.316325050022623</v>
+      </c>
+      <c r="M62" s="108" t="n">
+        <f aca="false">IF(M54=0,0,M61/M54)</f>
+        <v>0.298881448019685</v>
+      </c>
+      <c r="N62" s="94" t="n">
+        <f aca="false">IF(N54=0,0,N61/N54)</f>
+        <v>0.325115779267141</v>
+      </c>
+      <c r="O62" s="101"/>
+      <c r="P62" s="152" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="117" t="s">
+        <v>254</v>
+      </c>
+      <c r="B65" s="117"/>
+      <c r="C65" s="117"/>
+      <c r="D65" s="117"/>
+      <c r="E65" s="117"/>
+      <c r="F65" s="117"/>
+      <c r="G65" s="117"/>
+      <c r="H65" s="117"/>
+      <c r="I65" s="117"/>
+      <c r="J65" s="117"/>
+      <c r="K65" s="117"/>
+      <c r="L65" s="117"/>
+      <c r="M65" s="117"/>
+      <c r="N65" s="117"/>
+      <c r="O65" s="117"/>
+      <c r="P65" s="117"/>
+      <c r="Q65" s="117"/>
+    </row>
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="181" t="s">
+        <v>255</v>
+      </c>
+      <c r="B66" s="181"/>
+      <c r="C66" s="181"/>
+      <c r="D66" s="181"/>
+      <c r="E66" s="181"/>
+      <c r="F66" s="181"/>
+      <c r="G66" s="181"/>
+      <c r="H66" s="181"/>
+      <c r="I66" s="181"/>
+      <c r="J66" s="181"/>
+      <c r="K66" s="181"/>
+      <c r="L66" s="181"/>
+      <c r="M66" s="181"/>
+      <c r="N66" s="181"/>
+      <c r="O66" s="181"/>
+      <c r="P66" s="181"/>
+      <c r="Q66" s="181"/>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="182" t="s">
+        <v>256</v>
+      </c>
+      <c r="B68" s="182"/>
+      <c r="C68" s="182"/>
+      <c r="D68" s="182"/>
+      <c r="E68" s="182"/>
+      <c r="F68" s="182"/>
+      <c r="G68" s="182"/>
+      <c r="H68" s="182"/>
+      <c r="I68" s="182"/>
+    </row>
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="129" t="s">
+        <v>257</v>
+      </c>
+      <c r="B69" s="129" t="s">
+        <v>258</v>
+      </c>
+      <c r="C69" s="129" t="s">
+        <v>259</v>
+      </c>
+      <c r="D69" s="129" t="s">
+        <v>260</v>
+      </c>
+      <c r="E69" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F69" s="129" t="s">
+        <v>261</v>
+      </c>
+      <c r="G69" s="129" t="s">
+        <v>61</v>
+      </c>
+      <c r="H69" s="129" t="s">
+        <v>62</v>
+      </c>
+      <c r="I69" s="129" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="183" t="n">
+        <v>48</v>
+      </c>
+      <c r="B70" s="184" t="n">
+        <f aca="false">48*4900*0.82*12</f>
+        <v>2314368</v>
+      </c>
+      <c r="C70" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D70" s="184" t="n">
+        <f aca="false">B70+C70</f>
+        <v>2894625.6</v>
+      </c>
+      <c r="E70" s="184" t="n">
+        <f aca="false">48*Drivers!$E$25*12</f>
+        <v>1590000</v>
+      </c>
+      <c r="F70" s="184" t="n">
+        <f aca="false">D70*0.12</f>
+        <v>347355.072</v>
+      </c>
+      <c r="G70" s="184" t="n">
+        <f aca="false">E70+F70</f>
+        <v>1937355.072</v>
+      </c>
+      <c r="H70" s="185" t="n">
+        <f aca="false">D70-G70</f>
+        <v>957270.528</v>
+      </c>
+      <c r="I70" s="186" t="n">
+        <f aca="false">IF(D70=0,0,H70/D70)</f>
+        <v>0.330706163864508</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="187" t="n">
+        <v>50</v>
+      </c>
+      <c r="B71" s="188" t="n">
+        <f aca="false">50*4900*0.82*12</f>
+        <v>2410800</v>
+      </c>
+      <c r="C71" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D71" s="188" t="n">
+        <f aca="false">B71+C71</f>
+        <v>2991057.6</v>
+      </c>
+      <c r="E71" s="188" t="n">
+        <f aca="false">50*Drivers!$E$25*12</f>
+        <v>1656250</v>
+      </c>
+      <c r="F71" s="188" t="n">
+        <f aca="false">D71*0.12</f>
+        <v>358926.912</v>
+      </c>
+      <c r="G71" s="188" t="n">
+        <f aca="false">E71+F71</f>
+        <v>2015176.912</v>
+      </c>
+      <c r="H71" s="189" t="n">
+        <f aca="false">D71-G71</f>
+        <v>975880.688</v>
+      </c>
+      <c r="I71" s="190" t="n">
+        <f aca="false">IF(D71=0,0,H71/D71)</f>
+        <v>0.326266096647554</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="183" t="n">
+        <v>52</v>
+      </c>
+      <c r="B72" s="184" t="n">
+        <f aca="false">52*4900*0.82*12</f>
+        <v>2507232</v>
+      </c>
+      <c r="C72" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D72" s="184" t="n">
+        <f aca="false">B72+C72</f>
+        <v>3087489.6</v>
+      </c>
+      <c r="E72" s="184" t="n">
+        <f aca="false">52*Drivers!$E$25*12</f>
+        <v>1722500</v>
+      </c>
+      <c r="F72" s="184" t="n">
+        <f aca="false">D72*0.12</f>
+        <v>370498.752</v>
+      </c>
+      <c r="G72" s="184" t="n">
+        <f aca="false">E72+F72</f>
+        <v>2092998.752</v>
+      </c>
+      <c r="H72" s="185" t="n">
+        <f aca="false">D72-G72</f>
+        <v>994490.848</v>
+      </c>
+      <c r="I72" s="186" t="n">
+        <f aca="false">IF(D72=0,0,H72/D72)</f>
+        <v>0.322103383927188</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="191" t="n">
+        <v>54</v>
+      </c>
+      <c r="B73" s="192" t="n">
+        <f aca="false">54*4900*0.82*12</f>
+        <v>2603664</v>
+      </c>
+      <c r="C73" s="192" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D73" s="192" t="n">
+        <f aca="false">B73+C73</f>
+        <v>3183921.6</v>
+      </c>
+      <c r="E73" s="192" t="n">
+        <f aca="false">54*Drivers!$E$25*12</f>
+        <v>1788750</v>
+      </c>
+      <c r="F73" s="192" t="n">
+        <f aca="false">D73*0.12</f>
+        <v>382070.592</v>
+      </c>
+      <c r="G73" s="192" t="n">
+        <f aca="false">E73+F73</f>
+        <v>2170820.592</v>
+      </c>
+      <c r="H73" s="193" t="n">
+        <f aca="false">D73-G73</f>
+        <v>1013101.008</v>
+      </c>
+      <c r="I73" s="194" t="n">
+        <f aca="false">IF(D73=0,0,H73/D73)</f>
+        <v>0.318192824848451</v>
+      </c>
+      <c r="J73" s="195" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="183" t="n">
+        <v>56</v>
+      </c>
+      <c r="B74" s="184" t="n">
+        <f aca="false">56*4900*0.82*12</f>
+        <v>2700096</v>
+      </c>
+      <c r="C74" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D74" s="184" t="n">
+        <f aca="false">B74+C74</f>
+        <v>3280353.6</v>
+      </c>
+      <c r="E74" s="184" t="n">
+        <f aca="false">56*Drivers!$E$25*12</f>
+        <v>1855000</v>
+      </c>
+      <c r="F74" s="184" t="n">
+        <f aca="false">D74*0.12</f>
+        <v>393642.432</v>
+      </c>
+      <c r="G74" s="184" t="n">
+        <f aca="false">E74+F74</f>
+        <v>2248642.432</v>
+      </c>
+      <c r="H74" s="185" t="n">
+        <f aca="false">D74-G74</f>
+        <v>1031711.168</v>
+      </c>
+      <c r="I74" s="186" t="n">
+        <f aca="false">IF(D74=0,0,H74/D74)</f>
+        <v>0.314512181857468</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="187" t="n">
+        <v>58</v>
+      </c>
+      <c r="B75" s="188" t="n">
+        <f aca="false">58*4900*0.82*12</f>
+        <v>2796528</v>
+      </c>
+      <c r="C75" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D75" s="188" t="n">
+        <f aca="false">B75+C75</f>
+        <v>3376785.6</v>
+      </c>
+      <c r="E75" s="188" t="n">
+        <f aca="false">58*Drivers!$E$25*12</f>
+        <v>1921250</v>
+      </c>
+      <c r="F75" s="188" t="n">
+        <f aca="false">D75*0.12</f>
+        <v>405214.272</v>
+      </c>
+      <c r="G75" s="188" t="n">
+        <f aca="false">E75+F75</f>
+        <v>2326464.272</v>
+      </c>
+      <c r="H75" s="189" t="n">
+        <f aca="false">D75-G75</f>
+        <v>1050321.328</v>
+      </c>
+      <c r="I75" s="190" t="n">
+        <f aca="false">IF(D75=0,0,H75/D75)</f>
+        <v>0.31104175758153</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="183" t="n">
+        <v>60</v>
+      </c>
+      <c r="B76" s="184" t="n">
+        <f aca="false">60*4900*0.82*12</f>
+        <v>2892960</v>
+      </c>
+      <c r="C76" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D76" s="184" t="n">
+        <f aca="false">B76+C76</f>
+        <v>3473217.6</v>
+      </c>
+      <c r="E76" s="184" t="n">
+        <f aca="false">60*Drivers!$E$25*12</f>
+        <v>1987500</v>
+      </c>
+      <c r="F76" s="184" t="n">
+        <f aca="false">D76*0.12</f>
+        <v>416786.112</v>
+      </c>
+      <c r="G76" s="184" t="n">
+        <f aca="false">E76+F76</f>
+        <v>2404286.112</v>
+      </c>
+      <c r="H76" s="185" t="n">
+        <f aca="false">D76-G76</f>
+        <v>1068931.488</v>
+      </c>
+      <c r="I76" s="186" t="n">
+        <f aca="false">IF(D76=0,0,H76/D76)</f>
+        <v>0.307764042195341</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="187" t="n">
+        <v>62</v>
+      </c>
+      <c r="B77" s="188" t="n">
+        <f aca="false">62*4900*0.82*12</f>
+        <v>2989392</v>
+      </c>
+      <c r="C77" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D77" s="188" t="n">
+        <f aca="false">B77+C77</f>
+        <v>3569649.6</v>
+      </c>
+      <c r="E77" s="188" t="n">
+        <f aca="false">62*Drivers!$E$25*12</f>
+        <v>2053750</v>
+      </c>
+      <c r="F77" s="188" t="n">
+        <f aca="false">D77*0.12</f>
+        <v>428357.952</v>
+      </c>
+      <c r="G77" s="188" t="n">
+        <f aca="false">E77+F77</f>
+        <v>2482107.952</v>
+      </c>
+      <c r="H77" s="189" t="n">
+        <f aca="false">D77-G77</f>
+        <v>1087541.648</v>
+      </c>
+      <c r="I77" s="190" t="n">
+        <f aca="false">IF(D77=0,0,H77/D77)</f>
+        <v>0.304663417944439</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="182" t="s">
+        <v>264</v>
+      </c>
+      <c r="B80" s="182"/>
+      <c r="C80" s="182"/>
+      <c r="D80" s="182"/>
+      <c r="E80" s="182"/>
+      <c r="F80" s="182"/>
+      <c r="G80" s="182"/>
+      <c r="H80" s="182"/>
+      <c r="I80" s="182"/>
+    </row>
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="129" t="s">
+        <v>231</v>
+      </c>
+      <c r="B81" s="129" t="s">
+        <v>258</v>
+      </c>
+      <c r="C81" s="129" t="s">
+        <v>259</v>
+      </c>
+      <c r="D81" s="129" t="s">
+        <v>260</v>
+      </c>
+      <c r="E81" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F81" s="129" t="s">
+        <v>261</v>
+      </c>
+      <c r="G81" s="129" t="s">
+        <v>61</v>
+      </c>
+      <c r="H81" s="129" t="s">
+        <v>62</v>
+      </c>
+      <c r="I81" s="129" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="196" t="n">
+        <v>4400</v>
+      </c>
+      <c r="B82" s="184" t="n">
+        <f aca="false">55*4400*0.82*12</f>
+        <v>2381280</v>
+      </c>
+      <c r="C82" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D82" s="184" t="n">
+        <f aca="false">B82+C82</f>
+        <v>2961537.6</v>
+      </c>
+      <c r="E82" s="184" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F82" s="184" t="n">
+        <f aca="false">D82*0.12</f>
+        <v>355384.512</v>
+      </c>
+      <c r="G82" s="184" t="n">
+        <f aca="false">E82+F82</f>
+        <v>2177259.512</v>
+      </c>
+      <c r="H82" s="185" t="n">
+        <f aca="false">D82-G82</f>
+        <v>784278.088</v>
+      </c>
+      <c r="I82" s="186" t="n">
+        <f aca="false">IF(D82=0,0,H82/D82)</f>
+        <v>0.264821249610338</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="197" t="n">
+        <v>4600</v>
+      </c>
+      <c r="B83" s="188" t="n">
+        <f aca="false">55*4600*0.82*12</f>
+        <v>2489520</v>
+      </c>
+      <c r="C83" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D83" s="188" t="n">
+        <f aca="false">B83+C83</f>
+        <v>3069777.6</v>
+      </c>
+      <c r="E83" s="188" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F83" s="188" t="n">
+        <f aca="false">D83*0.12</f>
+        <v>368373.312</v>
+      </c>
+      <c r="G83" s="188" t="n">
+        <f aca="false">E83+F83</f>
+        <v>2190248.312</v>
+      </c>
+      <c r="H83" s="189" t="n">
+        <f aca="false">D83-G83</f>
+        <v>879529.288</v>
+      </c>
+      <c r="I83" s="190" t="n">
+        <f aca="false">IF(D83=0,0,H83/D83)</f>
+        <v>0.286512380571153</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="198" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B84" s="192" t="n">
+        <f aca="false">55*4800*0.82*12</f>
+        <v>2597760</v>
+      </c>
+      <c r="C84" s="192" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D84" s="192" t="n">
+        <f aca="false">B84+C84</f>
+        <v>3178017.6</v>
+      </c>
+      <c r="E84" s="192" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F84" s="192" t="n">
+        <f aca="false">D84*0.12</f>
+        <v>381362.112</v>
+      </c>
+      <c r="G84" s="192" t="n">
+        <f aca="false">E84+F84</f>
+        <v>2203237.112</v>
+      </c>
+      <c r="H84" s="193" t="n">
+        <f aca="false">D84-G84</f>
+        <v>974780.488</v>
+      </c>
+      <c r="I84" s="194" t="n">
+        <f aca="false">IF(D84=0,0,H84/D84)</f>
+        <v>0.306725956457887</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="197" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B85" s="188" t="n">
+        <f aca="false">55*5000*0.82*12</f>
+        <v>2706000</v>
+      </c>
+      <c r="C85" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D85" s="188" t="n">
+        <f aca="false">B85+C85</f>
+        <v>3286257.6</v>
+      </c>
+      <c r="E85" s="188" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F85" s="188" t="n">
+        <f aca="false">D85*0.12</f>
+        <v>394350.912</v>
+      </c>
+      <c r="G85" s="188" t="n">
+        <f aca="false">E85+F85</f>
+        <v>2216225.912</v>
+      </c>
+      <c r="H85" s="189" t="n">
+        <f aca="false">D85-G85</f>
+        <v>1070031.688</v>
+      </c>
+      <c r="I85" s="190" t="n">
+        <f aca="false">IF(D85=0,0,H85/D85)</f>
+        <v>0.325607976684482</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="196" t="n">
+        <v>5200</v>
+      </c>
+      <c r="B86" s="184" t="n">
+        <f aca="false">55*5200*0.82*12</f>
+        <v>2814240</v>
+      </c>
+      <c r="C86" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D86" s="184" t="n">
+        <f aca="false">B86+C86</f>
+        <v>3394497.6</v>
+      </c>
+      <c r="E86" s="184" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F86" s="184" t="n">
+        <f aca="false">D86*0.12</f>
+        <v>407339.712</v>
+      </c>
+      <c r="G86" s="184" t="n">
+        <f aca="false">E86+F86</f>
+        <v>2229214.712</v>
+      </c>
+      <c r="H86" s="185" t="n">
+        <f aca="false">D86-G86</f>
+        <v>1165282.888</v>
+      </c>
+      <c r="I86" s="186" t="n">
+        <f aca="false">IF(D86=0,0,H86/D86)</f>
+        <v>0.343285818790975</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="197" t="n">
+        <v>5400</v>
+      </c>
+      <c r="B87" s="188" t="n">
+        <f aca="false">55*5400*0.82*12</f>
+        <v>2922480</v>
+      </c>
+      <c r="C87" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D87" s="188" t="n">
+        <f aca="false">B87+C87</f>
+        <v>3502737.6</v>
+      </c>
+      <c r="E87" s="188" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F87" s="188" t="n">
+        <f aca="false">D87*0.12</f>
+        <v>420328.512</v>
+      </c>
+      <c r="G87" s="188" t="n">
+        <f aca="false">E87+F87</f>
+        <v>2242203.512</v>
+      </c>
+      <c r="H87" s="189" t="n">
+        <f aca="false">D87-G87</f>
+        <v>1260534.088</v>
+      </c>
+      <c r="I87" s="190" t="n">
+        <f aca="false">IF(D87=0,0,H87/D87)</f>
+        <v>0.359871115666786</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="182" t="s">
+        <v>265</v>
+      </c>
+      <c r="B90" s="182"/>
+      <c r="C90" s="182"/>
+      <c r="D90" s="182"/>
+      <c r="E90" s="182"/>
+      <c r="F90" s="182"/>
+      <c r="G90" s="182"/>
+      <c r="H90" s="182"/>
+      <c r="I90" s="182"/>
+    </row>
+    <row r="91" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="129" t="s">
+        <v>266</v>
+      </c>
+      <c r="B91" s="129" t="s">
+        <v>258</v>
+      </c>
+      <c r="C91" s="129" t="s">
+        <v>259</v>
+      </c>
+      <c r="D91" s="129" t="s">
+        <v>260</v>
+      </c>
+      <c r="E91" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F91" s="129" t="s">
+        <v>261</v>
+      </c>
+      <c r="G91" s="129" t="s">
+        <v>61</v>
+      </c>
+      <c r="H91" s="129" t="s">
+        <v>62</v>
+      </c>
+      <c r="I91" s="129" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="199" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B92" s="184" t="n">
+        <f aca="false">55*4900*0.7*12</f>
+        <v>2263800</v>
+      </c>
+      <c r="C92" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D92" s="184" t="n">
+        <f aca="false">B92+C92</f>
+        <v>2844057.6</v>
+      </c>
+      <c r="E92" s="184" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F92" s="184" t="n">
+        <f aca="false">D92*0.12</f>
+        <v>341286.912</v>
+      </c>
+      <c r="G92" s="184" t="n">
+        <f aca="false">E92+F92</f>
+        <v>2163161.912</v>
+      </c>
+      <c r="H92" s="185" t="n">
+        <f aca="false">D92-G92</f>
+        <v>680895.688</v>
+      </c>
+      <c r="I92" s="186" t="n">
+        <f aca="false">IF(D92=0,0,H92/D92)</f>
+        <v>0.239409950065709</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="200" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="B93" s="188" t="n">
+        <f aca="false">55*4900*0.72*12</f>
+        <v>2328480</v>
+      </c>
+      <c r="C93" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D93" s="188" t="n">
+        <f aca="false">B93+C93</f>
+        <v>2908737.6</v>
+      </c>
+      <c r="E93" s="188" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F93" s="188" t="n">
+        <f aca="false">D93*0.12</f>
+        <v>349048.512</v>
+      </c>
+      <c r="G93" s="188" t="n">
+        <f aca="false">E93+F93</f>
+        <v>2170923.512</v>
+      </c>
+      <c r="H93" s="189" t="n">
+        <f aca="false">D93-G93</f>
+        <v>737814.088</v>
+      </c>
+      <c r="I93" s="190" t="n">
+        <f aca="false">IF(D93=0,0,H93/D93)</f>
+        <v>0.253654399076768</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="199" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="B94" s="184" t="n">
+        <f aca="false">55*4900*0.74*12</f>
+        <v>2393160</v>
+      </c>
+      <c r="C94" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D94" s="184" t="n">
+        <f aca="false">B94+C94</f>
+        <v>2973417.6</v>
+      </c>
+      <c r="E94" s="184" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F94" s="184" t="n">
+        <f aca="false">D94*0.12</f>
+        <v>356810.112</v>
+      </c>
+      <c r="G94" s="184" t="n">
+        <f aca="false">E94+F94</f>
+        <v>2178685.112</v>
+      </c>
+      <c r="H94" s="185" t="n">
+        <f aca="false">D94-G94</f>
+        <v>794732.488</v>
+      </c>
+      <c r="I94" s="186" t="n">
+        <f aca="false">IF(D94=0,0,H94/D94)</f>
+        <v>0.267279136304298</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="200" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="B95" s="188" t="n">
+        <f aca="false">55*4900*0.76*12</f>
+        <v>2457840</v>
+      </c>
+      <c r="C95" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D95" s="188" t="n">
+        <f aca="false">B95+C95</f>
+        <v>3038097.6</v>
+      </c>
+      <c r="E95" s="188" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F95" s="188" t="n">
+        <f aca="false">D95*0.12</f>
+        <v>364571.712</v>
+      </c>
+      <c r="G95" s="188" t="n">
+        <f aca="false">E95+F95</f>
+        <v>2186446.712</v>
+      </c>
+      <c r="H95" s="189" t="n">
+        <f aca="false">D95-G95</f>
+        <v>851650.888</v>
+      </c>
+      <c r="I95" s="190" t="n">
+        <f aca="false">IF(D95=0,0,H95/D95)</f>
+        <v>0.280323742068063</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="199" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="B96" s="184" t="n">
+        <f aca="false">55*4900*0.78*12</f>
+        <v>2522520</v>
+      </c>
+      <c r="C96" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D96" s="184" t="n">
+        <f aca="false">B96+C96</f>
+        <v>3102777.6</v>
+      </c>
+      <c r="E96" s="184" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F96" s="184" t="n">
+        <f aca="false">D96*0.12</f>
+        <v>372333.312</v>
+      </c>
+      <c r="G96" s="184" t="n">
+        <f aca="false">E96+F96</f>
+        <v>2194208.312</v>
+      </c>
+      <c r="H96" s="185" t="n">
+        <f aca="false">D96-G96</f>
+        <v>908569.288</v>
+      </c>
+      <c r="I96" s="186" t="n">
+        <f aca="false">IF(D96=0,0,H96/D96)</f>
+        <v>0.292824496348046</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="200" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B97" s="188" t="n">
+        <f aca="false">55*4900*0.8*12</f>
+        <v>2587200</v>
+      </c>
+      <c r="C97" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D97" s="188" t="n">
+        <f aca="false">B97+C97</f>
+        <v>3167457.6</v>
+      </c>
+      <c r="E97" s="188" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F97" s="188" t="n">
+        <f aca="false">D97*0.12</f>
+        <v>380094.912</v>
+      </c>
+      <c r="G97" s="188" t="n">
+        <f aca="false">E97+F97</f>
+        <v>2201969.912</v>
+      </c>
+      <c r="H97" s="189" t="n">
+        <f aca="false">D97-G97</f>
+        <v>965487.688</v>
+      </c>
+      <c r="I97" s="190" t="n">
+        <f aca="false">IF(D97=0,0,H97/D97)</f>
+        <v>0.304814715751838</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="201" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="B98" s="192" t="n">
+        <f aca="false">55*4900*0.82*12</f>
+        <v>2651880</v>
+      </c>
+      <c r="C98" s="192" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D98" s="192" t="n">
+        <f aca="false">B98+C98</f>
+        <v>3232137.6</v>
+      </c>
+      <c r="E98" s="192" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F98" s="192" t="n">
+        <f aca="false">D98*0.12</f>
+        <v>387856.512</v>
+      </c>
+      <c r="G98" s="192" t="n">
+        <f aca="false">E98+F98</f>
+        <v>2209731.512</v>
+      </c>
+      <c r="H98" s="193" t="n">
+        <f aca="false">D98-G98</f>
+        <v>1022406.088</v>
+      </c>
+      <c r="I98" s="194" t="n">
+        <f aca="false">IF(D98=0,0,H98/D98)</f>
+        <v>0.316325050022623</v>
+      </c>
+      <c r="J98" s="195" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="200" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="B99" s="188" t="n">
+        <f aca="false">55*4900*0.84*12</f>
+        <v>2716560</v>
+      </c>
+      <c r="C99" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D99" s="188" t="n">
+        <f aca="false">B99+C99</f>
+        <v>3296817.6</v>
+      </c>
+      <c r="E99" s="188" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F99" s="188" t="n">
+        <f aca="false">D99*0.12</f>
+        <v>395618.112</v>
+      </c>
+      <c r="G99" s="188" t="n">
+        <f aca="false">E99+F99</f>
+        <v>2217493.112</v>
+      </c>
+      <c r="H99" s="189" t="n">
+        <f aca="false">D99-G99</f>
+        <v>1079324.488</v>
+      </c>
+      <c r="I99" s="190" t="n">
+        <f aca="false">IF(D99=0,0,H99/D99)</f>
+        <v>0.327383743644174</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="199" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="B100" s="184" t="n">
+        <f aca="false">55*4900*0.86*12</f>
+        <v>2781240</v>
+      </c>
+      <c r="C100" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D100" s="184" t="n">
+        <f aca="false">B100+C100</f>
+        <v>3361497.6</v>
+      </c>
+      <c r="E100" s="184" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F100" s="184" t="n">
+        <f aca="false">D100*0.12</f>
+        <v>403379.712</v>
+      </c>
+      <c r="G100" s="184" t="n">
+        <f aca="false">E100+F100</f>
+        <v>2225254.712</v>
+      </c>
+      <c r="H100" s="185" t="n">
+        <f aca="false">D100-G100</f>
+        <v>1136242.888</v>
+      </c>
+      <c r="I100" s="186" t="n">
+        <f aca="false">IF(D100=0,0,H100/D100)</f>
+        <v>0.338016867243933</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="200" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="B101" s="188" t="n">
+        <f aca="false">55*4900*0.88*12</f>
+        <v>2845920</v>
+      </c>
+      <c r="C101" s="188" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D101" s="188" t="n">
+        <f aca="false">B101+C101</f>
+        <v>3426177.6</v>
+      </c>
+      <c r="E101" s="188" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F101" s="188" t="n">
+        <f aca="false">D101*0.12</f>
+        <v>411141.312</v>
+      </c>
+      <c r="G101" s="188" t="n">
+        <f aca="false">E101+F101</f>
+        <v>2233016.312</v>
+      </c>
+      <c r="H101" s="189" t="n">
+        <f aca="false">D101-G101</f>
+        <v>1193161.288</v>
+      </c>
+      <c r="I101" s="190" t="n">
+        <f aca="false">IF(D101=0,0,H101/D101)</f>
+        <v>0.348248522785275</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="199" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B102" s="184" t="n">
+        <f aca="false">55*4900*0.9*12</f>
+        <v>2910600</v>
+      </c>
+      <c r="C102" s="184" t="n">
+        <f aca="false">N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="D102" s="184" t="n">
+        <f aca="false">B102+C102</f>
+        <v>3490857.6</v>
+      </c>
+      <c r="E102" s="184" t="n">
+        <f aca="false">55*Drivers!$E$25*12</f>
+        <v>1821875</v>
+      </c>
+      <c r="F102" s="184" t="n">
+        <f aca="false">D102*0.12</f>
+        <v>418902.912</v>
+      </c>
+      <c r="G102" s="184" t="n">
+        <f aca="false">E102+F102</f>
+        <v>2240777.912</v>
+      </c>
+      <c r="H102" s="185" t="n">
+        <f aca="false">D102-G102</f>
+        <v>1250079.688</v>
+      </c>
+      <c r="I102" s="186" t="n">
+        <f aca="false">IF(D102=0,0,H102/D102)</f>
+        <v>0.358101025948466</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="I3:Q3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="I4:Q4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I5:Q5"/>
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="C7:Q7"/>
+    <mergeCell ref="A13:Q13"/>
+    <mergeCell ref="A20:Q20"/>
+    <mergeCell ref="A40:Q40"/>
+    <mergeCell ref="A41:Q41"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A50:Q50"/>
+    <mergeCell ref="A65:Q65"/>
+    <mergeCell ref="A66:Q66"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="A90:I90"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B7" type="list">
+      <formula1>"Flat,Trend,Manual"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B43" type="list">
+      <formula1>"Base,Upside,Downside"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:F48"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="55"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="117" t="s">
-        <v>170</v>
-      </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
+      <c r="B2" s="202" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="202"/>
+      <c r="D2" s="202"/>
+      <c r="E2" s="202"/>
+      <c r="F2" s="202"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="118" t="s">
-        <v>171</v>
-      </c>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3" s="118" t="s">
-        <v>173</v>
+      <c r="B3" s="203" t="s">
+        <v>269</v>
+      </c>
+      <c r="C3" s="203"/>
+      <c r="D3" s="203" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3" s="203" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="119" t="s">
-        <v>174</v>
+      <c r="B4" s="204" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="120" t="s">
-        <v>175</v>
-      </c>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="120" t="s">
-        <v>177</v>
+      <c r="B5" s="205" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" s="205"/>
+      <c r="D5" s="205" t="s">
+        <v>274</v>
+      </c>
+      <c r="E5" s="205" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="120" t="s">
-        <v>178</v>
-      </c>
-      <c r="D6" s="121" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="122" t="s">
-        <v>180</v>
+      <c r="B6" s="205" t="s">
+        <v>276</v>
+      </c>
+      <c r="D6" s="206" t="s">
+        <v>277</v>
+      </c>
+      <c r="E6" s="207" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="120" t="s">
-        <v>181</v>
-      </c>
-      <c r="D7" s="121" t="s">
-        <v>182</v>
-      </c>
-      <c r="E7" s="122" t="s">
-        <v>183</v>
+      <c r="B7" s="205" t="s">
+        <v>279</v>
+      </c>
+      <c r="D7" s="206" t="s">
+        <v>280</v>
+      </c>
+      <c r="E7" s="207" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="120" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="121" t="s">
-        <v>185</v>
-      </c>
-      <c r="E8" s="122" t="s">
-        <v>186</v>
+      <c r="B8" s="205" t="s">
+        <v>282</v>
+      </c>
+      <c r="D8" s="206" t="s">
+        <v>283</v>
+      </c>
+      <c r="E8" s="207" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="205" t="s">
+        <v>285</v>
+      </c>
+      <c r="D9" s="206" t="s">
+        <v>286</v>
+      </c>
+      <c r="E9" s="207" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="205" t="s">
+        <v>288</v>
+      </c>
+      <c r="D10" s="206" t="s">
+        <v>289</v>
+      </c>
+      <c r="E10" s="207" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="205" t="s">
+        <v>291</v>
+      </c>
+      <c r="D11" s="206" t="s">
+        <v>292</v>
+      </c>
+      <c r="E11" s="207" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="205" t="s">
         <v>187</v>
       </c>
-      <c r="D9" s="121" t="s">
-        <v>188</v>
-      </c>
-      <c r="E9" s="122" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="120" t="s">
-        <v>190</v>
-      </c>
-      <c r="D10" s="121" t="s">
-        <v>191</v>
-      </c>
-      <c r="E10" s="122" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="120" t="s">
-        <v>193</v>
-      </c>
-      <c r="D11" s="121" t="s">
-        <v>194</v>
-      </c>
-      <c r="E11" s="122" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="120" t="s">
-        <v>196</v>
-      </c>
-      <c r="D12" s="121" t="s">
-        <v>197</v>
-      </c>
-      <c r="E12" s="122" t="s">
-        <v>198</v>
+      <c r="D12" s="206" t="s">
+        <v>294</v>
+      </c>
+      <c r="E12" s="207" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="120"/>
+      <c r="B13" s="205"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="119" t="s">
-        <v>199</v>
+      <c r="B14" s="204" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="120" t="s">
-        <v>200</v>
-      </c>
-      <c r="D15" s="121" t="s">
-        <v>201</v>
-      </c>
-      <c r="E15" s="122" t="s">
-        <v>202</v>
+      <c r="B15" s="205" t="s">
+        <v>297</v>
+      </c>
+      <c r="D15" s="206" t="s">
+        <v>298</v>
+      </c>
+      <c r="E15" s="207" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="120" t="s">
-        <v>203</v>
-      </c>
-      <c r="D16" s="121" t="s">
-        <v>204</v>
-      </c>
-      <c r="E16" s="122" t="s">
-        <v>205</v>
+      <c r="B16" s="205" t="s">
+        <v>300</v>
+      </c>
+      <c r="D16" s="206" t="s">
+        <v>301</v>
+      </c>
+      <c r="E16" s="207" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="120"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="122"/>
+      <c r="B17" s="205"/>
+      <c r="D17" s="206"/>
+      <c r="E17" s="207"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="39" t="s">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
     </row>
     <row r="19" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="120" t="s">
-        <v>207</v>
-      </c>
-      <c r="D19" s="123" t="s">
-        <v>208</v>
-      </c>
-      <c r="E19" s="124" t="s">
-        <v>209</v>
+      <c r="B19" s="205" t="s">
+        <v>304</v>
+      </c>
+      <c r="D19" s="208" t="s">
+        <v>305</v>
+      </c>
+      <c r="E19" s="209" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="120" t="s">
-        <v>210</v>
-      </c>
-      <c r="D20" s="123" t="s">
-        <v>211</v>
-      </c>
-      <c r="E20" s="124" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="120" t="s">
-        <v>213</v>
-      </c>
-      <c r="D21" s="125" t="s">
-        <v>214</v>
-      </c>
-      <c r="E21" s="124" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="120" t="s">
-        <v>216</v>
-      </c>
-      <c r="D22" s="123" t="s">
-        <v>217</v>
-      </c>
-      <c r="E22" s="124" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="120" t="s">
-        <v>219</v>
-      </c>
-      <c r="D23" s="123" t="s">
-        <v>220</v>
-      </c>
-      <c r="E23" s="124" t="s">
-        <v>221</v>
+      <c r="B20" s="205" t="s">
+        <v>307</v>
+      </c>
+      <c r="D20" s="208" t="s">
+        <v>308</v>
+      </c>
+      <c r="E20" s="209" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="205" t="s">
+        <v>310</v>
+      </c>
+      <c r="D21" s="208" t="s">
+        <v>311</v>
+      </c>
+      <c r="E21" s="209" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="205" t="s">
+        <v>313</v>
+      </c>
+      <c r="D22" s="208" t="s">
+        <v>314</v>
+      </c>
+      <c r="E22" s="209" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="205" t="s">
+        <v>316</v>
+      </c>
+      <c r="D23" s="208" t="s">
+        <v>317</v>
+      </c>
+      <c r="E23" s="209" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="120" t="s">
-        <v>222</v>
-      </c>
-      <c r="D24" s="125" t="s">
-        <v>223</v>
-      </c>
-      <c r="E24" s="124" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="120" t="s">
-        <v>225</v>
-      </c>
-      <c r="D25" s="126" t="s">
-        <v>226</v>
-      </c>
-      <c r="E25" s="124" t="s">
-        <v>227</v>
+      <c r="B24" s="205" t="s">
+        <v>319</v>
+      </c>
+      <c r="D24" s="208" t="s">
+        <v>320</v>
+      </c>
+      <c r="E24" s="209" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="205" t="s">
+        <v>322</v>
+      </c>
+      <c r="D25" s="208" t="s">
+        <v>323</v>
+      </c>
+      <c r="E25" s="209" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="120" t="s">
-        <v>228</v>
-      </c>
-      <c r="D26" s="126" t="s">
-        <v>229</v>
-      </c>
-      <c r="E26" s="124" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="120" t="s">
-        <v>231</v>
-      </c>
-      <c r="D27" s="126" t="s">
-        <v>232</v>
-      </c>
-      <c r="E27" s="124" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="120"/>
-      <c r="E28" s="121"/>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="120"/>
-      <c r="D29" s="121"/>
-      <c r="E29" s="122"/>
+      <c r="B26" s="205" t="s">
+        <v>325</v>
+      </c>
+      <c r="D26" s="208" t="s">
+        <v>326</v>
+      </c>
+      <c r="E26" s="209" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="205" t="s">
+        <v>328</v>
+      </c>
+      <c r="D27" s="210" t="s">
+        <v>329</v>
+      </c>
+      <c r="E27" s="209" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="205" t="s">
+        <v>331</v>
+      </c>
+      <c r="D28" s="210" t="s">
+        <v>332</v>
+      </c>
+      <c r="E28" s="209" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="205" t="s">
+        <v>334</v>
+      </c>
+      <c r="D29" s="210" t="s">
+        <v>335</v>
+      </c>
+      <c r="E29" s="209" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="120"/>
-      <c r="D30" s="121"/>
-      <c r="E30" s="122"/>
+      <c r="B30" s="205"/>
+      <c r="E30" s="211" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="120"/>
+      <c r="B31" s="205"/>
+      <c r="D31" s="206"/>
+      <c r="E31" s="207"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="119" t="s">
-        <v>234</v>
-      </c>
+      <c r="B32" s="205"/>
+      <c r="D32" s="206"/>
+      <c r="E32" s="207"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="120" t="s">
-        <v>235</v>
-      </c>
-      <c r="D33" s="121" t="s">
-        <v>236</v>
-      </c>
-      <c r="E33" s="127" t="s">
-        <v>237</v>
-      </c>
+      <c r="B33" s="205"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="120" t="s">
-        <v>238</v>
-      </c>
-      <c r="D34" s="121" t="s">
-        <v>239</v>
-      </c>
-      <c r="E34" s="127" t="s">
-        <v>240</v>
+      <c r="B34" s="204" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="120" t="s">
-        <v>241</v>
-      </c>
-      <c r="D35" s="121" t="s">
-        <v>236</v>
-      </c>
-      <c r="E35" s="127" t="s">
-        <v>242</v>
+      <c r="B35" s="205" t="s">
+        <v>339</v>
+      </c>
+      <c r="D35" s="206" t="s">
+        <v>340</v>
+      </c>
+      <c r="E35" s="212" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="128" t="s">
-        <v>243</v>
-      </c>
-      <c r="C36" s="121" t="s">
-        <v>244</v>
-      </c>
-      <c r="E36" s="127" t="s">
-        <v>245</v>
+      <c r="B36" s="205" t="s">
+        <v>342</v>
+      </c>
+      <c r="D36" s="206" t="s">
+        <v>343</v>
+      </c>
+      <c r="E36" s="212" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="120"/>
-      <c r="C37" s="129"/>
-      <c r="E37" s="127"/>
+      <c r="B37" s="205" t="s">
+        <v>345</v>
+      </c>
+      <c r="D37" s="206" t="s">
+        <v>340</v>
+      </c>
+      <c r="E37" s="212" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="119" t="s">
-        <v>246</v>
+      <c r="B38" s="157" t="s">
+        <v>347</v>
+      </c>
+      <c r="C38" s="206" t="s">
+        <v>348</v>
+      </c>
+      <c r="E38" s="212" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="120" t="s">
-        <v>247</v>
-      </c>
-      <c r="D39" s="121" t="s">
-        <v>248</v>
-      </c>
-      <c r="E39" s="122" t="s">
-        <v>249</v>
-      </c>
+      <c r="B39" s="205"/>
+      <c r="C39" s="213"/>
+      <c r="E39" s="212"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="120" t="s">
-        <v>250</v>
-      </c>
-      <c r="D40" s="121" t="s">
-        <v>251</v>
+      <c r="B40" s="204" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="120" t="s">
-        <v>252</v>
-      </c>
-      <c r="D41" s="121" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="130" t="s">
-        <v>254</v>
-      </c>
-      <c r="B45" s="131" t="s">
-        <v>255</v>
-      </c>
-      <c r="C45" s="127"/>
-    </row>
-    <row r="46" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="132" t="s">
-        <v>256</v>
-      </c>
-      <c r="B46" s="132"/>
-      <c r="C46" s="132"/>
-      <c r="D46" s="132"/>
+      <c r="B41" s="205" t="s">
+        <v>351</v>
+      </c>
+      <c r="D41" s="206" t="s">
+        <v>352</v>
+      </c>
+      <c r="E41" s="207" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="205" t="s">
+        <v>354</v>
+      </c>
+      <c r="D42" s="206" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="205" t="s">
+        <v>356</v>
+      </c>
+      <c r="D43" s="206" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="149" t="s">
+        <v>358</v>
+      </c>
+      <c r="B47" s="214" t="s">
+        <v>359</v>
+      </c>
+      <c r="C47" s="212"/>
+    </row>
+    <row r="48" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="215" t="s">
+        <v>360</v>
+      </c>
+      <c r="B48" s="215"/>
+      <c r="C48" s="215"/>
+      <c r="D48" s="215"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B18:E18"/>
-    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A48:D48"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/Analysis/Consultora_NovaTech_1.xlsx
+++ b/Analysis/Consultora_NovaTech_1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="441">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -457,6 +457,87 @@
   </si>
   <si>
     <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORECAST 2025 vs BUDGET 2025 — How does our forecast compare to the plan?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast = Forecast!N (annual total, Base method) | Budget = SUMIF(RawData cols I-M, 2024) | Variance = Forecast - Budget | Positive = forecast above budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠ CONVENTION: Revenue = Forecast - Budget (positive = good). Costs = Budget - Forecast (positive = good).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast 2025 (Base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variance %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commentary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVENUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast vs Budget consulting revenue. Difference = volume/rate assumption vs plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast above budget by €383K. Entire difference driven by utilization assumption: forecast uses 82% avg (consistent with 2022-2024 actuals) vs 71.7% implied in budget. HC (55 FTEs) and billing rate (€4,900) are aligned with budget. If utilization drops below 76%, consulting revenue converges to budget.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS forecast = €580K (same as budget — flat recurring contracts at budget level).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immaterial variance. MS forecast = budget (€580K flat recurring contracts). No assumption difference. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total revenue: forecast vs budget. Key top-line comparison.- underbudget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast exceeds budget by €383K. Driven entirely by consulting utilization assumption. MS on plan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast personnel = HC assumption × cost/head. Budget = RawData col K.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnel forecast below budget by €63K. Budget assumed cost/head of €2,856/month; forecast uses 2024 actuals (€2,760/month). Difference reflects salary increases budgeted for 2025 that may or may not materialise. If increases occur as planned, personnel cost converges to budget. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast = Revenue × 8%. Budget = RawData col L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations above budget by €31K. Forecast calculates operations as 8% of revenue — higher revenue drives higher ops costs automatically. Not an independent assumption: if revenue converges to budget, operations follow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast = Revenue × 4%. Budget = RawData col M.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same logic as operations. Forecast = 4% of revenue. Higher revenue = higher other costs. Dependent variable, not a standalone driver. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total costs: forecast vs budget.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total costs below budget by €87K despite higher revenue. Apparently counterintuitive: higher revenue should drive higher costs. Explained by two offsetting effects: (1) personnel below budget by €63K because 2024 actual cost/head (€2,760) is lower than budget assumption (€2,856) — a favourable variance independent of revenue; (2) operations and other above budget by €46K because they scale with revenue at 12% — higher revenue = higher variable costs. Net result: personnel saving (€63K) more than offsets the variable cost increase (€46K), leaving total costs €87K below budget. If salary increases materialise as budgeted, personnel converges to €1,885K and total costs flip to above budget by ~€24K </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA: forecast vs budget. Bottom line comparison — we are not planning to hit the target.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast EBITDA €400K above budget. Not as positive as it appears: higher revenue inflates ops and other costs, but personnel savings (€63K) and revenue upside (€383K) more than offset. Root cause = utilization assumption. Key risk: if utilization is 71.7% as budgeted, EBITDA converges to €667K. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin comparison. Expect ~23% both sides if costs scale proportionally.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin expansion vs budget driven by operating leverage: revenue grows faster than costs because personnel is semi-fixed (55 FTEs regardless of utilization). At 82% utilization, each additional billable hour drops almost entirely to EBITDA. This is the key insight: utilization is the single most important lever for margin in a consulting business.</t>
   </si>
   <si>
     <t xml:space="preserve">NovaTech Consulting Lda. — Profit &amp; Loss Statement</t>
@@ -924,9 +1005,6 @@
     <t xml:space="preserve">Internal estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠ To be recalculated from historical data in Week 4 forecasting model</t>
-  </si>
-  <si>
     <t xml:space="preserve">FINANCIAL ASSUMPTIONS</t>
   </si>
   <si>
@@ -1121,13 +1199,175 @@
   <si>
     <t xml:space="preserve">2. Budget in RawData cols I–M represents 2025 targets applied to 2024 rows as proxy — not a true 2025 actuals sheet.
 3. HC and billing rate assumptions do not exactly reproduce RawData totals — gap intentional, acknowledged in YoY Bridge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORECAST 2025 ASSUMPTIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast HC 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — +3 vs 2024 avg (52). Conservative hiring plan. Change in Forecast sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — +€300 YoY (trend: 2022=€4,000, 2023=€4,300, 2024=€4,600). Change in Forecast sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilization 2025 avg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~82% avg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — +2pp vs 2024. Seasonal pattern maintained. Change in Forecast sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS Revenue 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€580,000 flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED — Budget 2025 from RawData col J. €580K ÷ 12 = €48,333/month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS growth rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED — €580K/€530K - 1 = 9.43%. Comes from budget assumption in RawData, not an independent estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnel cost/head/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€2,760/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED — Drivers. RawData personnel 2024 ÷ avg HC ÷ 12. Not an assumption.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations % of revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED — historical avg 2022-2024: 168K/2.1M = 168K/2.4M = 212K/2.65M = 8.0% exact.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other % of revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED — historical avg 2022-2024: 84K/2.1M = 96K/2.4M = 106K/2.65M = 4.0% exact.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ops + Other combined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED — 8% + 4%. Used in scenario EBITDA calculations as shorthand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2% of revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — consistent with historical model. Low asset base for IT consultancy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRC tax rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal corporate tax rate 2024. Source: Autoridade Tributária.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast method default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat = avg Oct-Nov-Dec 2024. Change to Trend or Manual in Forecast!B7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO ASSUMPTIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base HC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trend continuation. +3 vs 2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€4,900/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+€300 YoY consistent with 2022-2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Util avg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2pp vs 2024 avg (~80%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upside HC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 FTEs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8 vs 2024. Accelerated hiring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upside Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€5,000/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+€100 above trend. Better client mix.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upside Util</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6pp vs 2024. Strong demand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downside HC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 FTEs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2 vs 2024. Attrition above plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downside Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€4,700/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-€100 below trend. Rate pressure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downside Util</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2pp vs 2024. Weaker demand.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
@@ -1137,10 +1377,9 @@
     <numFmt numFmtId="170" formatCode="0.00%"/>
     <numFmt numFmtId="171" formatCode="[$-409]#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="172" formatCode="[$-409]0.00%"/>
-    <numFmt numFmtId="173" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="174" formatCode="#,##0"/>
+    <numFmt numFmtId="173" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="65">
+  <fonts count="67">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1411,6 +1650,29 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -1571,13 +1833,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FFCC0000"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -1587,14 +1842,6 @@
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF1F4E79"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1627,6 +1874,14 @@
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1A7A4A"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1815,7 +2070,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="236">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2172,6 +2427,82 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="36" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="38" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2180,7 +2511,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="42" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2192,19 +2523,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="43" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="40" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="44" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="42" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="45" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2216,7 +2543,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2224,7 +2551,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="40" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="43" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2236,15 +2563,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="46" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="43" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="46" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2256,27 +2579,27 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="44" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="47" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="45" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="48" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="49" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2284,7 +2607,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="52" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2296,7 +2619,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="53" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2308,7 +2631,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="53" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2320,11 +2643,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="53" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="54" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2344,11 +2667,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2372,15 +2695,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2404,31 +2723,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="24" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="59" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2436,10 +2743,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="24" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2448,10 +2751,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="57" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2472,15 +2771,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2496,11 +2791,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2508,23 +2803,23 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="51" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="60" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="58" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="60" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="48" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="51" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="60" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2548,7 +2843,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2564,7 +2859,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2580,7 +2875,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2596,7 +2891,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2608,10 +2903,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2624,10 +2915,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="60" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2648,7 +2935,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2656,7 +2943,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2668,16 +2955,64 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="63" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="64" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="65" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="64" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="66" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="65" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2694,7 +3029,7 @@
     <cellStyle name="Sem nome4" xfId="23"/>
     <cellStyle name="Sem nome5" xfId="24"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -2734,6 +3069,34 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDDE8CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFDCDC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3151,11 +3514,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="13740888"/>
-        <c:axId val="52417224"/>
+        <c:axId val="92019572"/>
+        <c:axId val="9033078"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="13740888"/>
+        <c:axId val="92019572"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3220,7 +3583,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52417224"/>
+        <c:crossAx val="9033078"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3228,7 +3591,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="52417224"/>
+        <c:axId val="9033078"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3302,7 +3665,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13740888"/>
+        <c:crossAx val="92019572"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3569,11 +3932,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="33354593"/>
-        <c:axId val="93014793"/>
+        <c:axId val="87507132"/>
+        <c:axId val="22166508"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="33354593"/>
+        <c:axId val="87507132"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3638,7 +4001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93014793"/>
+        <c:crossAx val="22166508"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3646,7 +4009,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93014793"/>
+        <c:axId val="22166508"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3720,7 +4083,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33354593"/>
+        <c:crossAx val="87507132"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4122,11 +4485,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="37391902"/>
-        <c:axId val="68845488"/>
+        <c:axId val="27591740"/>
+        <c:axId val="20872244"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="37391902"/>
+        <c:axId val="27591740"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4191,7 +4554,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68845488"/>
+        <c:crossAx val="20872244"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4199,7 +4562,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="68845488"/>
+        <c:axId val="20872244"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4273,7 +4636,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37391902"/>
+        <c:crossAx val="27591740"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4370,10 +4733,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.160947151681537"/>
-          <c:y val="0.167158408790314"/>
-          <c:w val="0.68805765271105"/>
-          <c:h val="0.539017194017703"/>
+          <c:x val="0.160965564580712"/>
+          <c:y val="0.167192429022082"/>
+          <c:w val="0.688021965450177"/>
+          <c:h val="0.538923374376717"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -4554,11 +4917,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="10426299"/>
-        <c:axId val="45401228"/>
+        <c:axId val="29123828"/>
+        <c:axId val="28222350"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10426299"/>
+        <c:axId val="29123828"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4623,7 +4986,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45401228"/>
+        <c:crossAx val="28222350"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4631,7 +4994,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45401228"/>
+        <c:axId val="28222350"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4705,7 +5068,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10426299"/>
+        <c:crossAx val="29123828"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5639,10 +6002,10 @@
       <xdr:rowOff>142560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>371160</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>526680</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>131400</xdr:rowOff>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5651,7 +6014,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3703680" y="6012000"/>
-        <a:ext cx="6206400" cy="3493800"/>
+        <a:ext cx="6205680" cy="3493080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5670,9 +6033,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2453400</xdr:colOff>
+      <xdr:colOff>2452680</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>120240</xdr:rowOff>
+      <xdr:rowOff>119520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5680,8 +6043,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10926000" y="5735160"/>
-        <a:ext cx="5753880" cy="3233880"/>
+        <a:off x="11582640" y="5735160"/>
+        <a:ext cx="5753160" cy="3233160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5693,16 +6056,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>350640</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>140400</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>340560</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>19800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>416520</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>321840</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>1181160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5710,8 +6073,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4200120" y="9690120"/>
-        <a:ext cx="5755320" cy="3235320"/>
+        <a:off x="8097840" y="9744840"/>
+        <a:ext cx="5754600" cy="3234600"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5723,16 +6086,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>190800</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>780840</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>7200</xdr:rowOff>
+      <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>2610000</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>39960</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>427320</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>1306800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5740,8 +6103,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="21579000">
-        <a:off x="10542240" y="9556920"/>
-        <a:ext cx="6293880" cy="3538080"/>
+        <a:off x="13414320" y="9567720"/>
+        <a:ext cx="6293160" cy="3537360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8918,11 +9281,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="20.02"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="2" style="10" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="2" style="10" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="10" width="20.85"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="8" style="10" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="10" width="12.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="10" width="19.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="50.86"/>
@@ -10250,39 +10615,357 @@
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="T49" s="2"/>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q50" s="2" t="s">
-        <v>134</v>
-      </c>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="89" t="s">
+        <v>141</v>
+      </c>
+      <c r="B50" s="89"/>
+      <c r="C50" s="89"/>
+      <c r="D50" s="89"/>
+      <c r="E50" s="89"/>
+      <c r="F50" s="89"/>
+      <c r="G50" s="89"/>
+      <c r="H50" s="89"/>
+      <c r="I50" s="89"/>
+      <c r="J50" s="89"/>
+      <c r="K50" s="89"/>
+      <c r="L50" s="89"/>
+      <c r="M50" s="89"/>
+      <c r="N50" s="89"/>
+      <c r="O50" s="89"/>
+      <c r="P50" s="89"/>
+      <c r="Q50" s="89"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q51" s="2" t="s">
-        <v>136</v>
-      </c>
+      <c r="A51" s="90" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" s="90"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="90"/>
+      <c r="E51" s="90"/>
+      <c r="F51" s="90"/>
+      <c r="G51" s="90"/>
+      <c r="H51" s="90"/>
+      <c r="I51" s="90"/>
+      <c r="J51" s="90"/>
+      <c r="K51" s="90"/>
+      <c r="L51" s="90"/>
+      <c r="M51" s="90"/>
+      <c r="N51" s="90"/>
+      <c r="O51" s="90"/>
+      <c r="P51" s="90"/>
+      <c r="Q51" s="90"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q52" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="38"/>
+      <c r="K52" s="38"/>
+      <c r="L52" s="38"/>
+      <c r="M52" s="38"/>
+      <c r="N52" s="38"/>
+      <c r="O52" s="38"/>
+      <c r="P52" s="38"/>
+      <c r="Q52" s="38"/>
+    </row>
+    <row r="53" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="91" t="s">
+        <v>144</v>
+      </c>
+      <c r="C53" s="91" t="s">
+        <v>145</v>
+      </c>
+      <c r="D53" s="91" t="s">
+        <v>123</v>
+      </c>
+      <c r="E53" s="91" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" s="91" t="s">
+        <v>147</v>
+      </c>
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="92" t="s">
+        <v>148</v>
+      </c>
+      <c r="B54" s="93"/>
+      <c r="C54" s="93"/>
+      <c r="D54" s="93"/>
+      <c r="E54" s="93"/>
+      <c r="F54" s="93"/>
       <c r="T54" s="2"/>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q55" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N56" s="10" t="s">
-        <v>134</v>
+    <row r="55" customFormat="false" ht="157.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="94" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" s="95" t="n">
+        <f aca="false">Forecast!N22</f>
+        <v>2120000</v>
+      </c>
+      <c r="C55" s="96" t="n">
+        <f aca="false">SUMIF(RawData!A:A,"=2024",RawData!I:I)</f>
+        <v>2320000</v>
+      </c>
+      <c r="D55" s="96" t="n">
+        <f aca="false">B55-C55</f>
+        <v>-199999.999999996</v>
+      </c>
+      <c r="E55" s="97" t="n">
+        <f aca="false">IF(C55=0,0,D55/C55)</f>
+        <v>-0.0862068965517223</v>
+      </c>
+      <c r="F55" s="82" t="s">
+        <v>149</v>
+      </c>
+      <c r="G55" s="98" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="62.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="94" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="95" t="n">
+        <f aca="false">Forecast!N23</f>
+        <v>580257.6</v>
+      </c>
+      <c r="C56" s="96" t="n">
+        <f aca="false">SUMIF(RawData!A:A,2024,RawData!J:J)</f>
+        <v>580000</v>
+      </c>
+      <c r="D56" s="96" t="n">
+        <f aca="false">B56-C56</f>
+        <v>257.599999999977</v>
+      </c>
+      <c r="E56" s="97" t="n">
+        <f aca="false">IF(C56=0,0,D56/C56)</f>
+        <v>0.000444137931034443</v>
+      </c>
+      <c r="F56" s="82" t="s">
+        <v>151</v>
+      </c>
+      <c r="G56" s="99" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="62.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="100" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" s="95" t="n">
+        <f aca="false">Forecast!N24</f>
+        <v>2700257.6</v>
+      </c>
+      <c r="C57" s="101" t="n">
+        <f aca="false">SUMIF(RawData!A:A,2024,RawData!I:I)+SUMIF(RawData!A:A,2024,RawData!J:J)</f>
+        <v>2900000</v>
+      </c>
+      <c r="D57" s="101" t="n">
+        <f aca="false">B57-C57</f>
+        <v>-199742.399999996</v>
+      </c>
+      <c r="E57" s="102" t="n">
+        <f aca="false">IF(C57=0,0,D57/C57)</f>
+        <v>-0.0688766896551709</v>
+      </c>
+      <c r="F57" s="82" t="s">
+        <v>153</v>
+      </c>
+      <c r="G57" s="99" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="92" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" s="93"/>
+      <c r="C58" s="93"/>
+      <c r="D58" s="93"/>
+      <c r="E58" s="93"/>
+      <c r="F58" s="93"/>
+    </row>
+    <row r="59" customFormat="false" ht="157.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="94" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" s="95" t="n">
+        <f aca="false">Forecast!N26</f>
+        <v>1821875</v>
+      </c>
+      <c r="C59" s="96" t="n">
+        <f aca="false">SUMIF(RawData!A:A,2024,RawData!K:K)</f>
+        <v>1885000</v>
+      </c>
+      <c r="D59" s="96" t="n">
+        <f aca="false">C59-B59</f>
+        <v>63125</v>
+      </c>
+      <c r="E59" s="97" t="n">
+        <f aca="false">IF(C59=0,0,D59/C59)</f>
+        <v>0.0334880636604775</v>
+      </c>
+      <c r="F59" s="82" t="s">
+        <v>156</v>
+      </c>
+      <c r="G59" s="99" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" s="95" t="n">
+        <f aca="false">Forecast!N27</f>
+        <v>216020.608</v>
+      </c>
+      <c r="C60" s="96" t="n">
+        <f aca="false">SUMIF(RawData!A:A,2024,RawData!L:L)</f>
+        <v>232000</v>
+      </c>
+      <c r="D60" s="96" t="n">
+        <f aca="false">C60-B60</f>
+        <v>15979.3919999996</v>
+      </c>
+      <c r="E60" s="97" t="n">
+        <f aca="false">IF(C60=0,0,D60/C60)</f>
+        <v>0.0688766896551709</v>
+      </c>
+      <c r="F60" s="82" t="s">
+        <v>158</v>
+      </c>
+      <c r="G60" s="103" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" s="95" t="n">
+        <f aca="false">Forecast!N28</f>
+        <v>108010.304</v>
+      </c>
+      <c r="C61" s="96" t="n">
+        <f aca="false">SUMIF(RawData!A:A,2024,RawData!M:M)</f>
+        <v>116000</v>
+      </c>
+      <c r="D61" s="96" t="n">
+        <f aca="false">C61-B61</f>
+        <v>7989.69599999982</v>
+      </c>
+      <c r="E61" s="97" t="n">
+        <f aca="false">IF(C61=0,0,D61/C61)</f>
+        <v>0.0688766896551709</v>
+      </c>
+      <c r="F61" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="G61" s="103" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="357.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="100" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="95" t="n">
+        <f aca="false">Forecast!N29</f>
+        <v>2145905.912</v>
+      </c>
+      <c r="C62" s="101" t="n">
+        <f aca="false">SUMIF(RawData!A:A,2024,RawData!K:K)+SUMIF(RawData!A:A,2024,RawData!L:L)+SUMIF(RawData!A:A,2024,RawData!M:M)</f>
+        <v>2233000</v>
+      </c>
+      <c r="D62" s="101" t="n">
+        <f aca="false">C62-B62</f>
+        <v>87094.0879999958</v>
+      </c>
+      <c r="E62" s="102" t="n">
+        <f aca="false">IF(C62=0,0,D62/C62)</f>
+        <v>0.0390031742051034</v>
+      </c>
+      <c r="F62" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="G62" s="99" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="157.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="104" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="105" t="n">
+        <f aca="false">Forecast!N32</f>
+        <v>554351.688</v>
+      </c>
+      <c r="C63" s="105" t="n">
+        <f aca="false">SUMIF(RawData!A:A,2024,RawData!I:I)+SUMIF(RawData!A:A,2024,RawData!J:J)-SUMIF(RawData!A:A,2024,RawData!K:K)-SUMIF(RawData!A:A,2024,RawData!L:L)-SUMIF(RawData!A:A,2024,RawData!M:M)</f>
+        <v>667000</v>
+      </c>
+      <c r="D63" s="105" t="n">
+        <f aca="false">B63-C63</f>
+        <v>-112648.312</v>
+      </c>
+      <c r="E63" s="106" t="n">
+        <f aca="false">IF(C63=0,0,D63/C63)</f>
+        <v>-0.168888023988006</v>
+      </c>
+      <c r="F63" s="82" t="s">
+        <v>164</v>
+      </c>
+      <c r="G63" s="99" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="179.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="107" t="n">
+        <f aca="false">Forecast!N33</f>
+        <v>0.205295853254889</v>
+      </c>
+      <c r="C64" s="97" t="n">
+        <f aca="false">(SUMIF(RawData!A:A,2024,RawData!I:I)+SUMIF(RawData!A:A,2024,RawData!J:J)-SUMIF(RawData!A:A,2024,RawData!K:K)-SUMIF(RawData!A:A,2024,RawData!L:L)-SUMIF(RawData!A:A,2024,RawData!M:M))/(SUMIF(RawData!A:A,2024,RawData!I:I)+SUMIF(RawData!A:A,2024,RawData!J:J))</f>
+        <v>0.23</v>
+      </c>
+      <c r="D64" s="97" t="n">
+        <f aca="false">B64-C64</f>
+        <v>-0.0247041467451109</v>
+      </c>
+      <c r="F64" s="82" t="s">
+        <v>166</v>
+      </c>
+      <c r="G64" s="99" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A50:Q50"/>
+    <mergeCell ref="A51:Q51"/>
+    <mergeCell ref="A52:Q52"/>
+  </mergeCells>
   <conditionalFormatting sqref="P6:P8 N12:P14 B15:P15 N18:P18 C18:L18 N17:O18 P17">
     <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
@@ -10369,6 +11052,14 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D55:D65">
+    <cfRule type="cellIs" priority="22" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="23" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10396,7 +11087,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="37" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -10415,968 +11106,968 @@
       <c r="P1" s="37"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="89"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
+      <c r="A2" s="108"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="108"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="108"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="90" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="90" t="s">
+      <c r="A4" s="109" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="90" t="s">
+      <c r="C4" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="90" t="s">
+      <c r="D4" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="90" t="s">
+      <c r="E4" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="90" t="s">
+      <c r="F4" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="90" t="s">
+      <c r="G4" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="90" t="s">
+      <c r="H4" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="90" t="s">
+      <c r="I4" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="90" t="s">
+      <c r="J4" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="90" t="s">
+      <c r="K4" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="90" t="s">
+      <c r="L4" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="90" t="s">
+      <c r="M4" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="90" t="s">
+      <c r="N4" s="109" t="s">
         <v>99</v>
       </c>
-      <c r="O4" s="90" t="s">
-        <v>143</v>
+      <c r="O4" s="109" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="91" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="92" t="n">
+      <c r="A5" s="110" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="111" t="n">
         <f aca="false">Drivers!B8*Drivers!B14</f>
         <v>234600</v>
       </c>
-      <c r="C5" s="92" t="n">
+      <c r="C5" s="111" t="n">
         <f aca="false">Drivers!C8*Drivers!C14</f>
         <v>234600</v>
       </c>
-      <c r="D5" s="92" t="n">
+      <c r="D5" s="111" t="n">
         <f aca="false">Drivers!D8*Drivers!D14</f>
         <v>234600</v>
       </c>
-      <c r="E5" s="92" t="n">
+      <c r="E5" s="111" t="n">
         <f aca="false">Drivers!E8*Drivers!E14</f>
         <v>239200</v>
       </c>
-      <c r="F5" s="92" t="n">
+      <c r="F5" s="111" t="n">
         <f aca="false">Drivers!F8*Drivers!F14</f>
         <v>239200</v>
       </c>
-      <c r="G5" s="92" t="n">
+      <c r="G5" s="111" t="n">
         <f aca="false">Drivers!G8*Drivers!G14</f>
         <v>239200</v>
       </c>
-      <c r="H5" s="92" t="n">
+      <c r="H5" s="111" t="n">
         <f aca="false">Drivers!H8*Drivers!H14</f>
         <v>239200</v>
       </c>
-      <c r="I5" s="92" t="n">
+      <c r="I5" s="111" t="n">
         <f aca="false">Drivers!I8*Drivers!I14</f>
         <v>239200</v>
       </c>
-      <c r="J5" s="92" t="n">
+      <c r="J5" s="111" t="n">
         <f aca="false">Drivers!J8*Drivers!J14</f>
         <v>239200</v>
       </c>
-      <c r="K5" s="92" t="n">
+      <c r="K5" s="111" t="n">
         <f aca="false">Drivers!K8*Drivers!K14</f>
         <v>243800</v>
       </c>
-      <c r="L5" s="92" t="n">
+      <c r="L5" s="111" t="n">
         <f aca="false">Drivers!L8*Drivers!L14</f>
         <v>243800</v>
       </c>
-      <c r="M5" s="92" t="n">
+      <c r="M5" s="111" t="n">
         <f aca="false">Drivers!M8*Drivers!M14</f>
         <v>243800</v>
       </c>
-      <c r="N5" s="93" t="n">
+      <c r="N5" s="112" t="n">
         <f aca="false">SUM(B5:M5)</f>
         <v>2870400</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="O5" s="97" t="n">
         <f aca="false">IF(N7=0,0,N5/N7)</f>
         <v>0.844036697247707</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="91" t="s">
-        <v>145</v>
-      </c>
-      <c r="B6" s="95" t="n">
+      <c r="A6" s="110" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="113" t="n">
         <f aca="false">Drivers!B19</f>
         <v>44200</v>
       </c>
-      <c r="C6" s="95" t="n">
+      <c r="C6" s="113" t="n">
         <f aca="false">Drivers!C19</f>
         <v>44200</v>
       </c>
-      <c r="D6" s="95" t="n">
+      <c r="D6" s="113" t="n">
         <f aca="false">Drivers!D19</f>
         <v>44200</v>
       </c>
-      <c r="E6" s="95" t="n">
+      <c r="E6" s="113" t="n">
         <f aca="false">Drivers!E19</f>
         <v>44200</v>
       </c>
-      <c r="F6" s="95" t="n">
+      <c r="F6" s="113" t="n">
         <f aca="false">Drivers!F19</f>
         <v>44200</v>
       </c>
-      <c r="G6" s="95" t="n">
+      <c r="G6" s="113" t="n">
         <f aca="false">Drivers!G19</f>
         <v>44200</v>
       </c>
-      <c r="H6" s="95" t="n">
+      <c r="H6" s="113" t="n">
         <f aca="false">Drivers!H19</f>
         <v>44200</v>
       </c>
-      <c r="I6" s="95" t="n">
+      <c r="I6" s="113" t="n">
         <f aca="false">Drivers!I19</f>
         <v>44200</v>
       </c>
-      <c r="J6" s="95" t="n">
+      <c r="J6" s="113" t="n">
         <f aca="false">Drivers!J19</f>
         <v>44200</v>
       </c>
-      <c r="K6" s="95" t="n">
+      <c r="K6" s="113" t="n">
         <f aca="false">Drivers!K19</f>
         <v>44200</v>
       </c>
-      <c r="L6" s="95" t="n">
+      <c r="L6" s="113" t="n">
         <f aca="false">Drivers!L19</f>
         <v>44200</v>
       </c>
-      <c r="M6" s="95" t="n">
+      <c r="M6" s="113" t="n">
         <f aca="false">Drivers!M19</f>
         <v>44200</v>
       </c>
-      <c r="N6" s="93" t="n">
+      <c r="N6" s="112" t="n">
         <f aca="false">SUM(B6:M6)</f>
         <v>530400</v>
       </c>
-      <c r="O6" s="94" t="n">
+      <c r="O6" s="97" t="n">
         <f aca="false">IF(N7=0,0,N6/N7)</f>
         <v>0.155963302752294</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="96" t="s">
+      <c r="A7" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="97" t="n">
+      <c r="B7" s="115" t="n">
         <f aca="false">B5+B6</f>
         <v>278800</v>
       </c>
-      <c r="C7" s="97" t="n">
+      <c r="C7" s="115" t="n">
         <f aca="false">C5+C6</f>
         <v>278800</v>
       </c>
-      <c r="D7" s="97" t="n">
+      <c r="D7" s="115" t="n">
         <f aca="false">D5+D6</f>
         <v>278800</v>
       </c>
-      <c r="E7" s="97" t="n">
+      <c r="E7" s="115" t="n">
         <f aca="false">E5+E6</f>
         <v>283400</v>
       </c>
-      <c r="F7" s="97" t="n">
+      <c r="F7" s="115" t="n">
         <f aca="false">F5+F6</f>
         <v>283400</v>
       </c>
-      <c r="G7" s="97" t="n">
+      <c r="G7" s="115" t="n">
         <f aca="false">G5+G6</f>
         <v>283400</v>
       </c>
-      <c r="H7" s="97" t="n">
+      <c r="H7" s="115" t="n">
         <f aca="false">H5+H6</f>
         <v>283400</v>
       </c>
-      <c r="I7" s="97" t="n">
+      <c r="I7" s="115" t="n">
         <f aca="false">I5+I6</f>
         <v>283400</v>
       </c>
-      <c r="J7" s="97" t="n">
+      <c r="J7" s="115" t="n">
         <f aca="false">J5+J6</f>
         <v>283400</v>
       </c>
-      <c r="K7" s="97" t="n">
+      <c r="K7" s="115" t="n">
         <f aca="false">K5+K6</f>
         <v>288000</v>
       </c>
-      <c r="L7" s="97" t="n">
+      <c r="L7" s="115" t="n">
         <f aca="false">L5+L6</f>
         <v>288000</v>
       </c>
-      <c r="M7" s="97" t="n">
+      <c r="M7" s="115" t="n">
         <f aca="false">M5+M6</f>
         <v>288000</v>
       </c>
-      <c r="N7" s="98" t="n">
+      <c r="N7" s="116" t="n">
         <f aca="false">SUM(B7:M7)</f>
         <v>3400800</v>
       </c>
-      <c r="O7" s="99" t="n">
+      <c r="O7" s="117" t="n">
         <f aca="false">IF(N7=0,0,N7/N7)</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="91"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="100"/>
-      <c r="K8" s="100"/>
-      <c r="L8" s="100"/>
-      <c r="M8" s="100"/>
-      <c r="N8" s="101"/>
-      <c r="O8" s="101"/>
+      <c r="A8" s="110"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="118"/>
+      <c r="K8" s="118"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="118"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="119"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="91" t="s">
-        <v>146</v>
-      </c>
-      <c r="B9" s="95" t="n">
+      <c r="A9" s="110" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="113" t="n">
         <f aca="false">Drivers!B8*Drivers!E25</f>
         <v>140781.25</v>
       </c>
-      <c r="C9" s="95" t="n">
+      <c r="C9" s="113" t="n">
         <f aca="false">Drivers!C8*Drivers!E25</f>
         <v>140781.25</v>
       </c>
-      <c r="D9" s="95" t="n">
+      <c r="D9" s="113" t="n">
         <f aca="false">Drivers!D8*Drivers!E25</f>
         <v>140781.25</v>
       </c>
-      <c r="E9" s="95" t="n">
+      <c r="E9" s="113" t="n">
         <f aca="false">Drivers!E8*Drivers!E25</f>
         <v>143541.666666667</v>
       </c>
-      <c r="F9" s="95" t="n">
+      <c r="F9" s="113" t="n">
         <f aca="false">Drivers!F8*Drivers!E25</f>
         <v>143541.666666667</v>
       </c>
-      <c r="G9" s="95" t="n">
+      <c r="G9" s="113" t="n">
         <f aca="false">Drivers!G8*Drivers!E25</f>
         <v>143541.666666667</v>
       </c>
-      <c r="H9" s="95" t="n">
+      <c r="H9" s="113" t="n">
         <f aca="false">Drivers!H8*Drivers!E25</f>
         <v>143541.666666667</v>
       </c>
-      <c r="I9" s="95" t="n">
+      <c r="I9" s="113" t="n">
         <f aca="false">Drivers!I8*Drivers!E25</f>
         <v>143541.666666667</v>
       </c>
-      <c r="J9" s="95" t="n">
+      <c r="J9" s="113" t="n">
         <f aca="false">Drivers!J8*Drivers!E25</f>
         <v>143541.666666667</v>
       </c>
-      <c r="K9" s="95" t="n">
+      <c r="K9" s="113" t="n">
         <f aca="false">Drivers!K8*Drivers!E25</f>
         <v>146302.083333333</v>
       </c>
-      <c r="L9" s="95" t="n">
+      <c r="L9" s="113" t="n">
         <f aca="false">Drivers!L8*Drivers!E25</f>
         <v>146302.083333333</v>
       </c>
-      <c r="M9" s="95" t="n">
+      <c r="M9" s="113" t="n">
         <f aca="false">Drivers!M8*Drivers!E25</f>
         <v>146302.083333333</v>
       </c>
-      <c r="N9" s="93" t="n">
+      <c r="N9" s="112" t="n">
         <f aca="false">SUM(B9:M9)</f>
         <v>1722500</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="O9" s="97" t="n">
         <f aca="false">IF(N7=0,0,N9/N7)</f>
         <v>0.506498470948012</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="91" t="s">
-        <v>147</v>
-      </c>
-      <c r="B10" s="95" t="n">
+      <c r="A10" s="110" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="113" t="n">
         <f aca="false">B7*Drivers!D31</f>
         <v>22304</v>
       </c>
-      <c r="C10" s="95" t="n">
+      <c r="C10" s="113" t="n">
         <f aca="false">C7*Drivers!D31</f>
         <v>22304</v>
       </c>
-      <c r="D10" s="95" t="n">
+      <c r="D10" s="113" t="n">
         <f aca="false">D7*Drivers!D31</f>
         <v>22304</v>
       </c>
-      <c r="E10" s="95" t="n">
+      <c r="E10" s="113" t="n">
         <f aca="false">E7*Drivers!D31</f>
         <v>22672</v>
       </c>
-      <c r="F10" s="95" t="n">
+      <c r="F10" s="113" t="n">
         <f aca="false">F7*Drivers!D31</f>
         <v>22672</v>
       </c>
-      <c r="G10" s="95" t="n">
+      <c r="G10" s="113" t="n">
         <f aca="false">G7*Drivers!D31</f>
         <v>22672</v>
       </c>
-      <c r="H10" s="95" t="n">
+      <c r="H10" s="113" t="n">
         <f aca="false">H7*Drivers!D31</f>
         <v>22672</v>
       </c>
-      <c r="I10" s="95" t="n">
+      <c r="I10" s="113" t="n">
         <f aca="false">I7*Drivers!D31</f>
         <v>22672</v>
       </c>
-      <c r="J10" s="95" t="n">
+      <c r="J10" s="113" t="n">
         <f aca="false">J7*Drivers!D31</f>
         <v>22672</v>
       </c>
-      <c r="K10" s="95" t="n">
+      <c r="K10" s="113" t="n">
         <f aca="false">K7*Drivers!D31</f>
         <v>23040</v>
       </c>
-      <c r="L10" s="95" t="n">
+      <c r="L10" s="113" t="n">
         <f aca="false">L7*Drivers!D31</f>
         <v>23040</v>
       </c>
-      <c r="M10" s="95" t="n">
+      <c r="M10" s="113" t="n">
         <f aca="false">M7*Drivers!D31</f>
         <v>23040</v>
       </c>
-      <c r="N10" s="93" t="n">
+      <c r="N10" s="112" t="n">
         <f aca="false">SUM(B10:M10)</f>
         <v>272064</v>
       </c>
-      <c r="O10" s="94" t="n">
+      <c r="O10" s="97" t="n">
         <f aca="false">IF(N7=0,0,N10/N7)</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="91" t="s">
-        <v>148</v>
-      </c>
-      <c r="B11" s="95" t="n">
+      <c r="A11" s="110" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" s="113" t="n">
         <f aca="false">B7*Drivers!D37</f>
         <v>11152</v>
       </c>
-      <c r="C11" s="95" t="n">
+      <c r="C11" s="113" t="n">
         <f aca="false">C7*Drivers!D37</f>
         <v>11152</v>
       </c>
-      <c r="D11" s="95" t="n">
+      <c r="D11" s="113" t="n">
         <f aca="false">D7*Drivers!D37</f>
         <v>11152</v>
       </c>
-      <c r="E11" s="95" t="n">
+      <c r="E11" s="113" t="n">
         <f aca="false">E7*Drivers!D37</f>
         <v>11336</v>
       </c>
-      <c r="F11" s="95" t="n">
+      <c r="F11" s="113" t="n">
         <f aca="false">F7*Drivers!D37</f>
         <v>11336</v>
       </c>
-      <c r="G11" s="95" t="n">
+      <c r="G11" s="113" t="n">
         <f aca="false">G7*Drivers!D37</f>
         <v>11336</v>
       </c>
-      <c r="H11" s="95" t="n">
+      <c r="H11" s="113" t="n">
         <f aca="false">H7*Drivers!D37</f>
         <v>11336</v>
       </c>
-      <c r="I11" s="95" t="n">
+      <c r="I11" s="113" t="n">
         <f aca="false">I7*Drivers!D37</f>
         <v>11336</v>
       </c>
-      <c r="J11" s="95" t="n">
+      <c r="J11" s="113" t="n">
         <f aca="false">J7*Drivers!D37</f>
         <v>11336</v>
       </c>
-      <c r="K11" s="95" t="n">
+      <c r="K11" s="113" t="n">
         <f aca="false">K7*Drivers!D37</f>
         <v>11520</v>
       </c>
-      <c r="L11" s="95" t="n">
+      <c r="L11" s="113" t="n">
         <f aca="false">L7*Drivers!D37</f>
         <v>11520</v>
       </c>
-      <c r="M11" s="95" t="n">
+      <c r="M11" s="113" t="n">
         <f aca="false">M7*Drivers!D37</f>
         <v>11520</v>
       </c>
-      <c r="N11" s="93" t="n">
+      <c r="N11" s="112" t="n">
         <f aca="false">SUM(B11:M11)</f>
         <v>136032</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="O11" s="97" t="n">
         <f aca="false">IF(N7=0,0,N11/N7)</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="96" t="s">
+      <c r="A12" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="97" t="n">
+      <c r="B12" s="115" t="n">
         <f aca="false">B9+B10+B11</f>
         <v>174237.25</v>
       </c>
-      <c r="C12" s="97" t="n">
+      <c r="C12" s="115" t="n">
         <f aca="false">C9+C10+C11</f>
         <v>174237.25</v>
       </c>
-      <c r="D12" s="97" t="n">
+      <c r="D12" s="115" t="n">
         <f aca="false">D9+D10+D11</f>
         <v>174237.25</v>
       </c>
-      <c r="E12" s="97" t="n">
+      <c r="E12" s="115" t="n">
         <f aca="false">E9+E10+E11</f>
         <v>177549.666666667</v>
       </c>
-      <c r="F12" s="97" t="n">
+      <c r="F12" s="115" t="n">
         <f aca="false">F9+F10+F11</f>
         <v>177549.666666667</v>
       </c>
-      <c r="G12" s="97" t="n">
+      <c r="G12" s="115" t="n">
         <f aca="false">G9+G10+G11</f>
         <v>177549.666666667</v>
       </c>
-      <c r="H12" s="97" t="n">
+      <c r="H12" s="115" t="n">
         <f aca="false">H9+H10+H11</f>
         <v>177549.666666667</v>
       </c>
-      <c r="I12" s="97" t="n">
+      <c r="I12" s="115" t="n">
         <f aca="false">I9+I10+I11</f>
         <v>177549.666666667</v>
       </c>
-      <c r="J12" s="97" t="n">
+      <c r="J12" s="115" t="n">
         <f aca="false">J9+J10+J11</f>
         <v>177549.666666667</v>
       </c>
-      <c r="K12" s="97" t="n">
+      <c r="K12" s="115" t="n">
         <f aca="false">K9+K10+K11</f>
         <v>180862.083333333</v>
       </c>
-      <c r="L12" s="97" t="n">
+      <c r="L12" s="115" t="n">
         <f aca="false">L9+L10+L11</f>
         <v>180862.083333333</v>
       </c>
-      <c r="M12" s="97" t="n">
+      <c r="M12" s="115" t="n">
         <f aca="false">M9+M10+M11</f>
         <v>180862.083333333</v>
       </c>
-      <c r="N12" s="98" t="n">
+      <c r="N12" s="116" t="n">
         <f aca="false">SUM(B12:M12)</f>
         <v>2130596</v>
       </c>
-      <c r="O12" s="99" t="n">
+      <c r="O12" s="117" t="n">
         <f aca="false">IF(N7=0,0,N12/N7)</f>
         <v>0.626498470948012</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="91"/>
-      <c r="B13" s="100"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="100"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="100"/>
-      <c r="L13" s="100"/>
-      <c r="M13" s="100"/>
-      <c r="N13" s="101"/>
-      <c r="O13" s="101"/>
+      <c r="A13" s="110"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
+      <c r="K13" s="118"/>
+      <c r="L13" s="118"/>
+      <c r="M13" s="118"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="119"/>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="96" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="102" t="n">
+      <c r="A14" s="114" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="120" t="n">
         <f aca="false">B7-B12</f>
         <v>104562.75</v>
       </c>
-      <c r="C14" s="102" t="n">
+      <c r="C14" s="120" t="n">
         <f aca="false">C7-C12</f>
         <v>104562.75</v>
       </c>
-      <c r="D14" s="102" t="n">
+      <c r="D14" s="120" t="n">
         <f aca="false">D7-D12</f>
         <v>104562.75</v>
       </c>
-      <c r="E14" s="102" t="n">
+      <c r="E14" s="120" t="n">
         <f aca="false">E7-E12</f>
         <v>105850.333333333</v>
       </c>
-      <c r="F14" s="102" t="n">
+      <c r="F14" s="120" t="n">
         <f aca="false">F7-F12</f>
         <v>105850.333333333</v>
       </c>
-      <c r="G14" s="102" t="n">
+      <c r="G14" s="120" t="n">
         <f aca="false">G7-G12</f>
         <v>105850.333333333</v>
       </c>
-      <c r="H14" s="102" t="n">
+      <c r="H14" s="120" t="n">
         <f aca="false">H7-H12</f>
         <v>105850.333333333</v>
       </c>
-      <c r="I14" s="102" t="n">
+      <c r="I14" s="120" t="n">
         <f aca="false">I7-I12</f>
         <v>105850.333333333</v>
       </c>
-      <c r="J14" s="102" t="n">
+      <c r="J14" s="120" t="n">
         <f aca="false">J7-J12</f>
         <v>105850.333333333</v>
       </c>
-      <c r="K14" s="102" t="n">
+      <c r="K14" s="120" t="n">
         <f aca="false">K7-K12</f>
         <v>107137.916666667</v>
       </c>
-      <c r="L14" s="102" t="n">
+      <c r="L14" s="120" t="n">
         <f aca="false">L7-L12</f>
         <v>107137.916666667</v>
       </c>
-      <c r="M14" s="102" t="n">
+      <c r="M14" s="120" t="n">
         <f aca="false">M7-M12</f>
         <v>107137.916666667</v>
       </c>
-      <c r="N14" s="103" t="n">
+      <c r="N14" s="121" t="n">
         <f aca="false">SUM(B14:M14)</f>
         <v>1270204</v>
       </c>
-      <c r="O14" s="104" t="n">
+      <c r="O14" s="122" t="n">
         <f aca="false">IF(N7=0,0,N14/N7)</f>
         <v>0.373501529051988</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="105" t="s">
+      <c r="A15" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="106" t="n">
+      <c r="B15" s="123" t="n">
         <f aca="false">B14</f>
         <v>104562.75</v>
       </c>
-      <c r="C15" s="106" t="n">
+      <c r="C15" s="123" t="n">
         <f aca="false">C14</f>
         <v>104562.75</v>
       </c>
-      <c r="D15" s="106" t="n">
+      <c r="D15" s="123" t="n">
         <f aca="false">D14</f>
         <v>104562.75</v>
       </c>
-      <c r="E15" s="106" t="n">
+      <c r="E15" s="123" t="n">
         <f aca="false">E14</f>
         <v>105850.333333333</v>
       </c>
-      <c r="F15" s="106" t="n">
+      <c r="F15" s="123" t="n">
         <f aca="false">F14</f>
         <v>105850.333333333</v>
       </c>
-      <c r="G15" s="106" t="n">
+      <c r="G15" s="123" t="n">
         <f aca="false">G14</f>
         <v>105850.333333333</v>
       </c>
-      <c r="H15" s="106" t="n">
+      <c r="H15" s="123" t="n">
         <f aca="false">H14</f>
         <v>105850.333333333</v>
       </c>
-      <c r="I15" s="106" t="n">
+      <c r="I15" s="123" t="n">
         <f aca="false">I14</f>
         <v>105850.333333333</v>
       </c>
-      <c r="J15" s="106" t="n">
+      <c r="J15" s="123" t="n">
         <f aca="false">J14</f>
         <v>105850.333333333</v>
       </c>
-      <c r="K15" s="106" t="n">
+      <c r="K15" s="123" t="n">
         <f aca="false">K14</f>
         <v>107137.916666667</v>
       </c>
-      <c r="L15" s="106" t="n">
+      <c r="L15" s="123" t="n">
         <f aca="false">L14</f>
         <v>107137.916666667</v>
       </c>
-      <c r="M15" s="106" t="n">
+      <c r="M15" s="123" t="n">
         <f aca="false">M14</f>
         <v>107137.916666667</v>
       </c>
-      <c r="N15" s="106" t="n">
+      <c r="N15" s="123" t="n">
         <f aca="false">SUM(B15:M15)</f>
         <v>1270204</v>
       </c>
-      <c r="O15" s="107" t="n">
+      <c r="O15" s="124" t="n">
         <f aca="false">IF(N7=0,0,N15/N7)</f>
         <v>0.373501529051988</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="91" t="s">
-        <v>150</v>
-      </c>
-      <c r="B16" s="108" t="n">
+      <c r="A16" s="110" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" s="125" t="n">
         <f aca="false">IF(B7=0,0,B15/B7)</f>
         <v>0.375045731707317</v>
       </c>
-      <c r="C16" s="108" t="n">
+      <c r="C16" s="125" t="n">
         <f aca="false">IF(C7=0,0,C15/C7)</f>
         <v>0.375045731707317</v>
       </c>
-      <c r="D16" s="108" t="n">
+      <c r="D16" s="125" t="n">
         <f aca="false">IF(D7=0,0,D15/D7)</f>
         <v>0.375045731707317</v>
       </c>
-      <c r="E16" s="108" t="n">
+      <c r="E16" s="125" t="n">
         <f aca="false">IF(E7=0,0,E15/E7)</f>
         <v>0.373501529051988</v>
       </c>
-      <c r="F16" s="108" t="n">
+      <c r="F16" s="125" t="n">
         <f aca="false">IF(F7=0,0,F15/F7)</f>
         <v>0.373501529051988</v>
       </c>
-      <c r="G16" s="108" t="n">
+      <c r="G16" s="125" t="n">
         <f aca="false">IF(G7=0,0,G15/G7)</f>
         <v>0.373501529051988</v>
       </c>
-      <c r="H16" s="108" t="n">
+      <c r="H16" s="125" t="n">
         <f aca="false">IF(H7=0,0,H15/H7)</f>
         <v>0.373501529051988</v>
       </c>
-      <c r="I16" s="108" t="n">
+      <c r="I16" s="125" t="n">
         <f aca="false">IF(I7=0,0,I15/I7)</f>
         <v>0.373501529051988</v>
       </c>
-      <c r="J16" s="108" t="n">
+      <c r="J16" s="125" t="n">
         <f aca="false">IF(J7=0,0,J15/J7)</f>
         <v>0.373501529051988</v>
       </c>
-      <c r="K16" s="108" t="n">
+      <c r="K16" s="125" t="n">
         <f aca="false">IF(K7=0,0,K15/K7)</f>
         <v>0.372006655092593</v>
       </c>
-      <c r="L16" s="108" t="n">
+      <c r="L16" s="125" t="n">
         <f aca="false">IF(L7=0,0,L15/L7)</f>
         <v>0.372006655092593</v>
       </c>
-      <c r="M16" s="108" t="n">
+      <c r="M16" s="125" t="n">
         <f aca="false">IF(M7=0,0,M15/M7)</f>
         <v>0.372006655092593</v>
       </c>
-      <c r="N16" s="104" t="n">
+      <c r="N16" s="122" t="n">
         <f aca="false">IF(N7=0,0,N15/N7)</f>
         <v>0.373501529051988</v>
       </c>
-      <c r="O16" s="104"/>
+      <c r="O16" s="122"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="91"/>
-      <c r="B17" s="101"/>
-      <c r="C17" s="101"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="101"/>
-      <c r="H17" s="101"/>
-      <c r="I17" s="101"/>
-      <c r="J17" s="101"/>
-      <c r="K17" s="101"/>
-      <c r="L17" s="101"/>
-      <c r="M17" s="101"/>
-      <c r="N17" s="101"/>
-      <c r="O17" s="101"/>
+      <c r="A17" s="110"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="119"/>
+      <c r="L17" s="119"/>
+      <c r="M17" s="119"/>
+      <c r="N17" s="119"/>
+      <c r="O17" s="119"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="91" t="s">
-        <v>151</v>
-      </c>
-      <c r="B18" s="95" t="n">
+      <c r="A18" s="110" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" s="113" t="n">
         <f aca="false">0.02*B7</f>
         <v>5576</v>
       </c>
-      <c r="C18" s="95" t="n">
+      <c r="C18" s="113" t="n">
         <f aca="false">0.02*C7</f>
         <v>5576</v>
       </c>
-      <c r="D18" s="95" t="n">
+      <c r="D18" s="113" t="n">
         <f aca="false">0.02*D7</f>
         <v>5576</v>
       </c>
-      <c r="E18" s="95" t="n">
+      <c r="E18" s="113" t="n">
         <f aca="false">0.02*E7</f>
         <v>5668</v>
       </c>
-      <c r="F18" s="95" t="n">
+      <c r="F18" s="113" t="n">
         <f aca="false">0.02*F7</f>
         <v>5668</v>
       </c>
-      <c r="G18" s="95" t="n">
+      <c r="G18" s="113" t="n">
         <f aca="false">0.02*G7</f>
         <v>5668</v>
       </c>
-      <c r="H18" s="95" t="n">
+      <c r="H18" s="113" t="n">
         <f aca="false">0.02*H7</f>
         <v>5668</v>
       </c>
-      <c r="I18" s="95" t="n">
+      <c r="I18" s="113" t="n">
         <f aca="false">0.02*I7</f>
         <v>5668</v>
       </c>
-      <c r="J18" s="95" t="n">
+      <c r="J18" s="113" t="n">
         <f aca="false">0.02*J7</f>
         <v>5668</v>
       </c>
-      <c r="K18" s="95" t="n">
+      <c r="K18" s="113" t="n">
         <f aca="false">0.02*K7</f>
         <v>5760</v>
       </c>
-      <c r="L18" s="95" t="n">
+      <c r="L18" s="113" t="n">
         <f aca="false">0.02*L7</f>
         <v>5760</v>
       </c>
-      <c r="M18" s="95" t="n">
+      <c r="M18" s="113" t="n">
         <f aca="false">0.02*M7</f>
         <v>5760</v>
       </c>
-      <c r="N18" s="93" t="n">
+      <c r="N18" s="112" t="n">
         <f aca="false">SUM(B18:M18)</f>
         <v>68016</v>
       </c>
-      <c r="O18" s="94" t="n">
+      <c r="O18" s="97" t="n">
         <f aca="false">IF(N7=0,0,N18/N7)</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="77" t="s">
-        <v>152</v>
-      </c>
-      <c r="B19" s="97" t="n">
+        <v>179</v>
+      </c>
+      <c r="B19" s="115" t="n">
         <f aca="false">B15-B18</f>
         <v>98986.75</v>
       </c>
-      <c r="C19" s="97" t="n">
+      <c r="C19" s="115" t="n">
         <f aca="false">C15-C18</f>
         <v>98986.75</v>
       </c>
-      <c r="D19" s="97" t="n">
+      <c r="D19" s="115" t="n">
         <f aca="false">D15-D18</f>
         <v>98986.75</v>
       </c>
-      <c r="E19" s="97" t="n">
+      <c r="E19" s="115" t="n">
         <f aca="false">E15-E18</f>
         <v>100182.333333333</v>
       </c>
-      <c r="F19" s="97" t="n">
+      <c r="F19" s="115" t="n">
         <f aca="false">F15-F18</f>
         <v>100182.333333333</v>
       </c>
-      <c r="G19" s="97" t="n">
+      <c r="G19" s="115" t="n">
         <f aca="false">G15-G18</f>
         <v>100182.333333333</v>
       </c>
-      <c r="H19" s="97" t="n">
+      <c r="H19" s="115" t="n">
         <f aca="false">H15-H18</f>
         <v>100182.333333333</v>
       </c>
-      <c r="I19" s="97" t="n">
+      <c r="I19" s="115" t="n">
         <f aca="false">I15-I18</f>
         <v>100182.333333333</v>
       </c>
-      <c r="J19" s="97" t="n">
+      <c r="J19" s="115" t="n">
         <f aca="false">J15-J18</f>
         <v>100182.333333333</v>
       </c>
-      <c r="K19" s="97" t="n">
+      <c r="K19" s="115" t="n">
         <f aca="false">K15-K18</f>
         <v>101377.916666667</v>
       </c>
-      <c r="L19" s="97" t="n">
+      <c r="L19" s="115" t="n">
         <f aca="false">L15-L18</f>
         <v>101377.916666667</v>
       </c>
-      <c r="M19" s="97" t="n">
+      <c r="M19" s="115" t="n">
         <f aca="false">M15-M18</f>
         <v>101377.916666667</v>
       </c>
-      <c r="N19" s="98" t="n">
+      <c r="N19" s="116" t="n">
         <f aca="false">SUM(B19:M19)</f>
         <v>1202188</v>
       </c>
-      <c r="O19" s="99" t="n">
+      <c r="O19" s="117" t="n">
         <f aca="false">IF(N7=0,0,N19/N7)</f>
         <v>0.353501529051988</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="B20" s="110" t="n">
+      <c r="A20" s="126" t="s">
+        <v>180</v>
+      </c>
+      <c r="B20" s="127" t="n">
         <f aca="false">IF(B19&gt;0,B19*0.21,0)</f>
         <v>20787.2175</v>
       </c>
-      <c r="C20" s="110" t="n">
+      <c r="C20" s="127" t="n">
         <f aca="false">IF(C19&gt;0,C19*0.21,0)</f>
         <v>20787.2175</v>
       </c>
-      <c r="D20" s="110" t="n">
+      <c r="D20" s="127" t="n">
         <f aca="false">IF(D19&gt;0,D19*0.21,0)</f>
         <v>20787.2175</v>
       </c>
-      <c r="E20" s="110" t="n">
+      <c r="E20" s="127" t="n">
         <f aca="false">IF(E19&gt;0,E19*0.21,0)</f>
         <v>21038.29</v>
       </c>
-      <c r="F20" s="110" t="n">
+      <c r="F20" s="127" t="n">
         <f aca="false">IF(F19&gt;0,F19*0.21,0)</f>
         <v>21038.29</v>
       </c>
-      <c r="G20" s="110" t="n">
+      <c r="G20" s="127" t="n">
         <f aca="false">IF(G19&gt;0,G19*0.21,0)</f>
         <v>21038.29</v>
       </c>
-      <c r="H20" s="110" t="n">
+      <c r="H20" s="127" t="n">
         <f aca="false">IF(H19&gt;0,H19*0.21,0)</f>
         <v>21038.29</v>
       </c>
-      <c r="I20" s="110" t="n">
+      <c r="I20" s="127" t="n">
         <f aca="false">IF(I19&gt;0,I19*0.21,0)</f>
         <v>21038.29</v>
       </c>
-      <c r="J20" s="110" t="n">
+      <c r="J20" s="127" t="n">
         <f aca="false">IF(J19&gt;0,J19*0.21,0)</f>
         <v>21038.29</v>
       </c>
-      <c r="K20" s="110" t="n">
+      <c r="K20" s="127" t="n">
         <f aca="false">IF(K19&gt;0,K19*0.21,0)</f>
         <v>21289.3625</v>
       </c>
-      <c r="L20" s="110" t="n">
+      <c r="L20" s="127" t="n">
         <f aca="false">IF(L19&gt;0,L19*0.21,0)</f>
         <v>21289.3625</v>
       </c>
-      <c r="M20" s="110" t="n">
+      <c r="M20" s="127" t="n">
         <f aca="false">IF(M19&gt;0,M19*0.21,0)</f>
         <v>21289.3625</v>
       </c>
-      <c r="N20" s="93" t="n">
+      <c r="N20" s="112" t="n">
         <f aca="false">SUM(B20:M20)</f>
         <v>252459.48</v>
       </c>
-      <c r="O20" s="94" t="n">
+      <c r="O20" s="97" t="n">
         <f aca="false">IF(N7=0,0,N20/N7)</f>
         <v>0.0742353211009174</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="77" t="s">
-        <v>154</v>
-      </c>
-      <c r="B21" s="111" t="n">
+        <v>181</v>
+      </c>
+      <c r="B21" s="128" t="n">
         <f aca="false">B19-B20</f>
         <v>78199.5325</v>
       </c>
-      <c r="C21" s="111" t="n">
+      <c r="C21" s="128" t="n">
         <f aca="false">C19-C20</f>
         <v>78199.5325</v>
       </c>
-      <c r="D21" s="111" t="n">
+      <c r="D21" s="128" t="n">
         <f aca="false">D19-D20</f>
         <v>78199.5325</v>
       </c>
-      <c r="E21" s="111" t="n">
+      <c r="E21" s="128" t="n">
         <f aca="false">E19-E20</f>
         <v>79144.0433333333</v>
       </c>
-      <c r="F21" s="111" t="n">
+      <c r="F21" s="128" t="n">
         <f aca="false">F19-F20</f>
         <v>79144.0433333333</v>
       </c>
-      <c r="G21" s="111" t="n">
+      <c r="G21" s="128" t="n">
         <f aca="false">G19-G20</f>
         <v>79144.0433333333</v>
       </c>
-      <c r="H21" s="111" t="n">
+      <c r="H21" s="128" t="n">
         <f aca="false">H19-H20</f>
         <v>79144.0433333333</v>
       </c>
-      <c r="I21" s="111" t="n">
+      <c r="I21" s="128" t="n">
         <f aca="false">I19-I20</f>
         <v>79144.0433333333</v>
       </c>
-      <c r="J21" s="111" t="n">
+      <c r="J21" s="128" t="n">
         <f aca="false">J19-J20</f>
         <v>79144.0433333333</v>
       </c>
-      <c r="K21" s="111" t="n">
+      <c r="K21" s="128" t="n">
         <f aca="false">K19-K20</f>
         <v>80088.5541666667</v>
       </c>
-      <c r="L21" s="111" t="n">
+      <c r="L21" s="128" t="n">
         <f aca="false">L19-L20</f>
         <v>80088.5541666667</v>
       </c>
-      <c r="M21" s="111" t="n">
+      <c r="M21" s="128" t="n">
         <f aca="false">M19-M20</f>
         <v>80088.5541666667</v>
       </c>
-      <c r="N21" s="98" t="n">
+      <c r="N21" s="116" t="n">
         <f aca="false">SUM(B21:M21)</f>
         <v>949728.52</v>
       </c>
-      <c r="O21" s="99" t="n">
+      <c r="O21" s="117" t="n">
         <f aca="false">IF(N21=0,0,N21/N7)</f>
         <v>0.27926620795107</v>
       </c>
@@ -11407,26 +12098,26 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="112" t="s">
-        <v>155</v>
-      </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
+      <c r="B2" s="129" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11454,85 +12145,85 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="113" t="s">
-        <v>156</v>
+      <c r="B2" s="130" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="114"/>
+      <c r="B3" s="131"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="115" t="s">
-        <v>157</v>
+      <c r="B4" s="132" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="114"/>
+      <c r="B5" s="131"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="116" t="s">
-        <v>158</v>
+      <c r="B6" s="133" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="114" t="s">
-        <v>159</v>
+      <c r="B7" s="131" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="114" t="s">
-        <v>160</v>
+      <c r="B8" s="131" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="114" t="s">
-        <v>161</v>
+      <c r="B9" s="131" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="114"/>
+      <c r="B10" s="131"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="116" t="s">
-        <v>162</v>
+      <c r="B11" s="133" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="114" t="s">
-        <v>163</v>
+      <c r="B12" s="131" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="114" t="s">
-        <v>164</v>
+      <c r="B13" s="131" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="114" t="s">
-        <v>165</v>
+      <c r="B14" s="131" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="114"/>
+      <c r="B15" s="131"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="116" t="s">
-        <v>166</v>
+      <c r="B16" s="133" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="114" t="s">
-        <v>167</v>
+      <c r="B17" s="131" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="114" t="s">
-        <v>168</v>
+      <c r="B18" s="131" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="114" t="s">
-        <v>169</v>
+      <c r="B19" s="131" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -11555,13 +12246,13 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="20.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="34.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="43.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -11581,131 +12272,131 @@
       <c r="Q1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="117" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="117"/>
-      <c r="P2" s="117"/>
-      <c r="Q2" s="117"/>
+      <c r="A2" s="134" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="134"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="134"/>
+      <c r="M2" s="134"/>
+      <c r="N2" s="134"/>
+      <c r="O2" s="134"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="118" t="s">
-        <v>172</v>
-      </c>
-      <c r="B3" s="119" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="120" t="s">
-        <v>174</v>
-      </c>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="120"/>
-      <c r="O3" s="120"/>
-      <c r="P3" s="120"/>
-      <c r="Q3" s="120"/>
+      <c r="A3" s="135" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="136" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="137" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
+      <c r="L3" s="137"/>
+      <c r="M3" s="137"/>
+      <c r="N3" s="137"/>
+      <c r="O3" s="137"/>
+      <c r="P3" s="137"/>
+      <c r="Q3" s="137"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="121" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="122" t="s">
-        <v>176</v>
-      </c>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="123" t="s">
-        <v>177</v>
-      </c>
-      <c r="J4" s="123"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="123"/>
-      <c r="N4" s="123"/>
-      <c r="O4" s="123"/>
-      <c r="P4" s="123"/>
-      <c r="Q4" s="123"/>
+      <c r="A4" s="138" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4" s="139" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="139"/>
+      <c r="I4" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="J4" s="140"/>
+      <c r="K4" s="140"/>
+      <c r="L4" s="140"/>
+      <c r="M4" s="140"/>
+      <c r="N4" s="140"/>
+      <c r="O4" s="140"/>
+      <c r="P4" s="140"/>
+      <c r="Q4" s="140"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="124" t="s">
-        <v>178</v>
-      </c>
-      <c r="B5" s="125" t="s">
-        <v>179</v>
-      </c>
-      <c r="C5" s="125"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="126" t="s">
-        <v>180</v>
-      </c>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
-      <c r="L5" s="126"/>
-      <c r="M5" s="126"/>
-      <c r="N5" s="126"/>
-      <c r="O5" s="126"/>
-      <c r="P5" s="126"/>
-      <c r="Q5" s="126"/>
+      <c r="A5" s="141" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="142" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="142"/>
+      <c r="I5" s="143" t="s">
+        <v>207</v>
+      </c>
+      <c r="J5" s="143"/>
+      <c r="K5" s="143"/>
+      <c r="L5" s="143"/>
+      <c r="M5" s="143"/>
+      <c r="N5" s="143"/>
+      <c r="O5" s="143"/>
+      <c r="P5" s="143"/>
+      <c r="Q5" s="143"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="117" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="117"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="117"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
-      <c r="M6" s="117"/>
-      <c r="N6" s="117"/>
-      <c r="O6" s="117"/>
-      <c r="P6" s="117"/>
-      <c r="Q6" s="117"/>
+      <c r="A6" s="134" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="134"/>
+      <c r="C6" s="134"/>
+      <c r="D6" s="134"/>
+      <c r="E6" s="134"/>
+      <c r="F6" s="134"/>
+      <c r="G6" s="134"/>
+      <c r="H6" s="134"/>
+      <c r="I6" s="134"/>
+      <c r="J6" s="134"/>
+      <c r="K6" s="134"/>
+      <c r="L6" s="134"/>
+      <c r="M6" s="134"/>
+      <c r="N6" s="134"/>
+      <c r="O6" s="134"/>
+      <c r="P6" s="134"/>
+      <c r="Q6" s="134"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="B7" s="127" t="s">
-        <v>183</v>
+        <v>209</v>
+      </c>
+      <c r="B7" s="144" t="s">
+        <v>210</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="D7" s="38"/>
       <c r="E7" s="38"/>
@@ -11724,57 +12415,57 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="128" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="128" t="s">
+      <c r="C8" s="145" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="128" t="s">
+      <c r="D8" s="145" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="128" t="s">
+      <c r="E8" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="128" t="s">
+      <c r="F8" s="145" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="128" t="s">
+      <c r="G8" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="128" t="s">
+      <c r="H8" s="145" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="128" t="s">
+      <c r="I8" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="128" t="s">
+      <c r="J8" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="128" t="s">
+      <c r="K8" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="128" t="s">
+      <c r="L8" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="128" t="s">
+      <c r="M8" s="145" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="129" t="s">
-        <v>186</v>
-      </c>
-      <c r="O8" s="129" t="s">
-        <v>187</v>
-      </c>
-      <c r="P8" s="130" t="s">
-        <v>188</v>
+      <c r="N8" s="146" t="s">
+        <v>213</v>
+      </c>
+      <c r="O8" s="146" t="s">
+        <v>214</v>
+      </c>
+      <c r="P8" s="147" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="43" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="B9" s="44" t="n">
         <v>55</v>
@@ -11812,20 +12503,20 @@
       <c r="M9" s="44" t="n">
         <v>55</v>
       </c>
-      <c r="N9" s="131" t="n">
+      <c r="N9" s="148" t="n">
         <f aca="false">AVERAGE(B9:M9)</f>
         <v>55</v>
       </c>
-      <c r="O9" s="132" t="s">
-        <v>190</v>
-      </c>
-      <c r="P9" s="133" t="s">
-        <v>191</v>
+      <c r="O9" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="P9" s="150" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="B10" s="50" t="n">
         <v>4900</v>
@@ -11863,1431 +12554,1431 @@
       <c r="M10" s="50" t="n">
         <v>4900</v>
       </c>
-      <c r="N10" s="134" t="n">
+      <c r="N10" s="151" t="n">
         <f aca="false">AVERAGE(B10:M10)</f>
         <v>4900</v>
       </c>
-      <c r="O10" s="132" t="s">
-        <v>193</v>
-      </c>
-      <c r="P10" s="133" t="s">
-        <v>194</v>
+      <c r="O10" s="149" t="s">
+        <v>220</v>
+      </c>
+      <c r="P10" s="150" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="135" t="n">
+        <v>222</v>
+      </c>
+      <c r="B11" s="152" t="n">
         <v>0.76</v>
       </c>
-      <c r="C11" s="135" t="n">
+      <c r="C11" s="152" t="n">
         <v>0.79</v>
       </c>
-      <c r="D11" s="135" t="n">
+      <c r="D11" s="152" t="n">
         <v>0.82</v>
       </c>
-      <c r="E11" s="135" t="n">
+      <c r="E11" s="152" t="n">
         <v>0.86</v>
       </c>
-      <c r="F11" s="135" t="n">
+      <c r="F11" s="152" t="n">
         <v>0.89</v>
       </c>
-      <c r="G11" s="135" t="n">
+      <c r="G11" s="152" t="n">
         <v>0.89</v>
       </c>
-      <c r="H11" s="135" t="n">
+      <c r="H11" s="152" t="n">
         <v>0.87</v>
       </c>
-      <c r="I11" s="135" t="n">
+      <c r="I11" s="152" t="n">
         <v>0.84</v>
       </c>
-      <c r="J11" s="135" t="n">
+      <c r="J11" s="152" t="n">
         <v>0.86</v>
       </c>
-      <c r="K11" s="135" t="n">
+      <c r="K11" s="152" t="n">
         <v>0.84</v>
       </c>
-      <c r="L11" s="135" t="n">
+      <c r="L11" s="152" t="n">
         <v>0.82</v>
       </c>
-      <c r="M11" s="135" t="n">
+      <c r="M11" s="152" t="n">
         <v>0.79</v>
       </c>
-      <c r="N11" s="136" t="n">
+      <c r="N11" s="153" t="n">
         <f aca="false">AVERAGE(B11:M11)</f>
         <v>0.835833333333333</v>
       </c>
-      <c r="O11" s="132" t="s">
-        <v>196</v>
-      </c>
-      <c r="P11" s="133" t="s">
-        <v>197</v>
+      <c r="O11" s="149" t="s">
+        <v>223</v>
+      </c>
+      <c r="P11" s="150" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="137"/>
-      <c r="B12" s="138"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="138"/>
-      <c r="E12" s="138"/>
-      <c r="F12" s="138"/>
-      <c r="G12" s="138"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="138"/>
-      <c r="J12" s="138"/>
-      <c r="K12" s="138"/>
-      <c r="L12" s="138"/>
-      <c r="M12" s="138"/>
+      <c r="A12" s="154"/>
+      <c r="B12" s="155"/>
+      <c r="C12" s="155"/>
+      <c r="D12" s="155"/>
+      <c r="E12" s="155"/>
+      <c r="F12" s="155"/>
+      <c r="G12" s="155"/>
+      <c r="H12" s="155"/>
+      <c r="I12" s="155"/>
+      <c r="J12" s="155"/>
+      <c r="K12" s="155"/>
+      <c r="L12" s="155"/>
+      <c r="M12" s="155"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="117" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="117"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117"/>
-      <c r="F13" s="117"/>
-      <c r="G13" s="117"/>
-      <c r="H13" s="117"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="117"/>
-      <c r="K13" s="117"/>
-      <c r="L13" s="117"/>
-      <c r="M13" s="117"/>
-      <c r="N13" s="117"/>
-      <c r="O13" s="117"/>
-      <c r="P13" s="117"/>
-      <c r="Q13" s="117"/>
+      <c r="A13" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="B13" s="134"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="134"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="134"/>
+      <c r="K13" s="134"/>
+      <c r="L13" s="134"/>
+      <c r="M13" s="134"/>
+      <c r="N13" s="134"/>
+      <c r="O13" s="134"/>
+      <c r="P13" s="134"/>
+      <c r="Q13" s="134"/>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="128" t="s">
+      <c r="A14" s="145" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="145" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="145" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="145" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="145" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="145" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="145" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="145" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="145" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="145" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="145" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="145" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="145" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" s="145" t="s">
+        <v>99</v>
+      </c>
+      <c r="O14" s="145" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="135" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="128" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="128" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="128" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="128" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="128" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="128" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="128" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="128" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="128" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="128" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" s="128" t="s">
-        <v>24</v>
-      </c>
-      <c r="N14" s="128" t="s">
-        <v>99</v>
-      </c>
-      <c r="O14" s="128" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="118" t="s">
-        <v>172</v>
-      </c>
-      <c r="B15" s="139" t="n">
+      <c r="B15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="C15" s="139" t="n">
+      <c r="C15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="D15" s="139" t="n">
+      <c r="D15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="E15" s="139" t="n">
+      <c r="E15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="F15" s="139" t="n">
+      <c r="F15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="G15" s="139" t="n">
+      <c r="G15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="H15" s="139" t="n">
+      <c r="H15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="I15" s="139" t="n">
+      <c r="I15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="J15" s="139" t="n">
+      <c r="J15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="K15" s="139" t="n">
+      <c r="K15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="L15" s="139" t="n">
+      <c r="L15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="M15" s="139" t="n">
+      <c r="M15" s="101" t="n">
         <f aca="false">AVERAGE(RawData!D35,RawData!D36,RawData!D37)</f>
         <v>176666.666666667</v>
       </c>
-      <c r="N15" s="140" t="n">
+      <c r="N15" s="156" t="n">
         <f aca="false">SUM(B15:M15)</f>
         <v>2120000</v>
       </c>
-      <c r="O15" s="141" t="s">
-        <v>201</v>
+      <c r="O15" s="157" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="121" t="s">
-        <v>175</v>
-      </c>
-      <c r="B16" s="142" t="n">
+      <c r="A16" s="138" t="s">
+        <v>202</v>
+      </c>
+      <c r="B16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*13</f>
         <v>197866.666666667</v>
       </c>
-      <c r="C16" s="142" t="n">
+      <c r="C16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*14</f>
         <v>201128.205128205</v>
       </c>
-      <c r="D16" s="142" t="n">
+      <c r="D16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*15</f>
         <v>204389.743589744</v>
       </c>
-      <c r="E16" s="142" t="n">
+      <c r="E16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*16</f>
         <v>207651.282051282</v>
       </c>
-      <c r="F16" s="142" t="n">
+      <c r="F16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*17</f>
         <v>210912.820512821</v>
       </c>
-      <c r="G16" s="142" t="n">
-        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*13</f>
-        <v>197866.666666667</v>
-      </c>
-      <c r="H16" s="142" t="n">
+      <c r="G16" s="158" t="n">
+        <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*18</f>
+        <v>214174.358974359</v>
+      </c>
+      <c r="H16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*19</f>
         <v>217435.897435897</v>
       </c>
-      <c r="I16" s="142" t="n">
+      <c r="I16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*20</f>
         <v>220697.435897436</v>
       </c>
-      <c r="J16" s="142" t="n">
+      <c r="J16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*21</f>
         <v>223958.974358974</v>
       </c>
-      <c r="K16" s="142" t="n">
+      <c r="K16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*22</f>
         <v>227220.512820513</v>
       </c>
-      <c r="L16" s="142" t="n">
+      <c r="L16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*23</f>
         <v>230482.051282051</v>
       </c>
-      <c r="M16" s="142" t="n">
+      <c r="M16" s="158" t="n">
         <f aca="false">INTERCEPT(RawData!D26:D37,RawData!C26:C37)+SLOPE(RawData!D26:D37,RawData!C26:C37)*24</f>
         <v>233743.58974359</v>
       </c>
-      <c r="N16" s="143" t="n">
+      <c r="N16" s="159" t="n">
         <f aca="false">SUM(B16:M16)</f>
-        <v>2573353.84615385</v>
-      </c>
-      <c r="O16" s="141" t="s">
-        <v>202</v>
+        <v>2589661.53846154</v>
+      </c>
+      <c r="O16" s="157" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="124" t="s">
-        <v>178</v>
-      </c>
-      <c r="B17" s="144" t="n">
+      <c r="A17" s="141" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" s="160" t="n">
         <f aca="false">B9*B10*B11</f>
         <v>204820</v>
       </c>
-      <c r="C17" s="144" t="n">
+      <c r="C17" s="160" t="n">
         <f aca="false">C9*C10*C11</f>
         <v>212905</v>
       </c>
-      <c r="D17" s="144" t="n">
+      <c r="D17" s="160" t="n">
         <f aca="false">D9*D10*D11</f>
         <v>220990</v>
       </c>
-      <c r="E17" s="144" t="n">
+      <c r="E17" s="160" t="n">
         <f aca="false">E9*E10*E11</f>
         <v>231770</v>
       </c>
-      <c r="F17" s="144" t="n">
+      <c r="F17" s="160" t="n">
         <f aca="false">F9*F10*F11</f>
         <v>239855</v>
       </c>
-      <c r="G17" s="144" t="n">
+      <c r="G17" s="160" t="n">
         <f aca="false">G9*G10*G11</f>
         <v>239855</v>
       </c>
-      <c r="H17" s="144" t="n">
+      <c r="H17" s="160" t="n">
         <f aca="false">H9*H10*H11</f>
         <v>234465</v>
       </c>
-      <c r="I17" s="144" t="n">
+      <c r="I17" s="160" t="n">
         <f aca="false">I9*I10*I11</f>
         <v>226380</v>
       </c>
-      <c r="J17" s="144" t="n">
+      <c r="J17" s="160" t="n">
         <f aca="false">J9*J10*J11</f>
         <v>231770</v>
       </c>
-      <c r="K17" s="144" t="n">
+      <c r="K17" s="160" t="n">
         <f aca="false">K9*K10*K11</f>
         <v>226380</v>
       </c>
-      <c r="L17" s="144" t="n">
+      <c r="L17" s="160" t="n">
         <f aca="false">L9*L10*L11</f>
         <v>220990</v>
       </c>
-      <c r="M17" s="144" t="n">
+      <c r="M17" s="160" t="n">
         <f aca="false">M9*M10*M11</f>
         <v>212905</v>
       </c>
-      <c r="N17" s="145" t="n">
+      <c r="N17" s="161" t="n">
         <f aca="false">SUM(B17:M17)</f>
         <v>2703085</v>
       </c>
-      <c r="O17" s="141" t="s">
-        <v>203</v>
+      <c r="O17" s="157" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="146" t="s">
-        <v>204</v>
-      </c>
-      <c r="B18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",B15,IF($B$8="Trend",B16,B17))</f>
-        <v>204820</v>
-      </c>
-      <c r="C18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",C15,IF($B$8="Trend",C16,C17))</f>
-        <v>212905</v>
-      </c>
-      <c r="D18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",D15,IF($B$8="Trend",D16,D17))</f>
-        <v>220990</v>
-      </c>
-      <c r="E18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",E15,IF($B$8="Trend",E16,E17))</f>
-        <v>231770</v>
-      </c>
-      <c r="F18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",F15,IF($B$8="Trend",F16,F17))</f>
-        <v>239855</v>
-      </c>
-      <c r="G18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",G15,IF($B$8="Trend",G16,G17))</f>
-        <v>239855</v>
-      </c>
-      <c r="H18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",H15,IF($B$8="Trend",H16,H17))</f>
-        <v>234465</v>
-      </c>
-      <c r="I18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",I15,IF($B$8="Trend",I16,I17))</f>
-        <v>226380</v>
-      </c>
-      <c r="J18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",J15,IF($B$8="Trend",J16,J17))</f>
-        <v>231770</v>
-      </c>
-      <c r="K18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",K15,IF($B$8="Trend",K16,K17))</f>
-        <v>226380</v>
-      </c>
-      <c r="L18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",L15,IF($B$8="Trend",L16,L17))</f>
-        <v>220990</v>
-      </c>
-      <c r="M18" s="147" t="n">
-        <f aca="false">IF($B$8="Flat",M15,IF($B$8="Trend",M16,M17))</f>
-        <v>212905</v>
-      </c>
-      <c r="N18" s="147" t="n">
+      <c r="A18" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="B18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",B15,IF($B$7="Trend",B16,B17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="C18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",C15,IF($B$7="Trend",C16,C17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="D18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",D15,IF($B$7="Trend",D16,D17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="E18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",E15,IF($B$7="Trend",E16,E17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="F18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",F15,IF($B$7="Trend",F16,F17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="G18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",G15,IF($B$7="Trend",G16,G17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="H18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",H15,IF($B$7="Trend",H16,H17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="I18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",I15,IF($B$7="Trend",I16,I17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="J18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",J15,IF($B$7="Trend",J16,J17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="K18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",K15,IF($B$7="Trend",K16,K17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="L18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",L15,IF($B7="Trend",L16,L17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="M18" s="105" t="n">
+        <f aca="false">IF($B$7="Flat",M15,IF($B$7="Trend",M16,M17))</f>
+        <v>176666.666666667</v>
+      </c>
+      <c r="N18" s="105" t="n">
         <f aca="false">SUM(B18:M18)</f>
-        <v>2703085</v>
-      </c>
-      <c r="O18" s="148"/>
+        <v>2120000</v>
+      </c>
+      <c r="O18" s="163"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="117" t="s">
-        <v>205</v>
-      </c>
-      <c r="B20" s="117"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="117"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="117"/>
-      <c r="L20" s="117"/>
-      <c r="M20" s="117"/>
-      <c r="N20" s="117"/>
-      <c r="O20" s="117"/>
-      <c r="P20" s="117"/>
-      <c r="Q20" s="117"/>
+      <c r="A20" s="134" t="s">
+        <v>232</v>
+      </c>
+      <c r="B20" s="134"/>
+      <c r="C20" s="134"/>
+      <c r="D20" s="134"/>
+      <c r="E20" s="134"/>
+      <c r="F20" s="134"/>
+      <c r="G20" s="134"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="134"/>
+      <c r="K20" s="134"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="134"/>
+      <c r="N20" s="134"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="134"/>
+      <c r="Q20" s="134"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="130" t="s">
-        <v>142</v>
-      </c>
-      <c r="B21" s="129" t="s">
+      <c r="A21" s="147" t="s">
+        <v>169</v>
+      </c>
+      <c r="B21" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="129" t="s">
+      <c r="C21" s="146" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="129" t="s">
+      <c r="D21" s="146" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="129" t="s">
+      <c r="E21" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="129" t="s">
+      <c r="F21" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="129" t="s">
+      <c r="G21" s="146" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="129" t="s">
+      <c r="H21" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="I21" s="129" t="s">
+      <c r="I21" s="146" t="s">
         <v>20</v>
       </c>
-      <c r="J21" s="129" t="s">
+      <c r="J21" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="K21" s="129" t="s">
+      <c r="K21" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="L21" s="129" t="s">
+      <c r="L21" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="M21" s="129" t="s">
+      <c r="M21" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="N21" s="129" t="s">
+      <c r="N21" s="146" t="s">
         <v>99</v>
       </c>
-      <c r="O21" s="129" t="s">
-        <v>206</v>
-      </c>
-      <c r="P21" s="130" t="s">
-        <v>207</v>
+      <c r="O21" s="146" t="s">
+        <v>233</v>
+      </c>
+      <c r="P21" s="147" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="149" t="s">
+      <c r="A22" s="94" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="150" t="n">
+      <c r="B22" s="164" t="n">
         <f aca="false">B18</f>
-        <v>204820</v>
-      </c>
-      <c r="C22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="C22" s="164" t="n">
         <f aca="false">C18</f>
-        <v>212905</v>
-      </c>
-      <c r="D22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="D22" s="164" t="n">
         <f aca="false">D18</f>
-        <v>220990</v>
-      </c>
-      <c r="E22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="E22" s="164" t="n">
         <f aca="false">E18</f>
-        <v>231770</v>
-      </c>
-      <c r="F22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="F22" s="164" t="n">
         <f aca="false">F18</f>
-        <v>239855</v>
-      </c>
-      <c r="G22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="G22" s="164" t="n">
         <f aca="false">G18</f>
-        <v>239855</v>
-      </c>
-      <c r="H22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="H22" s="164" t="n">
         <f aca="false">H18</f>
-        <v>234465</v>
-      </c>
-      <c r="I22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="I22" s="164" t="n">
         <f aca="false">I18</f>
-        <v>226380</v>
-      </c>
-      <c r="J22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="J22" s="164" t="n">
         <f aca="false">J18</f>
-        <v>231770</v>
-      </c>
-      <c r="K22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="K22" s="164" t="n">
         <f aca="false">K18</f>
-        <v>226380</v>
-      </c>
-      <c r="L22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="L22" s="164" t="n">
         <f aca="false">L18</f>
-        <v>220990</v>
-      </c>
-      <c r="M22" s="150" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="M22" s="164" t="n">
         <f aca="false">M18</f>
-        <v>212905</v>
-      </c>
-      <c r="N22" s="151" t="n">
+        <v>176666.666666667</v>
+      </c>
+      <c r="N22" s="96" t="n">
         <f aca="false">SUM(B22:M22)</f>
-        <v>2703085</v>
-      </c>
-      <c r="O22" s="94" t="n">
+        <v>2120000</v>
+      </c>
+      <c r="O22" s="97" t="n">
         <f aca="false">IF(N24=0,0,N22/N24)</f>
-        <v>0.823272295739105</v>
-      </c>
-      <c r="P22" s="152" t="s">
-        <v>208</v>
+        <v>0.785110279848856</v>
+      </c>
+      <c r="P22" s="165" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="149" t="s">
+      <c r="A23" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="150" t="n">
+      <c r="B23" s="164" t="n">
         <f aca="false">Drivers!B19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="C23" s="150" t="n">
+      <c r="C23" s="164" t="n">
         <f aca="false">Drivers!C19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="D23" s="150" t="n">
+      <c r="D23" s="164" t="n">
         <f aca="false">Drivers!D19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="E23" s="150" t="n">
+      <c r="E23" s="164" t="n">
         <f aca="false">Drivers!E19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="F23" s="150" t="n">
+      <c r="F23" s="164" t="n">
         <f aca="false">Drivers!F19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="G23" s="150" t="n">
+      <c r="G23" s="164" t="n">
         <f aca="false">Drivers!G19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="H23" s="150" t="n">
+      <c r="H23" s="164" t="n">
         <f aca="false">Drivers!H19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="I23" s="150" t="n">
+      <c r="I23" s="164" t="n">
         <f aca="false">Drivers!I19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="J23" s="150" t="n">
+      <c r="J23" s="164" t="n">
         <f aca="false">Drivers!J19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="K23" s="150" t="n">
+      <c r="K23" s="164" t="n">
         <f aca="false">Drivers!K19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="L23" s="150" t="n">
+      <c r="L23" s="164" t="n">
         <f aca="false">Drivers!L19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="M23" s="150" t="n">
+      <c r="M23" s="164" t="n">
         <f aca="false">Drivers!M19*1.094</f>
         <v>48354.8</v>
       </c>
-      <c r="N23" s="151" t="n">
+      <c r="N23" s="96" t="n">
         <f aca="false">SUM(B23:M23)</f>
         <v>580257.6</v>
       </c>
-      <c r="O23" s="94" t="n">
+      <c r="O23" s="97" t="n">
         <f aca="false">IF(N24=0,0,N23/N24)</f>
-        <v>0.176727704260896</v>
-      </c>
-      <c r="P23" s="152" t="s">
-        <v>209</v>
+        <v>0.214889720151144</v>
+      </c>
+      <c r="P23" s="165" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>210</v>
-      </c>
-      <c r="B24" s="153" t="n">
+        <v>237</v>
+      </c>
+      <c r="B24" s="166" t="n">
         <f aca="false">B22+B23</f>
-        <v>253174.8</v>
-      </c>
-      <c r="C24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="C24" s="166" t="n">
         <f aca="false">C22+C23</f>
-        <v>261259.8</v>
-      </c>
-      <c r="D24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="D24" s="166" t="n">
         <f aca="false">D22+D23</f>
-        <v>269344.8</v>
-      </c>
-      <c r="E24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="E24" s="166" t="n">
         <f aca="false">E22+E23</f>
-        <v>280124.8</v>
-      </c>
-      <c r="F24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="F24" s="166" t="n">
         <f aca="false">F22+F23</f>
-        <v>288209.8</v>
-      </c>
-      <c r="G24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="G24" s="166" t="n">
         <f aca="false">G22+G23</f>
-        <v>288209.8</v>
-      </c>
-      <c r="H24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="H24" s="166" t="n">
         <f aca="false">H22+H23</f>
-        <v>282819.8</v>
-      </c>
-      <c r="I24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="I24" s="166" t="n">
         <f aca="false">I22+I23</f>
-        <v>274734.8</v>
-      </c>
-      <c r="J24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="J24" s="166" t="n">
         <f aca="false">J22+J23</f>
-        <v>280124.8</v>
-      </c>
-      <c r="K24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="K24" s="166" t="n">
         <f aca="false">K22+K23</f>
-        <v>274734.8</v>
-      </c>
-      <c r="L24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="L24" s="166" t="n">
         <f aca="false">L22+L23</f>
-        <v>269344.8</v>
-      </c>
-      <c r="M24" s="153" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="M24" s="166" t="n">
         <f aca="false">M22+M23</f>
-        <v>261259.8</v>
-      </c>
-      <c r="N24" s="154" t="n">
+        <v>225021.466666667</v>
+      </c>
+      <c r="N24" s="167" t="n">
         <f aca="false">SUM(B24:M24)</f>
-        <v>3283342.6</v>
-      </c>
-      <c r="O24" s="155" t="n">
+        <v>2700257.6</v>
+      </c>
+      <c r="O24" s="102" t="n">
         <f aca="false">IF(N24=0,0,N24/N24)</f>
         <v>1</v>
       </c>
-      <c r="P24" s="152" t="s">
-        <v>211</v>
+      <c r="P24" s="165" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="149"/>
-      <c r="B25" s="156"/>
-      <c r="C25" s="156"/>
-      <c r="D25" s="156"/>
-      <c r="E25" s="156"/>
-      <c r="F25" s="156"/>
-      <c r="G25" s="156"/>
-      <c r="H25" s="156"/>
-      <c r="I25" s="156"/>
-      <c r="J25" s="156"/>
-      <c r="K25" s="156"/>
-      <c r="L25" s="156"/>
-      <c r="M25" s="156"/>
-      <c r="N25" s="157"/>
-      <c r="O25" s="101"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="168"/>
+      <c r="C25" s="168"/>
+      <c r="D25" s="168"/>
+      <c r="E25" s="168"/>
+      <c r="F25" s="168"/>
+      <c r="G25" s="168"/>
+      <c r="H25" s="168"/>
+      <c r="I25" s="168"/>
+      <c r="J25" s="168"/>
+      <c r="K25" s="168"/>
+      <c r="L25" s="168"/>
+      <c r="M25" s="168"/>
+      <c r="N25" s="169"/>
+      <c r="O25" s="119"/>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="149" t="s">
+      <c r="A26" s="94" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="150" t="n">
+      <c r="B26" s="164" t="n">
         <f aca="false">B9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="C26" s="150" t="n">
+      <c r="C26" s="164" t="n">
         <f aca="false">C9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="D26" s="150" t="n">
+      <c r="D26" s="164" t="n">
         <f aca="false">D9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="E26" s="150" t="n">
+      <c r="E26" s="164" t="n">
         <f aca="false">E9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="F26" s="150" t="n">
+      <c r="F26" s="164" t="n">
         <f aca="false">F9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="G26" s="150" t="n">
+      <c r="G26" s="164" t="n">
         <f aca="false">G9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="H26" s="150" t="n">
+      <c r="H26" s="164" t="n">
         <f aca="false">H9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="I26" s="150" t="n">
+      <c r="I26" s="164" t="n">
         <f aca="false">I9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="J26" s="150" t="n">
+      <c r="J26" s="164" t="n">
         <f aca="false">J9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="K26" s="150" t="n">
+      <c r="K26" s="164" t="n">
         <f aca="false">K9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="L26" s="150" t="n">
+      <c r="L26" s="164" t="n">
         <f aca="false">L9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="M26" s="150" t="n">
+      <c r="M26" s="164" t="n">
         <f aca="false">M9*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="N26" s="151" t="n">
+      <c r="N26" s="96" t="n">
         <f aca="false">SUM(B26:M26)</f>
         <v>1821875</v>
       </c>
-      <c r="O26" s="94" t="n">
+      <c r="O26" s="97" t="n">
         <f aca="false">IF(N24=0,0,N26/N24)</f>
-        <v>0.554884220732859</v>
-      </c>
-      <c r="P26" s="152" t="s">
-        <v>212</v>
+        <v>0.67470414674511</v>
+      </c>
+      <c r="P26" s="165" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="149" t="s">
+      <c r="A27" s="94" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="150" t="n">
+      <c r="B27" s="164" t="n">
         <f aca="false">B24*0.08</f>
-        <v>20253.984</v>
-      </c>
-      <c r="C27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="C27" s="164" t="n">
         <f aca="false">C24*0.08</f>
-        <v>20900.784</v>
-      </c>
-      <c r="D27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="D27" s="164" t="n">
         <f aca="false">D24*0.08</f>
-        <v>21547.584</v>
-      </c>
-      <c r="E27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="E27" s="164" t="n">
         <f aca="false">E24*0.08</f>
-        <v>22409.984</v>
-      </c>
-      <c r="F27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="F27" s="164" t="n">
         <f aca="false">F24*0.08</f>
-        <v>23056.784</v>
-      </c>
-      <c r="G27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="G27" s="164" t="n">
         <f aca="false">G24*0.08</f>
-        <v>23056.784</v>
-      </c>
-      <c r="H27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="H27" s="164" t="n">
         <f aca="false">H24*0.08</f>
-        <v>22625.584</v>
-      </c>
-      <c r="I27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="I27" s="164" t="n">
         <f aca="false">I24*0.08</f>
-        <v>21978.784</v>
-      </c>
-      <c r="J27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="J27" s="164" t="n">
         <f aca="false">J24*0.08</f>
-        <v>22409.984</v>
-      </c>
-      <c r="K27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="K27" s="164" t="n">
         <f aca="false">K24*0.08</f>
-        <v>21978.784</v>
-      </c>
-      <c r="L27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="L27" s="164" t="n">
         <f aca="false">L24*0.08</f>
-        <v>21547.584</v>
-      </c>
-      <c r="M27" s="150" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="M27" s="164" t="n">
         <f aca="false">M24*0.08</f>
-        <v>20900.784</v>
-      </c>
-      <c r="N27" s="151" t="n">
+        <v>18001.7173333334</v>
+      </c>
+      <c r="N27" s="96" t="n">
         <f aca="false">SUM(B27:M27)</f>
-        <v>262667.408</v>
-      </c>
-      <c r="O27" s="94" t="n">
+        <v>216020.608</v>
+      </c>
+      <c r="O27" s="97" t="n">
         <f aca="false">IF(N24=0,0,N27/N24)</f>
         <v>0.08</v>
       </c>
-      <c r="P27" s="152" t="s">
-        <v>213</v>
+      <c r="P27" s="165" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="149" t="s">
+      <c r="A28" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="150" t="n">
+      <c r="B28" s="164" t="n">
         <f aca="false">B24*0.04</f>
-        <v>10126.992</v>
-      </c>
-      <c r="C28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="C28" s="164" t="n">
         <f aca="false">C24*0.04</f>
-        <v>10450.392</v>
-      </c>
-      <c r="D28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="D28" s="164" t="n">
         <f aca="false">D24*0.04</f>
-        <v>10773.792</v>
-      </c>
-      <c r="E28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="E28" s="164" t="n">
         <f aca="false">E24*0.04</f>
-        <v>11204.992</v>
-      </c>
-      <c r="F28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="F28" s="164" t="n">
         <f aca="false">F24*0.04</f>
-        <v>11528.392</v>
-      </c>
-      <c r="G28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="G28" s="164" t="n">
         <f aca="false">G24*0.04</f>
-        <v>11528.392</v>
-      </c>
-      <c r="H28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="H28" s="164" t="n">
         <f aca="false">H24*0.04</f>
-        <v>11312.792</v>
-      </c>
-      <c r="I28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="I28" s="164" t="n">
         <f aca="false">I24*0.04</f>
-        <v>10989.392</v>
-      </c>
-      <c r="J28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="J28" s="164" t="n">
         <f aca="false">J24*0.04</f>
-        <v>11204.992</v>
-      </c>
-      <c r="K28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="K28" s="164" t="n">
         <f aca="false">K24*0.04</f>
-        <v>10989.392</v>
-      </c>
-      <c r="L28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="L28" s="164" t="n">
         <f aca="false">L24*0.04</f>
-        <v>10773.792</v>
-      </c>
-      <c r="M28" s="150" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="M28" s="164" t="n">
         <f aca="false">M24*0.04</f>
-        <v>10450.392</v>
-      </c>
-      <c r="N28" s="151" t="n">
+        <v>9000.85866666668</v>
+      </c>
+      <c r="N28" s="96" t="n">
         <f aca="false">SUM(B28:M28)</f>
-        <v>131333.704</v>
-      </c>
-      <c r="O28" s="94" t="n">
+        <v>108010.304</v>
+      </c>
+      <c r="O28" s="97" t="n">
         <f aca="false">IF(N24=0,0,N28/N24)</f>
         <v>0.04</v>
       </c>
-      <c r="P28" s="152" t="s">
-        <v>214</v>
+      <c r="P28" s="165" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="B29" s="153" t="n">
+        <v>242</v>
+      </c>
+      <c r="B29" s="166" t="n">
         <f aca="false">B26+B27+B28</f>
-        <v>182203.892666667</v>
-      </c>
-      <c r="C29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="C29" s="166" t="n">
         <f aca="false">C26+C27+C28</f>
-        <v>183174.092666667</v>
-      </c>
-      <c r="D29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="D29" s="166" t="n">
         <f aca="false">D26+D27+D28</f>
-        <v>184144.292666667</v>
-      </c>
-      <c r="E29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="E29" s="166" t="n">
         <f aca="false">E26+E27+E28</f>
-        <v>185437.892666667</v>
-      </c>
-      <c r="F29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="F29" s="166" t="n">
         <f aca="false">F26+F27+F28</f>
-        <v>186408.092666667</v>
-      </c>
-      <c r="G29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="G29" s="166" t="n">
         <f aca="false">G26+G27+G28</f>
-        <v>186408.092666667</v>
-      </c>
-      <c r="H29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="H29" s="166" t="n">
         <f aca="false">H26+H27+H28</f>
-        <v>185761.292666667</v>
-      </c>
-      <c r="I29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="I29" s="166" t="n">
         <f aca="false">I26+I27+I28</f>
-        <v>184791.092666667</v>
-      </c>
-      <c r="J29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="J29" s="166" t="n">
         <f aca="false">J26+J27+J28</f>
-        <v>185437.892666667</v>
-      </c>
-      <c r="K29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="K29" s="166" t="n">
         <f aca="false">K26+K27+K28</f>
-        <v>184791.092666667</v>
-      </c>
-      <c r="L29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="L29" s="166" t="n">
         <f aca="false">L26+L27+L28</f>
-        <v>184144.292666667</v>
-      </c>
-      <c r="M29" s="153" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="M29" s="166" t="n">
         <f aca="false">M26+M27+M28</f>
-        <v>183174.092666667</v>
-      </c>
-      <c r="N29" s="154" t="n">
+        <v>178825.492666667</v>
+      </c>
+      <c r="N29" s="167" t="n">
         <f aca="false">SUM(B29:M29)</f>
-        <v>2215876.112</v>
-      </c>
-      <c r="O29" s="155" t="n">
+        <v>2145905.912</v>
+      </c>
+      <c r="O29" s="102" t="n">
         <f aca="false">IF(N24=0,0,N29/N24)</f>
-        <v>0.674884220732859</v>
-      </c>
-      <c r="P29" s="152" t="s">
-        <v>216</v>
+        <v>0.794704146745111</v>
+      </c>
+      <c r="P29" s="165" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="149"/>
-      <c r="B30" s="156"/>
-      <c r="C30" s="156"/>
-      <c r="D30" s="156"/>
-      <c r="E30" s="156"/>
-      <c r="F30" s="156"/>
-      <c r="G30" s="156"/>
-      <c r="H30" s="156"/>
-      <c r="I30" s="156"/>
-      <c r="J30" s="156"/>
-      <c r="K30" s="156"/>
-      <c r="L30" s="156"/>
-      <c r="M30" s="156"/>
-      <c r="N30" s="157"/>
-      <c r="O30" s="101"/>
+      <c r="A30" s="94"/>
+      <c r="B30" s="168"/>
+      <c r="C30" s="168"/>
+      <c r="D30" s="168"/>
+      <c r="E30" s="168"/>
+      <c r="F30" s="168"/>
+      <c r="G30" s="168"/>
+      <c r="H30" s="168"/>
+      <c r="I30" s="168"/>
+      <c r="J30" s="168"/>
+      <c r="K30" s="168"/>
+      <c r="L30" s="168"/>
+      <c r="M30" s="168"/>
+      <c r="N30" s="169"/>
+      <c r="O30" s="119"/>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="77" t="s">
-        <v>149</v>
-      </c>
-      <c r="B31" s="153" t="n">
+        <v>176</v>
+      </c>
+      <c r="B31" s="166" t="n">
         <f aca="false">B24-B29</f>
-        <v>70970.9073333333</v>
-      </c>
-      <c r="C31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="C31" s="166" t="n">
         <f aca="false">C24-C29</f>
-        <v>78085.7073333333</v>
-      </c>
-      <c r="D31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="D31" s="166" t="n">
         <f aca="false">D24-D29</f>
-        <v>85200.5073333333</v>
-      </c>
-      <c r="E31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="E31" s="166" t="n">
         <f aca="false">E24-E29</f>
-        <v>94686.9073333333</v>
-      </c>
-      <c r="F31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="F31" s="166" t="n">
         <f aca="false">F24-F29</f>
-        <v>101801.707333333</v>
-      </c>
-      <c r="G31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="G31" s="166" t="n">
         <f aca="false">G24-G29</f>
-        <v>101801.707333333</v>
-      </c>
-      <c r="H31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="H31" s="166" t="n">
         <f aca="false">H24-H29</f>
-        <v>97058.5073333333</v>
-      </c>
-      <c r="I31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="I31" s="166" t="n">
         <f aca="false">I24-I29</f>
-        <v>89943.7073333333</v>
-      </c>
-      <c r="J31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="J31" s="166" t="n">
         <f aca="false">J24-J29</f>
-        <v>94686.9073333333</v>
-      </c>
-      <c r="K31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="K31" s="166" t="n">
         <f aca="false">K24-K29</f>
-        <v>89943.7073333333</v>
-      </c>
-      <c r="L31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="L31" s="166" t="n">
         <f aca="false">L24-L29</f>
-        <v>85200.5073333333</v>
-      </c>
-      <c r="M31" s="153" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="M31" s="166" t="n">
         <f aca="false">M24-M29</f>
-        <v>78085.7073333333</v>
-      </c>
-      <c r="N31" s="154" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="N31" s="167" t="n">
         <f aca="false">SUM(B31:M31)</f>
-        <v>1067466.488</v>
-      </c>
-      <c r="O31" s="155" t="n">
+        <v>554351.688</v>
+      </c>
+      <c r="O31" s="102" t="n">
         <f aca="false">IF(N24=0,0,N31/N24)</f>
-        <v>0.325115779267141</v>
-      </c>
-      <c r="P31" s="152" t="e">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="P31" s="165" t="e">
         <f aca="false">revenue - total cost</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="105" t="s">
+      <c r="A32" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="147" t="n">
+      <c r="B32" s="105" t="n">
         <f aca="false">B31</f>
-        <v>70970.9073333333</v>
-      </c>
-      <c r="C32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="C32" s="105" t="n">
         <f aca="false">C31</f>
-        <v>78085.7073333333</v>
-      </c>
-      <c r="D32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="D32" s="105" t="n">
         <f aca="false">D31</f>
-        <v>85200.5073333333</v>
-      </c>
-      <c r="E32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="E32" s="105" t="n">
         <f aca="false">E31</f>
-        <v>94686.9073333333</v>
-      </c>
-      <c r="F32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="F32" s="105" t="n">
         <f aca="false">F31</f>
-        <v>101801.707333333</v>
-      </c>
-      <c r="G32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="G32" s="105" t="n">
         <f aca="false">G31</f>
-        <v>101801.707333333</v>
-      </c>
-      <c r="H32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="H32" s="105" t="n">
         <f aca="false">H31</f>
-        <v>97058.5073333333</v>
-      </c>
-      <c r="I32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="I32" s="105" t="n">
         <f aca="false">I31</f>
-        <v>89943.7073333333</v>
-      </c>
-      <c r="J32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="J32" s="105" t="n">
         <f aca="false">J31</f>
-        <v>94686.9073333333</v>
-      </c>
-      <c r="K32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="K32" s="105" t="n">
         <f aca="false">K31</f>
-        <v>89943.7073333333</v>
-      </c>
-      <c r="L32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="L32" s="105" t="n">
         <f aca="false">L31</f>
-        <v>85200.5073333333</v>
-      </c>
-      <c r="M32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="M32" s="105" t="n">
         <f aca="false">M31</f>
-        <v>78085.7073333333</v>
-      </c>
-      <c r="N32" s="147" t="n">
+        <v>46195.974</v>
+      </c>
+      <c r="N32" s="105" t="n">
         <f aca="false">SUM(B32:M32)</f>
-        <v>1067466.488</v>
-      </c>
-      <c r="O32" s="158" t="n">
+        <v>554351.688</v>
+      </c>
+      <c r="O32" s="106" t="n">
         <f aca="false">IF(N24=0,0,N32/N24)</f>
-        <v>0.325115779267141</v>
-      </c>
-      <c r="P32" s="152" t="s">
-        <v>217</v>
+        <v>0.205295853254889</v>
+      </c>
+      <c r="P32" s="165" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="149" t="s">
+      <c r="A33" s="94" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="108" t="n">
+      <c r="B33" s="125" t="n">
         <f aca="false">IF(B24=0,0,B32/B24)</f>
-        <v>0.280323742068063</v>
-      </c>
-      <c r="C33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="C33" s="125" t="n">
         <f aca="false">IF(C24=0,0,C32/C24)</f>
-        <v>0.298881448019685</v>
-      </c>
-      <c r="D33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="D33" s="125" t="n">
         <f aca="false">IF(D24=0,0,D32/D24)</f>
-        <v>0.316325050022623</v>
-      </c>
-      <c r="E33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="E33" s="125" t="n">
         <f aca="false">IF(E24=0,0,E32/E24)</f>
-        <v>0.338016867243933</v>
-      </c>
-      <c r="F33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="F33" s="125" t="n">
         <f aca="false">IF(F24=0,0,F32/F24)</f>
-        <v>0.353220838893519</v>
-      </c>
-      <c r="G33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="G33" s="125" t="n">
         <f aca="false">IF(G24=0,0,G32/G24)</f>
-        <v>0.353220838893519</v>
-      </c>
-      <c r="H33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="H33" s="125" t="n">
         <f aca="false">IF(H24=0,0,H32/H24)</f>
-        <v>0.343181443920593</v>
-      </c>
-      <c r="I33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="I33" s="125" t="n">
         <f aca="false">IF(I24=0,0,I32/I24)</f>
-        <v>0.327383743644174</v>
-      </c>
-      <c r="J33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="J33" s="125" t="n">
         <f aca="false">IF(J24=0,0,J32/J24)</f>
-        <v>0.338016867243933</v>
-      </c>
-      <c r="K33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="K33" s="125" t="n">
         <f aca="false">IF(K24=0,0,K32/K24)</f>
-        <v>0.327383743644174</v>
-      </c>
-      <c r="L33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="L33" s="125" t="n">
         <f aca="false">IF(L24=0,0,L32/L24)</f>
-        <v>0.316325050022623</v>
-      </c>
-      <c r="M33" s="108" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="M33" s="125" t="n">
         <f aca="false">IF(M24=0,0,M32/M24)</f>
-        <v>0.298881448019685</v>
-      </c>
-      <c r="N33" s="94" t="n">
+        <v>0.205295853254889</v>
+      </c>
+      <c r="N33" s="97" t="n">
         <f aca="false">IF(N24=0,0,N32/N24)</f>
-        <v>0.325115779267141</v>
-      </c>
-      <c r="O33" s="101"/>
-      <c r="P33" s="152" t="s">
-        <v>218</v>
+        <v>0.205295853254889</v>
+      </c>
+      <c r="O33" s="119"/>
+      <c r="P33" s="165" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="149"/>
-      <c r="B34" s="156"/>
-      <c r="C34" s="156"/>
-      <c r="D34" s="156"/>
-      <c r="E34" s="156"/>
-      <c r="F34" s="156"/>
-      <c r="G34" s="156"/>
-      <c r="H34" s="156"/>
-      <c r="I34" s="156"/>
-      <c r="J34" s="156"/>
-      <c r="K34" s="156"/>
-      <c r="L34" s="156"/>
-      <c r="M34" s="156"/>
-      <c r="N34" s="157"/>
-      <c r="O34" s="101"/>
+      <c r="A34" s="94"/>
+      <c r="B34" s="168"/>
+      <c r="C34" s="168"/>
+      <c r="D34" s="168"/>
+      <c r="E34" s="168"/>
+      <c r="F34" s="168"/>
+      <c r="G34" s="168"/>
+      <c r="H34" s="168"/>
+      <c r="I34" s="168"/>
+      <c r="J34" s="168"/>
+      <c r="K34" s="168"/>
+      <c r="L34" s="168"/>
+      <c r="M34" s="168"/>
+      <c r="N34" s="169"/>
+      <c r="O34" s="119"/>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="109" t="s">
-        <v>151</v>
-      </c>
-      <c r="B35" s="159" t="n">
+      <c r="A35" s="126" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" s="170" t="n">
         <f aca="false">B24*0.02</f>
-        <v>5063.496</v>
-      </c>
-      <c r="C35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="C35" s="170" t="n">
         <f aca="false">C24*0.02</f>
-        <v>5225.196</v>
-      </c>
-      <c r="D35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="D35" s="170" t="n">
         <f aca="false">D24*0.02</f>
-        <v>5386.896</v>
-      </c>
-      <c r="E35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="E35" s="170" t="n">
         <f aca="false">E24*0.02</f>
-        <v>5602.496</v>
-      </c>
-      <c r="F35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="F35" s="170" t="n">
         <f aca="false">F24*0.02</f>
-        <v>5764.196</v>
-      </c>
-      <c r="G35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="G35" s="170" t="n">
         <f aca="false">G24*0.02</f>
-        <v>5764.196</v>
-      </c>
-      <c r="H35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="H35" s="170" t="n">
         <f aca="false">H24*0.02</f>
-        <v>5656.396</v>
-      </c>
-      <c r="I35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="I35" s="170" t="n">
         <f aca="false">I24*0.02</f>
-        <v>5494.696</v>
-      </c>
-      <c r="J35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="J35" s="170" t="n">
         <f aca="false">J24*0.02</f>
-        <v>5602.496</v>
-      </c>
-      <c r="K35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="K35" s="170" t="n">
         <f aca="false">K24*0.02</f>
-        <v>5494.696</v>
-      </c>
-      <c r="L35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="L35" s="170" t="n">
         <f aca="false">L24*0.02</f>
-        <v>5386.896</v>
-      </c>
-      <c r="M35" s="159" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="M35" s="170" t="n">
         <f aca="false">M24*0.02</f>
-        <v>5225.196</v>
-      </c>
-      <c r="N35" s="160" t="n">
+        <v>4500.42933333334</v>
+      </c>
+      <c r="N35" s="171" t="n">
         <f aca="false">SUM(B35:M35)</f>
-        <v>65666.852</v>
-      </c>
-      <c r="O35" s="161" t="n">
+        <v>54005.1520000001</v>
+      </c>
+      <c r="O35" s="172" t="n">
         <f aca="false">IF(N24=0,0,N35/N24)</f>
         <v>0.02</v>
       </c>
-      <c r="P35" s="152" t="s">
-        <v>219</v>
+      <c r="P35" s="165" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="77" t="s">
-        <v>152</v>
-      </c>
-      <c r="B36" s="153" t="n">
+        <v>179</v>
+      </c>
+      <c r="B36" s="166" t="n">
         <f aca="false">B32-B35</f>
-        <v>65907.4113333333</v>
-      </c>
-      <c r="C36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="C36" s="166" t="n">
         <f aca="false">C32-C35</f>
-        <v>72860.5113333333</v>
-      </c>
-      <c r="D36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="D36" s="166" t="n">
         <f aca="false">D32-D35</f>
-        <v>79813.6113333334</v>
-      </c>
-      <c r="E36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="E36" s="166" t="n">
         <f aca="false">E32-E35</f>
-        <v>89084.4113333333</v>
-      </c>
-      <c r="F36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="F36" s="166" t="n">
         <f aca="false">F32-F35</f>
-        <v>96037.5113333333</v>
-      </c>
-      <c r="G36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="G36" s="166" t="n">
         <f aca="false">G32-G35</f>
-        <v>96037.5113333333</v>
-      </c>
-      <c r="H36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="H36" s="166" t="n">
         <f aca="false">H32-H35</f>
-        <v>91402.1113333334</v>
-      </c>
-      <c r="I36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="I36" s="166" t="n">
         <f aca="false">I32-I35</f>
-        <v>84449.0113333333</v>
-      </c>
-      <c r="J36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="J36" s="166" t="n">
         <f aca="false">J32-J35</f>
-        <v>89084.4113333333</v>
-      </c>
-      <c r="K36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="K36" s="166" t="n">
         <f aca="false">K32-K35</f>
-        <v>84449.0113333333</v>
-      </c>
-      <c r="L36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="L36" s="166" t="n">
         <f aca="false">L32-L35</f>
-        <v>79813.6113333334</v>
-      </c>
-      <c r="M36" s="153" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="M36" s="166" t="n">
         <f aca="false">M32-M35</f>
-        <v>72860.5113333333</v>
-      </c>
-      <c r="N36" s="154" t="n">
+        <v>41695.5446666667</v>
+      </c>
+      <c r="N36" s="167" t="n">
         <f aca="false">SUM(B36:M36)</f>
-        <v>1001799.636</v>
-      </c>
-      <c r="O36" s="155" t="n">
+        <v>500346.536</v>
+      </c>
+      <c r="O36" s="102" t="n">
         <f aca="false">IF(N24=0,0,N36/N24)</f>
-        <v>0.305115779267141</v>
-      </c>
-      <c r="P36" s="152" t="s">
-        <v>220</v>
+        <v>0.185295853254889</v>
+      </c>
+      <c r="P36" s="165" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="109" t="s">
-        <v>221</v>
-      </c>
-      <c r="B37" s="159" t="n">
+      <c r="A37" s="126" t="s">
+        <v>248</v>
+      </c>
+      <c r="B37" s="170" t="n">
         <f aca="false">IF(B36&gt;0,B36*0.21,0)</f>
-        <v>13840.55638</v>
-      </c>
-      <c r="C37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="C37" s="170" t="n">
         <f aca="false">IF(C36&gt;0,C36*0.21,0)</f>
-        <v>15300.70738</v>
-      </c>
-      <c r="D37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="D37" s="170" t="n">
         <f aca="false">IF(D36&gt;0,D36*0.21,0)</f>
-        <v>16760.85838</v>
-      </c>
-      <c r="E37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="E37" s="170" t="n">
         <f aca="false">IF(E36&gt;0,E36*0.21,0)</f>
-        <v>18707.72638</v>
-      </c>
-      <c r="F37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="F37" s="170" t="n">
         <f aca="false">IF(F36&gt;0,F36*0.21,0)</f>
-        <v>20167.87738</v>
-      </c>
-      <c r="G37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="G37" s="170" t="n">
         <f aca="false">IF(G36&gt;0,G36*0.21,0)</f>
-        <v>20167.87738</v>
-      </c>
-      <c r="H37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="H37" s="170" t="n">
         <f aca="false">IF(H36&gt;0,H36*0.21,0)</f>
-        <v>19194.44338</v>
-      </c>
-      <c r="I37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="I37" s="170" t="n">
         <f aca="false">IF(I36&gt;0,I36*0.21,0)</f>
-        <v>17734.29238</v>
-      </c>
-      <c r="J37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="J37" s="170" t="n">
         <f aca="false">IF(J36&gt;0,J36*0.21,0)</f>
-        <v>18707.72638</v>
-      </c>
-      <c r="K37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="K37" s="170" t="n">
         <f aca="false">IF(K36&gt;0,K36*0.21,0)</f>
-        <v>17734.29238</v>
-      </c>
-      <c r="L37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="L37" s="170" t="n">
         <f aca="false">IF(L36&gt;0,L36*0.21,0)</f>
-        <v>16760.85838</v>
-      </c>
-      <c r="M37" s="159" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="M37" s="170" t="n">
         <f aca="false">IF(M36&gt;0,M36*0.21,0)</f>
-        <v>15300.70738</v>
-      </c>
-      <c r="N37" s="160" t="n">
+        <v>8756.06438</v>
+      </c>
+      <c r="N37" s="171" t="n">
         <f aca="false">SUM(B37:M37)</f>
-        <v>210377.92356</v>
-      </c>
-      <c r="O37" s="161" t="n">
+        <v>105072.77256</v>
+      </c>
+      <c r="O37" s="172" t="n">
         <f aca="false">IF(N24=0,0,N37/N24)</f>
-        <v>0.0640743136460996</v>
-      </c>
-      <c r="P37" s="152" t="s">
-        <v>222</v>
+        <v>0.0389121291835267</v>
+      </c>
+      <c r="P37" s="165" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="77" t="s">
-        <v>154</v>
-      </c>
-      <c r="B38" s="153" t="n">
+        <v>181</v>
+      </c>
+      <c r="B38" s="166" t="n">
         <f aca="false">B36-B37</f>
-        <v>52066.8549533333</v>
-      </c>
-      <c r="C38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="C38" s="166" t="n">
         <f aca="false">C36-C37</f>
-        <v>57559.8039533333</v>
-      </c>
-      <c r="D38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="D38" s="166" t="n">
         <f aca="false">D36-D37</f>
-        <v>63052.7529533333</v>
-      </c>
-      <c r="E38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="E38" s="166" t="n">
         <f aca="false">E36-E37</f>
-        <v>70376.6849533333</v>
-      </c>
-      <c r="F38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="F38" s="166" t="n">
         <f aca="false">F36-F37</f>
-        <v>75869.6339533333</v>
-      </c>
-      <c r="G38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="G38" s="166" t="n">
         <f aca="false">G36-G37</f>
-        <v>75869.6339533333</v>
-      </c>
-      <c r="H38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="H38" s="166" t="n">
         <f aca="false">H36-H37</f>
-        <v>72207.6679533334</v>
-      </c>
-      <c r="I38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="I38" s="166" t="n">
         <f aca="false">I36-I37</f>
-        <v>66714.7189533333</v>
-      </c>
-      <c r="J38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="J38" s="166" t="n">
         <f aca="false">J36-J37</f>
-        <v>70376.6849533333</v>
-      </c>
-      <c r="K38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="K38" s="166" t="n">
         <f aca="false">K36-K37</f>
-        <v>66714.7189533333</v>
-      </c>
-      <c r="L38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="L38" s="166" t="n">
         <f aca="false">L36-L37</f>
-        <v>63052.7529533333</v>
-      </c>
-      <c r="M38" s="153" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="M38" s="166" t="n">
         <f aca="false">M36-M37</f>
-        <v>57559.8039533333</v>
-      </c>
-      <c r="N38" s="154" t="n">
+        <v>32939.4802866667</v>
+      </c>
+      <c r="N38" s="167" t="n">
         <f aca="false">SUM(B38:M38)</f>
-        <v>791421.71244</v>
-      </c>
-      <c r="O38" s="155" t="n">
+        <v>395273.76344</v>
+      </c>
+      <c r="O38" s="102" t="n">
         <f aca="false">IF(N24=0,0,N38/N24)</f>
-        <v>0.241041465621041</v>
-      </c>
-      <c r="P38" s="152" t="s">
-        <v>223</v>
+        <v>0.146383724071362</v>
+      </c>
+      <c r="P38" s="165" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="B40" s="117"/>
-      <c r="C40" s="117"/>
-      <c r="D40" s="117"/>
-      <c r="E40" s="117"/>
-      <c r="F40" s="117"/>
-      <c r="G40" s="117"/>
-      <c r="H40" s="117"/>
-      <c r="I40" s="117"/>
-      <c r="J40" s="117"/>
-      <c r="K40" s="117"/>
-      <c r="L40" s="117"/>
-      <c r="M40" s="117"/>
-      <c r="N40" s="117"/>
-      <c r="O40" s="117"/>
-      <c r="P40" s="117"/>
-      <c r="Q40" s="117"/>
+      <c r="A40" s="134" t="s">
+        <v>251</v>
+      </c>
+      <c r="B40" s="134"/>
+      <c r="C40" s="134"/>
+      <c r="D40" s="134"/>
+      <c r="E40" s="134"/>
+      <c r="F40" s="134"/>
+      <c r="G40" s="134"/>
+      <c r="H40" s="134"/>
+      <c r="I40" s="134"/>
+      <c r="J40" s="134"/>
+      <c r="K40" s="134"/>
+      <c r="L40" s="134"/>
+      <c r="M40" s="134"/>
+      <c r="N40" s="134"/>
+      <c r="O40" s="134"/>
+      <c r="P40" s="134"/>
+      <c r="Q40" s="134"/>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="B41" s="38"/>
       <c r="C41" s="38"/>
@@ -13308,16 +13999,16 @@
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="137" t="s">
-        <v>226</v>
-      </c>
-      <c r="B43" s="127" t="s">
-        <v>227</v>
+      <c r="A43" s="154" t="s">
+        <v>253</v>
+      </c>
+      <c r="B43" s="144" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="39" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="B44" s="39"/>
       <c r="C44" s="39"/>
@@ -13328,1178 +14019,1178 @@
       <c r="H44" s="39"/>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="129" t="s">
-        <v>229</v>
-      </c>
-      <c r="B45" s="129" t="s">
-        <v>230</v>
-      </c>
-      <c r="C45" s="129" t="s">
-        <v>231</v>
-      </c>
-      <c r="D45" s="129" t="s">
-        <v>232</v>
-      </c>
-      <c r="E45" s="129" t="s">
-        <v>233</v>
-      </c>
-      <c r="F45" s="129" t="s">
-        <v>234</v>
-      </c>
-      <c r="G45" s="129" t="s">
-        <v>235</v>
-      </c>
-      <c r="H45" s="129" t="s">
-        <v>236</v>
+      <c r="A45" s="146" t="s">
+        <v>256</v>
+      </c>
+      <c r="B45" s="146" t="s">
+        <v>257</v>
+      </c>
+      <c r="C45" s="146" t="s">
+        <v>258</v>
+      </c>
+      <c r="D45" s="146" t="s">
+        <v>259</v>
+      </c>
+      <c r="E45" s="146" t="s">
+        <v>260</v>
+      </c>
+      <c r="F45" s="146" t="s">
+        <v>261</v>
+      </c>
+      <c r="G45" s="146" t="s">
+        <v>262</v>
+      </c>
+      <c r="H45" s="146" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="162" t="s">
-        <v>227</v>
-      </c>
-      <c r="B46" s="163" t="n">
+      <c r="A46" s="173" t="s">
+        <v>254</v>
+      </c>
+      <c r="B46" s="174" t="n">
         <v>55</v>
       </c>
-      <c r="C46" s="163" t="n">
+      <c r="C46" s="174" t="n">
         <v>4900</v>
       </c>
-      <c r="D46" s="163" t="s">
-        <v>237</v>
-      </c>
-      <c r="E46" s="164" t="n">
+      <c r="D46" s="174" t="s">
+        <v>264</v>
+      </c>
+      <c r="E46" s="175" t="n">
         <f aca="false">55*4900*0.82*12+N23</f>
         <v>3232137.6</v>
       </c>
-      <c r="F46" s="165" t="n">
+      <c r="F46" s="176" t="n">
         <f aca="false">(55*4900*0.82*12+N23)-(55*Drivers!$E$25*12)-(55*4900*0.82*12+N23)*0.12</f>
         <v>1022406.088</v>
       </c>
-      <c r="G46" s="166" t="s">
-        <v>238</v>
-      </c>
-      <c r="H46" s="167" t="s">
-        <v>239</v>
+      <c r="G46" s="174" t="s">
+        <v>265</v>
+      </c>
+      <c r="H46" s="177" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="168" t="s">
-        <v>240</v>
-      </c>
-      <c r="B47" s="169" t="n">
+      <c r="A47" s="178" t="s">
+        <v>267</v>
+      </c>
+      <c r="B47" s="179" t="n">
         <v>60</v>
       </c>
-      <c r="C47" s="169" t="n">
+      <c r="C47" s="179" t="n">
         <v>5000</v>
       </c>
-      <c r="D47" s="169" t="s">
-        <v>241</v>
-      </c>
-      <c r="E47" s="170" t="n">
+      <c r="D47" s="179" t="s">
+        <v>268</v>
+      </c>
+      <c r="E47" s="180" t="n">
         <f aca="false">60*5000*0.86*12+N23</f>
         <v>3676257.6</v>
       </c>
-      <c r="F47" s="171" t="n">
+      <c r="F47" s="181" t="n">
         <f aca="false">(60*5000*0.86*12+N23)-(60*Drivers!$E$25*12)-(60*5000*0.86*12+N23)*0.12</f>
         <v>1247606.688</v>
       </c>
-      <c r="G47" s="171" t="n">
+      <c r="G47" s="181" t="n">
         <f aca="false">F47-F46</f>
         <v>225200.6</v>
       </c>
-      <c r="H47" s="172" t="s">
-        <v>242</v>
+      <c r="H47" s="182" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="173" t="s">
-        <v>243</v>
-      </c>
-      <c r="B48" s="174" t="n">
+      <c r="A48" s="183" t="s">
+        <v>270</v>
+      </c>
+      <c r="B48" s="184" t="n">
         <v>50</v>
       </c>
-      <c r="C48" s="174" t="n">
+      <c r="C48" s="184" t="n">
         <v>4700</v>
       </c>
-      <c r="D48" s="174" t="s">
-        <v>244</v>
-      </c>
-      <c r="E48" s="175" t="n">
+      <c r="D48" s="184" t="s">
+        <v>271</v>
+      </c>
+      <c r="E48" s="185" t="n">
         <f aca="false">50*4700*0.78*12+N23</f>
         <v>2779857.6</v>
       </c>
-      <c r="F48" s="176" t="n">
+      <c r="F48" s="186" t="n">
         <f aca="false">(50*4700*0.78*12+N23)-(50*Drivers!$E$25*12)-(50*4700*0.78*12+N23)*0.12</f>
         <v>790024.687999998</v>
       </c>
-      <c r="G48" s="176" t="n">
+      <c r="G48" s="186" t="n">
         <f aca="false">F48-F46</f>
         <v>-232381.4</v>
       </c>
-      <c r="H48" s="177" t="s">
-        <v>245</v>
+      <c r="H48" s="187" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="117" t="s">
-        <v>246</v>
-      </c>
-      <c r="B50" s="117"/>
-      <c r="C50" s="117"/>
-      <c r="D50" s="117"/>
-      <c r="E50" s="117"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="117"/>
-      <c r="H50" s="117"/>
-      <c r="I50" s="117"/>
-      <c r="J50" s="117"/>
-      <c r="K50" s="117"/>
-      <c r="L50" s="117"/>
-      <c r="M50" s="117"/>
-      <c r="N50" s="117"/>
-      <c r="O50" s="117"/>
-      <c r="P50" s="117"/>
-      <c r="Q50" s="117"/>
+      <c r="A50" s="134" t="s">
+        <v>273</v>
+      </c>
+      <c r="B50" s="134"/>
+      <c r="C50" s="134"/>
+      <c r="D50" s="134"/>
+      <c r="E50" s="134"/>
+      <c r="F50" s="134"/>
+      <c r="G50" s="134"/>
+      <c r="H50" s="134"/>
+      <c r="I50" s="134"/>
+      <c r="J50" s="134"/>
+      <c r="K50" s="134"/>
+      <c r="L50" s="134"/>
+      <c r="M50" s="134"/>
+      <c r="N50" s="134"/>
+      <c r="O50" s="134"/>
+      <c r="P50" s="134"/>
+      <c r="Q50" s="134"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="130" t="s">
-        <v>142</v>
-      </c>
-      <c r="B51" s="129" t="s">
+      <c r="A51" s="147" t="s">
+        <v>169</v>
+      </c>
+      <c r="B51" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="C51" s="129" t="s">
+      <c r="C51" s="146" t="s">
         <v>14</v>
       </c>
-      <c r="D51" s="129" t="s">
+      <c r="D51" s="146" t="s">
         <v>15</v>
       </c>
-      <c r="E51" s="129" t="s">
+      <c r="E51" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="F51" s="129" t="s">
+      <c r="F51" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="G51" s="129" t="s">
+      <c r="G51" s="146" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="129" t="s">
+      <c r="H51" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="I51" s="129" t="s">
+      <c r="I51" s="146" t="s">
         <v>20</v>
       </c>
-      <c r="J51" s="129" t="s">
+      <c r="J51" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="K51" s="129" t="s">
+      <c r="K51" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="L51" s="129" t="s">
+      <c r="L51" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="M51" s="129" t="s">
+      <c r="M51" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="N51" s="129" t="s">
+      <c r="N51" s="146" t="s">
         <v>99</v>
       </c>
-      <c r="O51" s="129" t="s">
-        <v>247</v>
-      </c>
-      <c r="P51" s="130" t="s">
+      <c r="O51" s="146" t="s">
+        <v>274</v>
+      </c>
+      <c r="P51" s="147" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="149" t="s">
+      <c r="A52" s="94" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="150" t="n">
+      <c r="B52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.76,IF($B$43="Upside",0.8,0.72)))</f>
         <v>204820</v>
       </c>
-      <c r="C52" s="150" t="n">
+      <c r="C52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.79,IF($B$43="Upside",0.83,0.75)))</f>
         <v>212905</v>
       </c>
-      <c r="D52" s="150" t="n">
+      <c r="D52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.82,IF($B$43="Upside",0.86,0.78)))</f>
         <v>220990</v>
       </c>
-      <c r="E52" s="150" t="n">
+      <c r="E52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.86,IF($B$43="Upside",0.9,0.82)))</f>
         <v>231770</v>
       </c>
-      <c r="F52" s="150" t="n">
+      <c r="F52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.89,IF($B$43="Upside",0.93,0.85)))</f>
         <v>239855</v>
       </c>
-      <c r="G52" s="150" t="n">
+      <c r="G52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.89,IF($B$43="Upside",0.93,0.85)))</f>
         <v>239855</v>
       </c>
-      <c r="H52" s="150" t="n">
+      <c r="H52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.87,IF($B$43="Upside",0.91,0.83)))</f>
         <v>234465</v>
       </c>
-      <c r="I52" s="150" t="n">
+      <c r="I52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.84,IF($B$43="Upside",0.88,0.8)))</f>
         <v>226380</v>
       </c>
-      <c r="J52" s="150" t="n">
+      <c r="J52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.86,IF($B$43="Upside",0.9,0.82)))</f>
         <v>231770</v>
       </c>
-      <c r="K52" s="150" t="n">
+      <c r="K52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.84,IF($B$43="Upside",0.88,0.8)))</f>
         <v>226380</v>
       </c>
-      <c r="L52" s="150" t="n">
+      <c r="L52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.82,IF($B$43="Upside",0.86,0.78)))</f>
         <v>220990</v>
       </c>
-      <c r="M52" s="150" t="n">
+      <c r="M52" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*(IF($B$43="Base",4900,IF($B$43="Upside",5000,4700)))*(IF($B$43="Base",0.79,IF($B$43="Upside",0.83,0.75)))</f>
         <v>212905</v>
       </c>
-      <c r="N52" s="151" t="n">
+      <c r="N52" s="96" t="n">
         <f aca="false">SUM(B52:M52)</f>
         <v>2703085</v>
       </c>
-      <c r="O52" s="178" t="n">
+      <c r="O52" s="188" t="n">
         <f aca="false">IF(N54=0,0,N52/N54)</f>
         <v>0.823272295739105</v>
       </c>
-      <c r="P52" s="152" t="s">
-        <v>248</v>
+      <c r="P52" s="165" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="149" t="s">
+      <c r="A53" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="150" t="n">
+      <c r="B53" s="164" t="n">
         <f aca="false">B23</f>
         <v>48354.8</v>
       </c>
-      <c r="C53" s="150" t="n">
+      <c r="C53" s="164" t="n">
         <f aca="false">C23</f>
         <v>48354.8</v>
       </c>
-      <c r="D53" s="150" t="n">
+      <c r="D53" s="164" t="n">
         <f aca="false">D23</f>
         <v>48354.8</v>
       </c>
-      <c r="E53" s="150" t="n">
+      <c r="E53" s="164" t="n">
         <f aca="false">E23</f>
         <v>48354.8</v>
       </c>
-      <c r="F53" s="150" t="n">
+      <c r="F53" s="164" t="n">
         <f aca="false">F23</f>
         <v>48354.8</v>
       </c>
-      <c r="G53" s="150" t="n">
+      <c r="G53" s="164" t="n">
         <f aca="false">G23</f>
         <v>48354.8</v>
       </c>
-      <c r="H53" s="150" t="n">
+      <c r="H53" s="164" t="n">
         <f aca="false">H23</f>
         <v>48354.8</v>
       </c>
-      <c r="I53" s="150" t="n">
+      <c r="I53" s="164" t="n">
         <f aca="false">I23</f>
         <v>48354.8</v>
       </c>
-      <c r="J53" s="150" t="n">
+      <c r="J53" s="164" t="n">
         <f aca="false">J23</f>
         <v>48354.8</v>
       </c>
-      <c r="K53" s="150" t="n">
+      <c r="K53" s="164" t="n">
         <f aca="false">K23</f>
         <v>48354.8</v>
       </c>
-      <c r="L53" s="150" t="n">
+      <c r="L53" s="164" t="n">
         <f aca="false">L23</f>
         <v>48354.8</v>
       </c>
-      <c r="M53" s="150" t="n">
+      <c r="M53" s="164" t="n">
         <f aca="false">M23</f>
         <v>48354.8</v>
       </c>
-      <c r="N53" s="151" t="n">
+      <c r="N53" s="96" t="n">
         <f aca="false">SUM(B53:M53)</f>
         <v>580257.6</v>
       </c>
-      <c r="O53" s="178" t="n">
+      <c r="O53" s="188" t="n">
         <f aca="false">IF(N54=0,0,N53/N54)</f>
         <v>0.176727704260896</v>
       </c>
-      <c r="P53" s="152" t="s">
-        <v>249</v>
+      <c r="P53" s="165" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="77" t="s">
-        <v>210</v>
-      </c>
-      <c r="B54" s="153" t="n">
+        <v>237</v>
+      </c>
+      <c r="B54" s="166" t="n">
         <f aca="false">B52+B53</f>
         <v>253174.8</v>
       </c>
-      <c r="C54" s="153" t="n">
+      <c r="C54" s="166" t="n">
         <f aca="false">C52+C53</f>
         <v>261259.8</v>
       </c>
-      <c r="D54" s="153" t="n">
+      <c r="D54" s="166" t="n">
         <f aca="false">D52+D53</f>
         <v>269344.8</v>
       </c>
-      <c r="E54" s="153" t="n">
+      <c r="E54" s="166" t="n">
         <f aca="false">E52+E53</f>
         <v>280124.8</v>
       </c>
-      <c r="F54" s="153" t="n">
+      <c r="F54" s="166" t="n">
         <f aca="false">F52+F53</f>
         <v>288209.8</v>
       </c>
-      <c r="G54" s="153" t="n">
+      <c r="G54" s="166" t="n">
         <f aca="false">G52+G53</f>
         <v>288209.8</v>
       </c>
-      <c r="H54" s="153" t="n">
+      <c r="H54" s="166" t="n">
         <f aca="false">H52+H53</f>
         <v>282819.8</v>
       </c>
-      <c r="I54" s="153" t="n">
+      <c r="I54" s="166" t="n">
         <f aca="false">I52+I53</f>
         <v>274734.8</v>
       </c>
-      <c r="J54" s="153" t="n">
+      <c r="J54" s="166" t="n">
         <f aca="false">J52+J53</f>
         <v>280124.8</v>
       </c>
-      <c r="K54" s="153" t="n">
+      <c r="K54" s="166" t="n">
         <f aca="false">K52+K53</f>
         <v>274734.8</v>
       </c>
-      <c r="L54" s="153" t="n">
+      <c r="L54" s="166" t="n">
         <f aca="false">L52+L53</f>
         <v>269344.8</v>
       </c>
-      <c r="M54" s="153" t="n">
+      <c r="M54" s="166" t="n">
         <f aca="false">M52+M53</f>
         <v>261259.8</v>
       </c>
-      <c r="N54" s="154" t="n">
+      <c r="N54" s="167" t="n">
         <f aca="false">SUM(B54:M54)</f>
         <v>3283342.6</v>
       </c>
-      <c r="O54" s="179" t="n">
+      <c r="O54" s="189" t="n">
         <f aca="false">IF(N54=0,0,N54/N54)</f>
         <v>1</v>
       </c>
-      <c r="P54" s="152" t="s">
-        <v>211</v>
+      <c r="P54" s="165" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="149"/>
-      <c r="B55" s="156"/>
-      <c r="C55" s="156"/>
-      <c r="D55" s="156"/>
-      <c r="E55" s="156"/>
-      <c r="F55" s="156"/>
-      <c r="G55" s="156"/>
-      <c r="H55" s="156"/>
-      <c r="I55" s="156"/>
-      <c r="J55" s="156"/>
-      <c r="K55" s="156"/>
-      <c r="L55" s="156"/>
-      <c r="M55" s="156"/>
-      <c r="N55" s="157"/>
-      <c r="O55" s="101"/>
+      <c r="A55" s="94"/>
+      <c r="B55" s="168"/>
+      <c r="C55" s="168"/>
+      <c r="D55" s="168"/>
+      <c r="E55" s="168"/>
+      <c r="F55" s="168"/>
+      <c r="G55" s="168"/>
+      <c r="H55" s="168"/>
+      <c r="I55" s="168"/>
+      <c r="J55" s="168"/>
+      <c r="K55" s="168"/>
+      <c r="L55" s="168"/>
+      <c r="M55" s="168"/>
+      <c r="N55" s="169"/>
+      <c r="O55" s="119"/>
     </row>
     <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="149" t="s">
+      <c r="A56" s="94" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="150" t="n">
+      <c r="B56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="C56" s="150" t="n">
+      <c r="C56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="D56" s="150" t="n">
+      <c r="D56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="E56" s="150" t="n">
+      <c r="E56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="F56" s="150" t="n">
+      <c r="F56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="G56" s="150" t="n">
+      <c r="G56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="H56" s="150" t="n">
+      <c r="H56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="I56" s="150" t="n">
+      <c r="I56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="J56" s="150" t="n">
+      <c r="J56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="K56" s="150" t="n">
+      <c r="K56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="L56" s="150" t="n">
+      <c r="L56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="M56" s="150" t="n">
+      <c r="M56" s="164" t="n">
         <f aca="false">(IF($B$43="Base",55,IF($B$43="Upside",60,50)))*Drivers!$E$25</f>
         <v>151822.916666667</v>
       </c>
-      <c r="N56" s="151" t="n">
+      <c r="N56" s="96" t="n">
         <f aca="false">SUM(B56:M56)</f>
         <v>1821875</v>
       </c>
-      <c r="O56" s="178" t="n">
+      <c r="O56" s="188" t="n">
         <f aca="false">IF(N54=0,0,N56/N54)</f>
         <v>0.554884220732859</v>
       </c>
-      <c r="P56" s="152" t="s">
-        <v>250</v>
+      <c r="P56" s="165" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="149" t="s">
+      <c r="A57" s="94" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="150" t="n">
+      <c r="B57" s="164" t="n">
         <f aca="false">B54*0.08</f>
         <v>20253.984</v>
       </c>
-      <c r="C57" s="150" t="n">
+      <c r="C57" s="164" t="n">
         <f aca="false">C54*0.08</f>
         <v>20900.784</v>
       </c>
-      <c r="D57" s="150" t="n">
+      <c r="D57" s="164" t="n">
         <f aca="false">D54*0.08</f>
         <v>21547.584</v>
       </c>
-      <c r="E57" s="150" t="n">
+      <c r="E57" s="164" t="n">
         <f aca="false">E54*0.08</f>
         <v>22409.984</v>
       </c>
-      <c r="F57" s="150" t="n">
+      <c r="F57" s="164" t="n">
         <f aca="false">F54*0.08</f>
         <v>23056.784</v>
       </c>
-      <c r="G57" s="150" t="n">
+      <c r="G57" s="164" t="n">
         <f aca="false">G54*0.08</f>
         <v>23056.784</v>
       </c>
-      <c r="H57" s="150" t="n">
+      <c r="H57" s="164" t="n">
         <f aca="false">H54*0.08</f>
         <v>22625.584</v>
       </c>
-      <c r="I57" s="150" t="n">
+      <c r="I57" s="164" t="n">
         <f aca="false">I54*0.08</f>
         <v>21978.784</v>
       </c>
-      <c r="J57" s="150" t="n">
+      <c r="J57" s="164" t="n">
         <f aca="false">J54*0.08</f>
         <v>22409.984</v>
       </c>
-      <c r="K57" s="150" t="n">
+      <c r="K57" s="164" t="n">
         <f aca="false">K54*0.08</f>
         <v>21978.784</v>
       </c>
-      <c r="L57" s="150" t="n">
+      <c r="L57" s="164" t="n">
         <f aca="false">L54*0.08</f>
         <v>21547.584</v>
       </c>
-      <c r="M57" s="150" t="n">
+      <c r="M57" s="164" t="n">
         <f aca="false">M54*0.08</f>
         <v>20900.784</v>
       </c>
-      <c r="N57" s="151" t="n">
+      <c r="N57" s="96" t="n">
         <f aca="false">SUM(B57:M57)</f>
         <v>262667.408</v>
       </c>
-      <c r="O57" s="178" t="n">
+      <c r="O57" s="188" t="n">
         <f aca="false">IF(N54=0,0,N57/N54)</f>
         <v>0.08</v>
       </c>
-      <c r="P57" s="152" t="s">
-        <v>251</v>
+      <c r="P57" s="165" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="149" t="s">
+      <c r="A58" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="150" t="n">
+      <c r="B58" s="164" t="n">
         <f aca="false">B54*0.04</f>
         <v>10126.992</v>
       </c>
-      <c r="C58" s="150" t="n">
+      <c r="C58" s="164" t="n">
         <f aca="false">C54*0.04</f>
         <v>10450.392</v>
       </c>
-      <c r="D58" s="150" t="n">
+      <c r="D58" s="164" t="n">
         <f aca="false">D54*0.04</f>
         <v>10773.792</v>
       </c>
-      <c r="E58" s="150" t="n">
+      <c r="E58" s="164" t="n">
         <f aca="false">E54*0.04</f>
         <v>11204.992</v>
       </c>
-      <c r="F58" s="150" t="n">
+      <c r="F58" s="164" t="n">
         <f aca="false">F54*0.04</f>
         <v>11528.392</v>
       </c>
-      <c r="G58" s="150" t="n">
+      <c r="G58" s="164" t="n">
         <f aca="false">G54*0.04</f>
         <v>11528.392</v>
       </c>
-      <c r="H58" s="150" t="n">
+      <c r="H58" s="164" t="n">
         <f aca="false">H54*0.04</f>
         <v>11312.792</v>
       </c>
-      <c r="I58" s="150" t="n">
+      <c r="I58" s="164" t="n">
         <f aca="false">I54*0.04</f>
         <v>10989.392</v>
       </c>
-      <c r="J58" s="150" t="n">
+      <c r="J58" s="164" t="n">
         <f aca="false">J54*0.04</f>
         <v>11204.992</v>
       </c>
-      <c r="K58" s="150" t="n">
+      <c r="K58" s="164" t="n">
         <f aca="false">K54*0.04</f>
         <v>10989.392</v>
       </c>
-      <c r="L58" s="150" t="n">
+      <c r="L58" s="164" t="n">
         <f aca="false">L54*0.04</f>
         <v>10773.792</v>
       </c>
-      <c r="M58" s="150" t="n">
+      <c r="M58" s="164" t="n">
         <f aca="false">M54*0.04</f>
         <v>10450.392</v>
       </c>
-      <c r="N58" s="151" t="n">
+      <c r="N58" s="96" t="n">
         <f aca="false">SUM(B58:M58)</f>
         <v>131333.704</v>
       </c>
-      <c r="O58" s="178" t="n">
+      <c r="O58" s="188" t="n">
         <f aca="false">IF(N54=0,0,N58/N54)</f>
         <v>0.04</v>
       </c>
-      <c r="P58" s="152" t="s">
-        <v>252</v>
+      <c r="P58" s="165" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="B59" s="153" t="n">
+        <v>242</v>
+      </c>
+      <c r="B59" s="166" t="n">
         <f aca="false">B56+B57+B58</f>
         <v>182203.892666667</v>
       </c>
-      <c r="C59" s="153" t="n">
+      <c r="C59" s="166" t="n">
         <f aca="false">C56+C57+C58</f>
         <v>183174.092666667</v>
       </c>
-      <c r="D59" s="153" t="n">
+      <c r="D59" s="166" t="n">
         <f aca="false">D56+D57+D58</f>
         <v>184144.292666667</v>
       </c>
-      <c r="E59" s="153" t="n">
+      <c r="E59" s="166" t="n">
         <f aca="false">E56+E57+E58</f>
         <v>185437.892666667</v>
       </c>
-      <c r="F59" s="153" t="n">
+      <c r="F59" s="166" t="n">
         <f aca="false">F56+F57+F58</f>
         <v>186408.092666667</v>
       </c>
-      <c r="G59" s="153" t="n">
+      <c r="G59" s="166" t="n">
         <f aca="false">G56+G57+G58</f>
         <v>186408.092666667</v>
       </c>
-      <c r="H59" s="153" t="n">
+      <c r="H59" s="166" t="n">
         <f aca="false">H56+H57+H58</f>
         <v>185761.292666667</v>
       </c>
-      <c r="I59" s="153" t="n">
+      <c r="I59" s="166" t="n">
         <f aca="false">I56+I57+I58</f>
         <v>184791.092666667</v>
       </c>
-      <c r="J59" s="153" t="n">
+      <c r="J59" s="166" t="n">
         <f aca="false">J56+J57+J58</f>
         <v>185437.892666667</v>
       </c>
-      <c r="K59" s="153" t="n">
+      <c r="K59" s="166" t="n">
         <f aca="false">K56+K57+K58</f>
         <v>184791.092666667</v>
       </c>
-      <c r="L59" s="153" t="n">
+      <c r="L59" s="166" t="n">
         <f aca="false">L56+L57+L58</f>
         <v>184144.292666667</v>
       </c>
-      <c r="M59" s="153" t="n">
+      <c r="M59" s="166" t="n">
         <f aca="false">M56+M57+M58</f>
         <v>183174.092666667</v>
       </c>
-      <c r="N59" s="154" t="n">
+      <c r="N59" s="167" t="n">
         <f aca="false">SUM(B59:M59)</f>
         <v>2215876.112</v>
       </c>
-      <c r="O59" s="179" t="n">
+      <c r="O59" s="189" t="n">
         <f aca="false">IF(N54=0,0,N59/N54)</f>
         <v>0.674884220732859</v>
       </c>
-      <c r="P59" s="152" t="s">
-        <v>216</v>
+      <c r="P59" s="165" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="149"/>
-      <c r="B60" s="156"/>
-      <c r="C60" s="156"/>
-      <c r="D60" s="156"/>
-      <c r="E60" s="156"/>
-      <c r="F60" s="156"/>
-      <c r="G60" s="156"/>
-      <c r="H60" s="156"/>
-      <c r="I60" s="156"/>
-      <c r="J60" s="156"/>
-      <c r="K60" s="156"/>
-      <c r="L60" s="156"/>
-      <c r="M60" s="156"/>
-      <c r="N60" s="157"/>
-      <c r="O60" s="101"/>
+      <c r="A60" s="94"/>
+      <c r="B60" s="168"/>
+      <c r="C60" s="168"/>
+      <c r="D60" s="168"/>
+      <c r="E60" s="168"/>
+      <c r="F60" s="168"/>
+      <c r="G60" s="168"/>
+      <c r="H60" s="168"/>
+      <c r="I60" s="168"/>
+      <c r="J60" s="168"/>
+      <c r="K60" s="168"/>
+      <c r="L60" s="168"/>
+      <c r="M60" s="168"/>
+      <c r="N60" s="169"/>
+      <c r="O60" s="119"/>
     </row>
     <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="105" t="s">
+      <c r="A61" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="B61" s="147" t="n">
+      <c r="B61" s="105" t="n">
         <f aca="false">B54-B59</f>
         <v>70970.9073333333</v>
       </c>
-      <c r="C61" s="147" t="n">
+      <c r="C61" s="105" t="n">
         <f aca="false">C54-C59</f>
         <v>78085.7073333333</v>
       </c>
-      <c r="D61" s="147" t="n">
+      <c r="D61" s="105" t="n">
         <f aca="false">D54-D59</f>
         <v>85200.5073333333</v>
       </c>
-      <c r="E61" s="147" t="n">
+      <c r="E61" s="105" t="n">
         <f aca="false">E54-E59</f>
         <v>94686.9073333333</v>
       </c>
-      <c r="F61" s="147" t="n">
+      <c r="F61" s="105" t="n">
         <f aca="false">F54-F59</f>
         <v>101801.707333333</v>
       </c>
-      <c r="G61" s="147" t="n">
+      <c r="G61" s="105" t="n">
         <f aca="false">G54-G59</f>
         <v>101801.707333333</v>
       </c>
-      <c r="H61" s="147" t="n">
+      <c r="H61" s="105" t="n">
         <f aca="false">H54-H59</f>
         <v>97058.5073333333</v>
       </c>
-      <c r="I61" s="147" t="n">
+      <c r="I61" s="105" t="n">
         <f aca="false">I54-I59</f>
         <v>89943.7073333333</v>
       </c>
-      <c r="J61" s="147" t="n">
+      <c r="J61" s="105" t="n">
         <f aca="false">J54-J59</f>
         <v>94686.9073333333</v>
       </c>
-      <c r="K61" s="147" t="n">
+      <c r="K61" s="105" t="n">
         <f aca="false">K54-K59</f>
         <v>89943.7073333333</v>
       </c>
-      <c r="L61" s="147" t="n">
+      <c r="L61" s="105" t="n">
         <f aca="false">L54-L59</f>
         <v>85200.5073333333</v>
       </c>
-      <c r="M61" s="147" t="n">
+      <c r="M61" s="105" t="n">
         <f aca="false">M54-M59</f>
         <v>78085.7073333333</v>
       </c>
-      <c r="N61" s="147" t="n">
+      <c r="N61" s="105" t="n">
         <f aca="false">SUM(B61:M61)</f>
         <v>1067466.488</v>
       </c>
-      <c r="O61" s="180" t="n">
+      <c r="O61" s="190" t="n">
         <f aca="false">IF(N54=0,0,N61/N54)</f>
         <v>0.325115779267141</v>
       </c>
-      <c r="P61" s="152" t="s">
-        <v>253</v>
+      <c r="P61" s="165" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="149" t="s">
+      <c r="A62" s="94" t="s">
         <v>63</v>
       </c>
-      <c r="B62" s="108" t="n">
+      <c r="B62" s="125" t="n">
         <f aca="false">IF(B54=0,0,B61/B54)</f>
         <v>0.280323742068063</v>
       </c>
-      <c r="C62" s="108" t="n">
+      <c r="C62" s="125" t="n">
         <f aca="false">IF(C54=0,0,C61/C54)</f>
         <v>0.298881448019685</v>
       </c>
-      <c r="D62" s="108" t="n">
+      <c r="D62" s="125" t="n">
         <f aca="false">IF(D54=0,0,D61/D54)</f>
         <v>0.316325050022623</v>
       </c>
-      <c r="E62" s="108" t="n">
+      <c r="E62" s="125" t="n">
         <f aca="false">IF(E54=0,0,E61/E54)</f>
         <v>0.338016867243933</v>
       </c>
-      <c r="F62" s="108" t="n">
+      <c r="F62" s="125" t="n">
         <f aca="false">IF(F54=0,0,F61/F54)</f>
         <v>0.353220838893519</v>
       </c>
-      <c r="G62" s="108" t="n">
+      <c r="G62" s="125" t="n">
         <f aca="false">IF(G54=0,0,G61/G54)</f>
         <v>0.353220838893519</v>
       </c>
-      <c r="H62" s="108" t="n">
+      <c r="H62" s="125" t="n">
         <f aca="false">IF(H54=0,0,H61/H54)</f>
         <v>0.343181443920593</v>
       </c>
-      <c r="I62" s="108" t="n">
+      <c r="I62" s="125" t="n">
         <f aca="false">IF(I54=0,0,I61/I54)</f>
         <v>0.327383743644174</v>
       </c>
-      <c r="J62" s="108" t="n">
+      <c r="J62" s="125" t="n">
         <f aca="false">IF(J54=0,0,J61/J54)</f>
         <v>0.338016867243933</v>
       </c>
-      <c r="K62" s="108" t="n">
+      <c r="K62" s="125" t="n">
         <f aca="false">IF(K54=0,0,K61/K54)</f>
         <v>0.327383743644174</v>
       </c>
-      <c r="L62" s="108" t="n">
+      <c r="L62" s="125" t="n">
         <f aca="false">IF(L54=0,0,L61/L54)</f>
         <v>0.316325050022623</v>
       </c>
-      <c r="M62" s="108" t="n">
+      <c r="M62" s="125" t="n">
         <f aca="false">IF(M54=0,0,M61/M54)</f>
         <v>0.298881448019685</v>
       </c>
-      <c r="N62" s="94" t="n">
+      <c r="N62" s="97" t="n">
         <f aca="false">IF(N54=0,0,N61/N54)</f>
         <v>0.325115779267141</v>
       </c>
-      <c r="O62" s="101"/>
-      <c r="P62" s="152" t="s">
-        <v>218</v>
+      <c r="O62" s="119"/>
+      <c r="P62" s="165" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="65" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="117" t="s">
-        <v>254</v>
-      </c>
-      <c r="B65" s="117"/>
-      <c r="C65" s="117"/>
-      <c r="D65" s="117"/>
-      <c r="E65" s="117"/>
-      <c r="F65" s="117"/>
-      <c r="G65" s="117"/>
-      <c r="H65" s="117"/>
-      <c r="I65" s="117"/>
-      <c r="J65" s="117"/>
-      <c r="K65" s="117"/>
-      <c r="L65" s="117"/>
-      <c r="M65" s="117"/>
-      <c r="N65" s="117"/>
-      <c r="O65" s="117"/>
-      <c r="P65" s="117"/>
-      <c r="Q65" s="117"/>
+      <c r="A65" s="134" t="s">
+        <v>281</v>
+      </c>
+      <c r="B65" s="134"/>
+      <c r="C65" s="134"/>
+      <c r="D65" s="134"/>
+      <c r="E65" s="134"/>
+      <c r="F65" s="134"/>
+      <c r="G65" s="134"/>
+      <c r="H65" s="134"/>
+      <c r="I65" s="134"/>
+      <c r="J65" s="134"/>
+      <c r="K65" s="134"/>
+      <c r="L65" s="134"/>
+      <c r="M65" s="134"/>
+      <c r="N65" s="134"/>
+      <c r="O65" s="134"/>
+      <c r="P65" s="134"/>
+      <c r="Q65" s="134"/>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="181" t="s">
-        <v>255</v>
-      </c>
-      <c r="B66" s="181"/>
-      <c r="C66" s="181"/>
-      <c r="D66" s="181"/>
-      <c r="E66" s="181"/>
-      <c r="F66" s="181"/>
-      <c r="G66" s="181"/>
-      <c r="H66" s="181"/>
-      <c r="I66" s="181"/>
-      <c r="J66" s="181"/>
-      <c r="K66" s="181"/>
-      <c r="L66" s="181"/>
-      <c r="M66" s="181"/>
-      <c r="N66" s="181"/>
-      <c r="O66" s="181"/>
-      <c r="P66" s="181"/>
-      <c r="Q66" s="181"/>
+      <c r="A66" s="191" t="s">
+        <v>282</v>
+      </c>
+      <c r="B66" s="191"/>
+      <c r="C66" s="191"/>
+      <c r="D66" s="191"/>
+      <c r="E66" s="191"/>
+      <c r="F66" s="191"/>
+      <c r="G66" s="191"/>
+      <c r="H66" s="191"/>
+      <c r="I66" s="191"/>
+      <c r="J66" s="191"/>
+      <c r="K66" s="191"/>
+      <c r="L66" s="191"/>
+      <c r="M66" s="191"/>
+      <c r="N66" s="191"/>
+      <c r="O66" s="191"/>
+      <c r="P66" s="191"/>
+      <c r="Q66" s="191"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="182" t="s">
-        <v>256</v>
-      </c>
-      <c r="B68" s="182"/>
-      <c r="C68" s="182"/>
-      <c r="D68" s="182"/>
-      <c r="E68" s="182"/>
-      <c r="F68" s="182"/>
-      <c r="G68" s="182"/>
-      <c r="H68" s="182"/>
-      <c r="I68" s="182"/>
+      <c r="A68" s="192" t="s">
+        <v>283</v>
+      </c>
+      <c r="B68" s="192"/>
+      <c r="C68" s="192"/>
+      <c r="D68" s="192"/>
+      <c r="E68" s="192"/>
+      <c r="F68" s="192"/>
+      <c r="G68" s="192"/>
+      <c r="H68" s="192"/>
+      <c r="I68" s="192"/>
     </row>
     <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="129" t="s">
-        <v>257</v>
-      </c>
-      <c r="B69" s="129" t="s">
-        <v>258</v>
-      </c>
-      <c r="C69" s="129" t="s">
-        <v>259</v>
-      </c>
-      <c r="D69" s="129" t="s">
-        <v>260</v>
-      </c>
-      <c r="E69" s="129" t="s">
+      <c r="A69" s="146" t="s">
+        <v>284</v>
+      </c>
+      <c r="B69" s="146" t="s">
+        <v>285</v>
+      </c>
+      <c r="C69" s="146" t="s">
+        <v>286</v>
+      </c>
+      <c r="D69" s="146" t="s">
+        <v>287</v>
+      </c>
+      <c r="E69" s="146" t="s">
         <v>110</v>
       </c>
-      <c r="F69" s="129" t="s">
-        <v>261</v>
-      </c>
-      <c r="G69" s="129" t="s">
+      <c r="F69" s="146" t="s">
+        <v>288</v>
+      </c>
+      <c r="G69" s="146" t="s">
         <v>61</v>
       </c>
-      <c r="H69" s="129" t="s">
+      <c r="H69" s="146" t="s">
         <v>62</v>
       </c>
-      <c r="I69" s="129" t="s">
-        <v>262</v>
+      <c r="I69" s="146" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="183" t="n">
+      <c r="A70" s="193" t="n">
         <v>48</v>
       </c>
-      <c r="B70" s="184" t="n">
+      <c r="B70" s="194" t="n">
         <f aca="false">48*4900*0.82*12</f>
         <v>2314368</v>
       </c>
-      <c r="C70" s="184" t="n">
+      <c r="C70" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D70" s="184" t="n">
+      <c r="D70" s="194" t="n">
         <f aca="false">B70+C70</f>
         <v>2894625.6</v>
       </c>
-      <c r="E70" s="184" t="n">
+      <c r="E70" s="194" t="n">
         <f aca="false">48*Drivers!$E$25*12</f>
         <v>1590000</v>
       </c>
-      <c r="F70" s="184" t="n">
+      <c r="F70" s="194" t="n">
         <f aca="false">D70*0.12</f>
         <v>347355.072</v>
       </c>
-      <c r="G70" s="184" t="n">
+      <c r="G70" s="194" t="n">
         <f aca="false">E70+F70</f>
         <v>1937355.072</v>
       </c>
-      <c r="H70" s="185" t="n">
+      <c r="H70" s="195" t="n">
         <f aca="false">D70-G70</f>
         <v>957270.528</v>
       </c>
-      <c r="I70" s="186" t="n">
+      <c r="I70" s="196" t="n">
         <f aca="false">IF(D70=0,0,H70/D70)</f>
         <v>0.330706163864508</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="187" t="n">
+      <c r="A71" s="197" t="n">
         <v>50</v>
       </c>
-      <c r="B71" s="188" t="n">
+      <c r="B71" s="198" t="n">
         <f aca="false">50*4900*0.82*12</f>
         <v>2410800</v>
       </c>
-      <c r="C71" s="188" t="n">
+      <c r="C71" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D71" s="188" t="n">
+      <c r="D71" s="198" t="n">
         <f aca="false">B71+C71</f>
         <v>2991057.6</v>
       </c>
-      <c r="E71" s="188" t="n">
+      <c r="E71" s="198" t="n">
         <f aca="false">50*Drivers!$E$25*12</f>
         <v>1656250</v>
       </c>
-      <c r="F71" s="188" t="n">
+      <c r="F71" s="198" t="n">
         <f aca="false">D71*0.12</f>
         <v>358926.912</v>
       </c>
-      <c r="G71" s="188" t="n">
+      <c r="G71" s="198" t="n">
         <f aca="false">E71+F71</f>
         <v>2015176.912</v>
       </c>
-      <c r="H71" s="189" t="n">
+      <c r="H71" s="199" t="n">
         <f aca="false">D71-G71</f>
         <v>975880.688</v>
       </c>
-      <c r="I71" s="190" t="n">
+      <c r="I71" s="200" t="n">
         <f aca="false">IF(D71=0,0,H71/D71)</f>
         <v>0.326266096647554</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="183" t="n">
+      <c r="A72" s="193" t="n">
         <v>52</v>
       </c>
-      <c r="B72" s="184" t="n">
+      <c r="B72" s="194" t="n">
         <f aca="false">52*4900*0.82*12</f>
         <v>2507232</v>
       </c>
-      <c r="C72" s="184" t="n">
+      <c r="C72" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D72" s="184" t="n">
+      <c r="D72" s="194" t="n">
         <f aca="false">B72+C72</f>
         <v>3087489.6</v>
       </c>
-      <c r="E72" s="184" t="n">
+      <c r="E72" s="194" t="n">
         <f aca="false">52*Drivers!$E$25*12</f>
         <v>1722500</v>
       </c>
-      <c r="F72" s="184" t="n">
+      <c r="F72" s="194" t="n">
         <f aca="false">D72*0.12</f>
         <v>370498.752</v>
       </c>
-      <c r="G72" s="184" t="n">
+      <c r="G72" s="194" t="n">
         <f aca="false">E72+F72</f>
         <v>2092998.752</v>
       </c>
-      <c r="H72" s="185" t="n">
+      <c r="H72" s="195" t="n">
         <f aca="false">D72-G72</f>
         <v>994490.848</v>
       </c>
-      <c r="I72" s="186" t="n">
+      <c r="I72" s="196" t="n">
         <f aca="false">IF(D72=0,0,H72/D72)</f>
         <v>0.322103383927188</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="191" t="n">
+      <c r="A73" s="201" t="n">
         <v>54</v>
       </c>
-      <c r="B73" s="192" t="n">
+      <c r="B73" s="202" t="n">
         <f aca="false">54*4900*0.82*12</f>
         <v>2603664</v>
       </c>
-      <c r="C73" s="192" t="n">
+      <c r="C73" s="202" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D73" s="192" t="n">
+      <c r="D73" s="202" t="n">
         <f aca="false">B73+C73</f>
         <v>3183921.6</v>
       </c>
-      <c r="E73" s="192" t="n">
+      <c r="E73" s="202" t="n">
         <f aca="false">54*Drivers!$E$25*12</f>
         <v>1788750</v>
       </c>
-      <c r="F73" s="192" t="n">
+      <c r="F73" s="202" t="n">
         <f aca="false">D73*0.12</f>
         <v>382070.592</v>
       </c>
-      <c r="G73" s="192" t="n">
+      <c r="G73" s="202" t="n">
         <f aca="false">E73+F73</f>
         <v>2170820.592</v>
       </c>
-      <c r="H73" s="193" t="n">
+      <c r="H73" s="203" t="n">
         <f aca="false">D73-G73</f>
         <v>1013101.008</v>
       </c>
-      <c r="I73" s="194" t="n">
+      <c r="I73" s="204" t="n">
         <f aca="false">IF(D73=0,0,H73/D73)</f>
         <v>0.318192824848451</v>
       </c>
-      <c r="J73" s="195" t="s">
-        <v>263</v>
+      <c r="J73" s="205" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="183" t="n">
+      <c r="A74" s="193" t="n">
         <v>56</v>
       </c>
-      <c r="B74" s="184" t="n">
+      <c r="B74" s="194" t="n">
         <f aca="false">56*4900*0.82*12</f>
         <v>2700096</v>
       </c>
-      <c r="C74" s="184" t="n">
+      <c r="C74" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D74" s="184" t="n">
+      <c r="D74" s="194" t="n">
         <f aca="false">B74+C74</f>
         <v>3280353.6</v>
       </c>
-      <c r="E74" s="184" t="n">
+      <c r="E74" s="194" t="n">
         <f aca="false">56*Drivers!$E$25*12</f>
         <v>1855000</v>
       </c>
-      <c r="F74" s="184" t="n">
+      <c r="F74" s="194" t="n">
         <f aca="false">D74*0.12</f>
         <v>393642.432</v>
       </c>
-      <c r="G74" s="184" t="n">
+      <c r="G74" s="194" t="n">
         <f aca="false">E74+F74</f>
         <v>2248642.432</v>
       </c>
-      <c r="H74" s="185" t="n">
+      <c r="H74" s="195" t="n">
         <f aca="false">D74-G74</f>
         <v>1031711.168</v>
       </c>
-      <c r="I74" s="186" t="n">
+      <c r="I74" s="196" t="n">
         <f aca="false">IF(D74=0,0,H74/D74)</f>
         <v>0.314512181857468</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="187" t="n">
+      <c r="A75" s="197" t="n">
         <v>58</v>
       </c>
-      <c r="B75" s="188" t="n">
+      <c r="B75" s="198" t="n">
         <f aca="false">58*4900*0.82*12</f>
         <v>2796528</v>
       </c>
-      <c r="C75" s="188" t="n">
+      <c r="C75" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D75" s="188" t="n">
+      <c r="D75" s="198" t="n">
         <f aca="false">B75+C75</f>
         <v>3376785.6</v>
       </c>
-      <c r="E75" s="188" t="n">
+      <c r="E75" s="198" t="n">
         <f aca="false">58*Drivers!$E$25*12</f>
         <v>1921250</v>
       </c>
-      <c r="F75" s="188" t="n">
+      <c r="F75" s="198" t="n">
         <f aca="false">D75*0.12</f>
         <v>405214.272</v>
       </c>
-      <c r="G75" s="188" t="n">
+      <c r="G75" s="198" t="n">
         <f aca="false">E75+F75</f>
         <v>2326464.272</v>
       </c>
-      <c r="H75" s="189" t="n">
+      <c r="H75" s="199" t="n">
         <f aca="false">D75-G75</f>
         <v>1050321.328</v>
       </c>
-      <c r="I75" s="190" t="n">
+      <c r="I75" s="200" t="n">
         <f aca="false">IF(D75=0,0,H75/D75)</f>
         <v>0.31104175758153</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="183" t="n">
+      <c r="A76" s="193" t="n">
         <v>60</v>
       </c>
-      <c r="B76" s="184" t="n">
+      <c r="B76" s="194" t="n">
         <f aca="false">60*4900*0.82*12</f>
         <v>2892960</v>
       </c>
-      <c r="C76" s="184" t="n">
+      <c r="C76" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D76" s="184" t="n">
+      <c r="D76" s="194" t="n">
         <f aca="false">B76+C76</f>
         <v>3473217.6</v>
       </c>
-      <c r="E76" s="184" t="n">
+      <c r="E76" s="194" t="n">
         <f aca="false">60*Drivers!$E$25*12</f>
         <v>1987500</v>
       </c>
-      <c r="F76" s="184" t="n">
+      <c r="F76" s="194" t="n">
         <f aca="false">D76*0.12</f>
         <v>416786.112</v>
       </c>
-      <c r="G76" s="184" t="n">
+      <c r="G76" s="194" t="n">
         <f aca="false">E76+F76</f>
         <v>2404286.112</v>
       </c>
-      <c r="H76" s="185" t="n">
+      <c r="H76" s="195" t="n">
         <f aca="false">D76-G76</f>
         <v>1068931.488</v>
       </c>
-      <c r="I76" s="186" t="n">
+      <c r="I76" s="196" t="n">
         <f aca="false">IF(D76=0,0,H76/D76)</f>
         <v>0.307764042195341</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="187" t="n">
+      <c r="A77" s="197" t="n">
         <v>62</v>
       </c>
-      <c r="B77" s="188" t="n">
+      <c r="B77" s="198" t="n">
         <f aca="false">62*4900*0.82*12</f>
         <v>2989392</v>
       </c>
-      <c r="C77" s="188" t="n">
+      <c r="C77" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D77" s="188" t="n">
+      <c r="D77" s="198" t="n">
         <f aca="false">B77+C77</f>
         <v>3569649.6</v>
       </c>
-      <c r="E77" s="188" t="n">
+      <c r="E77" s="198" t="n">
         <f aca="false">62*Drivers!$E$25*12</f>
         <v>2053750</v>
       </c>
-      <c r="F77" s="188" t="n">
+      <c r="F77" s="198" t="n">
         <f aca="false">D77*0.12</f>
         <v>428357.952</v>
       </c>
-      <c r="G77" s="188" t="n">
+      <c r="G77" s="198" t="n">
         <f aca="false">E77+F77</f>
         <v>2482107.952</v>
       </c>
-      <c r="H77" s="189" t="n">
+      <c r="H77" s="199" t="n">
         <f aca="false">D77-G77</f>
         <v>1087541.648</v>
       </c>
-      <c r="I77" s="190" t="n">
+      <c r="I77" s="200" t="n">
         <f aca="false">IF(D77=0,0,H77/D77)</f>
         <v>0.304663417944439</v>
       </c>
@@ -14507,265 +15198,265 @@
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="182" t="s">
-        <v>264</v>
-      </c>
-      <c r="B80" s="182"/>
-      <c r="C80" s="182"/>
-      <c r="D80" s="182"/>
-      <c r="E80" s="182"/>
-      <c r="F80" s="182"/>
-      <c r="G80" s="182"/>
-      <c r="H80" s="182"/>
-      <c r="I80" s="182"/>
+      <c r="A80" s="192" t="s">
+        <v>291</v>
+      </c>
+      <c r="B80" s="192"/>
+      <c r="C80" s="192"/>
+      <c r="D80" s="192"/>
+      <c r="E80" s="192"/>
+      <c r="F80" s="192"/>
+      <c r="G80" s="192"/>
+      <c r="H80" s="192"/>
+      <c r="I80" s="192"/>
     </row>
     <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="129" t="s">
-        <v>231</v>
-      </c>
-      <c r="B81" s="129" t="s">
+      <c r="A81" s="146" t="s">
         <v>258</v>
       </c>
-      <c r="C81" s="129" t="s">
-        <v>259</v>
-      </c>
-      <c r="D81" s="129" t="s">
-        <v>260</v>
-      </c>
-      <c r="E81" s="129" t="s">
+      <c r="B81" s="146" t="s">
+        <v>285</v>
+      </c>
+      <c r="C81" s="146" t="s">
+        <v>286</v>
+      </c>
+      <c r="D81" s="146" t="s">
+        <v>287</v>
+      </c>
+      <c r="E81" s="146" t="s">
         <v>110</v>
       </c>
-      <c r="F81" s="129" t="s">
-        <v>261</v>
-      </c>
-      <c r="G81" s="129" t="s">
+      <c r="F81" s="146" t="s">
+        <v>288</v>
+      </c>
+      <c r="G81" s="146" t="s">
         <v>61</v>
       </c>
-      <c r="H81" s="129" t="s">
+      <c r="H81" s="146" t="s">
         <v>62</v>
       </c>
-      <c r="I81" s="129" t="s">
-        <v>262</v>
+      <c r="I81" s="146" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="196" t="n">
+      <c r="A82" s="206" t="n">
         <v>4400</v>
       </c>
-      <c r="B82" s="184" t="n">
+      <c r="B82" s="194" t="n">
         <f aca="false">55*4400*0.82*12</f>
         <v>2381280</v>
       </c>
-      <c r="C82" s="184" t="n">
+      <c r="C82" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D82" s="184" t="n">
+      <c r="D82" s="194" t="n">
         <f aca="false">B82+C82</f>
         <v>2961537.6</v>
       </c>
-      <c r="E82" s="184" t="n">
+      <c r="E82" s="194" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F82" s="184" t="n">
+      <c r="F82" s="194" t="n">
         <f aca="false">D82*0.12</f>
         <v>355384.512</v>
       </c>
-      <c r="G82" s="184" t="n">
+      <c r="G82" s="194" t="n">
         <f aca="false">E82+F82</f>
         <v>2177259.512</v>
       </c>
-      <c r="H82" s="185" t="n">
+      <c r="H82" s="195" t="n">
         <f aca="false">D82-G82</f>
         <v>784278.088</v>
       </c>
-      <c r="I82" s="186" t="n">
+      <c r="I82" s="196" t="n">
         <f aca="false">IF(D82=0,0,H82/D82)</f>
         <v>0.264821249610338</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="197" t="n">
+      <c r="A83" s="207" t="n">
         <v>4600</v>
       </c>
-      <c r="B83" s="188" t="n">
+      <c r="B83" s="198" t="n">
         <f aca="false">55*4600*0.82*12</f>
         <v>2489520</v>
       </c>
-      <c r="C83" s="188" t="n">
+      <c r="C83" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D83" s="188" t="n">
+      <c r="D83" s="198" t="n">
         <f aca="false">B83+C83</f>
         <v>3069777.6</v>
       </c>
-      <c r="E83" s="188" t="n">
+      <c r="E83" s="198" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F83" s="188" t="n">
+      <c r="F83" s="198" t="n">
         <f aca="false">D83*0.12</f>
         <v>368373.312</v>
       </c>
-      <c r="G83" s="188" t="n">
+      <c r="G83" s="198" t="n">
         <f aca="false">E83+F83</f>
         <v>2190248.312</v>
       </c>
-      <c r="H83" s="189" t="n">
+      <c r="H83" s="199" t="n">
         <f aca="false">D83-G83</f>
         <v>879529.288</v>
       </c>
-      <c r="I83" s="190" t="n">
+      <c r="I83" s="200" t="n">
         <f aca="false">IF(D83=0,0,H83/D83)</f>
         <v>0.286512380571153</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="198" t="n">
+      <c r="A84" s="176" t="n">
         <v>4800</v>
       </c>
-      <c r="B84" s="192" t="n">
+      <c r="B84" s="202" t="n">
         <f aca="false">55*4800*0.82*12</f>
         <v>2597760</v>
       </c>
-      <c r="C84" s="192" t="n">
+      <c r="C84" s="202" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D84" s="192" t="n">
+      <c r="D84" s="202" t="n">
         <f aca="false">B84+C84</f>
         <v>3178017.6</v>
       </c>
-      <c r="E84" s="192" t="n">
+      <c r="E84" s="202" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F84" s="192" t="n">
+      <c r="F84" s="202" t="n">
         <f aca="false">D84*0.12</f>
         <v>381362.112</v>
       </c>
-      <c r="G84" s="192" t="n">
+      <c r="G84" s="202" t="n">
         <f aca="false">E84+F84</f>
         <v>2203237.112</v>
       </c>
-      <c r="H84" s="193" t="n">
+      <c r="H84" s="203" t="n">
         <f aca="false">D84-G84</f>
         <v>974780.488</v>
       </c>
-      <c r="I84" s="194" t="n">
+      <c r="I84" s="204" t="n">
         <f aca="false">IF(D84=0,0,H84/D84)</f>
         <v>0.306725956457887</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="197" t="n">
+      <c r="A85" s="207" t="n">
         <v>5000</v>
       </c>
-      <c r="B85" s="188" t="n">
+      <c r="B85" s="198" t="n">
         <f aca="false">55*5000*0.82*12</f>
         <v>2706000</v>
       </c>
-      <c r="C85" s="188" t="n">
+      <c r="C85" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D85" s="188" t="n">
+      <c r="D85" s="198" t="n">
         <f aca="false">B85+C85</f>
         <v>3286257.6</v>
       </c>
-      <c r="E85" s="188" t="n">
+      <c r="E85" s="198" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F85" s="188" t="n">
+      <c r="F85" s="198" t="n">
         <f aca="false">D85*0.12</f>
         <v>394350.912</v>
       </c>
-      <c r="G85" s="188" t="n">
+      <c r="G85" s="198" t="n">
         <f aca="false">E85+F85</f>
         <v>2216225.912</v>
       </c>
-      <c r="H85" s="189" t="n">
+      <c r="H85" s="199" t="n">
         <f aca="false">D85-G85</f>
         <v>1070031.688</v>
       </c>
-      <c r="I85" s="190" t="n">
+      <c r="I85" s="200" t="n">
         <f aca="false">IF(D85=0,0,H85/D85)</f>
         <v>0.325607976684482</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="196" t="n">
+      <c r="A86" s="206" t="n">
         <v>5200</v>
       </c>
-      <c r="B86" s="184" t="n">
+      <c r="B86" s="194" t="n">
         <f aca="false">55*5200*0.82*12</f>
         <v>2814240</v>
       </c>
-      <c r="C86" s="184" t="n">
+      <c r="C86" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D86" s="184" t="n">
+      <c r="D86" s="194" t="n">
         <f aca="false">B86+C86</f>
         <v>3394497.6</v>
       </c>
-      <c r="E86" s="184" t="n">
+      <c r="E86" s="194" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F86" s="184" t="n">
+      <c r="F86" s="194" t="n">
         <f aca="false">D86*0.12</f>
         <v>407339.712</v>
       </c>
-      <c r="G86" s="184" t="n">
+      <c r="G86" s="194" t="n">
         <f aca="false">E86+F86</f>
         <v>2229214.712</v>
       </c>
-      <c r="H86" s="185" t="n">
+      <c r="H86" s="195" t="n">
         <f aca="false">D86-G86</f>
         <v>1165282.888</v>
       </c>
-      <c r="I86" s="186" t="n">
+      <c r="I86" s="196" t="n">
         <f aca="false">IF(D86=0,0,H86/D86)</f>
         <v>0.343285818790975</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="197" t="n">
+      <c r="A87" s="207" t="n">
         <v>5400</v>
       </c>
-      <c r="B87" s="188" t="n">
+      <c r="B87" s="198" t="n">
         <f aca="false">55*5400*0.82*12</f>
         <v>2922480</v>
       </c>
-      <c r="C87" s="188" t="n">
+      <c r="C87" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D87" s="188" t="n">
+      <c r="D87" s="198" t="n">
         <f aca="false">B87+C87</f>
         <v>3502737.6</v>
       </c>
-      <c r="E87" s="188" t="n">
+      <c r="E87" s="198" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F87" s="188" t="n">
+      <c r="F87" s="198" t="n">
         <f aca="false">D87*0.12</f>
         <v>420328.512</v>
       </c>
-      <c r="G87" s="188" t="n">
+      <c r="G87" s="198" t="n">
         <f aca="false">E87+F87</f>
         <v>2242203.512</v>
       </c>
-      <c r="H87" s="189" t="n">
+      <c r="H87" s="199" t="n">
         <f aca="false">D87-G87</f>
         <v>1260534.088</v>
       </c>
-      <c r="I87" s="190" t="n">
+      <c r="I87" s="200" t="n">
         <f aca="false">IF(D87=0,0,H87/D87)</f>
         <v>0.359871115666786</v>
       </c>
@@ -14773,453 +15464,453 @@
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="90" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="182" t="s">
-        <v>265</v>
-      </c>
-      <c r="B90" s="182"/>
-      <c r="C90" s="182"/>
-      <c r="D90" s="182"/>
-      <c r="E90" s="182"/>
-      <c r="F90" s="182"/>
-      <c r="G90" s="182"/>
-      <c r="H90" s="182"/>
-      <c r="I90" s="182"/>
+      <c r="A90" s="192" t="s">
+        <v>292</v>
+      </c>
+      <c r="B90" s="192"/>
+      <c r="C90" s="192"/>
+      <c r="D90" s="192"/>
+      <c r="E90" s="192"/>
+      <c r="F90" s="192"/>
+      <c r="G90" s="192"/>
+      <c r="H90" s="192"/>
+      <c r="I90" s="192"/>
     </row>
     <row r="91" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="129" t="s">
-        <v>266</v>
-      </c>
-      <c r="B91" s="129" t="s">
-        <v>258</v>
-      </c>
-      <c r="C91" s="129" t="s">
-        <v>259</v>
-      </c>
-      <c r="D91" s="129" t="s">
-        <v>260</v>
-      </c>
-      <c r="E91" s="129" t="s">
+      <c r="A91" s="146" t="s">
+        <v>293</v>
+      </c>
+      <c r="B91" s="146" t="s">
+        <v>285</v>
+      </c>
+      <c r="C91" s="146" t="s">
+        <v>286</v>
+      </c>
+      <c r="D91" s="146" t="s">
+        <v>287</v>
+      </c>
+      <c r="E91" s="146" t="s">
         <v>110</v>
       </c>
-      <c r="F91" s="129" t="s">
-        <v>261</v>
-      </c>
-      <c r="G91" s="129" t="s">
+      <c r="F91" s="146" t="s">
+        <v>288</v>
+      </c>
+      <c r="G91" s="146" t="s">
         <v>61</v>
       </c>
-      <c r="H91" s="129" t="s">
+      <c r="H91" s="146" t="s">
         <v>62</v>
       </c>
-      <c r="I91" s="129" t="s">
-        <v>262</v>
+      <c r="I91" s="146" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="199" t="n">
+      <c r="A92" s="208" t="n">
         <v>0.7</v>
       </c>
-      <c r="B92" s="184" t="n">
+      <c r="B92" s="194" t="n">
         <f aca="false">55*4900*0.7*12</f>
         <v>2263800</v>
       </c>
-      <c r="C92" s="184" t="n">
+      <c r="C92" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D92" s="184" t="n">
+      <c r="D92" s="194" t="n">
         <f aca="false">B92+C92</f>
         <v>2844057.6</v>
       </c>
-      <c r="E92" s="184" t="n">
+      <c r="E92" s="194" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F92" s="184" t="n">
+      <c r="F92" s="194" t="n">
         <f aca="false">D92*0.12</f>
         <v>341286.912</v>
       </c>
-      <c r="G92" s="184" t="n">
+      <c r="G92" s="194" t="n">
         <f aca="false">E92+F92</f>
         <v>2163161.912</v>
       </c>
-      <c r="H92" s="185" t="n">
+      <c r="H92" s="195" t="n">
         <f aca="false">D92-G92</f>
         <v>680895.688</v>
       </c>
-      <c r="I92" s="186" t="n">
+      <c r="I92" s="196" t="n">
         <f aca="false">IF(D92=0,0,H92/D92)</f>
         <v>0.239409950065709</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="200" t="n">
+      <c r="A93" s="209" t="n">
         <v>0.72</v>
       </c>
-      <c r="B93" s="188" t="n">
+      <c r="B93" s="198" t="n">
         <f aca="false">55*4900*0.72*12</f>
         <v>2328480</v>
       </c>
-      <c r="C93" s="188" t="n">
+      <c r="C93" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D93" s="188" t="n">
+      <c r="D93" s="198" t="n">
         <f aca="false">B93+C93</f>
         <v>2908737.6</v>
       </c>
-      <c r="E93" s="188" t="n">
+      <c r="E93" s="198" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F93" s="188" t="n">
+      <c r="F93" s="198" t="n">
         <f aca="false">D93*0.12</f>
         <v>349048.512</v>
       </c>
-      <c r="G93" s="188" t="n">
+      <c r="G93" s="198" t="n">
         <f aca="false">E93+F93</f>
         <v>2170923.512</v>
       </c>
-      <c r="H93" s="189" t="n">
+      <c r="H93" s="199" t="n">
         <f aca="false">D93-G93</f>
         <v>737814.088</v>
       </c>
-      <c r="I93" s="190" t="n">
+      <c r="I93" s="200" t="n">
         <f aca="false">IF(D93=0,0,H93/D93)</f>
         <v>0.253654399076768</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="199" t="n">
+      <c r="A94" s="208" t="n">
         <v>0.74</v>
       </c>
-      <c r="B94" s="184" t="n">
+      <c r="B94" s="194" t="n">
         <f aca="false">55*4900*0.74*12</f>
         <v>2393160</v>
       </c>
-      <c r="C94" s="184" t="n">
+      <c r="C94" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D94" s="184" t="n">
+      <c r="D94" s="194" t="n">
         <f aca="false">B94+C94</f>
         <v>2973417.6</v>
       </c>
-      <c r="E94" s="184" t="n">
+      <c r="E94" s="194" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F94" s="184" t="n">
+      <c r="F94" s="194" t="n">
         <f aca="false">D94*0.12</f>
         <v>356810.112</v>
       </c>
-      <c r="G94" s="184" t="n">
+      <c r="G94" s="194" t="n">
         <f aca="false">E94+F94</f>
         <v>2178685.112</v>
       </c>
-      <c r="H94" s="185" t="n">
+      <c r="H94" s="195" t="n">
         <f aca="false">D94-G94</f>
         <v>794732.488</v>
       </c>
-      <c r="I94" s="186" t="n">
+      <c r="I94" s="196" t="n">
         <f aca="false">IF(D94=0,0,H94/D94)</f>
         <v>0.267279136304298</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="200" t="n">
+      <c r="A95" s="209" t="n">
         <v>0.76</v>
       </c>
-      <c r="B95" s="188" t="n">
+      <c r="B95" s="198" t="n">
         <f aca="false">55*4900*0.76*12</f>
         <v>2457840</v>
       </c>
-      <c r="C95" s="188" t="n">
+      <c r="C95" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D95" s="188" t="n">
+      <c r="D95" s="198" t="n">
         <f aca="false">B95+C95</f>
         <v>3038097.6</v>
       </c>
-      <c r="E95" s="188" t="n">
+      <c r="E95" s="198" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F95" s="188" t="n">
+      <c r="F95" s="198" t="n">
         <f aca="false">D95*0.12</f>
         <v>364571.712</v>
       </c>
-      <c r="G95" s="188" t="n">
+      <c r="G95" s="198" t="n">
         <f aca="false">E95+F95</f>
         <v>2186446.712</v>
       </c>
-      <c r="H95" s="189" t="n">
+      <c r="H95" s="199" t="n">
         <f aca="false">D95-G95</f>
         <v>851650.888</v>
       </c>
-      <c r="I95" s="190" t="n">
+      <c r="I95" s="200" t="n">
         <f aca="false">IF(D95=0,0,H95/D95)</f>
         <v>0.280323742068063</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="199" t="n">
+      <c r="A96" s="208" t="n">
         <v>0.78</v>
       </c>
-      <c r="B96" s="184" t="n">
+      <c r="B96" s="194" t="n">
         <f aca="false">55*4900*0.78*12</f>
         <v>2522520</v>
       </c>
-      <c r="C96" s="184" t="n">
+      <c r="C96" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D96" s="184" t="n">
+      <c r="D96" s="194" t="n">
         <f aca="false">B96+C96</f>
         <v>3102777.6</v>
       </c>
-      <c r="E96" s="184" t="n">
+      <c r="E96" s="194" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F96" s="184" t="n">
+      <c r="F96" s="194" t="n">
         <f aca="false">D96*0.12</f>
         <v>372333.312</v>
       </c>
-      <c r="G96" s="184" t="n">
+      <c r="G96" s="194" t="n">
         <f aca="false">E96+F96</f>
         <v>2194208.312</v>
       </c>
-      <c r="H96" s="185" t="n">
+      <c r="H96" s="195" t="n">
         <f aca="false">D96-G96</f>
         <v>908569.288</v>
       </c>
-      <c r="I96" s="186" t="n">
+      <c r="I96" s="196" t="n">
         <f aca="false">IF(D96=0,0,H96/D96)</f>
         <v>0.292824496348046</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="200" t="n">
+      <c r="A97" s="209" t="n">
         <v>0.8</v>
       </c>
-      <c r="B97" s="188" t="n">
+      <c r="B97" s="198" t="n">
         <f aca="false">55*4900*0.8*12</f>
         <v>2587200</v>
       </c>
-      <c r="C97" s="188" t="n">
+      <c r="C97" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D97" s="188" t="n">
+      <c r="D97" s="198" t="n">
         <f aca="false">B97+C97</f>
         <v>3167457.6</v>
       </c>
-      <c r="E97" s="188" t="n">
+      <c r="E97" s="198" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F97" s="188" t="n">
+      <c r="F97" s="198" t="n">
         <f aca="false">D97*0.12</f>
         <v>380094.912</v>
       </c>
-      <c r="G97" s="188" t="n">
+      <c r="G97" s="198" t="n">
         <f aca="false">E97+F97</f>
         <v>2201969.912</v>
       </c>
-      <c r="H97" s="189" t="n">
+      <c r="H97" s="199" t="n">
         <f aca="false">D97-G97</f>
         <v>965487.688</v>
       </c>
-      <c r="I97" s="190" t="n">
+      <c r="I97" s="200" t="n">
         <f aca="false">IF(D97=0,0,H97/D97)</f>
         <v>0.304814715751838</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="201" t="n">
+      <c r="A98" s="210" t="n">
         <v>0.82</v>
       </c>
-      <c r="B98" s="192" t="n">
+      <c r="B98" s="202" t="n">
         <f aca="false">55*4900*0.82*12</f>
         <v>2651880</v>
       </c>
-      <c r="C98" s="192" t="n">
+      <c r="C98" s="202" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D98" s="192" t="n">
+      <c r="D98" s="202" t="n">
         <f aca="false">B98+C98</f>
         <v>3232137.6</v>
       </c>
-      <c r="E98" s="192" t="n">
+      <c r="E98" s="202" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F98" s="192" t="n">
+      <c r="F98" s="202" t="n">
         <f aca="false">D98*0.12</f>
         <v>387856.512</v>
       </c>
-      <c r="G98" s="192" t="n">
+      <c r="G98" s="202" t="n">
         <f aca="false">E98+F98</f>
         <v>2209731.512</v>
       </c>
-      <c r="H98" s="193" t="n">
+      <c r="H98" s="203" t="n">
         <f aca="false">D98-G98</f>
         <v>1022406.088</v>
       </c>
-      <c r="I98" s="194" t="n">
+      <c r="I98" s="204" t="n">
         <f aca="false">IF(D98=0,0,H98/D98)</f>
         <v>0.316325050022623</v>
       </c>
-      <c r="J98" s="195" t="s">
-        <v>267</v>
+      <c r="J98" s="205" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="200" t="n">
+      <c r="A99" s="209" t="n">
         <v>0.84</v>
       </c>
-      <c r="B99" s="188" t="n">
+      <c r="B99" s="198" t="n">
         <f aca="false">55*4900*0.84*12</f>
         <v>2716560</v>
       </c>
-      <c r="C99" s="188" t="n">
+      <c r="C99" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D99" s="188" t="n">
+      <c r="D99" s="198" t="n">
         <f aca="false">B99+C99</f>
         <v>3296817.6</v>
       </c>
-      <c r="E99" s="188" t="n">
+      <c r="E99" s="198" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F99" s="188" t="n">
+      <c r="F99" s="198" t="n">
         <f aca="false">D99*0.12</f>
         <v>395618.112</v>
       </c>
-      <c r="G99" s="188" t="n">
+      <c r="G99" s="198" t="n">
         <f aca="false">E99+F99</f>
         <v>2217493.112</v>
       </c>
-      <c r="H99" s="189" t="n">
+      <c r="H99" s="199" t="n">
         <f aca="false">D99-G99</f>
         <v>1079324.488</v>
       </c>
-      <c r="I99" s="190" t="n">
+      <c r="I99" s="200" t="n">
         <f aca="false">IF(D99=0,0,H99/D99)</f>
         <v>0.327383743644174</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="199" t="n">
+      <c r="A100" s="208" t="n">
         <v>0.86</v>
       </c>
-      <c r="B100" s="184" t="n">
+      <c r="B100" s="194" t="n">
         <f aca="false">55*4900*0.86*12</f>
         <v>2781240</v>
       </c>
-      <c r="C100" s="184" t="n">
+      <c r="C100" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D100" s="184" t="n">
+      <c r="D100" s="194" t="n">
         <f aca="false">B100+C100</f>
         <v>3361497.6</v>
       </c>
-      <c r="E100" s="184" t="n">
+      <c r="E100" s="194" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F100" s="184" t="n">
+      <c r="F100" s="194" t="n">
         <f aca="false">D100*0.12</f>
         <v>403379.712</v>
       </c>
-      <c r="G100" s="184" t="n">
+      <c r="G100" s="194" t="n">
         <f aca="false">E100+F100</f>
         <v>2225254.712</v>
       </c>
-      <c r="H100" s="185" t="n">
+      <c r="H100" s="195" t="n">
         <f aca="false">D100-G100</f>
         <v>1136242.888</v>
       </c>
-      <c r="I100" s="186" t="n">
+      <c r="I100" s="196" t="n">
         <f aca="false">IF(D100=0,0,H100/D100)</f>
         <v>0.338016867243933</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="200" t="n">
+      <c r="A101" s="209" t="n">
         <v>0.88</v>
       </c>
-      <c r="B101" s="188" t="n">
+      <c r="B101" s="198" t="n">
         <f aca="false">55*4900*0.88*12</f>
         <v>2845920</v>
       </c>
-      <c r="C101" s="188" t="n">
+      <c r="C101" s="198" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D101" s="188" t="n">
+      <c r="D101" s="198" t="n">
         <f aca="false">B101+C101</f>
         <v>3426177.6</v>
       </c>
-      <c r="E101" s="188" t="n">
+      <c r="E101" s="198" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F101" s="188" t="n">
+      <c r="F101" s="198" t="n">
         <f aca="false">D101*0.12</f>
         <v>411141.312</v>
       </c>
-      <c r="G101" s="188" t="n">
+      <c r="G101" s="198" t="n">
         <f aca="false">E101+F101</f>
         <v>2233016.312</v>
       </c>
-      <c r="H101" s="189" t="n">
+      <c r="H101" s="199" t="n">
         <f aca="false">D101-G101</f>
         <v>1193161.288</v>
       </c>
-      <c r="I101" s="190" t="n">
+      <c r="I101" s="200" t="n">
         <f aca="false">IF(D101=0,0,H101/D101)</f>
         <v>0.348248522785275</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="199" t="n">
+      <c r="A102" s="208" t="n">
         <v>0.9</v>
       </c>
-      <c r="B102" s="184" t="n">
+      <c r="B102" s="194" t="n">
         <f aca="false">55*4900*0.9*12</f>
         <v>2910600</v>
       </c>
-      <c r="C102" s="184" t="n">
+      <c r="C102" s="194" t="n">
         <f aca="false">N23</f>
         <v>580257.6</v>
       </c>
-      <c r="D102" s="184" t="n">
+      <c r="D102" s="194" t="n">
         <f aca="false">B102+C102</f>
         <v>3490857.6</v>
       </c>
-      <c r="E102" s="184" t="n">
+      <c r="E102" s="194" t="n">
         <f aca="false">55*Drivers!$E$25*12</f>
         <v>1821875</v>
       </c>
-      <c r="F102" s="184" t="n">
+      <c r="F102" s="194" t="n">
         <f aca="false">D102*0.12</f>
         <v>418902.912</v>
       </c>
-      <c r="G102" s="184" t="n">
+      <c r="G102" s="194" t="n">
         <f aca="false">E102+F102</f>
         <v>2240777.912</v>
       </c>
-      <c r="H102" s="185" t="n">
+      <c r="H102" s="195" t="n">
         <f aca="false">D102-G102</f>
         <v>1250079.688</v>
       </c>
-      <c r="I102" s="186" t="n">
+      <c r="I102" s="196" t="n">
         <f aca="false">IF(D102=0,0,H102/D102)</f>
         <v>0.358101025948466</v>
       </c>
@@ -15286,421 +15977,669 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:F48"/>
+  <dimension ref="A2:E73"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="25.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="55"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="202" t="s">
-        <v>268</v>
-      </c>
-      <c r="C2" s="202"/>
-      <c r="D2" s="202"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="202"/>
+      <c r="A2" s="89" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="203" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" s="203"/>
-      <c r="D3" s="203" t="s">
-        <v>270</v>
-      </c>
-      <c r="E3" s="203" t="s">
-        <v>271</v>
+      <c r="A3" s="211" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" s="211"/>
+      <c r="C3" s="211" t="s">
+        <v>297</v>
+      </c>
+      <c r="D3" s="211" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="204" t="s">
-        <v>272</v>
+      <c r="A4" s="212" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="205" t="s">
-        <v>273</v>
-      </c>
-      <c r="C5" s="205"/>
-      <c r="D5" s="205" t="s">
-        <v>274</v>
-      </c>
-      <c r="E5" s="205" t="s">
-        <v>275</v>
+      <c r="A5" s="213" t="s">
+        <v>300</v>
+      </c>
+      <c r="B5" s="213"/>
+      <c r="C5" s="213" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" s="213" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="205" t="s">
-        <v>276</v>
-      </c>
-      <c r="D6" s="206" t="s">
-        <v>277</v>
-      </c>
-      <c r="E6" s="207" t="s">
-        <v>278</v>
+      <c r="A6" s="213" t="s">
+        <v>303</v>
+      </c>
+      <c r="C6" s="214" t="s">
+        <v>304</v>
+      </c>
+      <c r="D6" s="215" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="205" t="s">
-        <v>279</v>
-      </c>
-      <c r="D7" s="206" t="s">
-        <v>280</v>
-      </c>
-      <c r="E7" s="207" t="s">
-        <v>281</v>
+      <c r="A7" s="213" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="214" t="s">
+        <v>307</v>
+      </c>
+      <c r="D7" s="215" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="205" t="s">
-        <v>282</v>
-      </c>
-      <c r="D8" s="206" t="s">
-        <v>283</v>
-      </c>
-      <c r="E8" s="207" t="s">
-        <v>284</v>
+      <c r="A8" s="213" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="214" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" s="215" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="205" t="s">
-        <v>285</v>
-      </c>
-      <c r="D9" s="206" t="s">
-        <v>286</v>
-      </c>
-      <c r="E9" s="207" t="s">
-        <v>287</v>
+      <c r="A9" s="213" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9" s="214" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" s="215" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="205" t="s">
-        <v>288</v>
-      </c>
-      <c r="D10" s="206" t="s">
-        <v>289</v>
-      </c>
-      <c r="E10" s="207" t="s">
-        <v>290</v>
+      <c r="A10" s="213" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" s="214" t="s">
+        <v>316</v>
+      </c>
+      <c r="D10" s="215" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="205" t="s">
-        <v>291</v>
-      </c>
-      <c r="D11" s="206" t="s">
-        <v>292</v>
-      </c>
-      <c r="E11" s="207" t="s">
-        <v>293</v>
+      <c r="A11" s="213" t="s">
+        <v>318</v>
+      </c>
+      <c r="C11" s="214" t="s">
+        <v>319</v>
+      </c>
+      <c r="D11" s="215" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="205" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="206" t="s">
-        <v>294</v>
-      </c>
-      <c r="E12" s="207" t="s">
-        <v>295</v>
-      </c>
+      <c r="A12" s="213" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" s="214" t="s">
+        <v>321</v>
+      </c>
+      <c r="D12" s="215"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="205"/>
+      <c r="A13" s="213"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="204" t="s">
-        <v>296</v>
+      <c r="A14" s="212" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="205" t="s">
-        <v>297</v>
-      </c>
-      <c r="D15" s="206" t="s">
-        <v>298</v>
-      </c>
-      <c r="E15" s="207" t="s">
-        <v>299</v>
+      <c r="A15" s="213" t="s">
+        <v>323</v>
+      </c>
+      <c r="C15" s="214" t="s">
+        <v>324</v>
+      </c>
+      <c r="D15" s="215" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="205" t="s">
-        <v>300</v>
-      </c>
-      <c r="D16" s="206" t="s">
-        <v>301</v>
-      </c>
-      <c r="E16" s="207" t="s">
-        <v>302</v>
+      <c r="A16" s="213" t="s">
+        <v>326</v>
+      </c>
+      <c r="C16" s="214" t="s">
+        <v>327</v>
+      </c>
+      <c r="D16" s="215" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="205"/>
-      <c r="D17" s="206"/>
-      <c r="E17" s="207"/>
+      <c r="A17" s="213"/>
+      <c r="C17" s="214"/>
+      <c r="D17" s="215"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="39" t="s">
-        <v>303</v>
-      </c>
+      <c r="A18" s="39" t="s">
+        <v>329</v>
+      </c>
+      <c r="B18" s="39"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-    </row>
-    <row r="19" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="205" t="s">
-        <v>304</v>
-      </c>
-      <c r="D19" s="208" t="s">
-        <v>305</v>
-      </c>
-      <c r="E19" s="209" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="205" t="s">
-        <v>307</v>
-      </c>
-      <c r="D20" s="208" t="s">
-        <v>308</v>
-      </c>
-      <c r="E20" s="209" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="205" t="s">
-        <v>310</v>
-      </c>
-      <c r="D21" s="208" t="s">
-        <v>311</v>
-      </c>
-      <c r="E21" s="209" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="205" t="s">
-        <v>313</v>
-      </c>
-      <c r="D22" s="208" t="s">
-        <v>314</v>
-      </c>
-      <c r="E22" s="209" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="205" t="s">
-        <v>316</v>
-      </c>
-      <c r="D23" s="208" t="s">
-        <v>317</v>
-      </c>
-      <c r="E23" s="209" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="205" t="s">
-        <v>319</v>
-      </c>
-      <c r="D24" s="208" t="s">
-        <v>320</v>
-      </c>
-      <c r="E24" s="209" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="205" t="s">
-        <v>322</v>
-      </c>
-      <c r="D25" s="208" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="42.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="213" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="216" t="s">
+        <v>331</v>
+      </c>
+      <c r="D19" s="217" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="21.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="213" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" s="216" t="s">
+        <v>334</v>
+      </c>
+      <c r="D20" s="217" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="21.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="213" t="s">
+        <v>336</v>
+      </c>
+      <c r="C21" s="216" t="s">
+        <v>337</v>
+      </c>
+      <c r="D21" s="217" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="21.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="213" t="s">
+        <v>339</v>
+      </c>
+      <c r="C22" s="216" t="s">
+        <v>340</v>
+      </c>
+      <c r="D22" s="217" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="42.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="213" t="s">
+        <v>342</v>
+      </c>
+      <c r="C23" s="216" t="s">
+        <v>343</v>
+      </c>
+      <c r="D23" s="217" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="21.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="213" t="s">
+        <v>345</v>
+      </c>
+      <c r="C24" s="216" t="s">
+        <v>346</v>
+      </c>
+      <c r="D24" s="217" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="213" t="s">
+        <v>348</v>
+      </c>
+      <c r="C25" s="216" t="s">
+        <v>349</v>
+      </c>
+      <c r="D25" s="217" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="31.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="213" t="s">
+        <v>351</v>
+      </c>
+      <c r="C26" s="216" t="s">
+        <v>352</v>
+      </c>
+      <c r="D26" s="217" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="42.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="213" t="s">
+        <v>354</v>
+      </c>
+      <c r="C27" s="218" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" s="217" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="31.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="213" t="s">
+        <v>357</v>
+      </c>
+      <c r="C28" s="218" t="s">
+        <v>358</v>
+      </c>
+      <c r="D28" s="217" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="21.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="213" t="s">
+        <v>360</v>
+      </c>
+      <c r="C29" s="218" t="s">
+        <v>361</v>
+      </c>
+      <c r="D29" s="217" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="213"/>
+      <c r="D30" s="219" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="213"/>
+      <c r="C31" s="214"/>
+      <c r="D31" s="215"/>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="213"/>
+      <c r="C32" s="214"/>
+      <c r="D32" s="215"/>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="213"/>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="212" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="213" t="s">
+        <v>365</v>
+      </c>
+      <c r="C35" s="214" t="s">
+        <v>366</v>
+      </c>
+      <c r="D35" s="220" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="213" t="s">
+        <v>368</v>
+      </c>
+      <c r="C36" s="214" t="s">
+        <v>369</v>
+      </c>
+      <c r="D36" s="220" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="213" t="s">
+        <v>371</v>
+      </c>
+      <c r="C37" s="214" t="s">
+        <v>366</v>
+      </c>
+      <c r="D37" s="220" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="169" t="s">
+        <v>373</v>
+      </c>
+      <c r="B38" s="214" t="s">
+        <v>374</v>
+      </c>
+      <c r="D38" s="220" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="213"/>
+      <c r="B39" s="221"/>
+      <c r="D39" s="220"/>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="212" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="213" t="s">
+        <v>377</v>
+      </c>
+      <c r="C41" s="214" t="s">
+        <v>378</v>
+      </c>
+      <c r="D41" s="215" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="213" t="s">
+        <v>380</v>
+      </c>
+      <c r="C42" s="214" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="213" t="s">
+        <v>382</v>
+      </c>
+      <c r="C43" s="214" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="94" t="s">
+        <v>384</v>
+      </c>
+      <c r="B47" s="222" t="s">
+        <v>385</v>
+      </c>
+      <c r="C47" s="220"/>
+    </row>
+    <row r="48" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="223" t="s">
+        <v>386</v>
+      </c>
+      <c r="B48" s="223"/>
+      <c r="C48" s="223"/>
+      <c r="D48" s="223"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+    </row>
+    <row r="51" customFormat="false" ht="31.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="224" t="s">
+        <v>388</v>
+      </c>
+      <c r="B51" s="225" t="s">
+        <v>340</v>
+      </c>
+      <c r="C51" s="226" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="42.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="224" t="s">
+        <v>351</v>
+      </c>
+      <c r="B52" s="225" t="s">
+        <v>352</v>
+      </c>
+      <c r="C52" s="226" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="31.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="224" t="s">
+        <v>391</v>
+      </c>
+      <c r="B53" s="225" t="s">
+        <v>392</v>
+      </c>
+      <c r="C53" s="226" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="31.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="227" t="s">
+        <v>394</v>
+      </c>
+      <c r="B54" s="228" t="s">
+        <v>395</v>
+      </c>
+      <c r="C54" s="229" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="42.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="227" t="s">
+        <v>397</v>
+      </c>
+      <c r="B55" s="228" t="s">
+        <v>398</v>
+      </c>
+      <c r="C55" s="229" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="31.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="227" t="s">
+        <v>400</v>
+      </c>
+      <c r="B56" s="228" t="s">
+        <v>401</v>
+      </c>
+      <c r="C56" s="229" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="31.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="227" t="s">
+        <v>403</v>
+      </c>
+      <c r="B57" s="228" t="s">
+        <v>404</v>
+      </c>
+      <c r="C57" s="229" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="31.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="227" t="s">
+        <v>406</v>
+      </c>
+      <c r="B58" s="228" t="s">
+        <v>361</v>
+      </c>
+      <c r="C58" s="229" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="31.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="227" t="s">
+        <v>408</v>
+      </c>
+      <c r="B59" s="228" t="s">
+        <v>409</v>
+      </c>
+      <c r="C59" s="229" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="31.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="224" t="s">
         <v>323</v>
       </c>
-      <c r="E25" s="209" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="205" t="s">
-        <v>325</v>
-      </c>
-      <c r="D26" s="208" t="s">
-        <v>326</v>
-      </c>
-      <c r="E26" s="209" t="s">
+      <c r="B60" s="225" t="s">
+        <v>411</v>
+      </c>
+      <c r="C60" s="226" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="21.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="94" t="s">
+        <v>413</v>
+      </c>
+      <c r="B61" s="221" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="205" t="s">
-        <v>328</v>
-      </c>
-      <c r="D27" s="210" t="s">
-        <v>329</v>
-      </c>
-      <c r="E27" s="209" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="205" t="s">
-        <v>331</v>
-      </c>
-      <c r="D28" s="210" t="s">
-        <v>332</v>
-      </c>
-      <c r="E28" s="209" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="205" t="s">
-        <v>334</v>
-      </c>
-      <c r="D29" s="210" t="s">
-        <v>335</v>
-      </c>
-      <c r="E29" s="209" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="205"/>
-      <c r="E30" s="211" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="205"/>
-      <c r="D31" s="206"/>
-      <c r="E31" s="207"/>
-    </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="205"/>
-      <c r="D32" s="206"/>
-      <c r="E32" s="207"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="205"/>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="204" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="205" t="s">
-        <v>339</v>
-      </c>
-      <c r="D35" s="206" t="s">
+      <c r="C61" s="220" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="31.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="224" t="s">
+        <v>415</v>
+      </c>
+      <c r="B62" s="225" t="s">
+        <v>210</v>
+      </c>
+      <c r="C62" s="226" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="B64" s="39"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="100" t="s">
+        <v>418</v>
+      </c>
+      <c r="B65" s="230" t="s">
         <v>340</v>
       </c>
-      <c r="E35" s="212" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="205" t="s">
-        <v>342</v>
-      </c>
-      <c r="D36" s="206" t="s">
-        <v>343</v>
-      </c>
-      <c r="E36" s="212" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="205" t="s">
-        <v>345</v>
-      </c>
-      <c r="D37" s="206" t="s">
-        <v>340</v>
-      </c>
-      <c r="E37" s="212" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="157" t="s">
-        <v>347</v>
-      </c>
-      <c r="C38" s="206" t="s">
-        <v>348</v>
-      </c>
-      <c r="E38" s="212" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="205"/>
-      <c r="C39" s="213"/>
-      <c r="E39" s="212"/>
-    </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="204" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="205" t="s">
-        <v>351</v>
-      </c>
-      <c r="D41" s="206" t="s">
-        <v>352</v>
-      </c>
-      <c r="E41" s="207" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="205" t="s">
-        <v>354</v>
-      </c>
-      <c r="D42" s="206" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="205" t="s">
-        <v>356</v>
-      </c>
-      <c r="D43" s="206" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="149" t="s">
-        <v>358</v>
-      </c>
-      <c r="B47" s="214" t="s">
-        <v>359</v>
-      </c>
-      <c r="C47" s="212"/>
-    </row>
-    <row r="48" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="215" t="s">
-        <v>360</v>
-      </c>
-      <c r="B48" s="215"/>
-      <c r="C48" s="215"/>
-      <c r="D48" s="215"/>
+      <c r="C65" s="231" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="100" t="s">
+        <v>420</v>
+      </c>
+      <c r="B66" s="230" t="s">
+        <v>421</v>
+      </c>
+      <c r="C66" s="231" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="100" t="s">
+        <v>423</v>
+      </c>
+      <c r="B67" s="230" t="s">
+        <v>264</v>
+      </c>
+      <c r="C67" s="231" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="227" t="s">
+        <v>425</v>
+      </c>
+      <c r="B68" s="232" t="s">
+        <v>426</v>
+      </c>
+      <c r="C68" s="229" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="227" t="s">
+        <v>428</v>
+      </c>
+      <c r="B69" s="232" t="s">
+        <v>429</v>
+      </c>
+      <c r="C69" s="229" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="227" t="s">
+        <v>431</v>
+      </c>
+      <c r="B70" s="232" t="s">
+        <v>268</v>
+      </c>
+      <c r="C70" s="229" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="233" t="s">
+        <v>433</v>
+      </c>
+      <c r="B71" s="234" t="s">
+        <v>434</v>
+      </c>
+      <c r="C71" s="235" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="233" t="s">
+        <v>436</v>
+      </c>
+      <c r="B72" s="234" t="s">
+        <v>437</v>
+      </c>
+      <c r="C72" s="235" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="233" t="s">
+        <v>439</v>
+      </c>
+      <c r="B73" s="234" t="s">
+        <v>271</v>
+      </c>
+      <c r="C73" s="235" t="s">
+        <v>440</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B18:E18"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A64:D64"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
